--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,12 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rfd3fc0ab4e9b4864"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="R25d71140d5294382"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R932e5593f363451b"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="R0035e2c49a5344ad"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="Rfba1cf2612ed4f93"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="R3c9d62901da74fe4"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="R81463f91f7ac4041"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="Rff11a1f75a29483e"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R408b2e54f2ce4226"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="R389b81aea26c4511"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="Rb64e9b0ced244b84"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="R2b693d721ff14cf2"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="Rb2d0c026fca142aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,12 +21,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:styleSheet xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="16">
+  <x:fonts count="17">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -115,6 +116,10 @@
       <x:color rgb="FF17324D"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
   <x:fills count="9">
     <x:fill>
@@ -159,13 +164,107 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="12">
     <x:border/>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:left>
+      <x:right style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:right>
+      <x:top style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:top>
+      <x:bottom style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:left>
+      <x:right style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:left>
+      <x:right style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:right>
+      <x:bottom style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:left>
+      <x:top style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:top>
+      <x:bottom style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:top>
+      <x:bottom style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:right>
+      <x:top style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:top>
+      <x:bottom style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:left>
+      <x:bottom style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:right>
+      <x:bottom style="thick">
+        <x:color rgb="FF295D82"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="76">
+  <x:cellXfs count="99">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -266,14 +365,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -284,7 +383,7 @@
       <x:alignment wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -295,7 +394,7 @@
       <x:alignment vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -309,9 +408,71 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <ns1:xfComplement i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -384,6 +545,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -515,13 +680,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="92a3f409-76ea-46be-9ea1-249e1cabd481"/>
+        <xdr:cNvPr id="1" name="ac58e4d1-8157-4d7e-8e64-e1412a33002e"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd579bbbceb894b2c"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra9380553d3ac4522"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -842,30 +1007,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="51" t="str">
+      <x:c r="A1" s="72" t="str">
         <x:v>EOS R5 On-Camera Verification Progress</x:v>
       </x:c>
-      <x:c r="B1" s="51"/>
-      <x:c r="C1" s="51"/>
-      <x:c r="D1" s="51"/>
-      <x:c r="E1" s="51"/>
-      <x:c r="F1" s="51"/>
-      <x:c r="G1" s="51"/>
-      <x:c r="H1" s="51"/>
+      <x:c r="B1" s="72"/>
+      <x:c r="C1" s="72"/>
+      <x:c r="D1" s="72"/>
+      <x:c r="E1" s="72"/>
+      <x:c r="F1" s="72"/>
+      <x:c r="G1" s="72"/>
+      <x:c r="H1" s="72"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="51"/>
-      <x:c r="B2" s="51"/>
-      <x:c r="C2" s="51"/>
-      <x:c r="D2" s="51"/>
-      <x:c r="E2" s="51"/>
-      <x:c r="F2" s="51"/>
-      <x:c r="G2" s="51"/>
-      <x:c r="H2" s="51"/>
+      <x:c r="A2" s="72"/>
+      <x:c r="B2" s="72"/>
+      <x:c r="C2" s="72"/>
+      <x:c r="D2" s="72"/>
+      <x:c r="E2" s="72"/>
+      <x:c r="F2" s="72"/>
+      <x:c r="G2" s="72"/>
+      <x:c r="H2" s="72"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="38" t="str">
-        <x:v>Blank master template. Update the Checklist and C1-C3 Registration sheets in a separate local working copy. Only Verified, unambiguous results may be promoted to owner-confirmed project status.</x:v>
+        <x:v>Blank master template. Update the Checklist and C1-C3 Registration sheets in a separate working copy. Only Verified, unambiguous results may be promoted to owner-confirmed project status.</x:v>
       </x:c>
       <x:c r="B3" s="38"/>
       <x:c r="C3" s="38"/>
@@ -886,54 +1051,54 @@
       <x:c r="H4" s="38"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="54" t="str">
+      <x:c r="A6" s="75" t="str">
         <x:v>Total checklist items</x:v>
       </x:c>
-      <x:c r="B6" s="54" t="str"/>
-      <x:c r="C6" s="56" t="str">
+      <x:c r="B6" s="75" t="str"/>
+      <x:c r="C6" s="77" t="str">
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="D6" s="56" t="str"/>
-      <x:c r="E6" s="58" t="str">
+      <x:c r="D6" s="77" t="str"/>
+      <x:c r="E6" s="79" t="str">
         <x:v>In progress / pending</x:v>
       </x:c>
-      <x:c r="F6" s="58" t="str"/>
-      <x:c r="G6" s="60" t="str">
+      <x:c r="F6" s="79" t="str"/>
+      <x:c r="G6" s="81" t="str">
         <x:v>Needs attention</x:v>
       </x:c>
-      <x:c r="H6" s="60" t="str"/>
+      <x:c r="H6" s="81" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="64" t="n">
+      <x:c r="A7" s="85" t="n">
         <x:f>COUNTA('Checklist'!$A$6:$A$41)</x:f>
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B7" s="64"/>
-      <x:c r="C7" s="65" t="n">
+      <x:c r="B7" s="85"/>
+      <x:c r="C7" s="86" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="65"/>
-      <x:c r="E7" s="66" t="n">
+      <x:c r="D7" s="86"/>
+      <x:c r="E7" s="87" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,"In progress")+COUNTIF('Checklist'!$I$6:$I$41,"Configured—not registered")+COUNTIF('Checklist'!$I$6:$I$41,"Registered—pending read-back")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="66"/>
-      <x:c r="G7" s="67" t="n">
+      <x:c r="F7" s="87"/>
+      <x:c r="G7" s="88" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIF('Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIF('Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H7" s="67"/>
+      <x:c r="H7" s="88"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="64"/>
-      <x:c r="B8" s="64"/>
-      <x:c r="C8" s="65"/>
-      <x:c r="D8" s="65"/>
-      <x:c r="E8" s="66"/>
-      <x:c r="F8" s="66"/>
-      <x:c r="G8" s="67"/>
-      <x:c r="H8" s="67"/>
+      <x:c r="A8" s="85"/>
+      <x:c r="B8" s="85"/>
+      <x:c r="C8" s="86"/>
+      <x:c r="D8" s="86"/>
+      <x:c r="E8" s="87"/>
+      <x:c r="F8" s="87"/>
+      <x:c r="G8" s="88"/>
+      <x:c r="H8" s="88"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="str">
@@ -963,19 +1128,19 @@
       <x:c r="A12" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
-      <x:c r="B12" s="69" t="n">
+      <x:c r="B12" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A12)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="69" t="n">
+      <x:c r="C12" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="69" t="n">
+      <x:c r="D12" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="70" t="n">
+      <x:c r="E12" s="91" t="n">
         <x:f>IF(B12=0,0,(C12+COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B12)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -983,7 +1148,7 @@
       <x:c r="G12" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="H12" s="69" t="n">
+      <x:c r="H12" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G12)</x:f>
         <x:v>35</x:v>
       </x:c>
@@ -992,19 +1157,19 @@
       <x:c r="A13" t="str">
         <x:v>Controls</x:v>
       </x:c>
-      <x:c r="B13" s="69" t="n">
+      <x:c r="B13" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A13)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C13" s="69" t="n">
+      <x:c r="C13" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="69" t="n">
+      <x:c r="D13" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="70" t="n">
+      <x:c r="E13" s="91" t="n">
         <x:f>IF(B13=0,0,(C13+COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B13)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1012,7 +1177,7 @@
       <x:c r="G13" t="str">
         <x:v>In progress</x:v>
       </x:c>
-      <x:c r="H13" s="69" t="n">
+      <x:c r="H13" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G13)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1021,19 +1186,19 @@
       <x:c r="A14" t="str">
         <x:v>C1 Wildlife</x:v>
       </x:c>
-      <x:c r="B14" s="69" t="n">
+      <x:c r="B14" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A14)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C14" s="69" t="n">
+      <x:c r="C14" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="69" t="n">
+      <x:c r="D14" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="70" t="n">
+      <x:c r="E14" s="91" t="n">
         <x:f>IF(B14=0,0,(C14+COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B14)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1041,7 +1206,7 @@
       <x:c r="G14" t="str">
         <x:v>Configured—not registered</x:v>
       </x:c>
-      <x:c r="H14" s="69" t="n">
+      <x:c r="H14" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G14)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1050,19 +1215,19 @@
       <x:c r="A15" t="str">
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
-      <x:c r="B15" s="69" t="n">
+      <x:c r="B15" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A15)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C15" s="69" t="n">
+      <x:c r="C15" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D15" s="69" t="n">
+      <x:c r="D15" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="70" t="n">
+      <x:c r="E15" s="91" t="n">
         <x:f>IF(B15=0,0,(C15+COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B15)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1070,7 +1235,7 @@
       <x:c r="G15" t="str">
         <x:v>Registered—pending read-back</x:v>
       </x:c>
-      <x:c r="H15" s="69" t="n">
+      <x:c r="H15" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G15)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1079,19 +1244,19 @@
       <x:c r="A16" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
-      <x:c r="B16" s="69" t="n">
+      <x:c r="B16" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A16)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C16" s="69" t="n">
+      <x:c r="C16" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="69" t="n">
+      <x:c r="D16" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="70" t="n">
+      <x:c r="E16" s="91" t="n">
         <x:f>IF(B16=0,0,(C16+COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B16)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1099,7 +1264,7 @@
       <x:c r="G16" t="str">
         <x:v>Backup-Settings</x:v>
       </x:c>
-      <x:c r="H16" s="69" t="n">
+      <x:c r="H16" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G16)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1108,19 +1273,19 @@
       <x:c r="A17" t="str">
         <x:v>EFCS Tests</x:v>
       </x:c>
-      <x:c r="B17" s="69" t="n">
+      <x:c r="B17" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A17)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C17" s="69" t="n">
+      <x:c r="C17" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D17" s="69" t="n">
+      <x:c r="D17" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="70" t="n">
+      <x:c r="E17" s="91" t="n">
         <x:f>IF(B17=0,0,(C17+COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B17)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1128,7 +1293,7 @@
       <x:c r="G17" t="str">
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="H17" s="69" t="n">
+      <x:c r="H17" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G17)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1137,19 +1302,19 @@
       <x:c r="A18" t="str">
         <x:v>Finalization</x:v>
       </x:c>
-      <x:c r="B18" s="69" t="n">
+      <x:c r="B18" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A18)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C18" s="69" t="n">
+      <x:c r="C18" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D18" s="69" t="n">
+      <x:c r="D18" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="70" t="n">
+      <x:c r="E18" s="91" t="n">
         <x:f>IF(B18=0,0,(C18+COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B18)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1157,7 +1322,7 @@
       <x:c r="G18" t="str">
         <x:v>Failed—needs correction</x:v>
       </x:c>
-      <x:c r="H18" s="69" t="n">
+      <x:c r="H18" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G18)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1166,19 +1331,19 @@
       <x:c r="A19" t="str">
         <x:v>Project Update</x:v>
       </x:c>
-      <x:c r="B19" s="69" t="n">
+      <x:c r="B19" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A19)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C19" s="69" t="n">
+      <x:c r="C19" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D19" s="69" t="n">
+      <x:c r="D19" s="90" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E19" s="70" t="n">
+      <x:c r="E19" s="91" t="n">
         <x:f>IF(B19=0,0,(C19+COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B19)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1186,108 +1351,108 @@
       <x:c r="G19" t="str">
         <x:v>Inconclusive—needs retest</x:v>
       </x:c>
-      <x:c r="H19" s="69" t="n">
+      <x:c r="H19" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G19)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str"/>
-      <x:c r="B20" s="69" t="str"/>
-      <x:c r="C20" s="69" t="str"/>
-      <x:c r="D20" s="69" t="str"/>
-      <x:c r="E20" s="69" t="str"/>
+      <x:c r="B20" s="90" t="str"/>
+      <x:c r="C20" s="90" t="str"/>
+      <x:c r="D20" s="90" t="str"/>
+      <x:c r="E20" s="90" t="str"/>
       <x:c r="F20" t="str"/>
       <x:c r="G20" t="str">
         <x:v>Blocked</x:v>
       </x:c>
-      <x:c r="H20" s="69" t="n">
+      <x:c r="H20" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G20)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str"/>
-      <x:c r="B21" s="69" t="str"/>
-      <x:c r="C21" s="69" t="str"/>
-      <x:c r="D21" s="69" t="str"/>
-      <x:c r="E21" s="69" t="str"/>
+      <x:c r="B21" s="90" t="str"/>
+      <x:c r="C21" s="90" t="str"/>
+      <x:c r="D21" s="90" t="str"/>
+      <x:c r="E21" s="90" t="str"/>
       <x:c r="F21" t="str"/>
       <x:c r="G21" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="H21" s="69" t="n">
+      <x:c r="H21" s="90" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G21)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="71" t="str">
+      <x:c r="A23" s="92" t="str">
         <x:v>Recommended workflow</x:v>
       </x:c>
-      <x:c r="B23" s="71"/>
-      <x:c r="C23" s="71"/>
-      <x:c r="D23" s="71"/>
-      <x:c r="E23" s="71"/>
-      <x:c r="F23" s="71"/>
-      <x:c r="G23" s="71"/>
-      <x:c r="H23" s="71"/>
+      <x:c r="B23" s="92"/>
+      <x:c r="C23" s="92"/>
+      <x:c r="D23" s="92"/>
+      <x:c r="E23" s="92"/>
+      <x:c r="F23" s="92"/>
+      <x:c r="G23" s="92"/>
+      <x:c r="H23" s="92"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="75" t="str">
+      <x:c r="A24" s="96" t="str">
         <x:v>1. Save the starting camera configuration and document C1–C3.
 2. Disable Auto update, then configure and verify the SWITCH My Menu tab.
 3. Save Backup-Settings checkpoints after shared setup/controls and after C1–C3 read-back.
 4. Work through Checklist in Sequence order and use one Session ID per camera session.
 5. Filter Project Update? = Yes and Status = Verified before changing project evidence states.</x:v>
       </x:c>
-      <x:c r="B24" s="75"/>
-      <x:c r="C24" s="75"/>
-      <x:c r="D24" s="75"/>
-      <x:c r="E24" s="75"/>
-      <x:c r="F24" s="75"/>
-      <x:c r="G24" s="75"/>
-      <x:c r="H24" s="75"/>
+      <x:c r="B24" s="96"/>
+      <x:c r="C24" s="96"/>
+      <x:c r="D24" s="96"/>
+      <x:c r="E24" s="96"/>
+      <x:c r="F24" s="96"/>
+      <x:c r="G24" s="96"/>
+      <x:c r="H24" s="96"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="75"/>
-      <x:c r="B25" s="75"/>
-      <x:c r="C25" s="75"/>
-      <x:c r="D25" s="75"/>
-      <x:c r="E25" s="75"/>
-      <x:c r="F25" s="75"/>
-      <x:c r="G25" s="75"/>
-      <x:c r="H25" s="75"/>
+      <x:c r="A25" s="96"/>
+      <x:c r="B25" s="96"/>
+      <x:c r="C25" s="96"/>
+      <x:c r="D25" s="96"/>
+      <x:c r="E25" s="96"/>
+      <x:c r="F25" s="96"/>
+      <x:c r="G25" s="96"/>
+      <x:c r="H25" s="96"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="75"/>
-      <x:c r="B26" s="75"/>
-      <x:c r="C26" s="75"/>
-      <x:c r="D26" s="75"/>
-      <x:c r="E26" s="75"/>
-      <x:c r="F26" s="75"/>
-      <x:c r="G26" s="75"/>
-      <x:c r="H26" s="75"/>
+      <x:c r="A26" s="96"/>
+      <x:c r="B26" s="96"/>
+      <x:c r="C26" s="96"/>
+      <x:c r="D26" s="96"/>
+      <x:c r="E26" s="96"/>
+      <x:c r="F26" s="96"/>
+      <x:c r="G26" s="96"/>
+      <x:c r="H26" s="96"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="75"/>
-      <x:c r="B27" s="75"/>
-      <x:c r="C27" s="75"/>
-      <x:c r="D27" s="75"/>
-      <x:c r="E27" s="75"/>
-      <x:c r="F27" s="75"/>
-      <x:c r="G27" s="75"/>
-      <x:c r="H27" s="75"/>
+      <x:c r="A27" s="96"/>
+      <x:c r="B27" s="96"/>
+      <x:c r="C27" s="96"/>
+      <x:c r="D27" s="96"/>
+      <x:c r="E27" s="96"/>
+      <x:c r="F27" s="96"/>
+      <x:c r="G27" s="96"/>
+      <x:c r="H27" s="96"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="75"/>
-      <x:c r="B28" s="75"/>
-      <x:c r="C28" s="75"/>
-      <x:c r="D28" s="75"/>
-      <x:c r="E28" s="75"/>
-      <x:c r="F28" s="75"/>
-      <x:c r="G28" s="75"/>
-      <x:c r="H28" s="75"/>
+      <x:c r="A28" s="96"/>
+      <x:c r="B28" s="96"/>
+      <x:c r="C28" s="96"/>
+      <x:c r="D28" s="96"/>
+      <x:c r="E28" s="96"/>
+      <x:c r="F28" s="96"/>
+      <x:c r="G28" s="96"/>
+      <x:c r="H28" s="96"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3262,9 +3427,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R9bd4b6d438b742d9"/>
+  <x:drawing ns1:id="Re788128561ad475e"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R9d1036363ed040bb"/>
+    <x:tablePart ns1:id="Rfa70f8121d594d7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3289,45 +3454,59 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="34" t="str">
+      <x:c r="A1" s="48" t="str">
         <x:v>C1–C3 Registration: Configure → Register → Read Back → Verify</x:v>
       </x:c>
-      <x:c r="B1" s="34"/>
-      <x:c r="C1" s="34"/>
-      <x:c r="D1" s="34"/>
-      <x:c r="E1" s="34"/>
-      <x:c r="F1" s="34"/>
-      <x:c r="G1" s="34"/>
-      <x:c r="H1" s="34"/>
-      <x:c r="I1" s="34"/>
-      <x:c r="J1" s="34"/>
-      <x:c r="K1" s="34"/>
-      <x:c r="L1" s="34"/>
-      <x:c r="M1" s="34"/>
+      <x:c r="B1" s="54"/>
+      <x:c r="C1" s="55"/>
+      <x:c r="D1" s="55"/>
+      <x:c r="E1" s="56"/>
+      <x:c r="F1" s="54"/>
+      <x:c r="G1" s="55"/>
+      <x:c r="H1" s="55"/>
+      <x:c r="I1" s="56"/>
+      <x:c r="J1" s="54"/>
+      <x:c r="K1" s="55"/>
+      <x:c r="L1" s="55"/>
+      <x:c r="M1" s="56"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="38" t="str">
+      <x:c r="A2" s="49" t="str">
         <x:v>Work from a normal shooting mode. Validate the complete column before registering a slot. Record configuration and read-back separately for every setting.</x:v>
       </x:c>
-      <x:c r="B2" s="38"/>
+      <x:c r="B2" s="57"/>
       <x:c r="C2" s="38"/>
       <x:c r="D2" s="38"/>
-      <x:c r="E2" s="38"/>
-      <x:c r="F2" s="38"/>
+      <x:c r="E2" s="58"/>
+      <x:c r="F2" s="57"/>
       <x:c r="G2" s="38"/>
       <x:c r="H2" s="38"/>
-      <x:c r="I2" s="38"/>
-      <x:c r="J2" s="38"/>
+      <x:c r="I2" s="58"/>
+      <x:c r="J2" s="57"/>
       <x:c r="K2" s="38"/>
       <x:c r="L2" s="38"/>
-      <x:c r="M2" s="38"/>
-    </x:row>
-    <x:row r="3" ht="12" customHeight="1"/>
+      <x:c r="M2" s="58"/>
+    </x:row>
+    <x:row r="3" ht="12" customHeight="1">
+      <x:c r="A3" s="50"/>
+      <x:c r="B3" s="59"/>
+      <x:c r="C3" s="6"/>
+      <x:c r="D3" s="6"/>
+      <x:c r="E3" s="60"/>
+      <x:c r="F3" s="59"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="6"/>
+      <x:c r="I3" s="60"/>
+      <x:c r="J3" s="59"/>
+      <x:c r="K3" s="6"/>
+      <x:c r="L3" s="6"/>
+      <x:c r="M3" s="60"/>
+    </x:row>
     <x:row r="4">
-      <x:c r="A4" s="5" t="str">
+      <x:c r="A4" s="51" t="str">
         <x:v>Setting</x:v>
       </x:c>
-      <x:c r="B4" s="5" t="str">
+      <x:c r="B4" s="61" t="str">
         <x:v>C1 Wildlife Target</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
@@ -3336,10 +3515,10 @@
       <x:c r="D4" s="5" t="str">
         <x:v>C1 Read-back</x:v>
       </x:c>
-      <x:c r="E4" s="5" t="str">
+      <x:c r="E4" s="62" t="str">
         <x:v>C1 Notes</x:v>
       </x:c>
-      <x:c r="F4" s="5" t="str">
+      <x:c r="F4" s="61" t="str">
         <x:v>C2 Birds in Flight Target</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
@@ -3348,10 +3527,10 @@
       <x:c r="H4" s="5" t="str">
         <x:v>C2 Read-back</x:v>
       </x:c>
-      <x:c r="I4" s="5" t="str">
+      <x:c r="I4" s="62" t="str">
         <x:v>C2 Notes</x:v>
       </x:c>
-      <x:c r="J4" s="5" t="str">
+      <x:c r="J4" s="61" t="str">
         <x:v>C3 Landscape Target</x:v>
       </x:c>
       <x:c r="K4" s="5" t="str">
@@ -3360,15 +3539,15 @@
       <x:c r="L4" s="5" t="str">
         <x:v>C3 Read-back</x:v>
       </x:c>
-      <x:c r="M4" s="5" t="str">
+      <x:c r="M4" s="62" t="str">
         <x:v>C3 Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="45" t="str">
+      <x:c r="A5" s="52" t="str">
         <x:v>Mode</x:v>
       </x:c>
-      <x:c r="B5" s="46" t="str">
+      <x:c r="B5" s="63" t="str">
         <x:v>Fv</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
@@ -3377,8 +3556,8 @@
       <x:c r="D5" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E5" s="43" t="str"/>
-      <x:c r="F5" s="46" t="str">
+      <x:c r="E5" s="64" t="str"/>
+      <x:c r="F5" s="63" t="str">
         <x:v>Tv</x:v>
       </x:c>
       <x:c r="G5" s="43" t="str">
@@ -3387,8 +3566,8 @@
       <x:c r="H5" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I5" s="43" t="str"/>
-      <x:c r="J5" s="46" t="str">
+      <x:c r="I5" s="64" t="str"/>
+      <x:c r="J5" s="63" t="str">
         <x:v>Av</x:v>
       </x:c>
       <x:c r="K5" s="43" t="str">
@@ -3397,13 +3576,13 @@
       <x:c r="L5" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M5" s="43" t="str"/>
+      <x:c r="M5" s="64" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="45" t="str">
+      <x:c r="A6" s="52" t="str">
         <x:v>Metering</x:v>
       </x:c>
-      <x:c r="B6" s="46" t="str">
+      <x:c r="B6" s="63" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
@@ -3412,8 +3591,8 @@
       <x:c r="D6" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E6" s="43" t="str"/>
-      <x:c r="F6" s="46" t="str">
+      <x:c r="E6" s="64" t="str"/>
+      <x:c r="F6" s="63" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="G6" s="43" t="str">
@@ -3422,8 +3601,8 @@
       <x:c r="H6" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I6" s="43" t="str"/>
-      <x:c r="J6" s="46" t="str">
+      <x:c r="I6" s="64" t="str"/>
+      <x:c r="J6" s="63" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="K6" s="43" t="str">
@@ -3432,13 +3611,13 @@
       <x:c r="L6" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M6" s="43" t="str"/>
+      <x:c r="M6" s="64" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="45" t="str">
+      <x:c r="A7" s="52" t="str">
         <x:v>Exposure Compensation</x:v>
       </x:c>
-      <x:c r="B7" s="46" t="str">
+      <x:c r="B7" s="63" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="43" t="str">
@@ -3447,8 +3626,8 @@
       <x:c r="D7" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E7" s="43" t="str"/>
-      <x:c r="F7" s="46" t="str">
+      <x:c r="E7" s="64" t="str"/>
+      <x:c r="F7" s="63" t="str">
         <x:v>0 starting point</x:v>
       </x:c>
       <x:c r="G7" s="43" t="str">
@@ -3457,8 +3636,8 @@
       <x:c r="H7" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I7" s="43" t="str"/>
-      <x:c r="J7" s="46" t="str">
+      <x:c r="I7" s="64" t="str"/>
+      <x:c r="J7" s="63" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K7" s="43" t="str">
@@ -3467,13 +3646,13 @@
       <x:c r="L7" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M7" s="43" t="str"/>
+      <x:c r="M7" s="64" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="45" t="str">
+      <x:c r="A8" s="52" t="str">
         <x:v>Shutter Speed</x:v>
       </x:c>
-      <x:c r="B8" s="46" t="str">
+      <x:c r="B8" s="63" t="str">
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="C8" s="43" t="str">
@@ -3482,8 +3661,8 @@
       <x:c r="D8" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E8" s="43" t="str"/>
-      <x:c r="F8" s="46" t="str">
+      <x:c r="E8" s="64" t="str"/>
+      <x:c r="F8" s="63" t="str">
         <x:v>1/2500 sec.</x:v>
       </x:c>
       <x:c r="G8" s="43" t="str">
@@ -3492,8 +3671,8 @@
       <x:c r="H8" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I8" s="43" t="str"/>
-      <x:c r="J8" s="46" t="str">
+      <x:c r="I8" s="64" t="str"/>
+      <x:c r="J8" s="63" t="str">
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="K8" s="43" t="str">
@@ -3502,13 +3681,13 @@
       <x:c r="L8" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M8" s="43" t="str"/>
+      <x:c r="M8" s="64" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="45" t="str">
+      <x:c r="A9" s="52" t="str">
         <x:v>Aperture</x:v>
       </x:c>
-      <x:c r="B9" s="46" t="str">
+      <x:c r="B9" s="63" t="str">
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="C9" s="43" t="str">
@@ -3517,8 +3696,8 @@
       <x:c r="D9" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E9" s="43" t="str"/>
-      <x:c r="F9" s="46" t="str">
+      <x:c r="E9" s="64" t="str"/>
+      <x:c r="F9" s="63" t="str">
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="G9" s="43" t="str">
@@ -3527,8 +3706,8 @@
       <x:c r="H9" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I9" s="43" t="str"/>
-      <x:c r="J9" s="46" t="str">
+      <x:c r="I9" s="64" t="str"/>
+      <x:c r="J9" s="63" t="str">
         <x:v>f/9</x:v>
       </x:c>
       <x:c r="K9" s="43" t="str">
@@ -3537,13 +3716,13 @@
       <x:c r="L9" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M9" s="43" t="str"/>
+      <x:c r="M9" s="64" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="45" t="str">
+      <x:c r="A10" s="52" t="str">
         <x:v>ISO</x:v>
       </x:c>
-      <x:c r="B10" s="46" t="str">
+      <x:c r="B10" s="63" t="str">
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="C10" s="43" t="str">
@@ -3552,8 +3731,8 @@
       <x:c r="D10" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E10" s="43" t="str"/>
-      <x:c r="F10" s="46" t="str">
+      <x:c r="E10" s="64" t="str"/>
+      <x:c r="F10" s="63" t="str">
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="G10" s="43" t="str">
@@ -3562,8 +3741,8 @@
       <x:c r="H10" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I10" s="43" t="str"/>
-      <x:c r="J10" s="46" t="str">
+      <x:c r="I10" s="64" t="str"/>
+      <x:c r="J10" s="63" t="str">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K10" s="43" t="str">
@@ -3572,13 +3751,13 @@
       <x:c r="L10" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M10" s="43" t="str"/>
+      <x:c r="M10" s="64" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="45" t="str">
+      <x:c r="A11" s="52" t="str">
         <x:v>Auto ISO Maximum</x:v>
       </x:c>
-      <x:c r="B11" s="46" t="str">
+      <x:c r="B11" s="63" t="str">
         <x:v>12800</x:v>
       </x:c>
       <x:c r="C11" s="43" t="str">
@@ -3587,8 +3766,8 @@
       <x:c r="D11" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E11" s="43" t="str"/>
-      <x:c r="F11" s="46" t="str">
+      <x:c r="E11" s="64" t="str"/>
+      <x:c r="F11" s="63" t="str">
         <x:v>12800</x:v>
       </x:c>
       <x:c r="G11" s="43" t="str">
@@ -3597,8 +3776,8 @@
       <x:c r="H11" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I11" s="43" t="str"/>
-      <x:c r="J11" s="46" t="str">
+      <x:c r="I11" s="64" t="str"/>
+      <x:c r="J11" s="63" t="str">
         <x:v>12800; inactive at ISO 100</x:v>
       </x:c>
       <x:c r="K11" s="43" t="str">
@@ -3607,13 +3786,13 @@
       <x:c r="L11" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M11" s="43" t="str"/>
+      <x:c r="M11" s="64" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="45" t="str">
+      <x:c r="A12" s="52" t="str">
         <x:v>AF Operation</x:v>
       </x:c>
-      <x:c r="B12" s="46" t="str">
+      <x:c r="B12" s="63" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="C12" s="43" t="str">
@@ -3622,8 +3801,8 @@
       <x:c r="D12" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E12" s="43" t="str"/>
-      <x:c r="F12" s="46" t="str">
+      <x:c r="E12" s="64" t="str"/>
+      <x:c r="F12" s="63" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="G12" s="43" t="str">
@@ -3632,8 +3811,8 @@
       <x:c r="H12" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I12" s="43" t="str"/>
-      <x:c r="J12" s="46" t="str">
+      <x:c r="I12" s="64" t="str"/>
+      <x:c r="J12" s="63" t="str">
         <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="K12" s="43" t="str">
@@ -3642,13 +3821,13 @@
       <x:c r="L12" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M12" s="43" t="str"/>
+      <x:c r="M12" s="64" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="45" t="str">
+      <x:c r="A13" s="52" t="str">
         <x:v>AF Method</x:v>
       </x:c>
-      <x:c r="B13" s="46" t="str">
+      <x:c r="B13" s="63" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="C13" s="43" t="str">
@@ -3657,8 +3836,8 @@
       <x:c r="D13" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E13" s="43" t="str"/>
-      <x:c r="F13" s="46" t="str">
+      <x:c r="E13" s="64" t="str"/>
+      <x:c r="F13" s="63" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="G13" s="43" t="str">
@@ -3667,8 +3846,8 @@
       <x:c r="H13" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I13" s="43" t="str"/>
-      <x:c r="J13" s="46" t="str">
+      <x:c r="I13" s="64" t="str"/>
+      <x:c r="J13" s="63" t="str">
         <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="K13" s="43" t="str">
@@ -3677,13 +3856,13 @@
       <x:c r="L13" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M13" s="43" t="str"/>
+      <x:c r="M13" s="64" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="45" t="str">
+      <x:c r="A14" s="52" t="str">
         <x:v>Subject Detection</x:v>
       </x:c>
-      <x:c r="B14" s="46" t="str">
+      <x:c r="B14" s="63" t="str">
         <x:v>Animals</x:v>
       </x:c>
       <x:c r="C14" s="43" t="str">
@@ -3692,8 +3871,8 @@
       <x:c r="D14" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E14" s="43" t="str"/>
-      <x:c r="F14" s="46" t="str">
+      <x:c r="E14" s="64" t="str"/>
+      <x:c r="F14" s="63" t="str">
         <x:v>Animals</x:v>
       </x:c>
       <x:c r="G14" s="43" t="str">
@@ -3702,8 +3881,8 @@
       <x:c r="H14" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I14" s="43" t="str"/>
-      <x:c r="J14" s="46" t="str">
+      <x:c r="I14" s="64" t="str"/>
+      <x:c r="J14" s="63" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="K14" s="43" t="str">
@@ -3712,13 +3891,13 @@
       <x:c r="L14" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M14" s="43" t="str"/>
+      <x:c r="M14" s="64" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="45" t="str">
+      <x:c r="A15" s="52" t="str">
         <x:v>Eye Detection</x:v>
       </x:c>
-      <x:c r="B15" s="46" t="str">
+      <x:c r="B15" s="63" t="str">
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="C15" s="43" t="str">
@@ -3727,8 +3906,8 @@
       <x:c r="D15" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E15" s="43" t="str"/>
-      <x:c r="F15" s="46" t="str">
+      <x:c r="E15" s="64" t="str"/>
+      <x:c r="F15" s="63" t="str">
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="G15" s="43" t="str">
@@ -3737,8 +3916,8 @@
       <x:c r="H15" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I15" s="43" t="str"/>
-      <x:c r="J15" s="46" t="str">
+      <x:c r="I15" s="64" t="str"/>
+      <x:c r="J15" s="63" t="str">
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="K15" s="43" t="str">
@@ -3747,13 +3926,13 @@
       <x:c r="L15" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M15" s="43" t="str"/>
+      <x:c r="M15" s="64" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="45" t="str">
+      <x:c r="A16" s="52" t="str">
         <x:v>Drive Mode</x:v>
       </x:c>
-      <x:c r="B16" s="46" t="str">
+      <x:c r="B16" s="63" t="str">
         <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="C16" s="43" t="str">
@@ -3762,8 +3941,8 @@
       <x:c r="D16" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E16" s="43" t="str"/>
-      <x:c r="F16" s="46" t="str">
+      <x:c r="E16" s="64" t="str"/>
+      <x:c r="F16" s="63" t="str">
         <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="G16" s="43" t="str">
@@ -3772,8 +3951,8 @@
       <x:c r="H16" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I16" s="43" t="str"/>
-      <x:c r="J16" s="46" t="str">
+      <x:c r="I16" s="64" t="str"/>
+      <x:c r="J16" s="63" t="str">
         <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="K16" s="43" t="str">
@@ -3782,13 +3961,13 @@
       <x:c r="L16" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M16" s="43" t="str"/>
+      <x:c r="M16" s="64" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="45" t="str">
+      <x:c r="A17" s="52" t="str">
         <x:v>Shutter Type</x:v>
       </x:c>
-      <x:c r="B17" s="46" t="str">
+      <x:c r="B17" s="63" t="str">
         <x:v>EFCS</x:v>
       </x:c>
       <x:c r="C17" s="43" t="str">
@@ -3797,8 +3976,8 @@
       <x:c r="D17" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E17" s="43" t="str"/>
-      <x:c r="F17" s="46" t="str">
+      <x:c r="E17" s="64" t="str"/>
+      <x:c r="F17" s="63" t="str">
         <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="G17" s="43" t="str">
@@ -3807,8 +3986,8 @@
       <x:c r="H17" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I17" s="43" t="str"/>
-      <x:c r="J17" s="46" t="str">
+      <x:c r="I17" s="64" t="str"/>
+      <x:c r="J17" s="63" t="str">
         <x:v>EFCS</x:v>
       </x:c>
       <x:c r="K17" s="43" t="str">
@@ -3817,13 +3996,13 @@
       <x:c r="L17" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M17" s="43" t="str"/>
+      <x:c r="M17" s="64" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="45" t="str">
+      <x:c r="A18" s="52" t="str">
         <x:v>Image Stabilizer Mode</x:v>
       </x:c>
-      <x:c r="B18" s="46" t="str">
+      <x:c r="B18" s="63" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="C18" s="43" t="str">
@@ -3832,8 +4011,8 @@
       <x:c r="D18" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E18" s="43" t="str"/>
-      <x:c r="F18" s="46" t="str">
+      <x:c r="E18" s="64" t="str"/>
+      <x:c r="F18" s="63" t="str">
         <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="G18" s="43" t="str">
@@ -3842,8 +4021,8 @@
       <x:c r="H18" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I18" s="43" t="str"/>
-      <x:c r="J18" s="46" t="str">
+      <x:c r="I18" s="64" t="str"/>
+      <x:c r="J18" s="63" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="K18" s="43" t="str">
@@ -3852,13 +4031,13 @@
       <x:c r="L18" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M18" s="43" t="str"/>
+      <x:c r="M18" s="64" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="45" t="str">
+      <x:c r="A19" s="52" t="str">
         <x:v>IBIS</x:v>
       </x:c>
-      <x:c r="B19" s="47" t="b">
+      <x:c r="B19" s="65" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C19" s="43" t="str">
@@ -3867,8 +4046,8 @@
       <x:c r="D19" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E19" s="43" t="str"/>
-      <x:c r="F19" s="47" t="b">
+      <x:c r="E19" s="64" t="str"/>
+      <x:c r="F19" s="65" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="43" t="str">
@@ -3877,8 +4056,8 @@
       <x:c r="H19" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I19" s="43" t="str"/>
-      <x:c r="J19" s="47" t="b">
+      <x:c r="I19" s="64" t="str"/>
+      <x:c r="J19" s="65" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K19" s="43" t="str">
@@ -3887,13 +4066,13 @@
       <x:c r="L19" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M19" s="43" t="str"/>
+      <x:c r="M19" s="64" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="45" t="str">
+      <x:c r="A20" s="52" t="str">
         <x:v>Focus Bracketing</x:v>
       </x:c>
-      <x:c r="B20" s="46" t="str">
+      <x:c r="B20" s="63" t="str">
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="C20" s="43" t="str">
@@ -3902,8 +4081,8 @@
       <x:c r="D20" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E20" s="43" t="str"/>
-      <x:c r="F20" s="46" t="str">
+      <x:c r="E20" s="64" t="str"/>
+      <x:c r="F20" s="63" t="str">
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="G20" s="43" t="str">
@@ -3912,8 +4091,8 @@
       <x:c r="H20" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I20" s="43" t="str"/>
-      <x:c r="J20" s="46" t="str">
+      <x:c r="I20" s="64" t="str"/>
+      <x:c r="J20" s="63" t="str">
         <x:v>Disable; enable situationally</x:v>
       </x:c>
       <x:c r="K20" s="43" t="str">
@@ -3922,42 +4101,42 @@
       <x:c r="L20" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M20" s="43" t="str"/>
+      <x:c r="M20" s="64" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="45" t="str">
+      <x:c r="A21" s="53" t="str">
         <x:v>Lens IS switch</x:v>
       </x:c>
-      <x:c r="B21" s="46" t="str">
+      <x:c r="B21" s="66" t="str">
         <x:v>On; physical check</x:v>
       </x:c>
-      <x:c r="C21" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="D21" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E21" s="43" t="str"/>
-      <x:c r="F21" s="46" t="str">
+      <x:c r="C21" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="D21" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E21" s="68" t="str"/>
+      <x:c r="F21" s="66" t="str">
         <x:v>On; physical check</x:v>
       </x:c>
-      <x:c r="G21" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="H21" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I21" s="43" t="str"/>
-      <x:c r="J21" s="46" t="str">
+      <x:c r="G21" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H21" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I21" s="68" t="str"/>
+      <x:c r="J21" s="66" t="str">
         <x:v>On; handheld registration</x:v>
       </x:c>
-      <x:c r="K21" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="L21" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M21" s="43" t="str"/>
+      <x:c r="K21" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="L21" s="67" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M21" s="68" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3977,7 +4156,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rc7a6850cac954d41"/>
+    <x:tablePart ns1:id="R7db6c6a1cd8f4e5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4073,7 +4252,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="43" t="str"/>
-      <x:c r="B5" s="48" t="str"/>
+      <x:c r="B5" s="69" t="str"/>
       <x:c r="C5" s="43" t="str"/>
       <x:c r="D5" s="43" t="str"/>
       <x:c r="E5" s="43" t="str"/>
@@ -4087,7 +4266,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="43" t="str"/>
-      <x:c r="B6" s="48" t="str"/>
+      <x:c r="B6" s="69" t="str"/>
       <x:c r="C6" s="43" t="str"/>
       <x:c r="D6" s="43" t="str"/>
       <x:c r="E6" s="43" t="str"/>
@@ -4101,7 +4280,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="43" t="str"/>
-      <x:c r="B7" s="48" t="str"/>
+      <x:c r="B7" s="69" t="str"/>
       <x:c r="C7" s="43" t="str"/>
       <x:c r="D7" s="43" t="str"/>
       <x:c r="E7" s="43" t="str"/>
@@ -4115,7 +4294,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="43" t="str"/>
-      <x:c r="B8" s="48" t="str"/>
+      <x:c r="B8" s="69" t="str"/>
       <x:c r="C8" s="43" t="str"/>
       <x:c r="D8" s="43" t="str"/>
       <x:c r="E8" s="43" t="str"/>
@@ -4129,7 +4308,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="43" t="str"/>
-      <x:c r="B9" s="48" t="str"/>
+      <x:c r="B9" s="69" t="str"/>
       <x:c r="C9" s="43" t="str"/>
       <x:c r="D9" s="43" t="str"/>
       <x:c r="E9" s="43" t="str"/>
@@ -4143,7 +4322,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="43" t="str"/>
-      <x:c r="B10" s="48" t="str"/>
+      <x:c r="B10" s="69" t="str"/>
       <x:c r="C10" s="43" t="str"/>
       <x:c r="D10" s="43" t="str"/>
       <x:c r="E10" s="43" t="str"/>
@@ -4157,7 +4336,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="43" t="str"/>
-      <x:c r="B11" s="48" t="str"/>
+      <x:c r="B11" s="69" t="str"/>
       <x:c r="C11" s="43" t="str"/>
       <x:c r="D11" s="43" t="str"/>
       <x:c r="E11" s="43" t="str"/>
@@ -4171,7 +4350,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="43" t="str"/>
-      <x:c r="B12" s="48" t="str"/>
+      <x:c r="B12" s="69" t="str"/>
       <x:c r="C12" s="43" t="str"/>
       <x:c r="D12" s="43" t="str"/>
       <x:c r="E12" s="43" t="str"/>
@@ -4185,7 +4364,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="43" t="str"/>
-      <x:c r="B13" s="48" t="str"/>
+      <x:c r="B13" s="69" t="str"/>
       <x:c r="C13" s="43" t="str"/>
       <x:c r="D13" s="43" t="str"/>
       <x:c r="E13" s="43" t="str"/>
@@ -4199,7 +4378,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="43" t="str"/>
-      <x:c r="B14" s="48" t="str"/>
+      <x:c r="B14" s="69" t="str"/>
       <x:c r="C14" s="43" t="str"/>
       <x:c r="D14" s="43" t="str"/>
       <x:c r="E14" s="43" t="str"/>
@@ -4213,7 +4392,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="43" t="str"/>
-      <x:c r="B15" s="48" t="str"/>
+      <x:c r="B15" s="69" t="str"/>
       <x:c r="C15" s="43" t="str"/>
       <x:c r="D15" s="43" t="str"/>
       <x:c r="E15" s="43" t="str"/>
@@ -4227,7 +4406,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="43" t="str"/>
-      <x:c r="B16" s="48" t="str"/>
+      <x:c r="B16" s="69" t="str"/>
       <x:c r="C16" s="43" t="str"/>
       <x:c r="D16" s="43" t="str"/>
       <x:c r="E16" s="43" t="str"/>
@@ -4241,7 +4420,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="43" t="str"/>
-      <x:c r="B17" s="48" t="str"/>
+      <x:c r="B17" s="69" t="str"/>
       <x:c r="C17" s="43" t="str"/>
       <x:c r="D17" s="43" t="str"/>
       <x:c r="E17" s="43" t="str"/>
@@ -4255,7 +4434,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="43" t="str"/>
-      <x:c r="B18" s="48" t="str"/>
+      <x:c r="B18" s="69" t="str"/>
       <x:c r="C18" s="43" t="str"/>
       <x:c r="D18" s="43" t="str"/>
       <x:c r="E18" s="43" t="str"/>
@@ -4269,7 +4448,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="43" t="str"/>
-      <x:c r="B19" s="48" t="str"/>
+      <x:c r="B19" s="69" t="str"/>
       <x:c r="C19" s="43" t="str"/>
       <x:c r="D19" s="43" t="str"/>
       <x:c r="E19" s="43" t="str"/>
@@ -4283,7 +4462,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="43" t="str"/>
-      <x:c r="B20" s="48" t="str"/>
+      <x:c r="B20" s="69" t="str"/>
       <x:c r="C20" s="43" t="str"/>
       <x:c r="D20" s="43" t="str"/>
       <x:c r="E20" s="43" t="str"/>
@@ -4297,7 +4476,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="43" t="str"/>
-      <x:c r="B21" s="48" t="str"/>
+      <x:c r="B21" s="69" t="str"/>
       <x:c r="C21" s="43" t="str"/>
       <x:c r="D21" s="43" t="str"/>
       <x:c r="E21" s="43" t="str"/>
@@ -4311,7 +4490,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="43" t="str"/>
-      <x:c r="B22" s="48" t="str"/>
+      <x:c r="B22" s="69" t="str"/>
       <x:c r="C22" s="43" t="str"/>
       <x:c r="D22" s="43" t="str"/>
       <x:c r="E22" s="43" t="str"/>
@@ -4325,7 +4504,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="43" t="str"/>
-      <x:c r="B23" s="48" t="str"/>
+      <x:c r="B23" s="69" t="str"/>
       <x:c r="C23" s="43" t="str"/>
       <x:c r="D23" s="43" t="str"/>
       <x:c r="E23" s="43" t="str"/>
@@ -4339,7 +4518,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="43" t="str"/>
-      <x:c r="B24" s="48" t="str"/>
+      <x:c r="B24" s="69" t="str"/>
       <x:c r="C24" s="43" t="str"/>
       <x:c r="D24" s="43" t="str"/>
       <x:c r="E24" s="43" t="str"/>
@@ -4358,7 +4537,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1833c171888b4417"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd6b7ad3a76347c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5141,7 +5320,633 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc3d157278674bd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2722ed66f1c64b2b"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="78" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="str">
+        <x:v>Revision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="98" t="str">
+        <x:v>workbook_revision</x:v>
+      </x:c>
+      <x:c r="B2" s="98" t="str"/>
+      <x:c r="C2" s="98" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="98" t="str">
+        <x:v>source_fingerprint</x:v>
+      </x:c>
+      <x:c r="B3" s="98" t="str"/>
+      <x:c r="C3" s="98" t="str">
+        <x:v>sha256:027ae66ff43842715622c7d170c2718e8b7ae4b16d5892319836be05f8861ab0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B4" s="98" t="str">
+        <x:v>SETUP-01</x:v>
+      </x:c>
+      <x:c r="C4" s="98" t="str">
+        <x:v>sha256:6298d64e10367b2e38e5d41253bb816c1012479ab7612afc5a53ad66630e975f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B5" s="98" t="str">
+        <x:v>SETUP-02</x:v>
+      </x:c>
+      <x:c r="C5" s="98" t="str">
+        <x:v>sha256:2c28c37a65e2efee3349ec9d9c3a6e75de10e76697f1c3b5ec5ca8d1ceae0030</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B6" s="98" t="str">
+        <x:v>SETUP-03</x:v>
+      </x:c>
+      <x:c r="C6" s="98" t="str">
+        <x:v>sha256:eb596d6e2a1ad3dba500a053b487e07af4813566f59012575380f500c95740a3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B7" s="98" t="str">
+        <x:v>SETUP-MM-01</x:v>
+      </x:c>
+      <x:c r="C7" s="98" t="str">
+        <x:v>sha256:10c1951c74b44263db5ff6b5725ac0017ef930c909beb4e4acb1fb7b0d6a1e37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B8" s="98" t="str">
+        <x:v>SETUP-04</x:v>
+      </x:c>
+      <x:c r="C8" s="98" t="str">
+        <x:v>sha256:7aa728826b22f45cd601a8c9193b752d723f64e0860d54a7cbce4259e04600c5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B9" s="98" t="str">
+        <x:v>SETUP-05</x:v>
+      </x:c>
+      <x:c r="C9" s="98" t="str">
+        <x:v>sha256:fe40d0591ea5bb918a95096896c88e57973a17e604de841f7b2e42718910d160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B10" s="98" t="str">
+        <x:v>SETUP-06</x:v>
+      </x:c>
+      <x:c r="C10" s="98" t="str">
+        <x:v>sha256:beaf13d7430d2d3162636f073285172d26c909da7a8d59e4fa99be242e35555d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B11" s="98" t="str">
+        <x:v>SETUP-07</x:v>
+      </x:c>
+      <x:c r="C11" s="98" t="str">
+        <x:v>sha256:ae9a5f9d945a50c4ccc176c38f7c0029989fda3f1c58b5a69600eafb1b80cb79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B12" s="98" t="str">
+        <x:v>CTRL-CONFIG-01</x:v>
+      </x:c>
+      <x:c r="C12" s="98" t="str">
+        <x:v>sha256:5255a806565847c3cb210c1f8d9507d27ff69d5f711fbcaebfc48b18d08d9ffd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B13" s="98" t="str">
+        <x:v>BACKUP-SET-01</x:v>
+      </x:c>
+      <x:c r="C13" s="98" t="str">
+        <x:v>sha256:c8b709cad4c4eb614fa10afd8f3ee3e509cc2c66a5a1da4652b50dee3412f853</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B14" s="98" t="str">
+        <x:v>C1-CONFIG-01</x:v>
+      </x:c>
+      <x:c r="C14" s="98" t="str">
+        <x:v>sha256:bb51b8b1302bce99686d64b8b0cbf269285b79f05cdb854749bd64aea89b1012</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B15" s="98" t="str">
+        <x:v>C1-REG-01</x:v>
+      </x:c>
+      <x:c r="C15" s="98" t="str">
+        <x:v>sha256:f461ea2e61ae1e9b6979dce7f6745b9816601528fb68a6618d8eadcbdd17a502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B16" s="98" t="str">
+        <x:v>C1-READ-01</x:v>
+      </x:c>
+      <x:c r="C16" s="98" t="str">
+        <x:v>sha256:10a6be7db7226c276100bc1736c6201418a5cd05438549f1159ce0ce561d47bd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B17" s="98" t="str">
+        <x:v>C1-OPS-01</x:v>
+      </x:c>
+      <x:c r="C17" s="98" t="str">
+        <x:v>sha256:a9eb069693e2acc07f7f74fef525c73def1af24177d2490618dfb430558f3447</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B18" s="98" t="str">
+        <x:v>C2-CONFIG-01</x:v>
+      </x:c>
+      <x:c r="C18" s="98" t="str">
+        <x:v>sha256:f6bd4b38d09cefcd6ef7d79d6df02a5f7d08811ad471c4c65c5dba1acede5797</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B19" s="98" t="str">
+        <x:v>C2-REG-01</x:v>
+      </x:c>
+      <x:c r="C19" s="98" t="str">
+        <x:v>sha256:63fb5022c877bccd92feb9c02cb90b74feda63d1eb9993f889d0fe1420a6485e</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B20" s="98" t="str">
+        <x:v>C2-READ-01</x:v>
+      </x:c>
+      <x:c r="C20" s="98" t="str">
+        <x:v>sha256:ff4e52f0766604bfc924d274273adb0fecb5f24fa22997163f0ff7ca62568e84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B21" s="98" t="str">
+        <x:v>C2-OPS-01</x:v>
+      </x:c>
+      <x:c r="C21" s="98" t="str">
+        <x:v>sha256:1a9d7974ba1beac809f4901e4932230f9975a65d4fd4dc0095e2b7020b9ff262</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B22" s="98" t="str">
+        <x:v>C3-CONFIG-01</x:v>
+      </x:c>
+      <x:c r="C22" s="98" t="str">
+        <x:v>sha256:45e2ad8ae739d2475bad363b56afd793dbfeacf56f7a9c09cfe62d4d90d73b76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B23" s="98" t="str">
+        <x:v>C3-REG-01</x:v>
+      </x:c>
+      <x:c r="C23" s="98" t="str">
+        <x:v>sha256:9f5660b058d96ef2a52760a2323d545f63f41f2a651403cd58fde27e840fe894</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B24" s="98" t="str">
+        <x:v>C3-READ-01</x:v>
+      </x:c>
+      <x:c r="C24" s="98" t="str">
+        <x:v>sha256:778742d0d1c3d1effa3c73595a59bb77f362c9568e066b27aa362f9b7ce7d860</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B25" s="98" t="str">
+        <x:v>BACKUP-SET-02</x:v>
+      </x:c>
+      <x:c r="C25" s="98" t="str">
+        <x:v>sha256:884924d58217f4016aef83b195bd222dfb574f9d5ebf19c384f8014e3b0f6dc4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B26" s="98" t="str">
+        <x:v>C3-OPS-01</x:v>
+      </x:c>
+      <x:c r="C26" s="98" t="str">
+        <x:v>sha256:871d4c0cc392fa3e52b4d6f8ac15b759922a8b710c12006e6b1633d076ffeec3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B27" s="98" t="str">
+        <x:v>CTRL-AFON-01</x:v>
+      </x:c>
+      <x:c r="C27" s="98" t="str">
+        <x:v>sha256:f252e2d863b240907c921c3d4a3d318917f1ece11491b1efac56eed5ac7d0f96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B28" s="98" t="str">
+        <x:v>CTRL-AELOCK-01</x:v>
+      </x:c>
+      <x:c r="C28" s="98" t="str">
+        <x:v>sha256:d4faf5d8ee507a918a0c8e2b0879dcc44f1777165fc676dcbda956e992fcc0f5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B29" s="98" t="str">
+        <x:v>CTRL-DOF-01</x:v>
+      </x:c>
+      <x:c r="C29" s="98" t="str">
+        <x:v>sha256:84542934d1112e37aa42040c8d95b637393d4366ac13c443bf47ef2be662b860</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B30" s="98" t="str">
+        <x:v>CTRL-SET-01</x:v>
+      </x:c>
+      <x:c r="C30" s="98" t="str">
+        <x:v>sha256:16342ed08b4fc44ea0451a0a8935c8504303e9e01dae091aa87ab20c45ad6ad8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B31" s="98" t="str">
+        <x:v>CTRL-JOY-01</x:v>
+      </x:c>
+      <x:c r="C31" s="98" t="str">
+        <x:v>sha256:828c831b73117d3abc47657bd6986e93ca40a08458c77603a0085569656a2ed7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B32" s="98" t="str">
+        <x:v>EFCS-SHOCK-01</x:v>
+      </x:c>
+      <x:c r="C32" s="98" t="str">
+        <x:v>sha256:ea49c5e02cf4986fa87a0e77a31a16b4c8dceb72d35bf6ec4fa8b2ad5bf29018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B33" s="98" t="str">
+        <x:v>EFCS-BOKEH-01</x:v>
+      </x:c>
+      <x:c r="C33" s="98" t="str">
+        <x:v>sha256:3661cf4b3c827113f1bd6729a9c71f07e0934b73d2c287dac02bf2a66ff2a0ca</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B34" s="98" t="str">
+        <x:v>EFCS-LIGHT-01</x:v>
+      </x:c>
+      <x:c r="C34" s="98" t="str">
+        <x:v>sha256:97d1e6a03c7b029effa20b0c6994d82a304032923a0d6e76b693d8b2fe262568</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B35" s="98" t="str">
+        <x:v>EFCS-BURST-01</x:v>
+      </x:c>
+      <x:c r="C35" s="98" t="str">
+        <x:v>sha256:8fb04d8e137c7ade904313a65469ab549111962f3eef56b6d7645d3ebc58646c</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B36" s="98" t="str">
+        <x:v>FLASH-PLUTO-01</x:v>
+      </x:c>
+      <x:c r="C36" s="98" t="str">
+        <x:v>sha256:ae8d9581ed75d71e4f14e03057c0bdafeb110616c4390fce4cdc615093a09344</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B37" s="98" t="str">
+        <x:v>FINAL-READ-01</x:v>
+      </x:c>
+      <x:c r="C37" s="98" t="str">
+        <x:v>sha256:aabf42c50d977426a03aa33990ea7c2cf562640633a1fb7737e64ea5d5562d87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B38" s="98" t="str">
+        <x:v>FINAL-SAVE-01</x:v>
+      </x:c>
+      <x:c r="C38" s="98" t="str">
+        <x:v>sha256:2fe904eeee80a16c99d57a854d738093275a60b8573ff8d27ce3745b1913d636</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="98" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B39" s="98" t="str">
+        <x:v>PROJECT-UPDATE-01</x:v>
+      </x:c>
+      <x:c r="C39" s="98" t="str">
+        <x:v>sha256:fe0cbf03abfcc198510bcde5ef3fcd5f24e8de8a06946a6521c2e4c4ed3d4885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B40" s="98" t="str">
+        <x:v>Mode</x:v>
+      </x:c>
+      <x:c r="C40" s="98" t="str">
+        <x:v>sha256:16380d447ae550758ff49c344119374224a6b1c009504e23f6f4f93c11c00533</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B41" s="98" t="str">
+        <x:v>Metering</x:v>
+      </x:c>
+      <x:c r="C41" s="98" t="str">
+        <x:v>sha256:bc76af3dd5f76e718fe876deafcfbc0fd4a3f64d2a2eb64d2253751bd18f4eae</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B42" s="98" t="str">
+        <x:v>Exposure Compensation</x:v>
+      </x:c>
+      <x:c r="C42" s="98" t="str">
+        <x:v>sha256:88e1331bb1792dc8c402253666af51d91b4ff14bdf848d8f5715f7c5735374ee</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B43" s="98" t="str">
+        <x:v>Shutter Speed</x:v>
+      </x:c>
+      <x:c r="C43" s="98" t="str">
+        <x:v>sha256:50a59b23cd80339f63a7068a9f9b6618357bcc05eb6f986cc5c7a707e50c0a74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B44" s="98" t="str">
+        <x:v>Aperture</x:v>
+      </x:c>
+      <x:c r="C44" s="98" t="str">
+        <x:v>sha256:74b8c602aefe9109b324a5d3d0f5af54cafeaceae6f80e96effd7b7e7b7512a0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B45" s="98" t="str">
+        <x:v>ISO</x:v>
+      </x:c>
+      <x:c r="C45" s="98" t="str">
+        <x:v>sha256:3c57560fdad255af8dddd4afe759bf3a638ced62cd0b435fbcb39f539ed4d5cd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B46" s="98" t="str">
+        <x:v>Auto ISO Maximum</x:v>
+      </x:c>
+      <x:c r="C46" s="98" t="str">
+        <x:v>sha256:d9e3a1f832be05121fba7873fe44f0c6a69f48a85b28c62358a17838bc551386</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B47" s="98" t="str">
+        <x:v>AF Operation</x:v>
+      </x:c>
+      <x:c r="C47" s="98" t="str">
+        <x:v>sha256:e52a8877636b9e990324e5e59a10b6b8a0723c7699f752ac41a4e39a25ed8c94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B48" s="98" t="str">
+        <x:v>AF Method</x:v>
+      </x:c>
+      <x:c r="C48" s="98" t="str">
+        <x:v>sha256:ac30ce5e48a2e9e69db02806afb6a8c836dd8220dce399b57ed50b6ec3569d82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B49" s="98" t="str">
+        <x:v>Subject Detection</x:v>
+      </x:c>
+      <x:c r="C49" s="98" t="str">
+        <x:v>sha256:ca630f9c8761b1ba9bc261fc0264e1fdff6c6ebce7d3d60f68453c6e6c0fb66e</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B50" s="98" t="str">
+        <x:v>Eye Detection</x:v>
+      </x:c>
+      <x:c r="C50" s="98" t="str">
+        <x:v>sha256:d4f49e58f189bc2a85058e8030bdba5867549892594d4961911a877fc7774cc1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B51" s="98" t="str">
+        <x:v>Drive Mode</x:v>
+      </x:c>
+      <x:c r="C51" s="98" t="str">
+        <x:v>sha256:a407ab25d86c6b32e4618dffadce1bc9f7375731cceb32a9b15154cb636bbc93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B52" s="98" t="str">
+        <x:v>Shutter Type</x:v>
+      </x:c>
+      <x:c r="C52" s="98" t="str">
+        <x:v>sha256:e0eb3a601149113b744968c8d35c10e22707716e94c780644837edcabff082bb</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B53" s="98" t="str">
+        <x:v>Image Stabilizer Mode</x:v>
+      </x:c>
+      <x:c r="C53" s="98" t="str">
+        <x:v>sha256:cc5907ea77c17b747bda000cb9d24e886022b15d9be9b15be2fd7d3a6aa18fba</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B54" s="98" t="str">
+        <x:v>IBIS</x:v>
+      </x:c>
+      <x:c r="C54" s="98" t="str">
+        <x:v>sha256:d10f56172a85e3588b70cb9cc38fe4e1ddd6b261fb5185b7581241dda0d7e9ad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B55" s="98" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="C55" s="98" t="str">
+        <x:v>sha256:e8a1df3755fa1c6498cccfce7b113140b022e928f10c8ad2a3ff3ddf8690000a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="98" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B56" s="98" t="str">
+        <x:v>Lens IS switch</x:v>
+      </x:c>
+      <x:c r="C56" s="98" t="str">
+        <x:v>sha256:5a2f7cf7e224aef797784c3a79eb70c0a5ed8f1ae66c3227c01e8b25a206903e</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="R81463f91f7ac4041"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="Rff11a1f75a29483e"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R408b2e54f2ce4226"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="R389b81aea26c4511"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="Rb64e9b0ced244b84"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="R2b693d721ff14cf2"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="Rb2d0c026fca142aa"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="Re67f73a04c5d4d69"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="Rfcfce4ae01c74bd0"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R5d0572ae31904ce8"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="R6c86539fb02a459f"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="R5734d67e5a124ff2"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="Ra51c7ae0f92e44d2"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="R9d627e61e42a4fa1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -316,13 +316,13 @@
       <x:alignment wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -680,13 +680,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="ac58e4d1-8157-4d7e-8e64-e1412a33002e"/>
+        <xdr:cNvPr id="1" name="164a78ee-d4bd-4c73-b464-02802dd4e777"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra9380553d3ac4522"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rde42e7ee5373482b"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1496,11 +1496,11 @@
 <x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="7.440000057220459" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="13.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="29.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="17.780000686645508" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="13.890000343322754" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="25.780000686645508" hidden="0" customWidth="1"/>
@@ -1520,7 +1520,7 @@
     <x:row r="2" ht="30" customHeight="1"/>
     <x:row r="3" ht="33" customHeight="1"/>
     <x:row r="4" ht="9" customHeight="1"/>
-    <x:row r="5" ht="42" customHeight="1">
+    <x:row r="5" hidden="0">
       <x:c r="A5" s="5" t="str">
         <x:v>Test ID</x:v>
       </x:c>
@@ -1576,14 +1576,14 @@
         <x:v>Updated in Project</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="57" customHeight="1">
-      <x:c r="A6" s="21" t="str">
+    <x:row r="6" hidden="0">
+      <x:c r="A6" s="17" t="str">
         <x:v>SETUP-01</x:v>
       </x:c>
       <x:c r="B6" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="21" t="str">
+      <x:c r="C6" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
@@ -1625,14 +1625,14 @@
         <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="57" customHeight="1">
-      <x:c r="A7" s="21" t="str">
+    <x:row r="7" hidden="0">
+      <x:c r="A7" s="17" t="str">
         <x:v>SETUP-02</x:v>
       </x:c>
       <x:c r="B7" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="21" t="str">
+      <x:c r="C7" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
@@ -1674,14 +1674,14 @@
         <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="57" customHeight="1">
-      <x:c r="A8" s="21" t="str">
+    <x:row r="8" hidden="0">
+      <x:c r="A8" s="17" t="str">
         <x:v>SETUP-03</x:v>
       </x:c>
       <x:c r="B8" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C8" s="21" t="str">
+      <x:c r="C8" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
@@ -1727,14 +1727,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="88" customHeight="1">
-      <x:c r="A9" s="21" t="str">
+    <x:row r="9" hidden="0">
+      <x:c r="A9" s="17" t="str">
         <x:v>SETUP-MM-01</x:v>
       </x:c>
       <x:c r="B9" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C9" s="21" t="str">
+      <x:c r="C9" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
@@ -1778,14 +1778,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="87" customHeight="1">
-      <x:c r="A10" s="21" t="str">
+    <x:row r="10" hidden="0">
+      <x:c r="A10" s="17" t="str">
         <x:v>SETUP-04</x:v>
       </x:c>
       <x:c r="B10" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="str">
+      <x:c r="C10" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
@@ -1829,14 +1829,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="87" customHeight="1">
-      <x:c r="A11" s="21" t="str">
+    <x:row r="11" hidden="0">
+      <x:c r="A11" s="17" t="str">
         <x:v>SETUP-05</x:v>
       </x:c>
       <x:c r="B11" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="str">
+      <x:c r="C11" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D11" s="15" t="str">
@@ -1880,14 +1880,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="88" customHeight="1">
-      <x:c r="A12" s="21" t="str">
+    <x:row r="12" hidden="0">
+      <x:c r="A12" s="17" t="str">
         <x:v>SETUP-06</x:v>
       </x:c>
       <x:c r="B12" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="str">
+      <x:c r="C12" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D12" s="15" t="str">
@@ -1931,14 +1931,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="57" customHeight="1">
-      <x:c r="A13" s="21" t="str">
+    <x:row r="13" hidden="0">
+      <x:c r="A13" s="17" t="str">
         <x:v>SETUP-07</x:v>
       </x:c>
       <x:c r="B13" s="17" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="str">
+      <x:c r="C13" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D13" s="15" t="str">
@@ -1982,14 +1982,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="88" customHeight="1">
-      <x:c r="A14" s="21" t="str">
+    <x:row r="14" hidden="0">
+      <x:c r="A14" s="17" t="str">
         <x:v>CTRL-CONFIG-01</x:v>
       </x:c>
       <x:c r="B14" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="str">
+      <x:c r="C14" s="22" t="str">
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D14" s="15" t="str">
@@ -2033,14 +2033,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="72" customHeight="1">
-      <x:c r="A15" s="21" t="str">
+    <x:row r="15" hidden="0">
+      <x:c r="A15" s="17" t="str">
         <x:v>BACKUP-SET-01</x:v>
       </x:c>
       <x:c r="B15" s="17" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="str">
+      <x:c r="C15" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D15" s="15" t="str">
@@ -2082,14 +2082,14 @@
         <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="88" customHeight="1">
-      <x:c r="A16" s="21" t="str">
+    <x:row r="16" hidden="0">
+      <x:c r="A16" s="17" t="str">
         <x:v>C1-CONFIG-01</x:v>
       </x:c>
       <x:c r="B16" s="17" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="str">
+      <x:c r="C16" s="22" t="str">
         <x:v>C1 Wildlife</x:v>
       </x:c>
       <x:c r="D16" s="15" t="str">
@@ -2133,14 +2133,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="57" customHeight="1">
-      <x:c r="A17" s="21" t="str">
+    <x:row r="17" hidden="0">
+      <x:c r="A17" s="17" t="str">
         <x:v>C1-REG-01</x:v>
       </x:c>
       <x:c r="B17" s="17" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C17" s="21" t="str">
+      <x:c r="C17" s="22" t="str">
         <x:v>C1 Wildlife</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
@@ -2184,14 +2184,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="87" customHeight="1">
-      <x:c r="A18" s="21" t="str">
+    <x:row r="18" hidden="0">
+      <x:c r="A18" s="17" t="str">
         <x:v>C1-READ-01</x:v>
       </x:c>
       <x:c r="B18" s="17" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="str">
+      <x:c r="C18" s="22" t="str">
         <x:v>C1 Wildlife</x:v>
       </x:c>
       <x:c r="D18" s="15" t="str">
@@ -2235,14 +2235,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="57" customHeight="1">
-      <x:c r="A19" s="21" t="str">
+    <x:row r="19" hidden="0">
+      <x:c r="A19" s="17" t="str">
         <x:v>C1-OPS-01</x:v>
       </x:c>
       <x:c r="B19" s="17" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="str">
+      <x:c r="C19" s="22" t="str">
         <x:v>C1 Wildlife</x:v>
       </x:c>
       <x:c r="D19" s="15" t="str">
@@ -2286,14 +2286,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="88" customHeight="1">
-      <x:c r="A20" s="21" t="str">
+    <x:row r="20" hidden="0">
+      <x:c r="A20" s="17" t="str">
         <x:v>C2-CONFIG-01</x:v>
       </x:c>
       <x:c r="B20" s="17" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C20" s="21" t="str">
+      <x:c r="C20" s="22" t="str">
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
@@ -2337,14 +2337,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="57" customHeight="1">
-      <x:c r="A21" s="21" t="str">
+    <x:row r="21" hidden="0">
+      <x:c r="A21" s="17" t="str">
         <x:v>C2-REG-01</x:v>
       </x:c>
       <x:c r="B21" s="17" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C21" s="21" t="str">
+      <x:c r="C21" s="22" t="str">
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
       <x:c r="D21" s="15" t="str">
@@ -2388,14 +2388,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="87" customHeight="1">
-      <x:c r="A22" s="21" t="str">
+    <x:row r="22" hidden="0">
+      <x:c r="A22" s="17" t="str">
         <x:v>C2-READ-01</x:v>
       </x:c>
       <x:c r="B22" s="17" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C22" s="21" t="str">
+      <x:c r="C22" s="22" t="str">
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
       <x:c r="D22" s="15" t="str">
@@ -2439,14 +2439,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="57" customHeight="1">
-      <x:c r="A23" s="21" t="str">
+    <x:row r="23" hidden="0">
+      <x:c r="A23" s="17" t="str">
         <x:v>C2-OPS-01</x:v>
       </x:c>
       <x:c r="B23" s="17" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C23" s="21" t="str">
+      <x:c r="C23" s="22" t="str">
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
       <x:c r="D23" s="15" t="str">
@@ -2490,14 +2490,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="88" customHeight="1">
-      <x:c r="A24" s="21" t="str">
+    <x:row r="24" hidden="0">
+      <x:c r="A24" s="17" t="str">
         <x:v>C3-CONFIG-01</x:v>
       </x:c>
       <x:c r="B24" s="17" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C24" s="21" t="str">
+      <x:c r="C24" s="22" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="D24" s="15" t="str">
@@ -2541,14 +2541,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="57" customHeight="1">
-      <x:c r="A25" s="21" t="str">
+    <x:row r="25" hidden="0">
+      <x:c r="A25" s="17" t="str">
         <x:v>C3-REG-01</x:v>
       </x:c>
       <x:c r="B25" s="17" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C25" s="21" t="str">
+      <x:c r="C25" s="22" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="D25" s="15" t="str">
@@ -2592,14 +2592,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="87" customHeight="1">
-      <x:c r="A26" s="21" t="str">
+    <x:row r="26" hidden="0">
+      <x:c r="A26" s="17" t="str">
         <x:v>C3-READ-01</x:v>
       </x:c>
       <x:c r="B26" s="17" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C26" s="21" t="str">
+      <x:c r="C26" s="22" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="D26" s="15" t="str">
@@ -2643,14 +2643,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="57" customHeight="1">
-      <x:c r="A27" s="21" t="str">
+    <x:row r="27" hidden="0">
+      <x:c r="A27" s="17" t="str">
         <x:v>BACKUP-SET-02</x:v>
       </x:c>
       <x:c r="B27" s="17" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C27" s="21" t="str">
+      <x:c r="C27" s="22" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D27" s="15" t="str">
@@ -2692,14 +2692,14 @@
         <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="57" customHeight="1">
-      <x:c r="A28" s="21" t="str">
+    <x:row r="28" hidden="0">
+      <x:c r="A28" s="17" t="str">
         <x:v>C3-OPS-01</x:v>
       </x:c>
       <x:c r="B28" s="17" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C28" s="21" t="str">
+      <x:c r="C28" s="22" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="D28" s="15" t="str">
@@ -2743,14 +2743,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="72" customHeight="1">
-      <x:c r="A29" s="21" t="str">
+    <x:row r="29" hidden="0">
+      <x:c r="A29" s="17" t="str">
         <x:v>CTRL-AFON-01</x:v>
       </x:c>
       <x:c r="B29" s="17" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C29" s="21" t="str">
+      <x:c r="C29" s="22" t="str">
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D29" s="15" t="str">
@@ -2794,14 +2794,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="72" customHeight="1">
-      <x:c r="A30" s="21" t="str">
+    <x:row r="30" hidden="0">
+      <x:c r="A30" s="17" t="str">
         <x:v>CTRL-AELOCK-01</x:v>
       </x:c>
       <x:c r="B30" s="17" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C30" s="21" t="str">
+      <x:c r="C30" s="22" t="str">
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D30" s="15" t="str">
@@ -2845,14 +2845,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="57" customHeight="1">
-      <x:c r="A31" s="21" t="str">
+    <x:row r="31" hidden="0">
+      <x:c r="A31" s="17" t="str">
         <x:v>CTRL-DOF-01</x:v>
       </x:c>
       <x:c r="B31" s="17" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C31" s="21" t="str">
+      <x:c r="C31" s="22" t="str">
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D31" s="15" t="str">
@@ -2896,14 +2896,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="72" customHeight="1">
-      <x:c r="A32" s="21" t="str">
+    <x:row r="32" hidden="0">
+      <x:c r="A32" s="17" t="str">
         <x:v>CTRL-SET-01</x:v>
       </x:c>
       <x:c r="B32" s="17" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C32" s="21" t="str">
+      <x:c r="C32" s="22" t="str">
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D32" s="15" t="str">
@@ -2947,14 +2947,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="72" customHeight="1">
-      <x:c r="A33" s="21" t="str">
+    <x:row r="33" hidden="0">
+      <x:c r="A33" s="17" t="str">
         <x:v>CTRL-JOY-01</x:v>
       </x:c>
       <x:c r="B33" s="17" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C33" s="21" t="str">
+      <x:c r="C33" s="22" t="str">
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D33" s="15" t="str">
@@ -2998,14 +2998,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="57" customHeight="1">
-      <x:c r="A34" s="21" t="str">
+    <x:row r="34" hidden="0">
+      <x:c r="A34" s="17" t="str">
         <x:v>EFCS-SHOCK-01</x:v>
       </x:c>
       <x:c r="B34" s="17" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C34" s="21" t="str">
+      <x:c r="C34" s="22" t="str">
         <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D34" s="15" t="str">
@@ -3049,14 +3049,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="57" customHeight="1">
-      <x:c r="A35" s="21" t="str">
+    <x:row r="35" hidden="0">
+      <x:c r="A35" s="17" t="str">
         <x:v>EFCS-BOKEH-01</x:v>
       </x:c>
       <x:c r="B35" s="17" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C35" s="21" t="str">
+      <x:c r="C35" s="22" t="str">
         <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D35" s="15" t="str">
@@ -3100,14 +3100,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="72" customHeight="1">
-      <x:c r="A36" s="21" t="str">
+    <x:row r="36" hidden="0">
+      <x:c r="A36" s="17" t="str">
         <x:v>EFCS-LIGHT-01</x:v>
       </x:c>
       <x:c r="B36" s="17" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C36" s="21" t="str">
+      <x:c r="C36" s="22" t="str">
         <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D36" s="15" t="str">
@@ -3151,14 +3151,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="57" customHeight="1">
-      <x:c r="A37" s="21" t="str">
+    <x:row r="37" hidden="0">
+      <x:c r="A37" s="17" t="str">
         <x:v>EFCS-BURST-01</x:v>
       </x:c>
       <x:c r="B37" s="17" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C37" s="21" t="str">
+      <x:c r="C37" s="22" t="str">
         <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D37" s="15" t="str">
@@ -3202,14 +3202,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="88" customHeight="1">
-      <x:c r="A38" s="21" t="str">
+    <x:row r="38" hidden="0">
+      <x:c r="A38" s="17" t="str">
         <x:v>FLASH-PLUTO-01</x:v>
       </x:c>
       <x:c r="B38" s="17" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C38" s="21" t="str">
+      <x:c r="C38" s="22" t="str">
         <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D38" s="15" t="str">
@@ -3253,14 +3253,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="87" customHeight="1">
-      <x:c r="A39" s="21" t="str">
+    <x:row r="39" hidden="0">
+      <x:c r="A39" s="17" t="str">
         <x:v>FINAL-READ-01</x:v>
       </x:c>
       <x:c r="B39" s="17" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C39" s="21" t="str">
+      <x:c r="C39" s="22" t="str">
         <x:v>Finalization</x:v>
       </x:c>
       <x:c r="D39" s="15" t="str">
@@ -3304,14 +3304,14 @@
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="57" customHeight="1">
-      <x:c r="A40" s="21" t="str">
+    <x:row r="40" hidden="0">
+      <x:c r="A40" s="17" t="str">
         <x:v>FINAL-SAVE-01</x:v>
       </x:c>
       <x:c r="B40" s="17" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C40" s="21" t="str">
+      <x:c r="C40" s="22" t="str">
         <x:v>Finalization</x:v>
       </x:c>
       <x:c r="D40" s="15" t="str">
@@ -3353,14 +3353,14 @@
         <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="57" customHeight="1">
-      <x:c r="A41" s="21" t="str">
+    <x:row r="41" hidden="0">
+      <x:c r="A41" s="17" t="str">
         <x:v>PROJECT-UPDATE-01</x:v>
       </x:c>
       <x:c r="B41" s="17" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C41" s="21" t="str">
+      <x:c r="C41" s="22" t="str">
         <x:v>Project Update</x:v>
       </x:c>
       <x:c r="D41" s="15" t="str">
@@ -3427,9 +3427,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Re788128561ad475e"/>
+  <x:drawing ns1:id="Rbc98cf76d1eb4ed5"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rfa70f8121d594d7e"/>
+    <x:tablePart ns1:id="R2e933f0d7bd545d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3502,7 +3502,7 @@
       <x:c r="L3" s="6"/>
       <x:c r="M3" s="60"/>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" hidden="0">
       <x:c r="A4" s="51" t="str">
         <x:v>Setting</x:v>
       </x:c>
@@ -3543,7 +3543,7 @@
         <x:v>C3 Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" hidden="0">
       <x:c r="A5" s="52" t="str">
         <x:v>Mode</x:v>
       </x:c>
@@ -3578,7 +3578,7 @@
       </x:c>
       <x:c r="M5" s="64" t="str"/>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" hidden="0">
       <x:c r="A6" s="52" t="str">
         <x:v>Metering</x:v>
       </x:c>
@@ -3613,7 +3613,7 @@
       </x:c>
       <x:c r="M6" s="64" t="str"/>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" hidden="0">
       <x:c r="A7" s="52" t="str">
         <x:v>Exposure Compensation</x:v>
       </x:c>
@@ -3648,7 +3648,7 @@
       </x:c>
       <x:c r="M7" s="64" t="str"/>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" hidden="0">
       <x:c r="A8" s="52" t="str">
         <x:v>Shutter Speed</x:v>
       </x:c>
@@ -3683,7 +3683,7 @@
       </x:c>
       <x:c r="M8" s="64" t="str"/>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" hidden="0">
       <x:c r="A9" s="52" t="str">
         <x:v>Aperture</x:v>
       </x:c>
@@ -3718,7 +3718,7 @@
       </x:c>
       <x:c r="M9" s="64" t="str"/>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" hidden="0">
       <x:c r="A10" s="52" t="str">
         <x:v>ISO</x:v>
       </x:c>
@@ -3753,7 +3753,7 @@
       </x:c>
       <x:c r="M10" s="64" t="str"/>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" hidden="0">
       <x:c r="A11" s="52" t="str">
         <x:v>Auto ISO Maximum</x:v>
       </x:c>
@@ -3788,7 +3788,7 @@
       </x:c>
       <x:c r="M11" s="64" t="str"/>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" hidden="0">
       <x:c r="A12" s="52" t="str">
         <x:v>AF Operation</x:v>
       </x:c>
@@ -3823,7 +3823,7 @@
       </x:c>
       <x:c r="M12" s="64" t="str"/>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" hidden="0">
       <x:c r="A13" s="52" t="str">
         <x:v>AF Method</x:v>
       </x:c>
@@ -3858,7 +3858,7 @@
       </x:c>
       <x:c r="M13" s="64" t="str"/>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" hidden="0">
       <x:c r="A14" s="52" t="str">
         <x:v>Subject Detection</x:v>
       </x:c>
@@ -3893,7 +3893,7 @@
       </x:c>
       <x:c r="M14" s="64" t="str"/>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" hidden="0">
       <x:c r="A15" s="52" t="str">
         <x:v>Eye Detection</x:v>
       </x:c>
@@ -3928,7 +3928,7 @@
       </x:c>
       <x:c r="M15" s="64" t="str"/>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" hidden="0">
       <x:c r="A16" s="52" t="str">
         <x:v>Drive Mode</x:v>
       </x:c>
@@ -3963,7 +3963,7 @@
       </x:c>
       <x:c r="M16" s="64" t="str"/>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" hidden="0">
       <x:c r="A17" s="52" t="str">
         <x:v>Shutter Type</x:v>
       </x:c>
@@ -3998,7 +3998,7 @@
       </x:c>
       <x:c r="M17" s="64" t="str"/>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" hidden="0">
       <x:c r="A18" s="52" t="str">
         <x:v>Image Stabilizer Mode</x:v>
       </x:c>
@@ -4033,7 +4033,7 @@
       </x:c>
       <x:c r="M18" s="64" t="str"/>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" hidden="0">
       <x:c r="A19" s="52" t="str">
         <x:v>IBIS</x:v>
       </x:c>
@@ -4068,7 +4068,7 @@
       </x:c>
       <x:c r="M19" s="64" t="str"/>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" hidden="0">
       <x:c r="A20" s="52" t="str">
         <x:v>Focus Bracketing</x:v>
       </x:c>
@@ -4103,7 +4103,7 @@
       </x:c>
       <x:c r="M20" s="64" t="str"/>
     </x:row>
-    <x:row r="21">
+    <x:row r="21" hidden="0">
       <x:c r="A21" s="53" t="str">
         <x:v>Lens IS switch</x:v>
       </x:c>
@@ -4156,13 +4156,13 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R7db6c6a1cd8f4e5e"/>
+    <x:tablePart ns1:id="Rbc59291e99be4d89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14.220000267028809" hidden="0" customWidth="1"/>
@@ -4212,7 +4212,7 @@
       <x:c r="L2" s="38"/>
     </x:row>
     <x:row r="3" ht="12" customHeight="1"/>
-    <x:row r="4">
+    <x:row r="4" hidden="0">
       <x:c r="A4" s="5" t="str">
         <x:v>Session ID</x:v>
       </x:c>
@@ -4250,7 +4250,7 @@
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" hidden="0">
       <x:c r="A5" s="43" t="str"/>
       <x:c r="B5" s="69" t="str"/>
       <x:c r="C5" s="43" t="str"/>
@@ -4264,7 +4264,7 @@
       <x:c r="K5" s="43" t="str"/>
       <x:c r="L5" s="43" t="str"/>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" hidden="0">
       <x:c r="A6" s="43" t="str"/>
       <x:c r="B6" s="69" t="str"/>
       <x:c r="C6" s="43" t="str"/>
@@ -4278,7 +4278,7 @@
       <x:c r="K6" s="43" t="str"/>
       <x:c r="L6" s="43" t="str"/>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" hidden="0">
       <x:c r="A7" s="43" t="str"/>
       <x:c r="B7" s="69" t="str"/>
       <x:c r="C7" s="43" t="str"/>
@@ -4292,7 +4292,7 @@
       <x:c r="K7" s="43" t="str"/>
       <x:c r="L7" s="43" t="str"/>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" hidden="0">
       <x:c r="A8" s="43" t="str"/>
       <x:c r="B8" s="69" t="str"/>
       <x:c r="C8" s="43" t="str"/>
@@ -4306,7 +4306,7 @@
       <x:c r="K8" s="43" t="str"/>
       <x:c r="L8" s="43" t="str"/>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" hidden="0">
       <x:c r="A9" s="43" t="str"/>
       <x:c r="B9" s="69" t="str"/>
       <x:c r="C9" s="43" t="str"/>
@@ -4320,7 +4320,7 @@
       <x:c r="K9" s="43" t="str"/>
       <x:c r="L9" s="43" t="str"/>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" hidden="0">
       <x:c r="A10" s="43" t="str"/>
       <x:c r="B10" s="69" t="str"/>
       <x:c r="C10" s="43" t="str"/>
@@ -4334,7 +4334,7 @@
       <x:c r="K10" s="43" t="str"/>
       <x:c r="L10" s="43" t="str"/>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" hidden="0">
       <x:c r="A11" s="43" t="str"/>
       <x:c r="B11" s="69" t="str"/>
       <x:c r="C11" s="43" t="str"/>
@@ -4348,7 +4348,7 @@
       <x:c r="K11" s="43" t="str"/>
       <x:c r="L11" s="43" t="str"/>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" hidden="0">
       <x:c r="A12" s="43" t="str"/>
       <x:c r="B12" s="69" t="str"/>
       <x:c r="C12" s="43" t="str"/>
@@ -4362,7 +4362,7 @@
       <x:c r="K12" s="43" t="str"/>
       <x:c r="L12" s="43" t="str"/>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" hidden="0">
       <x:c r="A13" s="43" t="str"/>
       <x:c r="B13" s="69" t="str"/>
       <x:c r="C13" s="43" t="str"/>
@@ -4376,7 +4376,7 @@
       <x:c r="K13" s="43" t="str"/>
       <x:c r="L13" s="43" t="str"/>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" hidden="0">
       <x:c r="A14" s="43" t="str"/>
       <x:c r="B14" s="69" t="str"/>
       <x:c r="C14" s="43" t="str"/>
@@ -4390,7 +4390,7 @@
       <x:c r="K14" s="43" t="str"/>
       <x:c r="L14" s="43" t="str"/>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" hidden="0">
       <x:c r="A15" s="43" t="str"/>
       <x:c r="B15" s="69" t="str"/>
       <x:c r="C15" s="43" t="str"/>
@@ -4404,7 +4404,7 @@
       <x:c r="K15" s="43" t="str"/>
       <x:c r="L15" s="43" t="str"/>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" hidden="0">
       <x:c r="A16" s="43" t="str"/>
       <x:c r="B16" s="69" t="str"/>
       <x:c r="C16" s="43" t="str"/>
@@ -4418,7 +4418,7 @@
       <x:c r="K16" s="43" t="str"/>
       <x:c r="L16" s="43" t="str"/>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" hidden="0">
       <x:c r="A17" s="43" t="str"/>
       <x:c r="B17" s="69" t="str"/>
       <x:c r="C17" s="43" t="str"/>
@@ -4432,7 +4432,7 @@
       <x:c r="K17" s="43" t="str"/>
       <x:c r="L17" s="43" t="str"/>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" hidden="0">
       <x:c r="A18" s="43" t="str"/>
       <x:c r="B18" s="69" t="str"/>
       <x:c r="C18" s="43" t="str"/>
@@ -4446,7 +4446,7 @@
       <x:c r="K18" s="43" t="str"/>
       <x:c r="L18" s="43" t="str"/>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" hidden="0">
       <x:c r="A19" s="43" t="str"/>
       <x:c r="B19" s="69" t="str"/>
       <x:c r="C19" s="43" t="str"/>
@@ -4460,7 +4460,7 @@
       <x:c r="K19" s="43" t="str"/>
       <x:c r="L19" s="43" t="str"/>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" hidden="0">
       <x:c r="A20" s="43" t="str"/>
       <x:c r="B20" s="69" t="str"/>
       <x:c r="C20" s="43" t="str"/>
@@ -4474,7 +4474,7 @@
       <x:c r="K20" s="43" t="str"/>
       <x:c r="L20" s="43" t="str"/>
     </x:row>
-    <x:row r="21">
+    <x:row r="21" hidden="0">
       <x:c r="A21" s="43" t="str"/>
       <x:c r="B21" s="69" t="str"/>
       <x:c r="C21" s="43" t="str"/>
@@ -4488,7 +4488,7 @@
       <x:c r="K21" s="43" t="str"/>
       <x:c r="L21" s="43" t="str"/>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" hidden="0">
       <x:c r="A22" s="43" t="str"/>
       <x:c r="B22" s="69" t="str"/>
       <x:c r="C22" s="43" t="str"/>
@@ -4502,7 +4502,7 @@
       <x:c r="K22" s="43" t="str"/>
       <x:c r="L22" s="43" t="str"/>
     </x:row>
-    <x:row r="23">
+    <x:row r="23" hidden="0">
       <x:c r="A23" s="43" t="str"/>
       <x:c r="B23" s="69" t="str"/>
       <x:c r="C23" s="43" t="str"/>
@@ -4516,7 +4516,7 @@
       <x:c r="K23" s="43" t="str"/>
       <x:c r="L23" s="43" t="str"/>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" hidden="0">
       <x:c r="A24" s="43" t="str"/>
       <x:c r="B24" s="69" t="str"/>
       <x:c r="C24" s="43" t="str"/>
@@ -4537,7 +4537,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd6b7ad3a76347c6"/>
+    <x:tablePart ns1:id="R639f55e7a3f146fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4678,7 +4678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14.5600004196167" hidden="0" customWidth="1"/>
@@ -4688,7 +4688,7 @@
     <x:col min="5" max="5" width="10.329999923706055" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
+    <x:row r="1" hidden="0">
       <x:c r="A1" s="5" t="str">
         <x:v>Test ID</x:v>
       </x:c>
@@ -4705,7 +4705,7 @@
         <x:v>Sequence</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="40" customHeight="1">
+    <x:row r="2" hidden="0">
       <x:c r="A2" s="10" t="str">
         <x:v>SETUP-01</x:v>
       </x:c>
@@ -4722,7 +4722,7 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="40" customHeight="1">
+    <x:row r="3" hidden="0">
       <x:c r="A3" s="10" t="str">
         <x:v>SETUP-02</x:v>
       </x:c>
@@ -4739,7 +4739,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="40" customHeight="1">
+    <x:row r="4" hidden="0">
       <x:c r="A4" s="10" t="str">
         <x:v>SETUP-03</x:v>
       </x:c>
@@ -4756,7 +4756,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="70" customHeight="1">
+    <x:row r="5" hidden="0">
       <x:c r="A5" s="10" t="str">
         <x:v>SETUP-MM-01</x:v>
       </x:c>
@@ -4773,7 +4773,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="55" customHeight="1">
+    <x:row r="6" hidden="0">
       <x:c r="A6" s="10" t="str">
         <x:v>SETUP-04</x:v>
       </x:c>
@@ -4790,7 +4790,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="55" customHeight="1">
+    <x:row r="7" hidden="0">
       <x:c r="A7" s="10" t="str">
         <x:v>SETUP-05</x:v>
       </x:c>
@@ -4807,7 +4807,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="70" customHeight="1">
+    <x:row r="8" hidden="0">
       <x:c r="A8" s="10" t="str">
         <x:v>SETUP-06</x:v>
       </x:c>
@@ -4824,7 +4824,7 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="40" customHeight="1">
+    <x:row r="9" hidden="0">
       <x:c r="A9" s="10" t="str">
         <x:v>SETUP-07</x:v>
       </x:c>
@@ -4841,7 +4841,7 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="70" customHeight="1">
+    <x:row r="10" hidden="0">
       <x:c r="A10" s="10" t="str">
         <x:v>CTRL-CONFIG-01</x:v>
       </x:c>
@@ -4858,7 +4858,7 @@
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="40" customHeight="1">
+    <x:row r="11" hidden="0">
       <x:c r="A11" s="10" t="str">
         <x:v>BACKUP-SET-01</x:v>
       </x:c>
@@ -4875,7 +4875,7 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="70" customHeight="1">
+    <x:row r="12" hidden="0">
       <x:c r="A12" s="10" t="str">
         <x:v>C1-CONFIG-01</x:v>
       </x:c>
@@ -4892,7 +4892,7 @@
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="40" customHeight="1">
+    <x:row r="13" hidden="0">
       <x:c r="A13" s="10" t="str">
         <x:v>C1-REG-01</x:v>
       </x:c>
@@ -4909,7 +4909,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="55" customHeight="1">
+    <x:row r="14" hidden="0">
       <x:c r="A14" s="10" t="str">
         <x:v>C1-READ-01</x:v>
       </x:c>
@@ -4926,7 +4926,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="25" customHeight="1">
+    <x:row r="15" hidden="0">
       <x:c r="A15" s="10" t="str">
         <x:v>C1-OPS-01</x:v>
       </x:c>
@@ -4943,7 +4943,7 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="70" customHeight="1">
+    <x:row r="16" hidden="0">
       <x:c r="A16" s="10" t="str">
         <x:v>C2-CONFIG-01</x:v>
       </x:c>
@@ -4960,7 +4960,7 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="40" customHeight="1">
+    <x:row r="17" hidden="0">
       <x:c r="A17" s="10" t="str">
         <x:v>C2-REG-01</x:v>
       </x:c>
@@ -4977,7 +4977,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="55" customHeight="1">
+    <x:row r="18" hidden="0">
       <x:c r="A18" s="10" t="str">
         <x:v>C2-READ-01</x:v>
       </x:c>
@@ -4994,7 +4994,7 @@
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="25" customHeight="1">
+    <x:row r="19" hidden="0">
       <x:c r="A19" s="10" t="str">
         <x:v>C2-OPS-01</x:v>
       </x:c>
@@ -5011,7 +5011,7 @@
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="70" customHeight="1">
+    <x:row r="20" hidden="0">
       <x:c r="A20" s="10" t="str">
         <x:v>C3-CONFIG-01</x:v>
       </x:c>
@@ -5028,7 +5028,7 @@
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="40" customHeight="1">
+    <x:row r="21" hidden="0">
       <x:c r="A21" s="10" t="str">
         <x:v>C3-REG-01</x:v>
       </x:c>
@@ -5045,7 +5045,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="55" customHeight="1">
+    <x:row r="22" hidden="0">
       <x:c r="A22" s="10" t="str">
         <x:v>C3-READ-01</x:v>
       </x:c>
@@ -5062,7 +5062,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="40" customHeight="1">
+    <x:row r="23" hidden="0">
       <x:c r="A23" s="10" t="str">
         <x:v>BACKUP-SET-02</x:v>
       </x:c>
@@ -5079,7 +5079,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="25" customHeight="1">
+    <x:row r="24" hidden="0">
       <x:c r="A24" s="10" t="str">
         <x:v>C3-OPS-01</x:v>
       </x:c>
@@ -5096,7 +5096,7 @@
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="55" customHeight="1">
+    <x:row r="25" hidden="0">
       <x:c r="A25" s="10" t="str">
         <x:v>CTRL-AFON-01</x:v>
       </x:c>
@@ -5113,7 +5113,7 @@
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="55" customHeight="1">
+    <x:row r="26" hidden="0">
       <x:c r="A26" s="10" t="str">
         <x:v>CTRL-AELOCK-01</x:v>
       </x:c>
@@ -5130,7 +5130,7 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="40" customHeight="1">
+    <x:row r="27" hidden="0">
       <x:c r="A27" s="10" t="str">
         <x:v>CTRL-DOF-01</x:v>
       </x:c>
@@ -5147,7 +5147,7 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="25" customHeight="1">
+    <x:row r="28" hidden="0">
       <x:c r="A28" s="10" t="str">
         <x:v>CTRL-SET-01</x:v>
       </x:c>
@@ -5164,7 +5164,7 @@
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="40" customHeight="1">
+    <x:row r="29" hidden="0">
       <x:c r="A29" s="10" t="str">
         <x:v>CTRL-JOY-01</x:v>
       </x:c>
@@ -5181,7 +5181,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="40" customHeight="1">
+    <x:row r="30" hidden="0">
       <x:c r="A30" s="10" t="str">
         <x:v>EFCS-SHOCK-01</x:v>
       </x:c>
@@ -5198,7 +5198,7 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="40" customHeight="1">
+    <x:row r="31" hidden="0">
       <x:c r="A31" s="10" t="str">
         <x:v>EFCS-BOKEH-01</x:v>
       </x:c>
@@ -5215,7 +5215,7 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="40" customHeight="1">
+    <x:row r="32" hidden="0">
       <x:c r="A32" s="10" t="str">
         <x:v>EFCS-LIGHT-01</x:v>
       </x:c>
@@ -5232,7 +5232,7 @@
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="40" customHeight="1">
+    <x:row r="33" hidden="0">
       <x:c r="A33" s="10" t="str">
         <x:v>EFCS-BURST-01</x:v>
       </x:c>
@@ -5249,7 +5249,7 @@
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="70" customHeight="1">
+    <x:row r="34" hidden="0">
       <x:c r="A34" s="10" t="str">
         <x:v>FLASH-PLUTO-01</x:v>
       </x:c>
@@ -5266,7 +5266,7 @@
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="70" customHeight="1">
+    <x:row r="35" hidden="0">
       <x:c r="A35" s="10" t="str">
         <x:v>FINAL-READ-01</x:v>
       </x:c>
@@ -5283,7 +5283,7 @@
         <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="40" customHeight="1">
+    <x:row r="36" hidden="0">
       <x:c r="A36" s="10" t="str">
         <x:v>FINAL-SAVE-01</x:v>
       </x:c>
@@ -5300,7 +5300,7 @@
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="40" customHeight="1">
+    <x:row r="37" hidden="0">
       <x:c r="A37" s="10" t="str">
         <x:v>PROJECT-UPDATE-01</x:v>
       </x:c>
@@ -5320,7 +5320,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2722ed66f1c64b2b"/>
+    <x:tablePart ns1:id="Rbf8bb4418abf4902"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5360,7 +5360,7 @@
       </x:c>
       <x:c r="B3" s="98" t="str"/>
       <x:c r="C3" s="98" t="str">
-        <x:v>sha256:027ae66ff43842715622c7d170c2718e8b7ae4b16d5892319836be05f8861ab0</x:v>
+        <x:v>sha256:fc93ec9c0503081c08901734c9619654f36870e69f856801d5b3d1be3ad7dff3</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="Re67f73a04c5d4d69"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="Rfcfce4ae01c74bd0"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R5d0572ae31904ce8"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="R6c86539fb02a459f"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="R5734d67e5a124ff2"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="Ra51c7ae0f92e44d2"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="R9d627e61e42a4fa1"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rdd4796573f124d2f"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="R6df9c4097155430b"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="Rbc9c39fac4fa497c"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="R591dd2c6fce74e27"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="R89401d2fa8094aad"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="R04fd23ed5edf40a0"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="R1ad93d99d7894beb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +26,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="17">
+  <x:fonts count="19">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -56,6 +56,17 @@
       <x:i/>
       <x:sz val="11"/>
       <x:color rgb="FF17324D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF17324D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="1"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -145,17 +156,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2F5F7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F3E2"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -264,7 +275,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="99">
+  <x:cellXfs count="106">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -412,13 +423,24 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
@@ -428,6 +450,12 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
@@ -443,7 +471,9 @@
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -477,11 +507,11 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -490,36 +520,30 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -528,6 +552,12 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -538,23 +568,23 @@
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="11">
+  <x:dxfs count="15">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -607,6 +637,46 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -680,13 +750,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="164a78ee-d4bd-4c73-b464-02802dd4e777"/>
+        <xdr:cNvPr id="1" name="2190222f-37e5-478b-9a39-12d574bb5987"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rde42e7ee5373482b"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1e531527be234f1e"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -745,22 +815,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegistrationTable" displayName="RegistrationTable" ref="A4:M21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:M21"/>
-  <x:tableColumns count="13">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegistrationTable" displayName="RegistrationTable" ref="A4:N21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N21"/>
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="Setting"/>
-    <x:tableColumn id="2" name="C1 Wildlife Target"/>
-    <x:tableColumn id="3" name="C1 Configured"/>
-    <x:tableColumn id="4" name="C1 Read-back"/>
-    <x:tableColumn id="5" name="C1 Notes"/>
-    <x:tableColumn id="6" name="C2 Birds in Flight Target"/>
-    <x:tableColumn id="7" name="C2 Configured"/>
-    <x:tableColumn id="8" name="C2 Read-back"/>
-    <x:tableColumn id="9" name="C2 Notes"/>
-    <x:tableColumn id="10" name="C3 Landscape Target"/>
-    <x:tableColumn id="11" name="C3 Configured"/>
-    <x:tableColumn id="12" name="C3 Read-back"/>
-    <x:tableColumn id="13" name="C3 Notes"/>
+    <x:tableColumn id="2" name="Default Settings"/>
+    <x:tableColumn id="3" name="C1 Wildlife Target"/>
+    <x:tableColumn id="4" name="C1 Configured"/>
+    <x:tableColumn id="5" name="C1 Read-back"/>
+    <x:tableColumn id="6" name="C1 Notes"/>
+    <x:tableColumn id="7" name="C2 Birds in Flight Target"/>
+    <x:tableColumn id="8" name="C2 Configured"/>
+    <x:tableColumn id="9" name="C2 Read-back"/>
+    <x:tableColumn id="10" name="C2 Notes"/>
+    <x:tableColumn id="11" name="C3 Landscape Target"/>
+    <x:tableColumn id="12" name="C3 Configured"/>
+    <x:tableColumn id="13" name="C3 Read-back"/>
+    <x:tableColumn id="14" name="C3 Notes"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1007,26 +1078,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="72" t="str">
+      <x:c r="A1" s="79" t="str">
         <x:v>EOS R5 On-Camera Verification Progress</x:v>
       </x:c>
-      <x:c r="B1" s="72"/>
-      <x:c r="C1" s="72"/>
-      <x:c r="D1" s="72"/>
-      <x:c r="E1" s="72"/>
-      <x:c r="F1" s="72"/>
-      <x:c r="G1" s="72"/>
-      <x:c r="H1" s="72"/>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="72"/>
-      <x:c r="B2" s="72"/>
-      <x:c r="C2" s="72"/>
-      <x:c r="D2" s="72"/>
-      <x:c r="E2" s="72"/>
-      <x:c r="F2" s="72"/>
-      <x:c r="G2" s="72"/>
-      <x:c r="H2" s="72"/>
+      <x:c r="A2" s="79"/>
+      <x:c r="B2" s="79"/>
+      <x:c r="C2" s="79"/>
+      <x:c r="D2" s="79"/>
+      <x:c r="E2" s="79"/>
+      <x:c r="F2" s="79"/>
+      <x:c r="G2" s="79"/>
+      <x:c r="H2" s="79"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="38" t="str">
@@ -1051,54 +1122,54 @@
       <x:c r="H4" s="38"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="75" t="str">
+      <x:c r="A6" s="82" t="str">
         <x:v>Total checklist items</x:v>
       </x:c>
-      <x:c r="B6" s="75" t="str"/>
-      <x:c r="C6" s="77" t="str">
+      <x:c r="B6" s="82" t="str"/>
+      <x:c r="C6" s="84" t="str">
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="D6" s="77" t="str"/>
-      <x:c r="E6" s="79" t="str">
+      <x:c r="D6" s="84" t="str"/>
+      <x:c r="E6" s="86" t="str">
         <x:v>In progress / pending</x:v>
       </x:c>
-      <x:c r="F6" s="79" t="str"/>
-      <x:c r="G6" s="81" t="str">
+      <x:c r="F6" s="86" t="str"/>
+      <x:c r="G6" s="88" t="str">
         <x:v>Needs attention</x:v>
       </x:c>
-      <x:c r="H6" s="81" t="str"/>
+      <x:c r="H6" s="88" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="85" t="n">
+      <x:c r="A7" s="92" t="n">
         <x:f>COUNTA('Checklist'!$A$6:$A$41)</x:f>
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B7" s="85"/>
-      <x:c r="C7" s="86" t="n">
+      <x:c r="B7" s="92"/>
+      <x:c r="C7" s="93" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="86"/>
-      <x:c r="E7" s="87" t="n">
+      <x:c r="D7" s="93"/>
+      <x:c r="E7" s="94" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,"In progress")+COUNTIF('Checklist'!$I$6:$I$41,"Configured—not registered")+COUNTIF('Checklist'!$I$6:$I$41,"Registered—pending read-back")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="87"/>
-      <x:c r="G7" s="88" t="n">
+      <x:c r="F7" s="94"/>
+      <x:c r="G7" s="95" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIF('Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIF('Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H7" s="88"/>
+      <x:c r="H7" s="95"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="85"/>
-      <x:c r="B8" s="85"/>
-      <x:c r="C8" s="86"/>
-      <x:c r="D8" s="86"/>
-      <x:c r="E8" s="87"/>
-      <x:c r="F8" s="87"/>
-      <x:c r="G8" s="88"/>
-      <x:c r="H8" s="88"/>
+      <x:c r="A8" s="92"/>
+      <x:c r="B8" s="92"/>
+      <x:c r="C8" s="93"/>
+      <x:c r="D8" s="93"/>
+      <x:c r="E8" s="94"/>
+      <x:c r="F8" s="94"/>
+      <x:c r="G8" s="95"/>
+      <x:c r="H8" s="95"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="str">
@@ -1128,19 +1199,19 @@
       <x:c r="A12" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
-      <x:c r="B12" s="90" t="n">
+      <x:c r="B12" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A12)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="90" t="n">
+      <x:c r="C12" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="90" t="n">
+      <x:c r="D12" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="91" t="n">
+      <x:c r="E12" s="98" t="n">
         <x:f>IF(B12=0,0,(C12+COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B12)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1148,7 +1219,7 @@
       <x:c r="G12" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="H12" s="90" t="n">
+      <x:c r="H12" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G12)</x:f>
         <x:v>35</x:v>
       </x:c>
@@ -1157,19 +1228,19 @@
       <x:c r="A13" t="str">
         <x:v>Controls</x:v>
       </x:c>
-      <x:c r="B13" s="90" t="n">
+      <x:c r="B13" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A13)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C13" s="90" t="n">
+      <x:c r="C13" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="90" t="n">
+      <x:c r="D13" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="91" t="n">
+      <x:c r="E13" s="98" t="n">
         <x:f>IF(B13=0,0,(C13+COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B13)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1177,7 +1248,7 @@
       <x:c r="G13" t="str">
         <x:v>In progress</x:v>
       </x:c>
-      <x:c r="H13" s="90" t="n">
+      <x:c r="H13" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G13)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1186,19 +1257,19 @@
       <x:c r="A14" t="str">
         <x:v>C1 Wildlife</x:v>
       </x:c>
-      <x:c r="B14" s="90" t="n">
+      <x:c r="B14" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A14)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C14" s="90" t="n">
+      <x:c r="C14" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="90" t="n">
+      <x:c r="D14" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="91" t="n">
+      <x:c r="E14" s="98" t="n">
         <x:f>IF(B14=0,0,(C14+COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B14)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1206,7 +1277,7 @@
       <x:c r="G14" t="str">
         <x:v>Configured—not registered</x:v>
       </x:c>
-      <x:c r="H14" s="90" t="n">
+      <x:c r="H14" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G14)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1215,19 +1286,19 @@
       <x:c r="A15" t="str">
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
-      <x:c r="B15" s="90" t="n">
+      <x:c r="B15" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A15)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C15" s="90" t="n">
+      <x:c r="C15" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D15" s="90" t="n">
+      <x:c r="D15" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="91" t="n">
+      <x:c r="E15" s="98" t="n">
         <x:f>IF(B15=0,0,(C15+COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B15)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1235,7 +1306,7 @@
       <x:c r="G15" t="str">
         <x:v>Registered—pending read-back</x:v>
       </x:c>
-      <x:c r="H15" s="90" t="n">
+      <x:c r="H15" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G15)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1244,19 +1315,19 @@
       <x:c r="A16" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
-      <x:c r="B16" s="90" t="n">
+      <x:c r="B16" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A16)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C16" s="90" t="n">
+      <x:c r="C16" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="90" t="n">
+      <x:c r="D16" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="91" t="n">
+      <x:c r="E16" s="98" t="n">
         <x:f>IF(B16=0,0,(C16+COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B16)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1264,7 +1335,7 @@
       <x:c r="G16" t="str">
         <x:v>Backup-Settings</x:v>
       </x:c>
-      <x:c r="H16" s="90" t="n">
+      <x:c r="H16" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G16)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1273,19 +1344,19 @@
       <x:c r="A17" t="str">
         <x:v>EFCS Tests</x:v>
       </x:c>
-      <x:c r="B17" s="90" t="n">
+      <x:c r="B17" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A17)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C17" s="90" t="n">
+      <x:c r="C17" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D17" s="90" t="n">
+      <x:c r="D17" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="91" t="n">
+      <x:c r="E17" s="98" t="n">
         <x:f>IF(B17=0,0,(C17+COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B17)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1293,7 +1364,7 @@
       <x:c r="G17" t="str">
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="H17" s="90" t="n">
+      <x:c r="H17" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G17)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1302,19 +1373,19 @@
       <x:c r="A18" t="str">
         <x:v>Finalization</x:v>
       </x:c>
-      <x:c r="B18" s="90" t="n">
+      <x:c r="B18" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A18)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C18" s="90" t="n">
+      <x:c r="C18" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D18" s="90" t="n">
+      <x:c r="D18" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="91" t="n">
+      <x:c r="E18" s="98" t="n">
         <x:f>IF(B18=0,0,(C18+COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B18)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1322,7 +1393,7 @@
       <x:c r="G18" t="str">
         <x:v>Failed—needs correction</x:v>
       </x:c>
-      <x:c r="H18" s="90" t="n">
+      <x:c r="H18" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G18)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1331,19 +1402,19 @@
       <x:c r="A19" t="str">
         <x:v>Project Update</x:v>
       </x:c>
-      <x:c r="B19" s="90" t="n">
+      <x:c r="B19" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$C$6:$C$41,A19)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C19" s="90" t="n">
+      <x:c r="C19" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D19" s="90" t="n">
+      <x:c r="D19" s="97" t="n">
         <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E19" s="91" t="n">
+      <x:c r="E19" s="98" t="n">
         <x:f>IF(B19=0,0,(C19+COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B19)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1351,108 +1422,108 @@
       <x:c r="G19" t="str">
         <x:v>Inconclusive—needs retest</x:v>
       </x:c>
-      <x:c r="H19" s="90" t="n">
+      <x:c r="H19" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G19)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str"/>
-      <x:c r="B20" s="90" t="str"/>
-      <x:c r="C20" s="90" t="str"/>
-      <x:c r="D20" s="90" t="str"/>
-      <x:c r="E20" s="90" t="str"/>
+      <x:c r="B20" s="97" t="str"/>
+      <x:c r="C20" s="97" t="str"/>
+      <x:c r="D20" s="97" t="str"/>
+      <x:c r="E20" s="97" t="str"/>
       <x:c r="F20" t="str"/>
       <x:c r="G20" t="str">
         <x:v>Blocked</x:v>
       </x:c>
-      <x:c r="H20" s="90" t="n">
+      <x:c r="H20" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G20)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str"/>
-      <x:c r="B21" s="90" t="str"/>
-      <x:c r="C21" s="90" t="str"/>
-      <x:c r="D21" s="90" t="str"/>
-      <x:c r="E21" s="90" t="str"/>
+      <x:c r="B21" s="97" t="str"/>
+      <x:c r="C21" s="97" t="str"/>
+      <x:c r="D21" s="97" t="str"/>
+      <x:c r="E21" s="97" t="str"/>
       <x:c r="F21" t="str"/>
       <x:c r="G21" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="H21" s="90" t="n">
+      <x:c r="H21" s="97" t="n">
         <x:f>COUNTIF('Checklist'!$I$6:$I$41,G21)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="92" t="str">
+      <x:c r="A23" s="99" t="str">
         <x:v>Recommended workflow</x:v>
       </x:c>
-      <x:c r="B23" s="92"/>
-      <x:c r="C23" s="92"/>
-      <x:c r="D23" s="92"/>
-      <x:c r="E23" s="92"/>
-      <x:c r="F23" s="92"/>
-      <x:c r="G23" s="92"/>
-      <x:c r="H23" s="92"/>
+      <x:c r="B23" s="99"/>
+      <x:c r="C23" s="99"/>
+      <x:c r="D23" s="99"/>
+      <x:c r="E23" s="99"/>
+      <x:c r="F23" s="99"/>
+      <x:c r="G23" s="99"/>
+      <x:c r="H23" s="99"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="96" t="str">
+      <x:c r="A24" s="103" t="str">
         <x:v>1. Save the starting camera configuration and document C1–C3.
 2. Disable Auto update, then configure and verify the SWITCH My Menu tab.
 3. Save Backup-Settings checkpoints after shared setup/controls and after C1–C3 read-back.
 4. Work through Checklist in Sequence order and use one Session ID per camera session.
 5. Filter Project Update? = Yes and Status = Verified before changing project evidence states.</x:v>
       </x:c>
-      <x:c r="B24" s="96"/>
-      <x:c r="C24" s="96"/>
-      <x:c r="D24" s="96"/>
-      <x:c r="E24" s="96"/>
-      <x:c r="F24" s="96"/>
-      <x:c r="G24" s="96"/>
-      <x:c r="H24" s="96"/>
+      <x:c r="B24" s="103"/>
+      <x:c r="C24" s="103"/>
+      <x:c r="D24" s="103"/>
+      <x:c r="E24" s="103"/>
+      <x:c r="F24" s="103"/>
+      <x:c r="G24" s="103"/>
+      <x:c r="H24" s="103"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="96"/>
-      <x:c r="B25" s="96"/>
-      <x:c r="C25" s="96"/>
-      <x:c r="D25" s="96"/>
-      <x:c r="E25" s="96"/>
-      <x:c r="F25" s="96"/>
-      <x:c r="G25" s="96"/>
-      <x:c r="H25" s="96"/>
+      <x:c r="A25" s="103"/>
+      <x:c r="B25" s="103"/>
+      <x:c r="C25" s="103"/>
+      <x:c r="D25" s="103"/>
+      <x:c r="E25" s="103"/>
+      <x:c r="F25" s="103"/>
+      <x:c r="G25" s="103"/>
+      <x:c r="H25" s="103"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="96"/>
-      <x:c r="B26" s="96"/>
-      <x:c r="C26" s="96"/>
-      <x:c r="D26" s="96"/>
-      <x:c r="E26" s="96"/>
-      <x:c r="F26" s="96"/>
-      <x:c r="G26" s="96"/>
-      <x:c r="H26" s="96"/>
+      <x:c r="A26" s="103"/>
+      <x:c r="B26" s="103"/>
+      <x:c r="C26" s="103"/>
+      <x:c r="D26" s="103"/>
+      <x:c r="E26" s="103"/>
+      <x:c r="F26" s="103"/>
+      <x:c r="G26" s="103"/>
+      <x:c r="H26" s="103"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="96"/>
-      <x:c r="B27" s="96"/>
-      <x:c r="C27" s="96"/>
-      <x:c r="D27" s="96"/>
-      <x:c r="E27" s="96"/>
-      <x:c r="F27" s="96"/>
-      <x:c r="G27" s="96"/>
-      <x:c r="H27" s="96"/>
+      <x:c r="A27" s="103"/>
+      <x:c r="B27" s="103"/>
+      <x:c r="C27" s="103"/>
+      <x:c r="D27" s="103"/>
+      <x:c r="E27" s="103"/>
+      <x:c r="F27" s="103"/>
+      <x:c r="G27" s="103"/>
+      <x:c r="H27" s="103"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="96"/>
-      <x:c r="B28" s="96"/>
-      <x:c r="C28" s="96"/>
-      <x:c r="D28" s="96"/>
-      <x:c r="E28" s="96"/>
-      <x:c r="F28" s="96"/>
-      <x:c r="G28" s="96"/>
-      <x:c r="H28" s="96"/>
+      <x:c r="A28" s="103"/>
+      <x:c r="B28" s="103"/>
+      <x:c r="C28" s="103"/>
+      <x:c r="D28" s="103"/>
+      <x:c r="E28" s="103"/>
+      <x:c r="F28" s="103"/>
+      <x:c r="G28" s="103"/>
+      <x:c r="H28" s="103"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1462,29 +1533,29 @@
     <x:mergeCell ref="A24:H28"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="C7:C7">
-    <x:cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThanOrEqual">
+    <x:cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThanOrEqual">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E7:E7">
-    <x:cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThanOrEqual">
+    <x:cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThanOrEqual">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="G7:G7">
-    <x:cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThanOrEqual">
+    <x:cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThanOrEqual">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E12:E19">
-    <x:cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <x:cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <x:formula>1</x:formula>
     </x:cfRule>
-    <x:cfRule type="cellIs" dxfId="9" priority="5" operator="between">
+    <x:cfRule type="cellIs" dxfId="13" priority="5" operator="between">
       <x:formula>0.0001</x:formula>
       <x:formula>0.9999</x:formula>
     </x:cfRule>
-    <x:cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <x:cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -1789,14 +1860,14 @@
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>Shared capture and exposure defaults match the reference baseline.</x:v>
+        <x:v>Shared operational defaults match the complete C1-aligned reference baseline.</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
-        <x:v>Confirm cRAW, Full-frame, Evaluative metering, and Auto ISO maximum 12800.</x:v>
+        <x:v>Confirm Fv, shutter and aperture Auto, Auto ISO maximum 12800, Servo AF, Face + Tracking, Animals, Eye Detection Enable, High Speed Continuous, EFCS, Mode 1, cRAW, Full-frame, and Evaluative metering.</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
         <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Q screen; MM-SWITCH for Cropping/aspect ratio</x:v>
+        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio</x:v>
       </x:c>
       <x:c r="G10" s="29" t="str">
         <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
@@ -1804,7 +1875,7 @@
       </x:c>
       <x:c r="H10" s="15" t="str">
         <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Quick Control: Evaluative metering</x:v>
+        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting menu: IS (Image Stabilizer) mode</x:v>
       </x:c>
       <x:c r="I10" s="13" t="str">
         <x:v>Not started</x:v>
@@ -3427,9 +3498,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rbc98cf76d1eb4ed5"/>
+  <x:drawing ns1:id="Rc6659296c774453e"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R2e933f0d7bd545d8"/>
+    <x:tablePart ns1:id="R07faa2ff69f14cfa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3440,723 +3511,1115 @@
   <x:cols>
     <x:col min="1" max="1" width="22.219999313354492" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24.889999389648438" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.889999389648438" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24.889999389648438" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24.889999389648438" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="26.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24.889999389648438" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24.889999389648438" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="14.220000267028809" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="26.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="26.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="0.2199999988079071" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="0.2199999988079071" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="0.2199999988079071" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="0.2199999988079071" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="48" t="str">
+      <x:c r="A1" s="53" t="str">
         <x:v>C1–C3 Registration: Configure → Register → Read Back → Verify</x:v>
       </x:c>
-      <x:c r="B1" s="54"/>
-      <x:c r="C1" s="55"/>
-      <x:c r="D1" s="55"/>
-      <x:c r="E1" s="56"/>
-      <x:c r="F1" s="54"/>
-      <x:c r="G1" s="55"/>
-      <x:c r="H1" s="55"/>
-      <x:c r="I1" s="56"/>
-      <x:c r="J1" s="54"/>
-      <x:c r="K1" s="55"/>
-      <x:c r="L1" s="55"/>
-      <x:c r="M1" s="56"/>
+      <x:c r="B1" s="53"/>
+      <x:c r="C1" s="61"/>
+      <x:c r="D1" s="62"/>
+      <x:c r="E1" s="62"/>
+      <x:c r="F1" s="63"/>
+      <x:c r="G1" s="61"/>
+      <x:c r="H1" s="62"/>
+      <x:c r="I1" s="62"/>
+      <x:c r="J1" s="63"/>
+      <x:c r="K1" s="61"/>
+      <x:c r="L1" s="62"/>
+      <x:c r="M1" s="62"/>
+      <x:c r="N1" s="63"/>
+      <x:c r="O1" s="52"/>
+      <x:c r="P1" s="52"/>
+      <x:c r="Q1" s="52"/>
+      <x:c r="R1" s="52"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="49" t="str">
+      <x:c r="A2" s="54" t="str">
         <x:v>Work from a normal shooting mode. Validate the complete column before registering a slot. Record configuration and read-back separately for every setting.</x:v>
       </x:c>
-      <x:c r="B2" s="57"/>
-      <x:c r="C2" s="38"/>
+      <x:c r="B2" s="54"/>
+      <x:c r="C2" s="64"/>
       <x:c r="D2" s="38"/>
-      <x:c r="E2" s="58"/>
-      <x:c r="F2" s="57"/>
-      <x:c r="G2" s="38"/>
+      <x:c r="E2" s="38"/>
+      <x:c r="F2" s="65"/>
+      <x:c r="G2" s="64"/>
       <x:c r="H2" s="38"/>
-      <x:c r="I2" s="58"/>
-      <x:c r="J2" s="57"/>
-      <x:c r="K2" s="38"/>
+      <x:c r="I2" s="38"/>
+      <x:c r="J2" s="65"/>
+      <x:c r="K2" s="64"/>
       <x:c r="L2" s="38"/>
-      <x:c r="M2" s="58"/>
-    </x:row>
-    <x:row r="3" ht="12" customHeight="1">
-      <x:c r="A3" s="50"/>
-      <x:c r="B3" s="59"/>
-      <x:c r="C3" s="6"/>
+      <x:c r="M2" s="38"/>
+      <x:c r="N2" s="65"/>
+      <x:c r="O2" s="52"/>
+      <x:c r="P2" s="52"/>
+      <x:c r="Q2" s="52"/>
+      <x:c r="R2" s="52"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="55" t="str">
+        <x:v>Compare to:</x:v>
+      </x:c>
+      <x:c r="B3" s="55" t="str">
+        <x:v>Default Settings</x:v>
+      </x:c>
+      <x:c r="C3" s="66" t="str">
+        <x:v>Default Settings</x:v>
+      </x:c>
       <x:c r="D3" s="6"/>
-      <x:c r="E3" s="60"/>
-      <x:c r="F3" s="59"/>
-      <x:c r="G3" s="6"/>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="67"/>
+      <x:c r="G3" s="66" t="str">
+        <x:v>Default Settings</x:v>
+      </x:c>
       <x:c r="H3" s="6"/>
-      <x:c r="I3" s="60"/>
-      <x:c r="J3" s="59"/>
-      <x:c r="K3" s="6"/>
+      <x:c r="I3" s="6"/>
+      <x:c r="J3" s="67"/>
+      <x:c r="K3" s="66" t="str">
+        <x:v>Default Settings</x:v>
+      </x:c>
       <x:c r="L3" s="6"/>
-      <x:c r="M3" s="60"/>
+      <x:c r="M3" s="6"/>
+      <x:c r="N3" s="67"/>
+      <x:c r="O3" s="52"/>
+      <x:c r="P3" s="52"/>
+      <x:c r="Q3" s="52"/>
+      <x:c r="R3" s="52"/>
     </x:row>
     <x:row r="4" hidden="0">
-      <x:c r="A4" s="51" t="str">
+      <x:c r="A4" s="56" t="str">
         <x:v>Setting</x:v>
       </x:c>
-      <x:c r="B4" s="61" t="str">
+      <x:c r="B4" s="56" t="str">
+        <x:v>Default Settings</x:v>
+      </x:c>
+      <x:c r="C4" s="68" t="str">
         <x:v>C1 Wildlife Target</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="str">
+      <x:c r="D4" s="5" t="str">
         <x:v>C1 Configured</x:v>
       </x:c>
-      <x:c r="D4" s="5" t="str">
+      <x:c r="E4" s="5" t="str">
         <x:v>C1 Read-back</x:v>
       </x:c>
-      <x:c r="E4" s="62" t="str">
+      <x:c r="F4" s="69" t="str">
         <x:v>C1 Notes</x:v>
       </x:c>
-      <x:c r="F4" s="61" t="str">
+      <x:c r="G4" s="68" t="str">
         <x:v>C2 Birds in Flight Target</x:v>
       </x:c>
-      <x:c r="G4" s="5" t="str">
+      <x:c r="H4" s="5" t="str">
         <x:v>C2 Configured</x:v>
       </x:c>
-      <x:c r="H4" s="5" t="str">
+      <x:c r="I4" s="5" t="str">
         <x:v>C2 Read-back</x:v>
       </x:c>
-      <x:c r="I4" s="62" t="str">
+      <x:c r="J4" s="69" t="str">
         <x:v>C2 Notes</x:v>
       </x:c>
-      <x:c r="J4" s="61" t="str">
+      <x:c r="K4" s="68" t="str">
         <x:v>C3 Landscape Target</x:v>
       </x:c>
-      <x:c r="K4" s="5" t="str">
+      <x:c r="L4" s="5" t="str">
         <x:v>C3 Configured</x:v>
       </x:c>
-      <x:c r="L4" s="5" t="str">
+      <x:c r="M4" s="5" t="str">
         <x:v>C3 Read-back</x:v>
       </x:c>
-      <x:c r="M4" s="62" t="str">
+      <x:c r="N4" s="69" t="str">
         <x:v>C3 Notes</x:v>
       </x:c>
+      <x:c r="O4" s="52"/>
+      <x:c r="P4" s="52"/>
+      <x:c r="Q4" s="52"/>
+      <x:c r="R4" s="52"/>
     </x:row>
     <x:row r="5" hidden="0">
-      <x:c r="A5" s="52" t="str">
+      <x:c r="A5" s="57" t="str">
         <x:v>Mode</x:v>
       </x:c>
-      <x:c r="B5" s="63" t="str">
+      <x:c r="B5" s="59" t="str">
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="C5" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C5" s="70" t="str">
+        <x:v>Fv</x:v>
       </x:c>
       <x:c r="D5" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E5" s="64" t="str"/>
-      <x:c r="F5" s="63" t="str">
+      <x:c r="E5" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F5" s="71" t="str"/>
+      <x:c r="G5" s="70" t="str">
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="G5" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H5" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I5" s="64" t="str"/>
-      <x:c r="J5" s="63" t="str">
+      <x:c r="I5" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J5" s="71" t="str"/>
+      <x:c r="K5" s="70" t="str">
         <x:v>Av</x:v>
       </x:c>
-      <x:c r="K5" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L5" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M5" s="64" t="str"/>
+      <x:c r="M5" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N5" s="71" t="str"/>
+      <x:c r="O5" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B5,IF($B$3="C1 Wildlife",C5,IF($B$3="C2 Birds in Flight",G5,IF($B$3="C3 Landscape",K5,""))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="P5" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B5,IF($C$3="C1 Wildlife",C5,IF($C$3="C2 Birds in Flight",G5,IF($C$3="C3 Landscape",K5,""))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="Q5" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B5,IF($G$3="C1 Wildlife",C5,IF($G$3="C2 Birds in Flight",G5,IF($G$3="C3 Landscape",K5,""))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="R5" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B5,IF($K$3="C1 Wildlife",C5,IF($K$3="C2 Birds in Flight",G5,IF($K$3="C3 Landscape",K5,""))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" hidden="0">
-      <x:c r="A6" s="52" t="str">
+      <x:c r="A6" s="57" t="str">
         <x:v>Metering</x:v>
       </x:c>
-      <x:c r="B6" s="63" t="str">
+      <x:c r="B6" s="59" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="C6" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C6" s="70" t="str">
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="D6" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E6" s="64" t="str"/>
-      <x:c r="F6" s="63" t="str">
+      <x:c r="E6" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F6" s="71" t="str"/>
+      <x:c r="G6" s="70" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="G6" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H6" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I6" s="64" t="str"/>
-      <x:c r="J6" s="63" t="str">
+      <x:c r="I6" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J6" s="71" t="str"/>
+      <x:c r="K6" s="70" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="K6" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L6" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M6" s="64" t="str"/>
+      <x:c r="M6" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N6" s="71" t="str"/>
+      <x:c r="O6" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B6,IF($B$3="C1 Wildlife",C6,IF($B$3="C2 Birds in Flight",G6,IF($B$3="C3 Landscape",K6,""))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="P6" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B6,IF($C$3="C1 Wildlife",C6,IF($C$3="C2 Birds in Flight",G6,IF($C$3="C3 Landscape",K6,""))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="Q6" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B6,IF($G$3="C1 Wildlife",C6,IF($G$3="C2 Birds in Flight",G6,IF($G$3="C3 Landscape",K6,""))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="R6" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B6,IF($K$3="C1 Wildlife",C6,IF($K$3="C2 Birds in Flight",G6,IF($K$3="C3 Landscape",K6,""))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" hidden="0">
-      <x:c r="A7" s="52" t="str">
+      <x:c r="A7" s="57" t="str">
         <x:v>Exposure Compensation</x:v>
       </x:c>
-      <x:c r="B7" s="63" t="str">
+      <x:c r="B7" s="59" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C7" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C7" s="70" t="str">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E7" s="64" t="str"/>
-      <x:c r="F7" s="63" t="str">
+      <x:c r="E7" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F7" s="71" t="str"/>
+      <x:c r="G7" s="70" t="str">
         <x:v>0 starting point</x:v>
       </x:c>
-      <x:c r="G7" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H7" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I7" s="64" t="str"/>
-      <x:c r="J7" s="63" t="str">
+      <x:c r="I7" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J7" s="71" t="str"/>
+      <x:c r="K7" s="70" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K7" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L7" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M7" s="64" t="str"/>
+      <x:c r="M7" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N7" s="71" t="str"/>
+      <x:c r="O7" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B7,IF($B$3="C1 Wildlife",C7,IF($B$3="C2 Birds in Flight",G7,IF($B$3="C3 Landscape",K7,""))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B7,IF($C$3="C1 Wildlife",C7,IF($C$3="C2 Birds in Flight",G7,IF($C$3="C3 Landscape",K7,""))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B7,IF($G$3="C1 Wildlife",C7,IF($G$3="C2 Birds in Flight",G7,IF($G$3="C3 Landscape",K7,""))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B7,IF($K$3="C1 Wildlife",C7,IF($K$3="C2 Birds in Flight",G7,IF($K$3="C3 Landscape",K7,""))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" hidden="0">
-      <x:c r="A8" s="52" t="str">
+      <x:c r="A8" s="57" t="str">
         <x:v>Shutter Speed</x:v>
       </x:c>
-      <x:c r="B8" s="63" t="str">
+      <x:c r="B8" s="59" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="C8" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C8" s="70" t="str">
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="D8" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E8" s="64" t="str"/>
-      <x:c r="F8" s="63" t="str">
+      <x:c r="E8" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F8" s="71" t="str"/>
+      <x:c r="G8" s="70" t="str">
         <x:v>1/2500 sec.</x:v>
       </x:c>
-      <x:c r="G8" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H8" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I8" s="64" t="str"/>
-      <x:c r="J8" s="63" t="str">
+      <x:c r="I8" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J8" s="71" t="str"/>
+      <x:c r="K8" s="70" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="K8" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L8" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M8" s="64" t="str"/>
+      <x:c r="M8" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N8" s="71" t="str"/>
+      <x:c r="O8" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B8,IF($B$3="C1 Wildlife",C8,IF($B$3="C2 Birds in Flight",G8,IF($B$3="C3 Landscape",K8,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="P8" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B8,IF($C$3="C1 Wildlife",C8,IF($C$3="C2 Birds in Flight",G8,IF($C$3="C3 Landscape",K8,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Q8" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B8,IF($G$3="C1 Wildlife",C8,IF($G$3="C2 Birds in Flight",G8,IF($G$3="C3 Landscape",K8,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="R8" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B8,IF($K$3="C1 Wildlife",C8,IF($K$3="C2 Birds in Flight",G8,IF($K$3="C3 Landscape",K8,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" hidden="0">
-      <x:c r="A9" s="52" t="str">
+      <x:c r="A9" s="57" t="str">
         <x:v>Aperture</x:v>
       </x:c>
-      <x:c r="B9" s="63" t="str">
+      <x:c r="B9" s="59" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="C9" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C9" s="70" t="str">
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="D9" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E9" s="64" t="str"/>
-      <x:c r="F9" s="63" t="str">
+      <x:c r="E9" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F9" s="71" t="str"/>
+      <x:c r="G9" s="70" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="G9" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H9" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I9" s="64" t="str"/>
-      <x:c r="J9" s="63" t="str">
+      <x:c r="I9" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J9" s="71" t="str"/>
+      <x:c r="K9" s="70" t="str">
         <x:v>f/9</x:v>
       </x:c>
-      <x:c r="K9" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L9" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M9" s="64" t="str"/>
+      <x:c r="M9" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N9" s="71" t="str"/>
+      <x:c r="O9" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B9,IF($B$3="C1 Wildlife",C9,IF($B$3="C2 Birds in Flight",G9,IF($B$3="C3 Landscape",K9,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="P9" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B9,IF($C$3="C1 Wildlife",C9,IF($C$3="C2 Birds in Flight",G9,IF($C$3="C3 Landscape",K9,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Q9" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B9,IF($G$3="C1 Wildlife",C9,IF($G$3="C2 Birds in Flight",G9,IF($G$3="C3 Landscape",K9,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="R9" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B9,IF($K$3="C1 Wildlife",C9,IF($K$3="C2 Birds in Flight",G9,IF($K$3="C3 Landscape",K9,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" hidden="0">
-      <x:c r="A10" s="52" t="str">
+      <x:c r="A10" s="57" t="str">
         <x:v>ISO</x:v>
       </x:c>
-      <x:c r="B10" s="63" t="str">
+      <x:c r="B10" s="59" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="C10" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C10" s="70" t="str">
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="D10" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E10" s="64" t="str"/>
-      <x:c r="F10" s="63" t="str">
+      <x:c r="E10" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F10" s="71" t="str"/>
+      <x:c r="G10" s="70" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="G10" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H10" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I10" s="64" t="str"/>
-      <x:c r="J10" s="63" t="str">
+      <x:c r="I10" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J10" s="71" t="str"/>
+      <x:c r="K10" s="70" t="str">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K10" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L10" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M10" s="64" t="str"/>
+      <x:c r="M10" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N10" s="71" t="str"/>
+      <x:c r="O10" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B10,IF($B$3="C1 Wildlife",C10,IF($B$3="C2 Birds in Flight",G10,IF($B$3="C3 Landscape",K10,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="P10" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B10,IF($C$3="C1 Wildlife",C10,IF($C$3="C2 Birds in Flight",G10,IF($C$3="C3 Landscape",K10,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Q10" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B10,IF($G$3="C1 Wildlife",C10,IF($G$3="C2 Birds in Flight",G10,IF($G$3="C3 Landscape",K10,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="R10" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B10,IF($K$3="C1 Wildlife",C10,IF($K$3="C2 Birds in Flight",G10,IF($K$3="C3 Landscape",K10,""))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" hidden="0">
-      <x:c r="A11" s="52" t="str">
+      <x:c r="A11" s="57" t="str">
         <x:v>Auto ISO Maximum</x:v>
       </x:c>
-      <x:c r="B11" s="63" t="str">
+      <x:c r="B11" s="59" t="str">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="C11" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C11" s="70" t="str">
+        <x:v>12800</x:v>
       </x:c>
       <x:c r="D11" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E11" s="64" t="str"/>
-      <x:c r="F11" s="63" t="str">
+      <x:c r="E11" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F11" s="71" t="str"/>
+      <x:c r="G11" s="70" t="str">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="G11" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H11" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I11" s="64" t="str"/>
-      <x:c r="J11" s="63" t="str">
+      <x:c r="I11" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J11" s="71" t="str"/>
+      <x:c r="K11" s="70" t="str">
         <x:v>12800; inactive at ISO 100</x:v>
       </x:c>
-      <x:c r="K11" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L11" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M11" s="64" t="str"/>
+      <x:c r="M11" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N11" s="71" t="str"/>
+      <x:c r="O11" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B11,IF($B$3="C1 Wildlife",C11,IF($B$3="C2 Birds in Flight",G11,IF($B$3="C3 Landscape",K11,""))))</x:f>
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="P11" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B11,IF($C$3="C1 Wildlife",C11,IF($C$3="C2 Birds in Flight",G11,IF($C$3="C3 Landscape",K11,""))))</x:f>
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="Q11" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B11,IF($G$3="C1 Wildlife",C11,IF($G$3="C2 Birds in Flight",G11,IF($G$3="C3 Landscape",K11,""))))</x:f>
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="R11" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B11,IF($K$3="C1 Wildlife",C11,IF($K$3="C2 Birds in Flight",G11,IF($K$3="C3 Landscape",K11,""))))</x:f>
+        <x:v>12800</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" hidden="0">
-      <x:c r="A12" s="52" t="str">
+      <x:c r="A12" s="57" t="str">
         <x:v>AF Operation</x:v>
       </x:c>
-      <x:c r="B12" s="63" t="str">
+      <x:c r="B12" s="59" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="C12" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C12" s="70" t="str">
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="D12" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E12" s="64" t="str"/>
-      <x:c r="F12" s="63" t="str">
+      <x:c r="E12" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F12" s="71" t="str"/>
+      <x:c r="G12" s="70" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="G12" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H12" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I12" s="64" t="str"/>
-      <x:c r="J12" s="63" t="str">
+      <x:c r="I12" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J12" s="71" t="str"/>
+      <x:c r="K12" s="70" t="str">
         <x:v>One-Shot AF</x:v>
       </x:c>
-      <x:c r="K12" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L12" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M12" s="64" t="str"/>
+      <x:c r="M12" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N12" s="71" t="str"/>
+      <x:c r="O12" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B12,IF($B$3="C1 Wildlife",C12,IF($B$3="C2 Birds in Flight",G12,IF($B$3="C3 Landscape",K12,""))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="P12" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B12,IF($C$3="C1 Wildlife",C12,IF($C$3="C2 Birds in Flight",G12,IF($C$3="C3 Landscape",K12,""))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="Q12" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B12,IF($G$3="C1 Wildlife",C12,IF($G$3="C2 Birds in Flight",G12,IF($G$3="C3 Landscape",K12,""))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="R12" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B12,IF($K$3="C1 Wildlife",C12,IF($K$3="C2 Birds in Flight",G12,IF($K$3="C3 Landscape",K12,""))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" hidden="0">
-      <x:c r="A13" s="52" t="str">
+      <x:c r="A13" s="57" t="str">
         <x:v>AF Method</x:v>
       </x:c>
-      <x:c r="B13" s="63" t="str">
+      <x:c r="B13" s="59" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="C13" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C13" s="70" t="str">
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="D13" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E13" s="64" t="str"/>
-      <x:c r="F13" s="63" t="str">
+      <x:c r="E13" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F13" s="71" t="str"/>
+      <x:c r="G13" s="70" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="G13" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H13" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I13" s="64" t="str"/>
-      <x:c r="J13" s="63" t="str">
+      <x:c r="I13" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J13" s="71" t="str"/>
+      <x:c r="K13" s="70" t="str">
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="K13" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L13" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M13" s="64" t="str"/>
+      <x:c r="M13" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N13" s="71" t="str"/>
+      <x:c r="O13" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B13,IF($B$3="C1 Wildlife",C13,IF($B$3="C2 Birds in Flight",G13,IF($B$3="C3 Landscape",K13,""))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="P13" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B13,IF($C$3="C1 Wildlife",C13,IF($C$3="C2 Birds in Flight",G13,IF($C$3="C3 Landscape",K13,""))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="Q13" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B13,IF($G$3="C1 Wildlife",C13,IF($G$3="C2 Birds in Flight",G13,IF($G$3="C3 Landscape",K13,""))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="R13" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B13,IF($K$3="C1 Wildlife",C13,IF($K$3="C2 Birds in Flight",G13,IF($K$3="C3 Landscape",K13,""))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" hidden="0">
-      <x:c r="A14" s="52" t="str">
+      <x:c r="A14" s="57" t="str">
         <x:v>Subject Detection</x:v>
       </x:c>
-      <x:c r="B14" s="63" t="str">
+      <x:c r="B14" s="59" t="str">
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="C14" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C14" s="70" t="str">
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="D14" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E14" s="64" t="str"/>
-      <x:c r="F14" s="63" t="str">
+      <x:c r="E14" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F14" s="71" t="str"/>
+      <x:c r="G14" s="70" t="str">
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="G14" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H14" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I14" s="64" t="str"/>
-      <x:c r="J14" s="63" t="str">
+      <x:c r="I14" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J14" s="71" t="str"/>
+      <x:c r="K14" s="70" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="K14" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L14" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M14" s="64" t="str"/>
+      <x:c r="M14" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N14" s="71" t="str"/>
+      <x:c r="O14" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B14,IF($B$3="C1 Wildlife",C14,IF($B$3="C2 Birds in Flight",G14,IF($B$3="C3 Landscape",K14,""))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="P14" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B14,IF($C$3="C1 Wildlife",C14,IF($C$3="C2 Birds in Flight",G14,IF($C$3="C3 Landscape",K14,""))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="Q14" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B14,IF($G$3="C1 Wildlife",C14,IF($G$3="C2 Birds in Flight",G14,IF($G$3="C3 Landscape",K14,""))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="R14" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B14,IF($K$3="C1 Wildlife",C14,IF($K$3="C2 Birds in Flight",G14,IF($K$3="C3 Landscape",K14,""))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" hidden="0">
-      <x:c r="A15" s="52" t="str">
+      <x:c r="A15" s="57" t="str">
         <x:v>Eye Detection</x:v>
       </x:c>
-      <x:c r="B15" s="63" t="str">
+      <x:c r="B15" s="59" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="C15" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C15" s="70" t="str">
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="D15" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E15" s="64" t="str"/>
-      <x:c r="F15" s="63" t="str">
+      <x:c r="E15" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F15" s="71" t="str"/>
+      <x:c r="G15" s="70" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="G15" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H15" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I15" s="64" t="str"/>
-      <x:c r="J15" s="63" t="str">
+      <x:c r="I15" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J15" s="71" t="str"/>
+      <x:c r="K15" s="70" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="K15" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L15" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M15" s="64" t="str"/>
+      <x:c r="M15" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N15" s="71" t="str"/>
+      <x:c r="O15" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B15,IF($B$3="C1 Wildlife",C15,IF($B$3="C2 Birds in Flight",G15,IF($B$3="C3 Landscape",K15,""))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="P15" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B15,IF($C$3="C1 Wildlife",C15,IF($C$3="C2 Birds in Flight",G15,IF($C$3="C3 Landscape",K15,""))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="Q15" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B15,IF($G$3="C1 Wildlife",C15,IF($G$3="C2 Birds in Flight",G15,IF($G$3="C3 Landscape",K15,""))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="R15" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B15,IF($K$3="C1 Wildlife",C15,IF($K$3="C2 Birds in Flight",G15,IF($K$3="C3 Landscape",K15,""))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" hidden="0">
-      <x:c r="A16" s="52" t="str">
+      <x:c r="A16" s="57" t="str">
         <x:v>Drive Mode</x:v>
       </x:c>
-      <x:c r="B16" s="63" t="str">
+      <x:c r="B16" s="59" t="str">
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="C16" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C16" s="70" t="str">
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="D16" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E16" s="64" t="str"/>
-      <x:c r="F16" s="63" t="str">
+      <x:c r="E16" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F16" s="71" t="str"/>
+      <x:c r="G16" s="70" t="str">
         <x:v>High Speed Continuous+</x:v>
       </x:c>
-      <x:c r="G16" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H16" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I16" s="64" t="str"/>
-      <x:c r="J16" s="63" t="str">
+      <x:c r="I16" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J16" s="71" t="str"/>
+      <x:c r="K16" s="70" t="str">
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="K16" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L16" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M16" s="64" t="str"/>
+      <x:c r="M16" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N16" s="71" t="str"/>
+      <x:c r="O16" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B16,IF($B$3="C1 Wildlife",C16,IF($B$3="C2 Birds in Flight",G16,IF($B$3="C3 Landscape",K16,""))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="P16" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B16,IF($C$3="C1 Wildlife",C16,IF($C$3="C2 Birds in Flight",G16,IF($C$3="C3 Landscape",K16,""))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="Q16" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B16,IF($G$3="C1 Wildlife",C16,IF($G$3="C2 Birds in Flight",G16,IF($G$3="C3 Landscape",K16,""))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="R16" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B16,IF($K$3="C1 Wildlife",C16,IF($K$3="C2 Birds in Flight",G16,IF($K$3="C3 Landscape",K16,""))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" hidden="0">
-      <x:c r="A17" s="52" t="str">
+      <x:c r="A17" s="57" t="str">
         <x:v>Shutter Type</x:v>
       </x:c>
-      <x:c r="B17" s="63" t="str">
+      <x:c r="B17" s="59" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="C17" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C17" s="70" t="str">
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="D17" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E17" s="64" t="str"/>
-      <x:c r="F17" s="63" t="str">
+      <x:c r="E17" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F17" s="71" t="str"/>
+      <x:c r="G17" s="70" t="str">
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="G17" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H17" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I17" s="64" t="str"/>
-      <x:c r="J17" s="63" t="str">
+      <x:c r="I17" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J17" s="71" t="str"/>
+      <x:c r="K17" s="70" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="K17" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L17" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M17" s="64" t="str"/>
+      <x:c r="M17" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N17" s="71" t="str"/>
+      <x:c r="O17" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B17,IF($B$3="C1 Wildlife",C17,IF($B$3="C2 Birds in Flight",G17,IF($B$3="C3 Landscape",K17,""))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="P17" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B17,IF($C$3="C1 Wildlife",C17,IF($C$3="C2 Birds in Flight",G17,IF($C$3="C3 Landscape",K17,""))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="Q17" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B17,IF($G$3="C1 Wildlife",C17,IF($G$3="C2 Birds in Flight",G17,IF($G$3="C3 Landscape",K17,""))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="R17" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B17,IF($K$3="C1 Wildlife",C17,IF($K$3="C2 Birds in Flight",G17,IF($K$3="C3 Landscape",K17,""))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" hidden="0">
-      <x:c r="A18" s="52" t="str">
+      <x:c r="A18" s="57" t="str">
         <x:v>Image Stabilizer Mode</x:v>
       </x:c>
-      <x:c r="B18" s="63" t="str">
+      <x:c r="B18" s="59" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="C18" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C18" s="70" t="str">
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="D18" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E18" s="64" t="str"/>
-      <x:c r="F18" s="63" t="str">
+      <x:c r="E18" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F18" s="71" t="str"/>
+      <x:c r="G18" s="70" t="str">
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="G18" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H18" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I18" s="64" t="str"/>
-      <x:c r="J18" s="63" t="str">
+      <x:c r="I18" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J18" s="71" t="str"/>
+      <x:c r="K18" s="70" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="K18" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L18" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M18" s="64" t="str"/>
+      <x:c r="M18" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N18" s="71" t="str"/>
+      <x:c r="O18" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B18,IF($B$3="C1 Wildlife",C18,IF($B$3="C2 Birds in Flight",G18,IF($B$3="C3 Landscape",K18,""))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="P18" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B18,IF($C$3="C1 Wildlife",C18,IF($C$3="C2 Birds in Flight",G18,IF($C$3="C3 Landscape",K18,""))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="Q18" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B18,IF($G$3="C1 Wildlife",C18,IF($G$3="C2 Birds in Flight",G18,IF($G$3="C3 Landscape",K18,""))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="R18" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B18,IF($K$3="C1 Wildlife",C18,IF($K$3="C2 Birds in Flight",G18,IF($K$3="C3 Landscape",K18,""))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" hidden="0">
-      <x:c r="A19" s="52" t="str">
+      <x:c r="A19" s="57" t="str">
         <x:v>IBIS</x:v>
       </x:c>
-      <x:c r="B19" s="65" t="b">
+      <x:c r="B19" s="59" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="C19" s="72" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C19" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="D19" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E19" s="64" t="str"/>
-      <x:c r="F19" s="65" t="b">
+      <x:c r="E19" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F19" s="71" t="str"/>
+      <x:c r="G19" s="72" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G19" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H19" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I19" s="64" t="str"/>
-      <x:c r="J19" s="65" t="b">
+      <x:c r="I19" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J19" s="71" t="str"/>
+      <x:c r="K19" s="72" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K19" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L19" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M19" s="64" t="str"/>
+      <x:c r="M19" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N19" s="71" t="str"/>
+      <x:c r="O19" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B19,IF($B$3="C1 Wildlife",C19,IF($B$3="C2 Birds in Flight",G19,IF($B$3="C3 Landscape",K19,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="P19" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B19,IF($C$3="C1 Wildlife",C19,IF($C$3="C2 Birds in Flight",G19,IF($C$3="C3 Landscape",K19,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="Q19" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B19,IF($G$3="C1 Wildlife",C19,IF($G$3="C2 Birds in Flight",G19,IF($G$3="C3 Landscape",K19,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="R19" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B19,IF($K$3="C1 Wildlife",C19,IF($K$3="C2 Birds in Flight",G19,IF($K$3="C3 Landscape",K19,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" hidden="0">
-      <x:c r="A20" s="52" t="str">
+      <x:c r="A20" s="57" t="str">
         <x:v>Focus Bracketing</x:v>
       </x:c>
-      <x:c r="B20" s="63" t="str">
+      <x:c r="B20" s="59" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="C20" s="43" t="str">
-        <x:v>Not started</x:v>
+      <x:c r="C20" s="70" t="str">
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="D20" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="E20" s="64" t="str"/>
-      <x:c r="F20" s="63" t="str">
+      <x:c r="E20" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F20" s="71" t="str"/>
+      <x:c r="G20" s="70" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="G20" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="H20" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="I20" s="64" t="str"/>
-      <x:c r="J20" s="63" t="str">
+      <x:c r="I20" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J20" s="71" t="str"/>
+      <x:c r="K20" s="70" t="str">
         <x:v>Disable; enable situationally</x:v>
       </x:c>
-      <x:c r="K20" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
       <x:c r="L20" s="43" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="M20" s="64" t="str"/>
+      <x:c r="M20" s="43" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N20" s="71" t="str"/>
+      <x:c r="O20" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B20,IF($B$3="C1 Wildlife",C20,IF($B$3="C2 Birds in Flight",G20,IF($B$3="C3 Landscape",K20,""))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P20" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B20,IF($C$3="C1 Wildlife",C20,IF($C$3="C2 Birds in Flight",G20,IF($C$3="C3 Landscape",K20,""))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Q20" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B20,IF($G$3="C1 Wildlife",C20,IF($G$3="C2 Birds in Flight",G20,IF($G$3="C3 Landscape",K20,""))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="R20" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B20,IF($K$3="C1 Wildlife",C20,IF($K$3="C2 Birds in Flight",G20,IF($K$3="C3 Landscape",K20,""))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" hidden="0">
-      <x:c r="A21" s="53" t="str">
+      <x:c r="A21" s="58" t="str">
         <x:v>Lens IS switch</x:v>
       </x:c>
-      <x:c r="B21" s="66" t="str">
+      <x:c r="B21" s="60" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="C21" s="73" t="str">
         <x:v>On; physical check</x:v>
       </x:c>
-      <x:c r="C21" s="67" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="D21" s="67" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E21" s="68" t="str"/>
-      <x:c r="F21" s="66" t="str">
+      <x:c r="D21" s="74" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E21" s="74" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F21" s="75" t="str"/>
+      <x:c r="G21" s="73" t="str">
         <x:v>On; physical check</x:v>
       </x:c>
-      <x:c r="G21" s="67" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="H21" s="67" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I21" s="68" t="str"/>
-      <x:c r="J21" s="66" t="str">
+      <x:c r="H21" s="74" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I21" s="74" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J21" s="75" t="str"/>
+      <x:c r="K21" s="73" t="str">
         <x:v>On; handheld registration</x:v>
       </x:c>
-      <x:c r="K21" s="67" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="L21" s="67" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M21" s="68" t="str"/>
+      <x:c r="L21" s="74" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M21" s="74" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N21" s="75" t="str"/>
+      <x:c r="O21" s="52" t="str">
+        <x:f>IF($B$3="Default Settings",B21,IF($B$3="C1 Wildlife",C21,IF($B$3="C2 Birds in Flight",G21,IF($B$3="C3 Landscape",K21,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="P21" s="52" t="str">
+        <x:f>IF($C$3="Default Settings",B21,IF($C$3="C1 Wildlife",C21,IF($C$3="C2 Birds in Flight",G21,IF($C$3="C3 Landscape",K21,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="Q21" s="52" t="str">
+        <x:f>IF($G$3="Default Settings",B21,IF($G$3="C1 Wildlife",C21,IF($G$3="C2 Birds in Flight",G21,IF($G$3="C3 Landscape",K21,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="R21" s="52" t="str">
+        <x:f>IF($K$3="Default Settings",B21,IF($K$3="C1 Wildlife",C21,IF($K$3="C2 Birds in Flight",G21,IF($K$3="C3 Landscape",K21,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:M1"/>
-    <x:mergeCell ref="A2:M2"/>
+    <x:mergeCell ref="A1:N1"/>
+    <x:mergeCell ref="A2:N2"/>
   </x:mergeCells>
-  <x:dataValidations count="3">
-    <x:dataValidation type="list" sqref="C5:D21">
+  <x:conditionalFormatting sqref="B5:B21">
+    <x:cfRule type="cellIs" dxfId="5" priority="1" operator="notEqual">
+      <x:formula>$O5</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="C5:C21">
+    <x:cfRule type="cellIs" dxfId="6" priority="2" operator="notEqual">
+      <x:formula>$P5</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G5:G21">
+    <x:cfRule type="cellIs" dxfId="7" priority="3" operator="notEqual">
+      <x:formula>$Q5</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="K5:K21">
+    <x:cfRule type="cellIs" dxfId="8" priority="4" operator="notEqual">
+      <x:formula>$R5</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="7">
+    <x:dataValidation type="list" sqref="B3">
+      <x:formula1>"Default Settings,C1 Wildlife,C2 Birds in Flight,C3 Landscape"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C3">
+      <x:formula1>"Default Settings,C1 Wildlife,C2 Birds in Flight,C3 Landscape"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G3">
+      <x:formula1>"Default Settings,C1 Wildlife,C2 Birds in Flight,C3 Landscape"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K3">
+      <x:formula1>"Default Settings,C1 Wildlife,C2 Birds in Flight,C3 Landscape"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D5:E21">
       <x:formula1>"Not started,Pass,Fail,Needs retest,Not applicable"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="G5:H21">
+    <x:dataValidation type="list" sqref="H5:I21">
       <x:formula1>"Not started,Pass,Fail,Needs retest,Not applicable"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="K5:L21">
+    <x:dataValidation type="list" sqref="L5:M21">
       <x:formula1>"Not started,Pass,Fail,Needs retest,Not applicable"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rbc59291e99be4d89"/>
+    <x:tablePart ns1:id="Ra4d32262cf3447ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4252,7 +4715,7 @@
     </x:row>
     <x:row r="5" hidden="0">
       <x:c r="A5" s="43" t="str"/>
-      <x:c r="B5" s="69" t="str"/>
+      <x:c r="B5" s="76" t="str"/>
       <x:c r="C5" s="43" t="str"/>
       <x:c r="D5" s="43" t="str"/>
       <x:c r="E5" s="43" t="str"/>
@@ -4266,7 +4729,7 @@
     </x:row>
     <x:row r="6" hidden="0">
       <x:c r="A6" s="43" t="str"/>
-      <x:c r="B6" s="69" t="str"/>
+      <x:c r="B6" s="76" t="str"/>
       <x:c r="C6" s="43" t="str"/>
       <x:c r="D6" s="43" t="str"/>
       <x:c r="E6" s="43" t="str"/>
@@ -4280,7 +4743,7 @@
     </x:row>
     <x:row r="7" hidden="0">
       <x:c r="A7" s="43" t="str"/>
-      <x:c r="B7" s="69" t="str"/>
+      <x:c r="B7" s="76" t="str"/>
       <x:c r="C7" s="43" t="str"/>
       <x:c r="D7" s="43" t="str"/>
       <x:c r="E7" s="43" t="str"/>
@@ -4294,7 +4757,7 @@
     </x:row>
     <x:row r="8" hidden="0">
       <x:c r="A8" s="43" t="str"/>
-      <x:c r="B8" s="69" t="str"/>
+      <x:c r="B8" s="76" t="str"/>
       <x:c r="C8" s="43" t="str"/>
       <x:c r="D8" s="43" t="str"/>
       <x:c r="E8" s="43" t="str"/>
@@ -4308,7 +4771,7 @@
     </x:row>
     <x:row r="9" hidden="0">
       <x:c r="A9" s="43" t="str"/>
-      <x:c r="B9" s="69" t="str"/>
+      <x:c r="B9" s="76" t="str"/>
       <x:c r="C9" s="43" t="str"/>
       <x:c r="D9" s="43" t="str"/>
       <x:c r="E9" s="43" t="str"/>
@@ -4322,7 +4785,7 @@
     </x:row>
     <x:row r="10" hidden="0">
       <x:c r="A10" s="43" t="str"/>
-      <x:c r="B10" s="69" t="str"/>
+      <x:c r="B10" s="76" t="str"/>
       <x:c r="C10" s="43" t="str"/>
       <x:c r="D10" s="43" t="str"/>
       <x:c r="E10" s="43" t="str"/>
@@ -4336,7 +4799,7 @@
     </x:row>
     <x:row r="11" hidden="0">
       <x:c r="A11" s="43" t="str"/>
-      <x:c r="B11" s="69" t="str"/>
+      <x:c r="B11" s="76" t="str"/>
       <x:c r="C11" s="43" t="str"/>
       <x:c r="D11" s="43" t="str"/>
       <x:c r="E11" s="43" t="str"/>
@@ -4350,7 +4813,7 @@
     </x:row>
     <x:row r="12" hidden="0">
       <x:c r="A12" s="43" t="str"/>
-      <x:c r="B12" s="69" t="str"/>
+      <x:c r="B12" s="76" t="str"/>
       <x:c r="C12" s="43" t="str"/>
       <x:c r="D12" s="43" t="str"/>
       <x:c r="E12" s="43" t="str"/>
@@ -4364,7 +4827,7 @@
     </x:row>
     <x:row r="13" hidden="0">
       <x:c r="A13" s="43" t="str"/>
-      <x:c r="B13" s="69" t="str"/>
+      <x:c r="B13" s="76" t="str"/>
       <x:c r="C13" s="43" t="str"/>
       <x:c r="D13" s="43" t="str"/>
       <x:c r="E13" s="43" t="str"/>
@@ -4378,7 +4841,7 @@
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14" s="43" t="str"/>
-      <x:c r="B14" s="69" t="str"/>
+      <x:c r="B14" s="76" t="str"/>
       <x:c r="C14" s="43" t="str"/>
       <x:c r="D14" s="43" t="str"/>
       <x:c r="E14" s="43" t="str"/>
@@ -4392,7 +4855,7 @@
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="43" t="str"/>
-      <x:c r="B15" s="69" t="str"/>
+      <x:c r="B15" s="76" t="str"/>
       <x:c r="C15" s="43" t="str"/>
       <x:c r="D15" s="43" t="str"/>
       <x:c r="E15" s="43" t="str"/>
@@ -4406,7 +4869,7 @@
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="43" t="str"/>
-      <x:c r="B16" s="69" t="str"/>
+      <x:c r="B16" s="76" t="str"/>
       <x:c r="C16" s="43" t="str"/>
       <x:c r="D16" s="43" t="str"/>
       <x:c r="E16" s="43" t="str"/>
@@ -4420,7 +4883,7 @@
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="43" t="str"/>
-      <x:c r="B17" s="69" t="str"/>
+      <x:c r="B17" s="76" t="str"/>
       <x:c r="C17" s="43" t="str"/>
       <x:c r="D17" s="43" t="str"/>
       <x:c r="E17" s="43" t="str"/>
@@ -4434,7 +4897,7 @@
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="43" t="str"/>
-      <x:c r="B18" s="69" t="str"/>
+      <x:c r="B18" s="76" t="str"/>
       <x:c r="C18" s="43" t="str"/>
       <x:c r="D18" s="43" t="str"/>
       <x:c r="E18" s="43" t="str"/>
@@ -4448,7 +4911,7 @@
     </x:row>
     <x:row r="19" hidden="0">
       <x:c r="A19" s="43" t="str"/>
-      <x:c r="B19" s="69" t="str"/>
+      <x:c r="B19" s="76" t="str"/>
       <x:c r="C19" s="43" t="str"/>
       <x:c r="D19" s="43" t="str"/>
       <x:c r="E19" s="43" t="str"/>
@@ -4462,7 +4925,7 @@
     </x:row>
     <x:row r="20" hidden="0">
       <x:c r="A20" s="43" t="str"/>
-      <x:c r="B20" s="69" t="str"/>
+      <x:c r="B20" s="76" t="str"/>
       <x:c r="C20" s="43" t="str"/>
       <x:c r="D20" s="43" t="str"/>
       <x:c r="E20" s="43" t="str"/>
@@ -4476,7 +4939,7 @@
     </x:row>
     <x:row r="21" hidden="0">
       <x:c r="A21" s="43" t="str"/>
-      <x:c r="B21" s="69" t="str"/>
+      <x:c r="B21" s="76" t="str"/>
       <x:c r="C21" s="43" t="str"/>
       <x:c r="D21" s="43" t="str"/>
       <x:c r="E21" s="43" t="str"/>
@@ -4490,7 +4953,7 @@
     </x:row>
     <x:row r="22" hidden="0">
       <x:c r="A22" s="43" t="str"/>
-      <x:c r="B22" s="69" t="str"/>
+      <x:c r="B22" s="76" t="str"/>
       <x:c r="C22" s="43" t="str"/>
       <x:c r="D22" s="43" t="str"/>
       <x:c r="E22" s="43" t="str"/>
@@ -4504,7 +4967,7 @@
     </x:row>
     <x:row r="23" hidden="0">
       <x:c r="A23" s="43" t="str"/>
-      <x:c r="B23" s="69" t="str"/>
+      <x:c r="B23" s="76" t="str"/>
       <x:c r="C23" s="43" t="str"/>
       <x:c r="D23" s="43" t="str"/>
       <x:c r="E23" s="43" t="str"/>
@@ -4518,7 +4981,7 @@
     </x:row>
     <x:row r="24" hidden="0">
       <x:c r="A24" s="43" t="str"/>
-      <x:c r="B24" s="69" t="str"/>
+      <x:c r="B24" s="76" t="str"/>
       <x:c r="C24" s="43" t="str"/>
       <x:c r="D24" s="43" t="str"/>
       <x:c r="E24" s="43" t="str"/>
@@ -4537,7 +5000,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R639f55e7a3f146fc"/>
+    <x:tablePart ns1:id="R0998df073d3a4758"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4550,6 +5013,7 @@
     <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="31" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="31" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4565,6 +5029,9 @@
       <x:c r="D1" s="5" t="str">
         <x:v>Registration Result</x:v>
       </x:c>
+      <x:c r="E1" s="5" t="str">
+        <x:v>Comparison Target</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
@@ -4578,6 +5045,9 @@
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>Default Settings</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4593,6 +5063,9 @@
       <x:c r="D3" s="7" t="str">
         <x:v>Pass</x:v>
       </x:c>
+      <x:c r="E3" s="7" t="str">
+        <x:v>C1 Wildlife</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="7" t="str">
@@ -4607,6 +5080,9 @@
       <x:c r="D4" s="7" t="str">
         <x:v>Fail</x:v>
       </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>C2 Birds in Flight</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="7" t="str">
@@ -4619,6 +5095,9 @@
       <x:c r="D5" s="7" t="str">
         <x:v>Needs retest</x:v>
       </x:c>
+      <x:c r="E5" s="7" t="str">
+        <x:v>C3 Landscape</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="7" t="str">
@@ -4631,6 +5110,7 @@
       <x:c r="D6" s="7" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
+      <x:c r="E6" s="7"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="7" t="str">
@@ -4639,6 +5119,7 @@
       <x:c r="B7" s="7"/>
       <x:c r="C7" s="7"/>
       <x:c r="D7" s="7"/>
+      <x:c r="E7" s="7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="7" t="str">
@@ -4647,6 +5128,7 @@
       <x:c r="B8" s="7"/>
       <x:c r="C8" s="7"/>
       <x:c r="D8" s="7"/>
+      <x:c r="E8" s="7"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="7" t="str">
@@ -4655,6 +5137,7 @@
       <x:c r="B9" s="7"/>
       <x:c r="C9" s="7"/>
       <x:c r="D9" s="7"/>
+      <x:c r="E9" s="7"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="7" t="str">
@@ -4663,6 +5146,7 @@
       <x:c r="B10" s="7"/>
       <x:c r="C10" s="7"/>
       <x:c r="D10" s="7"/>
+      <x:c r="E10" s="7"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="7" t="str">
@@ -4671,6 +5155,7 @@
       <x:c r="B11" s="7"/>
       <x:c r="C11" s="7"/>
       <x:c r="D11" s="7"/>
+      <x:c r="E11" s="7"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4778,13 +5263,13 @@
         <x:v>SETUP-04</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
-        <x:v>Q screen; MM-SWITCH for Cropping/aspect ratio</x:v>
+        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Quick Control: Evaluative metering</x:v>
+        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting menu: IS (Image Stabilizer) mode</x:v>
       </x:c>
       <x:c r="E6" s="17" t="n">
         <x:v>5</x:v>
@@ -5320,7 +5805,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rbf8bb4418abf4902"/>
+    <x:tablePart ns1:id="R6190d70f3fae42e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5346,603 +5831,603 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="98" t="str">
+      <x:c r="A2" s="105" t="str">
         <x:v>workbook_revision</x:v>
       </x:c>
-      <x:c r="B2" s="98" t="str"/>
-      <x:c r="C2" s="98" t="str">
+      <x:c r="B2" s="105" t="str"/>
+      <x:c r="C2" s="105" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="98" t="str">
+      <x:c r="A3" s="105" t="str">
         <x:v>source_fingerprint</x:v>
       </x:c>
-      <x:c r="B3" s="98" t="str"/>
-      <x:c r="C3" s="98" t="str">
-        <x:v>sha256:fc93ec9c0503081c08901734c9619654f36870e69f856801d5b3d1be3ad7dff3</x:v>
+      <x:c r="B3" s="105" t="str"/>
+      <x:c r="C3" s="105" t="str">
+        <x:v>sha256:968f506ee79f26894f64dc617f7c33cbb260fc0ded6fe3e573fbf7549e79da56</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="98" t="str">
+      <x:c r="A4" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B4" s="98" t="str">
+      <x:c r="B4" s="105" t="str">
         <x:v>SETUP-01</x:v>
       </x:c>
-      <x:c r="C4" s="98" t="str">
+      <x:c r="C4" s="105" t="str">
         <x:v>sha256:6298d64e10367b2e38e5d41253bb816c1012479ab7612afc5a53ad66630e975f</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="98" t="str">
+      <x:c r="A5" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B5" s="98" t="str">
+      <x:c r="B5" s="105" t="str">
         <x:v>SETUP-02</x:v>
       </x:c>
-      <x:c r="C5" s="98" t="str">
+      <x:c r="C5" s="105" t="str">
         <x:v>sha256:2c28c37a65e2efee3349ec9d9c3a6e75de10e76697f1c3b5ec5ca8d1ceae0030</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="98" t="str">
+      <x:c r="A6" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B6" s="98" t="str">
+      <x:c r="B6" s="105" t="str">
         <x:v>SETUP-03</x:v>
       </x:c>
-      <x:c r="C6" s="98" t="str">
+      <x:c r="C6" s="105" t="str">
         <x:v>sha256:eb596d6e2a1ad3dba500a053b487e07af4813566f59012575380f500c95740a3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="98" t="str">
+      <x:c r="A7" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B7" s="98" t="str">
+      <x:c r="B7" s="105" t="str">
         <x:v>SETUP-MM-01</x:v>
       </x:c>
-      <x:c r="C7" s="98" t="str">
+      <x:c r="C7" s="105" t="str">
         <x:v>sha256:10c1951c74b44263db5ff6b5725ac0017ef930c909beb4e4acb1fb7b0d6a1e37</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="98" t="str">
+      <x:c r="A8" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B8" s="98" t="str">
+      <x:c r="B8" s="105" t="str">
         <x:v>SETUP-04</x:v>
       </x:c>
-      <x:c r="C8" s="98" t="str">
-        <x:v>sha256:7aa728826b22f45cd601a8c9193b752d723f64e0860d54a7cbce4259e04600c5</x:v>
+      <x:c r="C8" s="105" t="str">
+        <x:v>sha256:0fd3d39f08967cfa6c6072c55ec3ea4582751e1df839097908d8157e9e08ce0a</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="98" t="str">
+      <x:c r="A9" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B9" s="98" t="str">
+      <x:c r="B9" s="105" t="str">
         <x:v>SETUP-05</x:v>
       </x:c>
-      <x:c r="C9" s="98" t="str">
+      <x:c r="C9" s="105" t="str">
         <x:v>sha256:fe40d0591ea5bb918a95096896c88e57973a17e604de841f7b2e42718910d160</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="98" t="str">
+      <x:c r="A10" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B10" s="98" t="str">
+      <x:c r="B10" s="105" t="str">
         <x:v>SETUP-06</x:v>
       </x:c>
-      <x:c r="C10" s="98" t="str">
+      <x:c r="C10" s="105" t="str">
         <x:v>sha256:beaf13d7430d2d3162636f073285172d26c909da7a8d59e4fa99be242e35555d</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="98" t="str">
+      <x:c r="A11" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B11" s="98" t="str">
+      <x:c r="B11" s="105" t="str">
         <x:v>SETUP-07</x:v>
       </x:c>
-      <x:c r="C11" s="98" t="str">
+      <x:c r="C11" s="105" t="str">
         <x:v>sha256:ae9a5f9d945a50c4ccc176c38f7c0029989fda3f1c58b5a69600eafb1b80cb79</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="98" t="str">
+      <x:c r="A12" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B12" s="98" t="str">
+      <x:c r="B12" s="105" t="str">
         <x:v>CTRL-CONFIG-01</x:v>
       </x:c>
-      <x:c r="C12" s="98" t="str">
+      <x:c r="C12" s="105" t="str">
         <x:v>sha256:5255a806565847c3cb210c1f8d9507d27ff69d5f711fbcaebfc48b18d08d9ffd</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="98" t="str">
+      <x:c r="A13" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B13" s="98" t="str">
+      <x:c r="B13" s="105" t="str">
         <x:v>BACKUP-SET-01</x:v>
       </x:c>
-      <x:c r="C13" s="98" t="str">
+      <x:c r="C13" s="105" t="str">
         <x:v>sha256:c8b709cad4c4eb614fa10afd8f3ee3e509cc2c66a5a1da4652b50dee3412f853</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="98" t="str">
+      <x:c r="A14" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B14" s="98" t="str">
+      <x:c r="B14" s="105" t="str">
         <x:v>C1-CONFIG-01</x:v>
       </x:c>
-      <x:c r="C14" s="98" t="str">
+      <x:c r="C14" s="105" t="str">
         <x:v>sha256:bb51b8b1302bce99686d64b8b0cbf269285b79f05cdb854749bd64aea89b1012</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="98" t="str">
+      <x:c r="A15" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B15" s="98" t="str">
+      <x:c r="B15" s="105" t="str">
         <x:v>C1-REG-01</x:v>
       </x:c>
-      <x:c r="C15" s="98" t="str">
+      <x:c r="C15" s="105" t="str">
         <x:v>sha256:f461ea2e61ae1e9b6979dce7f6745b9816601528fb68a6618d8eadcbdd17a502</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="98" t="str">
+      <x:c r="A16" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B16" s="98" t="str">
+      <x:c r="B16" s="105" t="str">
         <x:v>C1-READ-01</x:v>
       </x:c>
-      <x:c r="C16" s="98" t="str">
+      <x:c r="C16" s="105" t="str">
         <x:v>sha256:10a6be7db7226c276100bc1736c6201418a5cd05438549f1159ce0ce561d47bd</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="98" t="str">
+      <x:c r="A17" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B17" s="98" t="str">
+      <x:c r="B17" s="105" t="str">
         <x:v>C1-OPS-01</x:v>
       </x:c>
-      <x:c r="C17" s="98" t="str">
+      <x:c r="C17" s="105" t="str">
         <x:v>sha256:a9eb069693e2acc07f7f74fef525c73def1af24177d2490618dfb430558f3447</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="98" t="str">
+      <x:c r="A18" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B18" s="98" t="str">
+      <x:c r="B18" s="105" t="str">
         <x:v>C2-CONFIG-01</x:v>
       </x:c>
-      <x:c r="C18" s="98" t="str">
+      <x:c r="C18" s="105" t="str">
         <x:v>sha256:f6bd4b38d09cefcd6ef7d79d6df02a5f7d08811ad471c4c65c5dba1acede5797</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="98" t="str">
+      <x:c r="A19" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B19" s="98" t="str">
+      <x:c r="B19" s="105" t="str">
         <x:v>C2-REG-01</x:v>
       </x:c>
-      <x:c r="C19" s="98" t="str">
+      <x:c r="C19" s="105" t="str">
         <x:v>sha256:63fb5022c877bccd92feb9c02cb90b74feda63d1eb9993f889d0fe1420a6485e</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="98" t="str">
+      <x:c r="A20" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B20" s="98" t="str">
+      <x:c r="B20" s="105" t="str">
         <x:v>C2-READ-01</x:v>
       </x:c>
-      <x:c r="C20" s="98" t="str">
+      <x:c r="C20" s="105" t="str">
         <x:v>sha256:ff4e52f0766604bfc924d274273adb0fecb5f24fa22997163f0ff7ca62568e84</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="98" t="str">
+      <x:c r="A21" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B21" s="98" t="str">
+      <x:c r="B21" s="105" t="str">
         <x:v>C2-OPS-01</x:v>
       </x:c>
-      <x:c r="C21" s="98" t="str">
+      <x:c r="C21" s="105" t="str">
         <x:v>sha256:1a9d7974ba1beac809f4901e4932230f9975a65d4fd4dc0095e2b7020b9ff262</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="98" t="str">
+      <x:c r="A22" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B22" s="98" t="str">
+      <x:c r="B22" s="105" t="str">
         <x:v>C3-CONFIG-01</x:v>
       </x:c>
-      <x:c r="C22" s="98" t="str">
+      <x:c r="C22" s="105" t="str">
         <x:v>sha256:45e2ad8ae739d2475bad363b56afd793dbfeacf56f7a9c09cfe62d4d90d73b76</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="98" t="str">
+      <x:c r="A23" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B23" s="98" t="str">
+      <x:c r="B23" s="105" t="str">
         <x:v>C3-REG-01</x:v>
       </x:c>
-      <x:c r="C23" s="98" t="str">
+      <x:c r="C23" s="105" t="str">
         <x:v>sha256:9f5660b058d96ef2a52760a2323d545f63f41f2a651403cd58fde27e840fe894</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="98" t="str">
+      <x:c r="A24" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B24" s="98" t="str">
+      <x:c r="B24" s="105" t="str">
         <x:v>C3-READ-01</x:v>
       </x:c>
-      <x:c r="C24" s="98" t="str">
+      <x:c r="C24" s="105" t="str">
         <x:v>sha256:778742d0d1c3d1effa3c73595a59bb77f362c9568e066b27aa362f9b7ce7d860</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="98" t="str">
+      <x:c r="A25" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B25" s="98" t="str">
+      <x:c r="B25" s="105" t="str">
         <x:v>BACKUP-SET-02</x:v>
       </x:c>
-      <x:c r="C25" s="98" t="str">
+      <x:c r="C25" s="105" t="str">
         <x:v>sha256:884924d58217f4016aef83b195bd222dfb574f9d5ebf19c384f8014e3b0f6dc4</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="98" t="str">
+      <x:c r="A26" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B26" s="98" t="str">
+      <x:c r="B26" s="105" t="str">
         <x:v>C3-OPS-01</x:v>
       </x:c>
-      <x:c r="C26" s="98" t="str">
+      <x:c r="C26" s="105" t="str">
         <x:v>sha256:871d4c0cc392fa3e52b4d6f8ac15b759922a8b710c12006e6b1633d076ffeec3</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="98" t="str">
+      <x:c r="A27" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B27" s="98" t="str">
+      <x:c r="B27" s="105" t="str">
         <x:v>CTRL-AFON-01</x:v>
       </x:c>
-      <x:c r="C27" s="98" t="str">
+      <x:c r="C27" s="105" t="str">
         <x:v>sha256:f252e2d863b240907c921c3d4a3d318917f1ece11491b1efac56eed5ac7d0f96</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="98" t="str">
+      <x:c r="A28" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B28" s="98" t="str">
+      <x:c r="B28" s="105" t="str">
         <x:v>CTRL-AELOCK-01</x:v>
       </x:c>
-      <x:c r="C28" s="98" t="str">
+      <x:c r="C28" s="105" t="str">
         <x:v>sha256:d4faf5d8ee507a918a0c8e2b0879dcc44f1777165fc676dcbda956e992fcc0f5</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="98" t="str">
+      <x:c r="A29" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B29" s="98" t="str">
+      <x:c r="B29" s="105" t="str">
         <x:v>CTRL-DOF-01</x:v>
       </x:c>
-      <x:c r="C29" s="98" t="str">
+      <x:c r="C29" s="105" t="str">
         <x:v>sha256:84542934d1112e37aa42040c8d95b637393d4366ac13c443bf47ef2be662b860</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="98" t="str">
+      <x:c r="A30" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B30" s="98" t="str">
+      <x:c r="B30" s="105" t="str">
         <x:v>CTRL-SET-01</x:v>
       </x:c>
-      <x:c r="C30" s="98" t="str">
+      <x:c r="C30" s="105" t="str">
         <x:v>sha256:16342ed08b4fc44ea0451a0a8935c8504303e9e01dae091aa87ab20c45ad6ad8</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="98" t="str">
+      <x:c r="A31" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B31" s="98" t="str">
+      <x:c r="B31" s="105" t="str">
         <x:v>CTRL-JOY-01</x:v>
       </x:c>
-      <x:c r="C31" s="98" t="str">
+      <x:c r="C31" s="105" t="str">
         <x:v>sha256:828c831b73117d3abc47657bd6986e93ca40a08458c77603a0085569656a2ed7</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="98" t="str">
+      <x:c r="A32" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B32" s="98" t="str">
+      <x:c r="B32" s="105" t="str">
         <x:v>EFCS-SHOCK-01</x:v>
       </x:c>
-      <x:c r="C32" s="98" t="str">
+      <x:c r="C32" s="105" t="str">
         <x:v>sha256:ea49c5e02cf4986fa87a0e77a31a16b4c8dceb72d35bf6ec4fa8b2ad5bf29018</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="98" t="str">
+      <x:c r="A33" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B33" s="98" t="str">
+      <x:c r="B33" s="105" t="str">
         <x:v>EFCS-BOKEH-01</x:v>
       </x:c>
-      <x:c r="C33" s="98" t="str">
+      <x:c r="C33" s="105" t="str">
         <x:v>sha256:3661cf4b3c827113f1bd6729a9c71f07e0934b73d2c287dac02bf2a66ff2a0ca</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="98" t="str">
+      <x:c r="A34" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B34" s="98" t="str">
+      <x:c r="B34" s="105" t="str">
         <x:v>EFCS-LIGHT-01</x:v>
       </x:c>
-      <x:c r="C34" s="98" t="str">
+      <x:c r="C34" s="105" t="str">
         <x:v>sha256:97d1e6a03c7b029effa20b0c6994d82a304032923a0d6e76b693d8b2fe262568</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="98" t="str">
+      <x:c r="A35" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B35" s="98" t="str">
+      <x:c r="B35" s="105" t="str">
         <x:v>EFCS-BURST-01</x:v>
       </x:c>
-      <x:c r="C35" s="98" t="str">
+      <x:c r="C35" s="105" t="str">
         <x:v>sha256:8fb04d8e137c7ade904313a65469ab549111962f3eef56b6d7645d3ebc58646c</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="98" t="str">
+      <x:c r="A36" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B36" s="98" t="str">
+      <x:c r="B36" s="105" t="str">
         <x:v>FLASH-PLUTO-01</x:v>
       </x:c>
-      <x:c r="C36" s="98" t="str">
+      <x:c r="C36" s="105" t="str">
         <x:v>sha256:ae8d9581ed75d71e4f14e03057c0bdafeb110616c4390fce4cdc615093a09344</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="98" t="str">
+      <x:c r="A37" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B37" s="98" t="str">
+      <x:c r="B37" s="105" t="str">
         <x:v>FINAL-READ-01</x:v>
       </x:c>
-      <x:c r="C37" s="98" t="str">
+      <x:c r="C37" s="105" t="str">
         <x:v>sha256:aabf42c50d977426a03aa33990ea7c2cf562640633a1fb7737e64ea5d5562d87</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="98" t="str">
+      <x:c r="A38" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B38" s="98" t="str">
+      <x:c r="B38" s="105" t="str">
         <x:v>FINAL-SAVE-01</x:v>
       </x:c>
-      <x:c r="C38" s="98" t="str">
+      <x:c r="C38" s="105" t="str">
         <x:v>sha256:2fe904eeee80a16c99d57a854d738093275a60b8573ff8d27ce3745b1913d636</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="98" t="str">
+      <x:c r="A39" s="105" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B39" s="98" t="str">
+      <x:c r="B39" s="105" t="str">
         <x:v>PROJECT-UPDATE-01</x:v>
       </x:c>
-      <x:c r="C39" s="98" t="str">
+      <x:c r="C39" s="105" t="str">
         <x:v>sha256:fe0cbf03abfcc198510bcde5ef3fcd5f24e8de8a06946a6521c2e4c4ed3d4885</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="98" t="str">
+      <x:c r="A40" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B40" s="98" t="str">
+      <x:c r="B40" s="105" t="str">
         <x:v>Mode</x:v>
       </x:c>
-      <x:c r="C40" s="98" t="str">
+      <x:c r="C40" s="105" t="str">
         <x:v>sha256:16380d447ae550758ff49c344119374224a6b1c009504e23f6f4f93c11c00533</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="98" t="str">
+      <x:c r="A41" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B41" s="98" t="str">
+      <x:c r="B41" s="105" t="str">
         <x:v>Metering</x:v>
       </x:c>
-      <x:c r="C41" s="98" t="str">
+      <x:c r="C41" s="105" t="str">
         <x:v>sha256:bc76af3dd5f76e718fe876deafcfbc0fd4a3f64d2a2eb64d2253751bd18f4eae</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="98" t="str">
+      <x:c r="A42" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B42" s="98" t="str">
+      <x:c r="B42" s="105" t="str">
         <x:v>Exposure Compensation</x:v>
       </x:c>
-      <x:c r="C42" s="98" t="str">
+      <x:c r="C42" s="105" t="str">
         <x:v>sha256:88e1331bb1792dc8c402253666af51d91b4ff14bdf848d8f5715f7c5735374ee</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="98" t="str">
+      <x:c r="A43" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B43" s="98" t="str">
+      <x:c r="B43" s="105" t="str">
         <x:v>Shutter Speed</x:v>
       </x:c>
-      <x:c r="C43" s="98" t="str">
+      <x:c r="C43" s="105" t="str">
         <x:v>sha256:50a59b23cd80339f63a7068a9f9b6618357bcc05eb6f986cc5c7a707e50c0a74</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="98" t="str">
+      <x:c r="A44" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B44" s="98" t="str">
+      <x:c r="B44" s="105" t="str">
         <x:v>Aperture</x:v>
       </x:c>
-      <x:c r="C44" s="98" t="str">
+      <x:c r="C44" s="105" t="str">
         <x:v>sha256:74b8c602aefe9109b324a5d3d0f5af54cafeaceae6f80e96effd7b7e7b7512a0</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="98" t="str">
+      <x:c r="A45" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B45" s="98" t="str">
+      <x:c r="B45" s="105" t="str">
         <x:v>ISO</x:v>
       </x:c>
-      <x:c r="C45" s="98" t="str">
+      <x:c r="C45" s="105" t="str">
         <x:v>sha256:3c57560fdad255af8dddd4afe759bf3a638ced62cd0b435fbcb39f539ed4d5cd</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="98" t="str">
+      <x:c r="A46" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B46" s="98" t="str">
+      <x:c r="B46" s="105" t="str">
         <x:v>Auto ISO Maximum</x:v>
       </x:c>
-      <x:c r="C46" s="98" t="str">
+      <x:c r="C46" s="105" t="str">
         <x:v>sha256:d9e3a1f832be05121fba7873fe44f0c6a69f48a85b28c62358a17838bc551386</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="98" t="str">
+      <x:c r="A47" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B47" s="98" t="str">
+      <x:c r="B47" s="105" t="str">
         <x:v>AF Operation</x:v>
       </x:c>
-      <x:c r="C47" s="98" t="str">
+      <x:c r="C47" s="105" t="str">
         <x:v>sha256:e52a8877636b9e990324e5e59a10b6b8a0723c7699f752ac41a4e39a25ed8c94</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="98" t="str">
+      <x:c r="A48" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B48" s="98" t="str">
+      <x:c r="B48" s="105" t="str">
         <x:v>AF Method</x:v>
       </x:c>
-      <x:c r="C48" s="98" t="str">
+      <x:c r="C48" s="105" t="str">
         <x:v>sha256:ac30ce5e48a2e9e69db02806afb6a8c836dd8220dce399b57ed50b6ec3569d82</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="98" t="str">
+      <x:c r="A49" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B49" s="98" t="str">
+      <x:c r="B49" s="105" t="str">
         <x:v>Subject Detection</x:v>
       </x:c>
-      <x:c r="C49" s="98" t="str">
+      <x:c r="C49" s="105" t="str">
         <x:v>sha256:ca630f9c8761b1ba9bc261fc0264e1fdff6c6ebce7d3d60f68453c6e6c0fb66e</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="98" t="str">
+      <x:c r="A50" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B50" s="98" t="str">
+      <x:c r="B50" s="105" t="str">
         <x:v>Eye Detection</x:v>
       </x:c>
-      <x:c r="C50" s="98" t="str">
+      <x:c r="C50" s="105" t="str">
         <x:v>sha256:d4f49e58f189bc2a85058e8030bdba5867549892594d4961911a877fc7774cc1</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="98" t="str">
+      <x:c r="A51" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B51" s="98" t="str">
+      <x:c r="B51" s="105" t="str">
         <x:v>Drive Mode</x:v>
       </x:c>
-      <x:c r="C51" s="98" t="str">
+      <x:c r="C51" s="105" t="str">
         <x:v>sha256:a407ab25d86c6b32e4618dffadce1bc9f7375731cceb32a9b15154cb636bbc93</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="98" t="str">
+      <x:c r="A52" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B52" s="98" t="str">
+      <x:c r="B52" s="105" t="str">
         <x:v>Shutter Type</x:v>
       </x:c>
-      <x:c r="C52" s="98" t="str">
+      <x:c r="C52" s="105" t="str">
         <x:v>sha256:e0eb3a601149113b744968c8d35c10e22707716e94c780644837edcabff082bb</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="98" t="str">
+      <x:c r="A53" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B53" s="98" t="str">
+      <x:c r="B53" s="105" t="str">
         <x:v>Image Stabilizer Mode</x:v>
       </x:c>
-      <x:c r="C53" s="98" t="str">
+      <x:c r="C53" s="105" t="str">
         <x:v>sha256:cc5907ea77c17b747bda000cb9d24e886022b15d9be9b15be2fd7d3a6aa18fba</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="98" t="str">
+      <x:c r="A54" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B54" s="98" t="str">
+      <x:c r="B54" s="105" t="str">
         <x:v>IBIS</x:v>
       </x:c>
-      <x:c r="C54" s="98" t="str">
+      <x:c r="C54" s="105" t="str">
         <x:v>sha256:d10f56172a85e3588b70cb9cc38fe4e1ddd6b261fb5185b7581241dda0d7e9ad</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="98" t="str">
+      <x:c r="A55" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B55" s="98" t="str">
+      <x:c r="B55" s="105" t="str">
         <x:v>Focus Bracketing</x:v>
       </x:c>
-      <x:c r="C55" s="98" t="str">
+      <x:c r="C55" s="105" t="str">
         <x:v>sha256:e8a1df3755fa1c6498cccfce7b113140b022e928f10c8ad2a3ff3ddf8690000a</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="98" t="str">
+      <x:c r="A56" s="105" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B56" s="98" t="str">
+      <x:c r="B56" s="105" t="str">
         <x:v>Lens IS switch</x:v>
       </x:c>
-      <x:c r="C56" s="98" t="str">
+      <x:c r="C56" s="105" t="str">
         <x:v>sha256:5a2f7cf7e224aef797784c3a79eb70c0a5ed8f1ae66c3227c01e8b25a206903e</x:v>
       </x:c>
     </x:row>

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rdd4796573f124d2f"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="R6df9c4097155430b"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="Rbc9c39fac4fa497c"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="R591dd2c6fce74e27"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="R89401d2fa8094aad"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="R04fd23ed5edf40a0"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="R1ad93d99d7894beb"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rf42239416cc64623"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="Rca956a9c1da54fc0"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R822032b91d324fac"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="R30b3a13289ae4a64"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="R6e29e7f967294565"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="R801ae5ee8d96480c"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="Rb1d06e4697ee430a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
@@ -275,7 +275,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="106">
+  <x:cellXfs count="100">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -373,55 +373,17 @@
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <ns1:xfComplement i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <ns1:xfComplement i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <ns1:xfComplement i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <ns1:xfComplement i="0"/>
-        </x:ext>
-      </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <ns1:xfComplement i="0"/>
-        </x:ext>
-      </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -486,14 +448,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <ns1:xfComplement i="0"/>
-        </x:ext>
-      </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -750,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="2190222f-37e5-478b-9a39-12d574bb5987"/>
+        <xdr:cNvPr id="1" name="95b3fb75-e462-4be5-bffc-f6f83026826f"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1e531527be234f1e"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R35548a0a0f5e42c5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -770,26 +724,9 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="VerificationChecklist" displayName="VerificationChecklist" ref="A5:R41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:R41"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="VerificationChecklist" displayName="VerificationChecklist" ref="A5:R42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:R42"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="Test ID"/>
     <x:tableColumn id="2" name="Sequence"/>
@@ -815,8 +752,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegistrationTable" displayName="RegistrationTable" ref="A4:N21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegistrationTable" displayName="RegistrationTable" ref="A4:N22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N22"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Setting"/>
     <x:tableColumn id="2" name="Default Settings"/>
@@ -859,8 +796,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="VerificationMenu" displayName="VerificationMenu" ref="A1:E37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:E37"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="VerificationMenu" displayName="VerificationMenu" ref="A1:E38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E38"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Test ID"/>
     <x:tableColumn id="2" name="Best Access"/>
@@ -1078,26 +1015,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="79" t="str">
+      <x:c r="A1" s="73" t="str">
         <x:v>EOS R5 On-Camera Verification Progress</x:v>
       </x:c>
-      <x:c r="B1" s="79"/>
-      <x:c r="C1" s="79"/>
-      <x:c r="D1" s="79"/>
-      <x:c r="E1" s="79"/>
-      <x:c r="F1" s="79"/>
-      <x:c r="G1" s="79"/>
-      <x:c r="H1" s="79"/>
+      <x:c r="B1" s="73"/>
+      <x:c r="C1" s="73"/>
+      <x:c r="D1" s="73"/>
+      <x:c r="E1" s="73"/>
+      <x:c r="F1" s="73"/>
+      <x:c r="G1" s="73"/>
+      <x:c r="H1" s="73"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="79"/>
-      <x:c r="B2" s="79"/>
-      <x:c r="C2" s="79"/>
-      <x:c r="D2" s="79"/>
-      <x:c r="E2" s="79"/>
-      <x:c r="F2" s="79"/>
-      <x:c r="G2" s="79"/>
-      <x:c r="H2" s="79"/>
+      <x:c r="A2" s="73"/>
+      <x:c r="B2" s="73"/>
+      <x:c r="C2" s="73"/>
+      <x:c r="D2" s="73"/>
+      <x:c r="E2" s="73"/>
+      <x:c r="F2" s="73"/>
+      <x:c r="G2" s="73"/>
+      <x:c r="H2" s="73"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="38" t="str">
@@ -1122,54 +1059,54 @@
       <x:c r="H4" s="38"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="82" t="str">
+      <x:c r="A6" s="76" t="str">
         <x:v>Total checklist items</x:v>
       </x:c>
-      <x:c r="B6" s="82" t="str"/>
-      <x:c r="C6" s="84" t="str">
+      <x:c r="B6" s="76" t="str"/>
+      <x:c r="C6" s="78" t="str">
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="D6" s="84" t="str"/>
-      <x:c r="E6" s="86" t="str">
+      <x:c r="D6" s="78" t="str"/>
+      <x:c r="E6" s="80" t="str">
         <x:v>In progress / pending</x:v>
       </x:c>
-      <x:c r="F6" s="86" t="str"/>
-      <x:c r="G6" s="88" t="str">
+      <x:c r="F6" s="80" t="str"/>
+      <x:c r="G6" s="82" t="str">
         <x:v>Needs attention</x:v>
       </x:c>
-      <x:c r="H6" s="88" t="str"/>
+      <x:c r="H6" s="82" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="92" t="n">
-        <x:f>COUNTA('Checklist'!$A$6:$A$41)</x:f>
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B7" s="92"/>
-      <x:c r="C7" s="93" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,"Verified")</x:f>
+      <x:c r="A7" s="86" t="n">
+        <x:f>COUNTA('Checklist'!$A$6:$A$42)</x:f>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B7" s="86"/>
+      <x:c r="C7" s="87" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="93"/>
-      <x:c r="E7" s="94" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,"In progress")+COUNTIF('Checklist'!$I$6:$I$41,"Configured—not registered")+COUNTIF('Checklist'!$I$6:$I$41,"Registered—pending read-back")</x:f>
+      <x:c r="D7" s="87"/>
+      <x:c r="E7" s="88" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,"In progress")+COUNTIF('Checklist'!$I$6:$I$42,"Configured—not registered")+COUNTIF('Checklist'!$I$6:$I$42,"Registered—pending read-back")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="94"/>
-      <x:c r="G7" s="95" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIF('Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIF('Checklist'!$I$6:$I$41,"Blocked")</x:f>
+      <x:c r="F7" s="88"/>
+      <x:c r="G7" s="89" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,"Failed—needs correction")+COUNTIF('Checklist'!$I$6:$I$42,"Inconclusive—needs retest")+COUNTIF('Checklist'!$I$6:$I$42,"Blocked")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H7" s="95"/>
+      <x:c r="H7" s="89"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="92"/>
-      <x:c r="B8" s="92"/>
-      <x:c r="C8" s="93"/>
-      <x:c r="D8" s="93"/>
-      <x:c r="E8" s="94"/>
-      <x:c r="F8" s="94"/>
-      <x:c r="G8" s="95"/>
-      <x:c r="H8" s="95"/>
+      <x:c r="A8" s="86"/>
+      <x:c r="B8" s="86"/>
+      <x:c r="C8" s="87"/>
+      <x:c r="D8" s="87"/>
+      <x:c r="E8" s="88"/>
+      <x:c r="F8" s="88"/>
+      <x:c r="G8" s="89"/>
+      <x:c r="H8" s="89"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="str">
@@ -1199,57 +1136,57 @@
       <x:c r="A12" t="str">
         <x:v>Camera Setup</x:v>
       </x:c>
-      <x:c r="B12" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$C$6:$C$41,A12)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Verified")</x:f>
+      <x:c r="B12" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$C$6:$C$42,A12)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C12" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A12,'Checklist'!$I$6:$I$42,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
+      <x:c r="D12" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A12,'Checklist'!$I$6:$I$42,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$42,A12,'Checklist'!$I$6:$I$42,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$42,A12,'Checklist'!$I$6:$I$42,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="98" t="n">
-        <x:f>IF(B12=0,0,(C12+COUNTIFS('Checklist'!$C$6:$C$41,A12,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B12)</x:f>
+      <x:c r="E12" s="92" t="n">
+        <x:f>IF(B12=0,0,(C12+COUNTIFS('Checklist'!$C$6:$C$42,A12,'Checklist'!$I$6:$I$42,"Backup-Settings"))/B12)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F12" t="str"/>
       <x:c r="G12" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="H12" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G12)</x:f>
-        <x:v>35</x:v>
+      <x:c r="H12" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G12)</x:f>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
         <x:v>Controls</x:v>
       </x:c>
-      <x:c r="B13" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$C$6:$C$41,A13)</x:f>
+      <x:c r="B13" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$C$6:$C$42,A13)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C13" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Verified")</x:f>
+      <x:c r="C13" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A13,'Checklist'!$I$6:$I$42,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
+      <x:c r="D13" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A13,'Checklist'!$I$6:$I$42,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$42,A13,'Checklist'!$I$6:$I$42,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$42,A13,'Checklist'!$I$6:$I$42,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="98" t="n">
-        <x:f>IF(B13=0,0,(C13+COUNTIFS('Checklist'!$C$6:$C$41,A13,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B13)</x:f>
+      <x:c r="E13" s="92" t="n">
+        <x:f>IF(B13=0,0,(C13+COUNTIFS('Checklist'!$C$6:$C$42,A13,'Checklist'!$I$6:$I$42,"Backup-Settings"))/B13)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F13" t="str"/>
       <x:c r="G13" t="str">
         <x:v>In progress</x:v>
       </x:c>
-      <x:c r="H13" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G13)</x:f>
+      <x:c r="H13" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G13)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1257,28 +1194,28 @@
       <x:c r="A14" t="str">
         <x:v>C1 Wildlife</x:v>
       </x:c>
-      <x:c r="B14" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$C$6:$C$41,A14)</x:f>
+      <x:c r="B14" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$C$6:$C$42,A14)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C14" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Verified")</x:f>
+      <x:c r="C14" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A14,'Checklist'!$I$6:$I$42,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
+      <x:c r="D14" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A14,'Checklist'!$I$6:$I$42,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$42,A14,'Checklist'!$I$6:$I$42,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$42,A14,'Checklist'!$I$6:$I$42,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="98" t="n">
-        <x:f>IF(B14=0,0,(C14+COUNTIFS('Checklist'!$C$6:$C$41,A14,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B14)</x:f>
+      <x:c r="E14" s="92" t="n">
+        <x:f>IF(B14=0,0,(C14+COUNTIFS('Checklist'!$C$6:$C$42,A14,'Checklist'!$I$6:$I$42,"Backup-Settings"))/B14)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F14" t="str"/>
       <x:c r="G14" t="str">
         <x:v>Configured—not registered</x:v>
       </x:c>
-      <x:c r="H14" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G14)</x:f>
+      <x:c r="H14" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G14)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1286,28 +1223,28 @@
       <x:c r="A15" t="str">
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
-      <x:c r="B15" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$C$6:$C$41,A15)</x:f>
+      <x:c r="B15" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$C$6:$C$42,A15)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C15" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Verified")</x:f>
+      <x:c r="C15" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A15,'Checklist'!$I$6:$I$42,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D15" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
+      <x:c r="D15" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A15,'Checklist'!$I$6:$I$42,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$42,A15,'Checklist'!$I$6:$I$42,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$42,A15,'Checklist'!$I$6:$I$42,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="98" t="n">
-        <x:f>IF(B15=0,0,(C15+COUNTIFS('Checklist'!$C$6:$C$41,A15,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B15)</x:f>
+      <x:c r="E15" s="92" t="n">
+        <x:f>IF(B15=0,0,(C15+COUNTIFS('Checklist'!$C$6:$C$42,A15,'Checklist'!$I$6:$I$42,"Backup-Settings"))/B15)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F15" t="str"/>
       <x:c r="G15" t="str">
         <x:v>Registered—pending read-back</x:v>
       </x:c>
-      <x:c r="H15" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G15)</x:f>
+      <x:c r="H15" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G15)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1315,28 +1252,28 @@
       <x:c r="A16" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
-      <x:c r="B16" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$C$6:$C$41,A16)</x:f>
+      <x:c r="B16" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$C$6:$C$42,A16)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C16" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Verified")</x:f>
+      <x:c r="C16" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A16,'Checklist'!$I$6:$I$42,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
+      <x:c r="D16" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A16,'Checklist'!$I$6:$I$42,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$42,A16,'Checklist'!$I$6:$I$42,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$42,A16,'Checklist'!$I$6:$I$42,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="98" t="n">
-        <x:f>IF(B16=0,0,(C16+COUNTIFS('Checklist'!$C$6:$C$41,A16,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B16)</x:f>
+      <x:c r="E16" s="92" t="n">
+        <x:f>IF(B16=0,0,(C16+COUNTIFS('Checklist'!$C$6:$C$42,A16,'Checklist'!$I$6:$I$42,"Backup-Settings"))/B16)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F16" t="str"/>
       <x:c r="G16" t="str">
         <x:v>Backup-Settings</x:v>
       </x:c>
-      <x:c r="H16" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G16)</x:f>
+      <x:c r="H16" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G16)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1344,28 +1281,28 @@
       <x:c r="A17" t="str">
         <x:v>EFCS Tests</x:v>
       </x:c>
-      <x:c r="B17" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$C$6:$C$41,A17)</x:f>
+      <x:c r="B17" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$C$6:$C$42,A17)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C17" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Verified")</x:f>
+      <x:c r="C17" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A17,'Checklist'!$I$6:$I$42,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D17" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
+      <x:c r="D17" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A17,'Checklist'!$I$6:$I$42,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$42,A17,'Checklist'!$I$6:$I$42,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$42,A17,'Checklist'!$I$6:$I$42,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="98" t="n">
-        <x:f>IF(B17=0,0,(C17+COUNTIFS('Checklist'!$C$6:$C$41,A17,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B17)</x:f>
+      <x:c r="E17" s="92" t="n">
+        <x:f>IF(B17=0,0,(C17+COUNTIFS('Checklist'!$C$6:$C$42,A17,'Checklist'!$I$6:$I$42,"Backup-Settings"))/B17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F17" t="str"/>
       <x:c r="G17" t="str">
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="H17" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G17)</x:f>
+      <x:c r="H17" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G17)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1373,28 +1310,28 @@
       <x:c r="A18" t="str">
         <x:v>Finalization</x:v>
       </x:c>
-      <x:c r="B18" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$C$6:$C$41,A18)</x:f>
+      <x:c r="B18" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$C$6:$C$42,A18)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C18" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Verified")</x:f>
+      <x:c r="C18" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A18,'Checklist'!$I$6:$I$42,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D18" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
+      <x:c r="D18" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A18,'Checklist'!$I$6:$I$42,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$42,A18,'Checklist'!$I$6:$I$42,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$42,A18,'Checklist'!$I$6:$I$42,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="98" t="n">
-        <x:f>IF(B18=0,0,(C18+COUNTIFS('Checklist'!$C$6:$C$41,A18,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B18)</x:f>
+      <x:c r="E18" s="92" t="n">
+        <x:f>IF(B18=0,0,(C18+COUNTIFS('Checklist'!$C$6:$C$42,A18,'Checklist'!$I$6:$I$42,"Backup-Settings"))/B18)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F18" t="str"/>
       <x:c r="G18" t="str">
         <x:v>Failed—needs correction</x:v>
       </x:c>
-      <x:c r="H18" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G18)</x:f>
+      <x:c r="H18" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G18)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1402,128 +1339,128 @@
       <x:c r="A19" t="str">
         <x:v>Project Update</x:v>
       </x:c>
-      <x:c r="B19" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$C$6:$C$41,A19)</x:f>
+      <x:c r="B19" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$C$6:$C$42,A19)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C19" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Verified")</x:f>
+      <x:c r="C19" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A19,'Checklist'!$I$6:$I$42,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D19" s="97" t="n">
-        <x:f>COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Blocked")</x:f>
+      <x:c r="D19" s="91" t="n">
+        <x:f>COUNTIFS('Checklist'!$C$6:$C$42,A19,'Checklist'!$I$6:$I$42,"Failed—needs correction")+COUNTIFS('Checklist'!$C$6:$C$42,A19,'Checklist'!$I$6:$I$42,"Inconclusive—needs retest")+COUNTIFS('Checklist'!$C$6:$C$42,A19,'Checklist'!$I$6:$I$42,"Blocked")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E19" s="98" t="n">
-        <x:f>IF(B19=0,0,(C19+COUNTIFS('Checklist'!$C$6:$C$41,A19,'Checklist'!$I$6:$I$41,"Backup-Settings"))/B19)</x:f>
+      <x:c r="E19" s="92" t="n">
+        <x:f>IF(B19=0,0,(C19+COUNTIFS('Checklist'!$C$6:$C$42,A19,'Checklist'!$I$6:$I$42,"Backup-Settings"))/B19)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F19" t="str"/>
       <x:c r="G19" t="str">
         <x:v>Inconclusive—needs retest</x:v>
       </x:c>
-      <x:c r="H19" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G19)</x:f>
+      <x:c r="H19" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G19)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str"/>
-      <x:c r="B20" s="97" t="str"/>
-      <x:c r="C20" s="97" t="str"/>
-      <x:c r="D20" s="97" t="str"/>
-      <x:c r="E20" s="97" t="str"/>
+      <x:c r="B20" s="91" t="str"/>
+      <x:c r="C20" s="91" t="str"/>
+      <x:c r="D20" s="91" t="str"/>
+      <x:c r="E20" s="91" t="str"/>
       <x:c r="F20" t="str"/>
       <x:c r="G20" t="str">
         <x:v>Blocked</x:v>
       </x:c>
-      <x:c r="H20" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G20)</x:f>
+      <x:c r="H20" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G20)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str"/>
-      <x:c r="B21" s="97" t="str"/>
-      <x:c r="C21" s="97" t="str"/>
-      <x:c r="D21" s="97" t="str"/>
-      <x:c r="E21" s="97" t="str"/>
+      <x:c r="B21" s="91" t="str"/>
+      <x:c r="C21" s="91" t="str"/>
+      <x:c r="D21" s="91" t="str"/>
+      <x:c r="E21" s="91" t="str"/>
       <x:c r="F21" t="str"/>
       <x:c r="G21" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="H21" s="97" t="n">
-        <x:f>COUNTIF('Checklist'!$I$6:$I$41,G21)</x:f>
+      <x:c r="H21" s="91" t="n">
+        <x:f>COUNTIF('Checklist'!$I$6:$I$42,G21)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="99" t="str">
+      <x:c r="A23" s="93" t="str">
         <x:v>Recommended workflow</x:v>
       </x:c>
-      <x:c r="B23" s="99"/>
-      <x:c r="C23" s="99"/>
-      <x:c r="D23" s="99"/>
-      <x:c r="E23" s="99"/>
-      <x:c r="F23" s="99"/>
-      <x:c r="G23" s="99"/>
-      <x:c r="H23" s="99"/>
+      <x:c r="B23" s="93"/>
+      <x:c r="C23" s="93"/>
+      <x:c r="D23" s="93"/>
+      <x:c r="E23" s="93"/>
+      <x:c r="F23" s="93"/>
+      <x:c r="G23" s="93"/>
+      <x:c r="H23" s="93"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="103" t="str">
+      <x:c r="A24" s="97" t="str">
         <x:v>1. Save the starting camera configuration and document C1–C3.
-2. Disable Auto update, then configure and verify the SWITCH My Menu tab.
+2. Disable Auto update, then configure and verify the SWITCH and AF Case My Menu tabs.
 3. Save Backup-Settings checkpoints after shared setup/controls and after C1–C3 read-back.
 4. Work through Checklist in Sequence order and use one Session ID per camera session.
 5. Filter Project Update? = Yes and Status = Verified before changing project evidence states.</x:v>
       </x:c>
-      <x:c r="B24" s="103"/>
-      <x:c r="C24" s="103"/>
-      <x:c r="D24" s="103"/>
-      <x:c r="E24" s="103"/>
-      <x:c r="F24" s="103"/>
-      <x:c r="G24" s="103"/>
-      <x:c r="H24" s="103"/>
+      <x:c r="B24" s="97"/>
+      <x:c r="C24" s="97"/>
+      <x:c r="D24" s="97"/>
+      <x:c r="E24" s="97"/>
+      <x:c r="F24" s="97"/>
+      <x:c r="G24" s="97"/>
+      <x:c r="H24" s="97"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="103"/>
-      <x:c r="B25" s="103"/>
-      <x:c r="C25" s="103"/>
-      <x:c r="D25" s="103"/>
-      <x:c r="E25" s="103"/>
-      <x:c r="F25" s="103"/>
-      <x:c r="G25" s="103"/>
-      <x:c r="H25" s="103"/>
+      <x:c r="A25" s="97"/>
+      <x:c r="B25" s="97"/>
+      <x:c r="C25" s="97"/>
+      <x:c r="D25" s="97"/>
+      <x:c r="E25" s="97"/>
+      <x:c r="F25" s="97"/>
+      <x:c r="G25" s="97"/>
+      <x:c r="H25" s="97"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="103"/>
-      <x:c r="B26" s="103"/>
-      <x:c r="C26" s="103"/>
-      <x:c r="D26" s="103"/>
-      <x:c r="E26" s="103"/>
-      <x:c r="F26" s="103"/>
-      <x:c r="G26" s="103"/>
-      <x:c r="H26" s="103"/>
+      <x:c r="A26" s="97"/>
+      <x:c r="B26" s="97"/>
+      <x:c r="C26" s="97"/>
+      <x:c r="D26" s="97"/>
+      <x:c r="E26" s="97"/>
+      <x:c r="F26" s="97"/>
+      <x:c r="G26" s="97"/>
+      <x:c r="H26" s="97"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="103"/>
-      <x:c r="B27" s="103"/>
-      <x:c r="C27" s="103"/>
-      <x:c r="D27" s="103"/>
-      <x:c r="E27" s="103"/>
-      <x:c r="F27" s="103"/>
-      <x:c r="G27" s="103"/>
-      <x:c r="H27" s="103"/>
+      <x:c r="A27" s="97"/>
+      <x:c r="B27" s="97"/>
+      <x:c r="C27" s="97"/>
+      <x:c r="D27" s="97"/>
+      <x:c r="E27" s="97"/>
+      <x:c r="F27" s="97"/>
+      <x:c r="G27" s="97"/>
+      <x:c r="H27" s="97"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="103"/>
-      <x:c r="B28" s="103"/>
-      <x:c r="C28" s="103"/>
-      <x:c r="D28" s="103"/>
-      <x:c r="E28" s="103"/>
-      <x:c r="F28" s="103"/>
-      <x:c r="G28" s="103"/>
-      <x:c r="H28" s="103"/>
+      <x:c r="A28" s="97"/>
+      <x:c r="B28" s="97"/>
+      <x:c r="C28" s="97"/>
+      <x:c r="D28" s="97"/>
+      <x:c r="E28" s="97"/>
+      <x:c r="F28" s="97"/>
+      <x:c r="G28" s="97"/>
+      <x:c r="H28" s="97"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1664,15 +1601,15 @@
         <x:v>Save the current complete camera configuration to the card.</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A6,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A6,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
         <x:v>MENU</x:v>
       </x:c>
       <x:c r="G6" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A6,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A6,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="H6" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A6,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A6,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
         <x:v>Save/load cam settings on card &gt; Save to card</x:v>
       </x:c>
       <x:c r="I6" s="13" t="str">
@@ -1713,15 +1650,15 @@
         <x:v>Record current C1, C2, and C3 contents before changing them.</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A7,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A7,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
         <x:v>M-Fn recall; photograph or record</x:v>
       </x:c>
       <x:c r="G7" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A7,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A7,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>No menu</x:v>
       </x:c>
       <x:c r="H7" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A7,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A7,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
         <x:v>Recall C1, C2, and C3 and photograph or record their settings</x:v>
       </x:c>
       <x:c r="I7" s="13" t="str">
@@ -1762,15 +1699,15 @@
         <x:v>Set Custom shooting mode Auto update to Disable.</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A8,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A8,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
         <x:v>MENU</x:v>
       </x:c>
       <x:c r="G8" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A8,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A8,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="H8" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A8,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A8,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
         <x:v>Custom shooting mode (C1-C3) &gt; Auto update set. &gt; Disable</x:v>
       </x:c>
       <x:c r="I8" s="13" t="str">
@@ -1809,22 +1746,22 @@
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>The approved SWITCH My Menu tab exists with the five approved shortcuts in the correct order and one open position.</x:v>
+        <x:v>The approved SWITCH My Menu tab exists with its five shortcuts in the correct order and retains one open position.</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
-        <x:v>Configure and verify the SWITCH My Menu tab before profile registration.</x:v>
+        <x:v>Configure and verify My Menu: SWITCH before profile registration.</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A9,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A9,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
         <x:v>My Menu</x:v>
       </x:c>
       <x:c r="G9" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A9,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A9,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>My Menu</x:v>
       </x:c>
       <x:c r="H9" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A9,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Create tab SWITCH; register in order: Subject to detect, Shutter mode, Focus bracketing, IS (Image Stabilizer) mode, Cropping/aspect ratio; leave position 6 open</x:v>
+        <x:f>IFERROR(VLOOKUP($A9,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Create tab SWITCH; register Subject to detect, Shutter mode, Focus bracketing, IS (Image Stabilizer) mode, and Cropping/aspect ratio in order; leave position 6 open.</x:v>
       </x:c>
       <x:c r="I9" s="13" t="str">
         <x:v>Not started</x:v>
@@ -1851,7 +1788,7 @@
     </x:row>
     <x:row r="10" hidden="0">
       <x:c r="A10" s="17" t="str">
-        <x:v>SETUP-04</x:v>
+        <x:v>SETUP-MM-AF-01</x:v>
       </x:c>
       <x:c r="B10" s="17" t="n">
         <x:v>5</x:v>
@@ -1860,22 +1797,22 @@
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>Shared operational defaults match the complete C1-aligned reference baseline.</x:v>
+        <x:v>The approved AF Case My Menu tab exists with all three shortcuts in the correct order, and Servo AF opens the complete Case selector without changing AF Operation.</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
-        <x:v>Confirm Fv, shutter and aperture Auto, Auto ISO maximum 12800, Servo AF, Face + Tracking, Animals, Eye Detection Enable, High Speed Continuous, EFCS, Mode 1, cRAW, Full-frame, and Evaluative metering.</x:v>
+        <x:v>Configure and verify My Menu: AF Case before shared setup or profile registration.</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio</x:v>
+        <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>My Menu</x:v>
       </x:c>
       <x:c r="G10" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Multiple</x:v>
+        <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>My Menu</x:v>
       </x:c>
       <x:c r="H10" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting menu: IS (Image Stabilizer) mode</x:v>
+        <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Create tab AF Case; register Servo AF, Tracking Sensitivity, and Accel./Decel. tracking in order; confirm Servo AF opens the complete Case 1–4 / Case A selector and does not change AF Operation.</x:v>
       </x:c>
       <x:c r="I10" s="13" t="str">
         <x:v>Not started</x:v>
@@ -1885,7 +1822,7 @@
       <x:c r="L10" s="15" t="str"/>
       <x:c r="M10" s="15" t="str"/>
       <x:c r="N10" s="15" t="str">
-        <x:v>Check Camera Setup Essentials and Camera Defaults.</x:v>
+        <x:v>Configure AF Case immediately after SWITCH and before shared defaults, controls, or C1–C3 registration.</x:v>
       </x:c>
       <x:c r="O10" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -1894,7 +1831,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q10" s="15" t="str">
-        <x:v>00 Master/baseline.yaml; Camera Setup Essentials</x:v>
+        <x:v>00 Master/setting_access.yaml; controls.md; Back-Button AF guide; project memory</x:v>
       </x:c>
       <x:c r="R10" s="17" t="str">
         <x:v>No</x:v>
@@ -1902,7 +1839,7 @@
     </x:row>
     <x:row r="11" hidden="0">
       <x:c r="A11" s="17" t="str">
-        <x:v>SETUP-05</x:v>
+        <x:v>SETUP-04</x:v>
       </x:c>
       <x:c r="B11" s="17" t="n">
         <x:v>6</x:v>
@@ -1911,22 +1848,22 @@
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D11" s="15" t="str">
-        <x:v>Exposure review tools are available in every profile.</x:v>
+        <x:v>Shared operational defaults match the complete C1-aligned reference baseline.</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
-        <x:v>Confirm RGB histogram and highlight alert are enabled.</x:v>
+        <x:v>Confirm Fv, shutter and aperture Auto, Auto ISO maximum 12800, Servo AF with Case A (Auto), Face + Tracking, Animals, Eye Detection Enable, High Speed Continuous, EFCS, Mode 1, cRAW, Full-frame, and Evaluative metering.</x:v>
       </x:c>
       <x:c r="F11" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A11,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A11,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio; MM-AF Case for Servo AF Case</x:v>
       </x:c>
       <x:c r="G11" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A11,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A11,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H11" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A11,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shooting 7: Shooting info. disp. &gt; Screen info. settings &gt; Histogram &gt; RGB; Playback 5: Highlight alert &gt; Enable</x:v>
+        <x:f>IFERROR(VLOOKUP($A11,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; My Menu AF Case &gt; Servo AF or AF3 &gt; Servo AF characteristics: Case A; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting menu: IS (Image Stabilizer) mode</x:v>
       </x:c>
       <x:c r="I11" s="13" t="str">
         <x:v>Not started</x:v>
@@ -1936,7 +1873,7 @@
       <x:c r="L11" s="15" t="str"/>
       <x:c r="M11" s="15" t="str"/>
       <x:c r="N11" s="15" t="str">
-        <x:v>Check display settings.</x:v>
+        <x:v>Check Camera Setup Essentials and Camera Defaults.</x:v>
       </x:c>
       <x:c r="O11" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -1953,7 +1890,7 @@
     </x:row>
     <x:row r="12" hidden="0">
       <x:c r="A12" s="17" t="str">
-        <x:v>SETUP-06</x:v>
+        <x:v>SETUP-05</x:v>
       </x:c>
       <x:c r="B12" s="17" t="n">
         <x:v>7</x:v>
@@ -1962,22 +1899,22 @@
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D12" s="15" t="str">
-        <x:v>Specialty functions do not interfere with the verification session.</x:v>
+        <x:v>Exposure review tools are available in every profile.</x:v>
       </x:c>
       <x:c r="E12" s="15" t="str">
-        <x:v>Confirm High ISO NR, Long Exposure NR, Continuous AF, Electronic full-time MF, and IBIS High Resolution Shot are Off.</x:v>
+        <x:v>Confirm RGB histogram and highlight alert are enabled.</x:v>
       </x:c>
       <x:c r="F12" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A12,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A12,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
         <x:v>MENU</x:v>
       </x:c>
       <x:c r="G12" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A12,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A12,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H12" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A12,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shooting 4: Long exp. noise reduction and High ISO speed NR; AF1: Continuous AF; AF menu: Lens electronic MF; Shooting 5: IBIS High resolution shot</x:v>
+        <x:f>IFERROR(VLOOKUP($A12,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Shooting 7: Shooting info. disp. &gt; Screen info. settings &gt; Histogram &gt; RGB; Playback 5: Highlight alert &gt; Enable</x:v>
       </x:c>
       <x:c r="I12" s="13" t="str">
         <x:v>Not started</x:v>
@@ -1987,7 +1924,7 @@
       <x:c r="L12" s="15" t="str"/>
       <x:c r="M12" s="15" t="str"/>
       <x:c r="N12" s="15" t="str">
-        <x:v>Review Set &amp; Forget settings.</x:v>
+        <x:v>Check display settings.</x:v>
       </x:c>
       <x:c r="O12" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2004,7 +1941,7 @@
     </x:row>
     <x:row r="13" hidden="0">
       <x:c r="A13" s="17" t="str">
-        <x:v>SETUP-07</x:v>
+        <x:v>SETUP-06</x:v>
       </x:c>
       <x:c r="B13" s="17" t="n">
         <x:v>8</x:v>
@@ -2013,22 +1950,22 @@
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D13" s="15" t="str">
-        <x:v>Manual-focus aid matches the approved setup.</x:v>
+        <x:v>Specialty functions do not interfere with the verification session.</x:v>
       </x:c>
       <x:c r="E13" s="15" t="str">
-        <x:v>Confirm MF Peaking is On, Low, Red.</x:v>
+        <x:v>Confirm High ISO NR, Long Exposure NR, Continuous AF, Electronic full-time MF, and IBIS High Resolution Shot are Off.</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A13,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A13,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
         <x:v>MENU</x:v>
       </x:c>
       <x:c r="G13" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A13,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>AF menu</x:v>
+        <x:f>IFERROR(VLOOKUP($A13,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H13" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A13,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>MF peaking settings &gt; Peaking: On; Level: Low; Color: Red</x:v>
+        <x:f>IFERROR(VLOOKUP($A13,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Shooting 4: Long exp. noise reduction and High ISO speed NR; AF1: Continuous AF; AF menu: Lens electronic MF; Shooting 5: IBIS High resolution shot</x:v>
       </x:c>
       <x:c r="I13" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2038,7 +1975,7 @@
       <x:c r="L13" s="15" t="str"/>
       <x:c r="M13" s="15" t="str"/>
       <x:c r="N13" s="15" t="str">
-        <x:v>Review MF Peaking settings.</x:v>
+        <x:v>Review Set &amp; Forget settings.</x:v>
       </x:c>
       <x:c r="O13" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2047,7 +1984,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q13" s="15" t="str">
-        <x:v>Camera Setup Essentials; R5 Quick Reference</x:v>
+        <x:v>00 Master/baseline.yaml; Camera Setup Essentials</x:v>
       </x:c>
       <x:c r="R13" s="17" t="str">
         <x:v>No</x:v>
@@ -2055,31 +1992,31 @@
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14" s="17" t="str">
-        <x:v>CTRL-CONFIG-01</x:v>
+        <x:v>SETUP-07</x:v>
       </x:c>
       <x:c r="B14" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C14" s="22" t="str">
-        <x:v>Controls</x:v>
+        <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D14" s="15" t="str">
-        <x:v>Every shared physical control matches the approved assignment and INFO details.</x:v>
+        <x:v>Manual-focus aid matches the approved setup.</x:v>
       </x:c>
       <x:c r="E14" s="15" t="str">
-        <x:v>Configure shutter half-press, AF-ON, AE Lock, AF Point Selection, Lens AF, DOF, SET, joystick, dials, Control Ring, and M-Fn.</x:v>
+        <x:v>Confirm MF Peaking is On, Low, Red.</x:v>
       </x:c>
       <x:c r="F14" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A14,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Physical controls; MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A14,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="G14" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A14,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Custom Functions 3</x:v>
+        <x:f>IFERROR(VLOOKUP($A14,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>AF menu</x:v>
       </x:c>
       <x:c r="H14" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A14,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Customize buttons and Customize dials; use Customize buttons for shutter half-press, AF-ON, AE Lock, AF Point Selection, lens AF, DOF, SET, joystick, and M-Fn</x:v>
+        <x:f>IFERROR(VLOOKUP($A14,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>MF peaking settings &gt; Peaking: On; Level: Low; Color: Red</x:v>
       </x:c>
       <x:c r="I14" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2089,7 +2026,7 @@
       <x:c r="L14" s="15" t="str"/>
       <x:c r="M14" s="15" t="str"/>
       <x:c r="N14" s="15" t="str">
-        <x:v>Configure each control before registering C1.</x:v>
+        <x:v>Review MF Peaking settings.</x:v>
       </x:c>
       <x:c r="O14" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2098,7 +2035,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q14" s="15" t="str">
-        <x:v>controls.md; data/canon_r5_custom_controls_current.yaml; Back-Button AF guide</x:v>
+        <x:v>Camera Setup Essentials; R5 Quick Reference</x:v>
       </x:c>
       <x:c r="R14" s="17" t="str">
         <x:v>No</x:v>
@@ -2106,31 +2043,31 @@
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="17" t="str">
-        <x:v>BACKUP-SET-01</x:v>
+        <x:v>CTRL-CONFIG-01</x:v>
       </x:c>
       <x:c r="B15" s="17" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C15" s="22" t="str">
-        <x:v>Camera Setup</x:v>
+        <x:v>Controls</x:v>
       </x:c>
       <x:c r="D15" s="15" t="str">
-        <x:v>A recoverable checkpoint exists after shared settings, SWITCH, and physical controls are configured.</x:v>
+        <x:v>Every shared physical control matches the approved assignment and INFO details.</x:v>
       </x:c>
       <x:c r="E15" s="15" t="str">
-        <x:v>Save a checkpoint copy of the complete camera configuration and record it in Sessions.</x:v>
+        <x:v>Configure shutter half-press, AF-ON, AE Lock, AF Point Selection, Lens AF, DOF, SET, joystick, dials, Control Ring, and M-Fn.</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A15,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A15,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Physical controls; MENU</x:v>
       </x:c>
       <x:c r="G15" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A15,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Set-up 5</x:v>
+        <x:f>IFERROR(VLOOKUP($A15,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="H15" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A15,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
+        <x:f>IFERROR(VLOOKUP($A15,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Customize buttons and Customize dials; use Customize buttons for shutter half-press, AF-ON, AE Lock, AF Point Selection, lens AF, DOF, SET, joystick, and M-Fn</x:v>
       </x:c>
       <x:c r="I15" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2140,46 +2077,48 @@
       <x:c r="L15" s="15" t="str"/>
       <x:c r="M15" s="15" t="str"/>
       <x:c r="N15" s="15" t="str">
-        <x:v>After saving, set Status to Backup-Settings before configuring C1.</x:v>
+        <x:v>Configure each control before registering C1.</x:v>
       </x:c>
       <x:c r="O15" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
       </x:c>
       <x:c r="P15" s="17" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q15" s="15" t="str">
+        <x:v>controls.md; data/canon_r5_custom_controls_current.yaml; Back-Button AF guide</x:v>
+      </x:c>
+      <x:c r="R15" s="17" t="str">
         <x:v>No</x:v>
-      </x:c>
-      <x:c r="Q15" s="15" t="str"/>
-      <x:c r="R15" s="17" t="str">
-        <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="17" t="str">
-        <x:v>C1-CONFIG-01</x:v>
+        <x:v>BACKUP-SET-01</x:v>
       </x:c>
       <x:c r="B16" s="17" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="22" t="str">
-        <x:v>C1 Wildlife</x:v>
+        <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D16" s="15" t="str">
-        <x:v>Every C1 target setting matches the C1–C3 Registration sheet.</x:v>
+        <x:v>A recoverable checkpoint exists after shared settings, SWITCH, AF Case, and physical controls are configured.</x:v>
       </x:c>
       <x:c r="E16" s="15" t="str">
-        <x:v>Build the complete C1 Wildlife environment in a normal shooting mode.</x:v>
+        <x:v>Save a checkpoint copy of the complete camera configuration and record it in Sessions.</x:v>
       </x:c>
       <x:c r="F16" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A16,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Q, dials, AF controls, MM-SWITCH, lens IS switch</x:v>
+        <x:f>IFERROR(VLOOKUP($A16,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="G16" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A16,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Multiple</x:v>
+        <x:f>IFERROR(VLOOKUP($A16,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="H16" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A16,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, AF Drive mode, and lens IS switch</x:v>
+        <x:f>IFERROR(VLOOKUP($A16,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
       </x:c>
       <x:c r="I16" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2189,24 +2128,22 @@
       <x:c r="L16" s="15" t="str"/>
       <x:c r="M16" s="15" t="str"/>
       <x:c r="N16" s="15" t="str">
-        <x:v>Configure from a normal shooting mode, not recalled C1.</x:v>
+        <x:v>After saving, set Status to Backup-Settings before configuring C1.</x:v>
       </x:c>
       <x:c r="O16" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
       </x:c>
       <x:c r="P16" s="17" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="Q16" s="15" t="str">
-        <x:v>controls.md; data/canon_r5_custom_controls_current.yaml; Wildlife profile</x:v>
-      </x:c>
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q16" s="15" t="str"/>
       <x:c r="R16" s="17" t="str">
-        <x:v>No</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="17" t="str">
-        <x:v>C1-REG-01</x:v>
+        <x:v>C1-CONFIG-01</x:v>
       </x:c>
       <x:c r="B17" s="17" t="n">
         <x:v>12</x:v>
@@ -2215,22 +2152,22 @@
         <x:v>C1 Wildlife</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
-        <x:v>C1 registration completes without overwriting C2 or C3.</x:v>
+        <x:v>Every C1 target setting matches the C1–C3 Registration sheet.</x:v>
       </x:c>
       <x:c r="E17" s="15" t="str">
-        <x:v>Register the validated Wildlife environment to C1.</x:v>
+        <x:v>Build the complete C1 Wildlife environment in a normal shooting mode.</x:v>
       </x:c>
       <x:c r="F17" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A17,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A17,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Q, dials, AF controls, MM-SWITCH, MM-AF Case, lens IS switch</x:v>
       </x:c>
       <x:c r="G17" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A17,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Set-up 5</x:v>
+        <x:f>IFERROR(VLOOKUP($A17,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H17" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A17,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C1</x:v>
+        <x:f>IFERROR(VLOOKUP($A17,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, My Menu AF Case or AF3 Servo AF characteristics, AF Drive mode, and lens IS switch</x:v>
       </x:c>
       <x:c r="I17" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2240,7 +2177,7 @@
       <x:c r="L17" s="15" t="str"/>
       <x:c r="M17" s="15" t="str"/>
       <x:c r="N17" s="15" t="str">
-        <x:v>Register only after every C1 setting is checked.</x:v>
+        <x:v>Configure from a normal shooting mode, not recalled C1.</x:v>
       </x:c>
       <x:c r="O17" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2249,7 +2186,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q17" s="15" t="str">
-        <x:v>controls.md; Back-Button AF guide</x:v>
+        <x:v>controls.md; data/canon_r5_custom_controls_current.yaml; Wildlife profile</x:v>
       </x:c>
       <x:c r="R17" s="17" t="str">
         <x:v>No</x:v>
@@ -2257,7 +2194,7 @@
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="17" t="str">
-        <x:v>C1-READ-01</x:v>
+        <x:v>C1-REG-01</x:v>
       </x:c>
       <x:c r="B18" s="17" t="n">
         <x:v>13</x:v>
@@ -2266,22 +2203,22 @@
         <x:v>C1 Wildlife</x:v>
       </x:c>
       <x:c r="D18" s="15" t="str">
-        <x:v>Every recalled value matches the validated C1 column.</x:v>
+        <x:v>C1 registration completes without overwriting C2 or C3.</x:v>
       </x:c>
       <x:c r="E18" s="15" t="str">
-        <x:v>Leave the setup state, recall C1 with M-Fn, and read back every setting.</x:v>
+        <x:v>Register the validated Wildlife environment to C1.</x:v>
       </x:c>
       <x:c r="F18" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A18,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>M-Fn recall; Q; MM-SWITCH; MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A18,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="G18" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A18,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>No single menu</x:v>
+        <x:f>IFERROR(VLOOKUP($A18,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="H18" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A18,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Recall C1 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
+        <x:f>IFERROR(VLOOKUP($A18,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C1</x:v>
       </x:c>
       <x:c r="I18" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2291,7 +2228,7 @@
       <x:c r="L18" s="15" t="str"/>
       <x:c r="M18" s="15" t="str"/>
       <x:c r="N18" s="15" t="str">
-        <x:v>Record discrepancies before proceeding to C2.</x:v>
+        <x:v>Register only after every C1 setting is checked.</x:v>
       </x:c>
       <x:c r="O18" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2300,7 +2237,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q18" s="15" t="str">
-        <x:v>controls.md; project memory</x:v>
+        <x:v>controls.md; Back-Button AF guide</x:v>
       </x:c>
       <x:c r="R18" s="17" t="str">
         <x:v>No</x:v>
@@ -2308,7 +2245,7 @@
     </x:row>
     <x:row r="19" hidden="0">
       <x:c r="A19" s="17" t="str">
-        <x:v>C1-OPS-01</x:v>
+        <x:v>C1-READ-01</x:v>
       </x:c>
       <x:c r="B19" s="17" t="n">
         <x:v>14</x:v>
@@ -2317,22 +2254,22 @@
         <x:v>C1 Wildlife</x:v>
       </x:c>
       <x:c r="D19" s="15" t="str">
-        <x:v>C1 recalls a usable Wildlife environment and controls behave as intended.</x:v>
+        <x:v>Every recalled value matches the validated C1 column.</x:v>
       </x:c>
       <x:c r="E19" s="15" t="str">
-        <x:v>Perform a short Wildlife operational test.</x:v>
+        <x:v>Leave the setup state, recall C1 with M-Fn, and read back every setting.</x:v>
       </x:c>
       <x:c r="F19" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A19,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Physical controls</x:v>
+        <x:f>IFERROR(VLOOKUP($A19,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>M-Fn recall; Q; MM-SWITCH; MM-AF Case; MENU</x:v>
       </x:c>
       <x:c r="G19" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A19,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>No menu</x:v>
+        <x:f>IFERROR(VLOOKUP($A19,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>No single menu</x:v>
       </x:c>
       <x:c r="H19" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A19,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Operational shooting test</x:v>
+        <x:f>IFERROR(VLOOKUP($A19,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Recall C1 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
       </x:c>
       <x:c r="I19" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2342,7 +2279,7 @@
       <x:c r="L19" s="15" t="str"/>
       <x:c r="M19" s="15" t="str"/>
       <x:c r="N19" s="15" t="str">
-        <x:v>Test acquisition, precision AF, exposure, and continuous drive.</x:v>
+        <x:v>Record discrepancies before proceeding to C2.</x:v>
       </x:c>
       <x:c r="O19" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2351,7 +2288,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q19" s="15" t="str">
-        <x:v>controls.md; Wildlife profile</x:v>
+        <x:v>controls.md; project memory</x:v>
       </x:c>
       <x:c r="R19" s="17" t="str">
         <x:v>No</x:v>
@@ -2359,31 +2296,31 @@
     </x:row>
     <x:row r="20" hidden="0">
       <x:c r="A20" s="17" t="str">
-        <x:v>C2-CONFIG-01</x:v>
+        <x:v>C1-OPS-01</x:v>
       </x:c>
       <x:c r="B20" s="17" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C20" s="22" t="str">
-        <x:v>C2 Birds in Flight</x:v>
+        <x:v>C1 Wildlife</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
-        <x:v>Every C2 target setting matches the C1–C3 Registration sheet.</x:v>
+        <x:v>C1 recalls a usable Wildlife environment and controls behave as intended.</x:v>
       </x:c>
       <x:c r="E20" s="15" t="str">
-        <x:v>Return to a normal mode and build the complete C2 Birds in Flight environment.</x:v>
+        <x:v>Perform a short Wildlife operational test.</x:v>
       </x:c>
       <x:c r="F20" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A20,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Q, dials, AF controls, MM-SWITCH, lens IS switch</x:v>
+        <x:f>IFERROR(VLOOKUP($A20,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Physical controls</x:v>
       </x:c>
       <x:c r="G20" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A20,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Multiple</x:v>
+        <x:f>IFERROR(VLOOKUP($A20,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>No menu</x:v>
       </x:c>
       <x:c r="H20" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A20,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, AF Drive mode, and lens IS switch</x:v>
+        <x:f>IFERROR(VLOOKUP($A20,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Operational shooting test</x:v>
       </x:c>
       <x:c r="I20" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2393,7 +2330,7 @@
       <x:c r="L20" s="15" t="str"/>
       <x:c r="M20" s="15" t="str"/>
       <x:c r="N20" s="15" t="str">
-        <x:v>Do not build C2 while working inside recalled C1.</x:v>
+        <x:v>Test acquisition, precision AF, exposure, and continuous drive.</x:v>
       </x:c>
       <x:c r="O20" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2402,7 +2339,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q20" s="15" t="str">
-        <x:v>Birds in Flight profile; Back-Button AF guide</x:v>
+        <x:v>controls.md; Wildlife profile</x:v>
       </x:c>
       <x:c r="R20" s="17" t="str">
         <x:v>No</x:v>
@@ -2410,7 +2347,7 @@
     </x:row>
     <x:row r="21" hidden="0">
       <x:c r="A21" s="17" t="str">
-        <x:v>C2-REG-01</x:v>
+        <x:v>C2-CONFIG-01</x:v>
       </x:c>
       <x:c r="B21" s="17" t="n">
         <x:v>16</x:v>
@@ -2419,22 +2356,22 @@
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
       <x:c r="D21" s="15" t="str">
-        <x:v>C2 registration completes without changing C1.</x:v>
+        <x:v>Every C2 target setting matches the C1–C3 Registration sheet.</x:v>
       </x:c>
       <x:c r="E21" s="15" t="str">
-        <x:v>Register the validated Birds in Flight environment to C2.</x:v>
+        <x:v>Return to a normal mode and build the complete C2 Birds in Flight environment.</x:v>
       </x:c>
       <x:c r="F21" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A21,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A21,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Q, dials, AF controls, MM-SWITCH, MM-AF Case, lens IS switch</x:v>
       </x:c>
       <x:c r="G21" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A21,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Set-up 5</x:v>
+        <x:f>IFERROR(VLOOKUP($A21,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H21" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A21,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C2</x:v>
+        <x:f>IFERROR(VLOOKUP($A21,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, My Menu AF Case or AF3 Servo AF characteristics, AF Drive mode, and lens IS switch</x:v>
       </x:c>
       <x:c r="I21" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2444,7 +2381,7 @@
       <x:c r="L21" s="15" t="str"/>
       <x:c r="M21" s="15" t="str"/>
       <x:c r="N21" s="15" t="str">
-        <x:v>Register only after every C2 setting is checked.</x:v>
+        <x:v>Do not build C2 while working inside recalled C1.</x:v>
       </x:c>
       <x:c r="O21" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2453,7 +2390,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q21" s="15" t="str">
-        <x:v>controls.md; Back-Button AF guide</x:v>
+        <x:v>Birds in Flight profile; Back-Button AF guide</x:v>
       </x:c>
       <x:c r="R21" s="17" t="str">
         <x:v>No</x:v>
@@ -2461,7 +2398,7 @@
     </x:row>
     <x:row r="22" hidden="0">
       <x:c r="A22" s="17" t="str">
-        <x:v>C2-READ-01</x:v>
+        <x:v>C2-REG-01</x:v>
       </x:c>
       <x:c r="B22" s="17" t="n">
         <x:v>17</x:v>
@@ -2470,22 +2407,22 @@
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
       <x:c r="D22" s="15" t="str">
-        <x:v>Every recalled value matches the validated C2 column.</x:v>
+        <x:v>C2 registration completes without changing C1.</x:v>
       </x:c>
       <x:c r="E22" s="15" t="str">
-        <x:v>Recall C2 and read back every setting.</x:v>
+        <x:v>Register the validated Birds in Flight environment to C2.</x:v>
       </x:c>
       <x:c r="F22" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A22,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>M-Fn recall; Q; MM-SWITCH; MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A22,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="G22" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A22,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>No single menu</x:v>
+        <x:f>IFERROR(VLOOKUP($A22,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="H22" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A22,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Recall C2 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
+        <x:f>IFERROR(VLOOKUP($A22,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C2</x:v>
       </x:c>
       <x:c r="I22" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2495,7 +2432,7 @@
       <x:c r="L22" s="15" t="str"/>
       <x:c r="M22" s="15" t="str"/>
       <x:c r="N22" s="15" t="str">
-        <x:v>Recheck C1 after the C2 read-back.</x:v>
+        <x:v>Register only after every C2 setting is checked.</x:v>
       </x:c>
       <x:c r="O22" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2504,7 +2441,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q22" s="15" t="str">
-        <x:v>controls.md; project memory</x:v>
+        <x:v>controls.md; Back-Button AF guide</x:v>
       </x:c>
       <x:c r="R22" s="17" t="str">
         <x:v>No</x:v>
@@ -2512,7 +2449,7 @@
     </x:row>
     <x:row r="23" hidden="0">
       <x:c r="A23" s="17" t="str">
-        <x:v>C2-OPS-01</x:v>
+        <x:v>C2-READ-01</x:v>
       </x:c>
       <x:c r="B23" s="17" t="n">
         <x:v>18</x:v>
@@ -2521,22 +2458,22 @@
         <x:v>C2 Birds in Flight</x:v>
       </x:c>
       <x:c r="D23" s="15" t="str">
-        <x:v>C2 provides 1/2500 sec., Mechanical shutter, H+, animal tracking, and Mode 3.</x:v>
+        <x:v>Every recalled value matches the validated C2 column.</x:v>
       </x:c>
       <x:c r="E23" s="15" t="str">
-        <x:v>Perform a short Birds in Flight operational test.</x:v>
+        <x:v>Recall C2 and read back every setting.</x:v>
       </x:c>
       <x:c r="F23" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A23,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Physical controls</x:v>
+        <x:f>IFERROR(VLOOKUP($A23,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>M-Fn recall; Q; MM-SWITCH; MM-AF Case; MENU</x:v>
       </x:c>
       <x:c r="G23" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A23,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>No menu</x:v>
+        <x:f>IFERROR(VLOOKUP($A23,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>No single menu</x:v>
       </x:c>
       <x:c r="H23" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A23,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Operational shooting test</x:v>
+        <x:f>IFERROR(VLOOKUP($A23,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Recall C2 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
       </x:c>
       <x:c r="I23" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2546,7 +2483,7 @@
       <x:c r="L23" s="15" t="str"/>
       <x:c r="M23" s="15" t="str"/>
       <x:c r="N23" s="15" t="str">
-        <x:v>Test tracking and burst behavior on a moving target.</x:v>
+        <x:v>Recheck C1 after the C2 read-back.</x:v>
       </x:c>
       <x:c r="O23" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2555,7 +2492,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q23" s="15" t="str">
-        <x:v>Birds in Flight profile</x:v>
+        <x:v>controls.md; project memory</x:v>
       </x:c>
       <x:c r="R23" s="17" t="str">
         <x:v>No</x:v>
@@ -2563,31 +2500,31 @@
     </x:row>
     <x:row r="24" hidden="0">
       <x:c r="A24" s="17" t="str">
-        <x:v>C3-CONFIG-01</x:v>
+        <x:v>C2-OPS-01</x:v>
       </x:c>
       <x:c r="B24" s="17" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="22" t="str">
-        <x:v>C3 Landscape</x:v>
+        <x:v>C2 Birds in Flight</x:v>
       </x:c>
       <x:c r="D24" s="15" t="str">
-        <x:v>Every C3 target setting matches the C1–C3 Registration sheet.</x:v>
+        <x:v>C2 provides 1/2500 sec., Mechanical shutter, H+, Servo AF Case 4, animal tracking, and Mode 3.</x:v>
       </x:c>
       <x:c r="E24" s="15" t="str">
-        <x:v>Return to a normal mode and build the complete C3 Landscape environment.</x:v>
+        <x:v>Perform a short Birds in Flight operational test.</x:v>
       </x:c>
       <x:c r="F24" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A24,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Q, dials, AF controls, MM-SWITCH, lens IS switch</x:v>
+        <x:f>IFERROR(VLOOKUP($A24,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Physical controls</x:v>
       </x:c>
       <x:c r="G24" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A24,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Multiple</x:v>
+        <x:f>IFERROR(VLOOKUP($A24,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>No menu</x:v>
       </x:c>
       <x:c r="H24" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A24,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, AF Drive mode, and lens IS switch</x:v>
+        <x:f>IFERROR(VLOOKUP($A24,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Operational shooting test</x:v>
       </x:c>
       <x:c r="I24" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2597,7 +2534,7 @@
       <x:c r="L24" s="15" t="str"/>
       <x:c r="M24" s="15" t="str"/>
       <x:c r="N24" s="15" t="str">
-        <x:v>Do not build C3 while working inside C1 or C2.</x:v>
+        <x:v>Test tracking and burst behavior on a moving target.</x:v>
       </x:c>
       <x:c r="O24" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2606,7 +2543,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q24" s="15" t="str">
-        <x:v>Landscape profile; Back-Button AF guide</x:v>
+        <x:v>Birds in Flight profile</x:v>
       </x:c>
       <x:c r="R24" s="17" t="str">
         <x:v>No</x:v>
@@ -2614,7 +2551,7 @@
     </x:row>
     <x:row r="25" hidden="0">
       <x:c r="A25" s="17" t="str">
-        <x:v>C3-REG-01</x:v>
+        <x:v>C3-CONFIG-01</x:v>
       </x:c>
       <x:c r="B25" s="17" t="n">
         <x:v>20</x:v>
@@ -2623,22 +2560,22 @@
         <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="D25" s="15" t="str">
-        <x:v>C3 registration completes without changing C1 or C2.</x:v>
+        <x:v>Every C3 target setting matches the C1–C3 Registration sheet.</x:v>
       </x:c>
       <x:c r="E25" s="15" t="str">
-        <x:v>Register the validated Landscape environment to C3.</x:v>
+        <x:v>Return to a normal mode and build the complete C3 Landscape environment.</x:v>
       </x:c>
       <x:c r="F25" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A25,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A25,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Q, dials, AF controls, MM-SWITCH, lens IS switch</x:v>
       </x:c>
       <x:c r="G25" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A25,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Set-up 5</x:v>
+        <x:f>IFERROR(VLOOKUP($A25,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H25" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A25,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C3</x:v>
+        <x:f>IFERROR(VLOOKUP($A25,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, AF Drive mode, and lens IS switch</x:v>
       </x:c>
       <x:c r="I25" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2648,7 +2585,7 @@
       <x:c r="L25" s="15" t="str"/>
       <x:c r="M25" s="15" t="str"/>
       <x:c r="N25" s="15" t="str">
-        <x:v>Register only after every C3 setting is checked.</x:v>
+        <x:v>Do not build C3 while working inside C1 or C2.</x:v>
       </x:c>
       <x:c r="O25" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2657,7 +2594,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q25" s="15" t="str">
-        <x:v>controls.md; Back-Button AF guide</x:v>
+        <x:v>Landscape profile; Back-Button AF guide</x:v>
       </x:c>
       <x:c r="R25" s="17" t="str">
         <x:v>No</x:v>
@@ -2665,7 +2602,7 @@
     </x:row>
     <x:row r="26" hidden="0">
       <x:c r="A26" s="17" t="str">
-        <x:v>C3-READ-01</x:v>
+        <x:v>C3-REG-01</x:v>
       </x:c>
       <x:c r="B26" s="17" t="n">
         <x:v>21</x:v>
@@ -2674,22 +2611,22 @@
         <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="D26" s="15" t="str">
-        <x:v>Every recalled value matches the validated C3 column.</x:v>
+        <x:v>C3 registration completes without changing C1 or C2.</x:v>
       </x:c>
       <x:c r="E26" s="15" t="str">
-        <x:v>Recall C3 and read back every setting.</x:v>
+        <x:v>Register the validated Landscape environment to C3.</x:v>
       </x:c>
       <x:c r="F26" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A26,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>M-Fn recall; Q; MM-SWITCH; MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A26,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="G26" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A26,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>No single menu</x:v>
+        <x:f>IFERROR(VLOOKUP($A26,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="H26" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A26,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Recall C3 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
+        <x:f>IFERROR(VLOOKUP($A26,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C3</x:v>
       </x:c>
       <x:c r="I26" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2699,7 +2636,7 @@
       <x:c r="L26" s="15" t="str"/>
       <x:c r="M26" s="15" t="str"/>
       <x:c r="N26" s="15" t="str">
-        <x:v>Recall C1, C2, and C3 in sequence afterward.</x:v>
+        <x:v>Register only after every C3 setting is checked.</x:v>
       </x:c>
       <x:c r="O26" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2708,7 +2645,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q26" s="15" t="str">
-        <x:v>controls.md; project memory</x:v>
+        <x:v>controls.md; Back-Button AF guide</x:v>
       </x:c>
       <x:c r="R26" s="17" t="str">
         <x:v>No</x:v>
@@ -2716,31 +2653,31 @@
     </x:row>
     <x:row r="27" hidden="0">
       <x:c r="A27" s="17" t="str">
-        <x:v>BACKUP-SET-02</x:v>
+        <x:v>C3-READ-01</x:v>
       </x:c>
       <x:c r="B27" s="17" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C27" s="22" t="str">
-        <x:v>Camera Setup</x:v>
+        <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="D27" s="15" t="str">
-        <x:v>A recoverable checkpoint exists after C1, C2, and C3 are registered and read back.</x:v>
+        <x:v>Every recalled value matches the validated C3 column.</x:v>
       </x:c>
       <x:c r="E27" s="15" t="str">
-        <x:v>Save a checkpoint copy of the complete camera configuration and record it in Sessions.</x:v>
+        <x:v>Recall C3 and read back every setting.</x:v>
       </x:c>
       <x:c r="F27" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A27,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A27,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>M-Fn recall; Q; MM-SWITCH; MENU</x:v>
       </x:c>
       <x:c r="G27" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A27,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Set-up 5</x:v>
+        <x:f>IFERROR(VLOOKUP($A27,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>No single menu</x:v>
       </x:c>
       <x:c r="H27" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A27,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
+        <x:f>IFERROR(VLOOKUP($A27,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Recall C3 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
       </x:c>
       <x:c r="I27" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2750,46 +2687,48 @@
       <x:c r="L27" s="15" t="str"/>
       <x:c r="M27" s="15" t="str"/>
       <x:c r="N27" s="15" t="str">
-        <x:v>After saving, set Status to Backup-Settings before operational control and shutter testing.</x:v>
+        <x:v>Recall C1, C2, and C3 in sequence afterward.</x:v>
       </x:c>
       <x:c r="O27" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
       </x:c>
       <x:c r="P27" s="17" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q27" s="15" t="str">
+        <x:v>controls.md; project memory</x:v>
+      </x:c>
+      <x:c r="R27" s="17" t="str">
         <x:v>No</x:v>
-      </x:c>
-      <x:c r="Q27" s="15" t="str"/>
-      <x:c r="R27" s="17" t="str">
-        <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
     <x:row r="28" hidden="0">
       <x:c r="A28" s="17" t="str">
-        <x:v>C3-OPS-01</x:v>
+        <x:v>BACKUP-SET-02</x:v>
       </x:c>
       <x:c r="B28" s="17" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C28" s="22" t="str">
-        <x:v>C3 Landscape</x:v>
+        <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D28" s="15" t="str">
-        <x:v>C3 provides Av, f/9, ISO 100, One-Shot, 1-Point, Single Shot, and EFCS.</x:v>
+        <x:v>A recoverable checkpoint exists after C1, C2, and C3 are registered and read back.</x:v>
       </x:c>
       <x:c r="E28" s="15" t="str">
-        <x:v>Perform a short Landscape operational test.</x:v>
+        <x:v>Save a checkpoint copy of the complete camera configuration and record it in Sessions.</x:v>
       </x:c>
       <x:c r="F28" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A28,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Physical controls</x:v>
+        <x:f>IFERROR(VLOOKUP($A28,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="G28" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A28,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>No menu</x:v>
+        <x:f>IFERROR(VLOOKUP($A28,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="H28" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A28,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Operational shooting test</x:v>
+        <x:f>IFERROR(VLOOKUP($A28,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
       </x:c>
       <x:c r="I28" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2799,48 +2738,46 @@
       <x:c r="L28" s="15" t="str"/>
       <x:c r="M28" s="15" t="str"/>
       <x:c r="N28" s="15" t="str">
-        <x:v>Test handheld starting state, then tripod situational changes.</x:v>
+        <x:v>After saving, set Status to Backup-Settings before operational control and shutter testing.</x:v>
       </x:c>
       <x:c r="O28" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
       </x:c>
       <x:c r="P28" s="17" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="Q28" s="15" t="str">
-        <x:v>Landscape profile</x:v>
-      </x:c>
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q28" s="15" t="str"/>
       <x:c r="R28" s="17" t="str">
-        <x:v>No</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
     <x:row r="29" hidden="0">
       <x:c r="A29" s="17" t="str">
-        <x:v>CTRL-AFON-01</x:v>
+        <x:v>C3-OPS-01</x:v>
       </x:c>
       <x:c r="B29" s="17" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="C29" s="22" t="str">
-        <x:v>Controls</x:v>
+        <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="D29" s="15" t="str">
-        <x:v>AF-ON invokes Face + Tracking while maintaining the current AF Operation and Servo characteristics.</x:v>
+        <x:v>C3 provides Av, f/9, ISO 100, One-Shot, 1-Point, Single Shot, and EFCS.</x:v>
       </x:c>
       <x:c r="E29" s="15" t="str">
-        <x:v>Verify AF-ON in Servo and One-Shot environments.</x:v>
+        <x:v>Perform a short Landscape operational test.</x:v>
       </x:c>
       <x:c r="F29" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A29,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>AF-ON; INFO</x:v>
+        <x:f>IFERROR(VLOOKUP($A29,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Physical controls</x:v>
       </x:c>
       <x:c r="G29" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A29,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Custom Functions 3</x:v>
+        <x:f>IFERROR(VLOOKUP($A29,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>No menu</x:v>
       </x:c>
       <x:c r="H29" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A29,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Customize buttons &gt; AF-ON; press INFO to verify AF Operation, AF Method, and Servo AF characteristics</x:v>
+        <x:f>IFERROR(VLOOKUP($A29,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Operational shooting test</x:v>
       </x:c>
       <x:c r="I29" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2850,7 +2787,7 @@
       <x:c r="L29" s="15" t="str"/>
       <x:c r="M29" s="15" t="str"/>
       <x:c r="N29" s="15" t="str">
-        <x:v>Run in C1/C2 and again in C3.</x:v>
+        <x:v>Test handheld starting state, then tripod situational changes.</x:v>
       </x:c>
       <x:c r="O29" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2859,7 +2796,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q29" s="15" t="str">
-        <x:v>controls.md; data/canon_r5_custom_controls_current.yaml; project memory</x:v>
+        <x:v>Landscape profile</x:v>
       </x:c>
       <x:c r="R29" s="17" t="str">
         <x:v>No</x:v>
@@ -2867,7 +2804,7 @@
     </x:row>
     <x:row r="30" hidden="0">
       <x:c r="A30" s="17" t="str">
-        <x:v>CTRL-AELOCK-01</x:v>
+        <x:v>CTRL-AFON-01</x:v>
       </x:c>
       <x:c r="B30" s="17" t="n">
         <x:v>25</x:v>
@@ -2876,22 +2813,22 @@
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D30" s="15" t="str">
-        <x:v>AE Lock invokes 1-Point AF while maintaining the current AF Operation and last point position.</x:v>
+        <x:v>AF-ON invokes Face + Tracking while maintaining the current AF Operation and Servo characteristics.</x:v>
       </x:c>
       <x:c r="E30" s="15" t="str">
-        <x:v>Verify AE Lock in Servo and One-Shot environments.</x:v>
+        <x:v>Verify AF-ON in Servo and One-Shot environments.</x:v>
       </x:c>
       <x:c r="F30" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A30,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>AE Lock; INFO</x:v>
+        <x:f>IFERROR(VLOOKUP($A30,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>AF-ON; INFO</x:v>
       </x:c>
       <x:c r="G30" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A30,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A30,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="H30" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A30,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Customize buttons &gt; AE Lock; press INFO to verify AF Operation, AF Method, and Servo AF characteristics</x:v>
+        <x:f>IFERROR(VLOOKUP($A30,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Customize buttons &gt; AF-ON; press INFO to verify AF Operation, AF Method, and Servo AF characteristics</x:v>
       </x:c>
       <x:c r="I30" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2918,7 +2855,7 @@
     </x:row>
     <x:row r="31" hidden="0">
       <x:c r="A31" s="17" t="str">
-        <x:v>CTRL-DOF-01</x:v>
+        <x:v>CTRL-AELOCK-01</x:v>
       </x:c>
       <x:c r="B31" s="17" t="n">
         <x:v>26</x:v>
@@ -2927,22 +2864,22 @@
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D31" s="15" t="str">
-        <x:v>DOF changes AF Operation and both AF-start buttons respect the changed state.</x:v>
+        <x:v>AE Lock invokes 1-Point AF while maintaining the current AF Operation and last point position.</x:v>
       </x:c>
       <x:c r="E31" s="15" t="str">
-        <x:v>Verify the DOF One-Shot ↔ Servo switch.</x:v>
+        <x:v>Verify AE Lock in Servo and One-Shot environments.</x:v>
       </x:c>
       <x:c r="F31" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A31,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>DOF button</x:v>
+        <x:f>IFERROR(VLOOKUP($A31,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>AE Lock; INFO</x:v>
       </x:c>
       <x:c r="G31" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A31,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A31,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="H31" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A31,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Customize buttons &gt; Depth-of-field preview &gt; One-Shot AF ↔ Servo AF</x:v>
+        <x:f>IFERROR(VLOOKUP($A31,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Customize buttons &gt; AE Lock; press INFO to verify AF Operation, AF Method, and Servo AF characteristics</x:v>
       </x:c>
       <x:c r="I31" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2952,7 +2889,7 @@
       <x:c r="L31" s="15" t="str"/>
       <x:c r="M31" s="15" t="str"/>
       <x:c r="N31" s="15" t="str">
-        <x:v>Test both directions from C1/C2 and C3.</x:v>
+        <x:v>Run in C1/C2 and again in C3.</x:v>
       </x:c>
       <x:c r="O31" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -2961,7 +2898,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q31" s="15" t="str">
-        <x:v>controls.md; project memory</x:v>
+        <x:v>controls.md; data/canon_r5_custom_controls_current.yaml; project memory</x:v>
       </x:c>
       <x:c r="R31" s="17" t="str">
         <x:v>No</x:v>
@@ -2969,7 +2906,7 @@
     </x:row>
     <x:row r="32" hidden="0">
       <x:c r="A32" s="17" t="str">
-        <x:v>CTRL-SET-01</x:v>
+        <x:v>CTRL-DOF-01</x:v>
       </x:c>
       <x:c r="B32" s="17" t="n">
         <x:v>27</x:v>
@@ -2978,22 +2915,22 @@
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D32" s="15" t="str">
-        <x:v>SET toggles Eye Detection with Face + Tracking and does not imply active eye detection with deliberate-point AF.</x:v>
+        <x:v>DOF changes AF Operation and both AF-start buttons respect the changed state.</x:v>
       </x:c>
       <x:c r="E32" s="15" t="str">
-        <x:v>Verify SET Eye Detection behavior.</x:v>
+        <x:v>Verify the DOF One-Shot ↔ Servo switch.</x:v>
       </x:c>
       <x:c r="F32" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A32,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>SET button</x:v>
+        <x:f>IFERROR(VLOOKUP($A32,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>DOF button</x:v>
       </x:c>
       <x:c r="G32" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A32,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A32,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="H32" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A32,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Customize buttons &gt; SET &gt; Eye detection</x:v>
+        <x:f>IFERROR(VLOOKUP($A32,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Customize buttons &gt; Depth-of-field preview &gt; One-Shot AF ↔ Servo AF</x:v>
       </x:c>
       <x:c r="I32" s="13" t="str">
         <x:v>Not started</x:v>
@@ -3003,7 +2940,7 @@
       <x:c r="L32" s="15" t="str"/>
       <x:c r="M32" s="15" t="str"/>
       <x:c r="N32" s="15" t="str">
-        <x:v>Test Face + Tracking, 1-Point AF, and Spot AF.</x:v>
+        <x:v>Test both directions from C1/C2 and C3.</x:v>
       </x:c>
       <x:c r="O32" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -3012,7 +2949,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q32" s="15" t="str">
-        <x:v>controls.md; data/canon_r5_custom_controls_current.yaml; project memory</x:v>
+        <x:v>controls.md; project memory</x:v>
       </x:c>
       <x:c r="R32" s="17" t="str">
         <x:v>No</x:v>
@@ -3020,7 +2957,7 @@
     </x:row>
     <x:row r="33" hidden="0">
       <x:c r="A33" s="17" t="str">
-        <x:v>CTRL-JOY-01</x:v>
+        <x:v>CTRL-SET-01</x:v>
       </x:c>
       <x:c r="B33" s="17" t="n">
         <x:v>28</x:v>
@@ -3029,22 +2966,22 @@
         <x:v>Controls</x:v>
       </x:c>
       <x:c r="D33" s="15" t="str">
-        <x:v>Movement selects the intended point or subject; observed recenter and Face Select behavior are recorded.</x:v>
+        <x:v>SET toggles Eye Detection with Face + Tracking and does not imply active eye detection with deliberate-point AF.</x:v>
       </x:c>
       <x:c r="E33" s="15" t="str">
-        <x:v>Verify joystick movement and straight-press behavior.</x:v>
+        <x:v>Verify SET Eye Detection behavior.</x:v>
       </x:c>
       <x:c r="F33" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A33,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Joystick</x:v>
+        <x:f>IFERROR(VLOOKUP($A33,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>SET button</x:v>
       </x:c>
       <x:c r="G33" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A33,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A33,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="H33" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A33,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Customize buttons &gt; Multi-controller &gt; Direct AF point selection</x:v>
+        <x:f>IFERROR(VLOOKUP($A33,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Customize buttons &gt; SET &gt; Eye detection</x:v>
       </x:c>
       <x:c r="I33" s="13" t="str">
         <x:v>Not started</x:v>
@@ -3054,7 +2991,7 @@
       <x:c r="L33" s="15" t="str"/>
       <x:c r="M33" s="15" t="str"/>
       <x:c r="N33" s="15" t="str">
-        <x:v>Record single-border, double-border, release, and Face Select Off behavior.</x:v>
+        <x:v>Test Face + Tracking, 1-Point AF, and Spot AF.</x:v>
       </x:c>
       <x:c r="O33" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -3063,7 +3000,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q33" s="15" t="str">
-        <x:v>controls.md; project memory; Back-Button AF guide</x:v>
+        <x:v>controls.md; data/canon_r5_custom_controls_current.yaml; project memory</x:v>
       </x:c>
       <x:c r="R33" s="17" t="str">
         <x:v>No</x:v>
@@ -3071,31 +3008,31 @@
     </x:row>
     <x:row r="34" hidden="0">
       <x:c r="A34" s="17" t="str">
-        <x:v>EFCS-SHOCK-01</x:v>
+        <x:v>CTRL-JOY-01</x:v>
       </x:c>
       <x:c r="B34" s="17" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C34" s="22" t="str">
-        <x:v>EFCS Tests</x:v>
+        <x:v>Controls</x:v>
       </x:c>
       <x:c r="D34" s="15" t="str">
-        <x:v>At least five matched frames per shutter speed and mode are available for comparison.</x:v>
+        <x:v>Movement selects the intended point or subject; observed recenter and Face Select behavior are recorded.</x:v>
       </x:c>
       <x:c r="E34" s="15" t="str">
-        <x:v>Compare EFCS and Mechanical tripod sharpness at 1/8–1/60 sec.</x:v>
+        <x:v>Verify joystick movement and straight-press behavior.</x:v>
       </x:c>
       <x:c r="F34" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A34,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MM-SWITCH</x:v>
+        <x:f>IFERROR(VLOOKUP($A34,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Joystick</x:v>
       </x:c>
       <x:c r="G34" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A34,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Shooting 6</x:v>
+        <x:f>IFERROR(VLOOKUP($A34,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="H34" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A34,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shutter mode; use EFCS and Mechanical for the comparison</x:v>
+        <x:f>IFERROR(VLOOKUP($A34,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Customize buttons &gt; Multi-controller &gt; Direct AF point selection</x:v>
       </x:c>
       <x:c r="I34" s="13" t="str">
         <x:v>Not started</x:v>
@@ -3105,7 +3042,7 @@
       <x:c r="L34" s="15" t="str"/>
       <x:c r="M34" s="15" t="str"/>
       <x:c r="N34" s="15" t="str">
-        <x:v>Use a detailed static target, stabilization Off, and remote/timer release.</x:v>
+        <x:v>Record single-border, double-border, release, and Face Select Off behavior.</x:v>
       </x:c>
       <x:c r="O34" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -3114,7 +3051,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q34" s="15" t="str">
-        <x:v>00 Master/baseline.yaml; EFCS decision; R5 Quick Reference</x:v>
+        <x:v>controls.md; project memory; Back-Button AF guide</x:v>
       </x:c>
       <x:c r="R34" s="17" t="str">
         <x:v>No</x:v>
@@ -3122,7 +3059,7 @@
     </x:row>
     <x:row r="35" hidden="0">
       <x:c r="A35" s="17" t="str">
-        <x:v>EFCS-BOKEH-01</x:v>
+        <x:v>EFCS-SHOCK-01</x:v>
       </x:c>
       <x:c r="B35" s="17" t="n">
         <x:v>30</x:v>
@@ -3131,21 +3068,21 @@
         <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D35" s="15" t="str">
-        <x:v>Matched frames show whether EFCS clips out-of-focus highlights at fast shutter speeds.</x:v>
+        <x:v>At least five matched frames per shutter speed and mode are available for comparison.</x:v>
       </x:c>
       <x:c r="E35" s="15" t="str">
-        <x:v>Compare EFCS and Mechanical bokeh with the EF 50mm f/1.4 at 1/1000–1/8000 sec.</x:v>
+        <x:v>Compare EFCS and Mechanical tripod sharpness at 1/8–1/60 sec.</x:v>
       </x:c>
       <x:c r="F35" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A35,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A35,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
         <x:v>MM-SWITCH</x:v>
       </x:c>
       <x:c r="G35" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A35,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A35,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Shooting 6</x:v>
       </x:c>
       <x:c r="H35" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A35,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A35,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
         <x:v>Shutter mode; use EFCS and Mechanical for the comparison</x:v>
       </x:c>
       <x:c r="I35" s="13" t="str">
@@ -3156,7 +3093,7 @@
       <x:c r="L35" s="15" t="str"/>
       <x:c r="M35" s="15" t="str"/>
       <x:c r="N35" s="15" t="str">
-        <x:v>Use distinct point highlights and constant focus distance.</x:v>
+        <x:v>Use a detailed static target, stabilization Off, and remote/timer release.</x:v>
       </x:c>
       <x:c r="O35" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -3165,7 +3102,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q35" s="15" t="str">
-        <x:v>People profile; EFCS decision; R5 Quick Reference</x:v>
+        <x:v>00 Master/baseline.yaml; EFCS decision; R5 Quick Reference</x:v>
       </x:c>
       <x:c r="R35" s="17" t="str">
         <x:v>No</x:v>
@@ -3173,7 +3110,7 @@
     </x:row>
     <x:row r="36" hidden="0">
       <x:c r="A36" s="17" t="str">
-        <x:v>EFCS-LIGHT-01</x:v>
+        <x:v>EFCS-BOKEH-01</x:v>
       </x:c>
       <x:c r="B36" s="17" t="n">
         <x:v>31</x:v>
@@ -3182,22 +3119,22 @@
         <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D36" s="15" t="str">
-        <x:v>Exposure and color consistency are assessed at Sports shutter speeds with Anti-flicker Off and On.</x:v>
+        <x:v>Matched frames show whether EFCS clips out-of-focus highlights at fast shutter speeds.</x:v>
       </x:c>
       <x:c r="E36" s="15" t="str">
-        <x:v>Compare EFCS and Mechanical under representative LED or fluorescent lighting.</x:v>
+        <x:v>Compare EFCS and Mechanical bokeh with the EF 50mm f/1.4 at 1/1000–1/8000 sec.</x:v>
       </x:c>
       <x:c r="F36" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A36,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MM-SWITCH; MENU for Anti-flicker</x:v>
+        <x:f>IFERROR(VLOOKUP($A36,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MM-SWITCH</x:v>
       </x:c>
       <x:c r="G36" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A36,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Multiple</x:v>
+        <x:f>IFERROR(VLOOKUP($A36,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Shooting 6</x:v>
       </x:c>
       <x:c r="H36" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A36,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shooting 6: Shutter mode; Shooting 2: Anti-flicker shoot.</x:v>
+        <x:f>IFERROR(VLOOKUP($A36,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Shutter mode; use EFCS and Mechanical for the comparison</x:v>
       </x:c>
       <x:c r="I36" s="13" t="str">
         <x:v>Not started</x:v>
@@ -3207,7 +3144,7 @@
       <x:c r="L36" s="15" t="str"/>
       <x:c r="M36" s="15" t="str"/>
       <x:c r="N36" s="15" t="str">
-        <x:v>Use actual indoor Sports lighting when practical.</x:v>
+        <x:v>Use distinct point highlights and constant focus distance.</x:v>
       </x:c>
       <x:c r="O36" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -3216,7 +3153,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q36" s="15" t="str">
-        <x:v>Sports profile; EFCS decision; R5 Quick Reference</x:v>
+        <x:v>People profile; EFCS decision; R5 Quick Reference</x:v>
       </x:c>
       <x:c r="R36" s="17" t="str">
         <x:v>No</x:v>
@@ -3224,7 +3161,7 @@
     </x:row>
     <x:row r="37" hidden="0">
       <x:c r="A37" s="17" t="str">
-        <x:v>EFCS-BURST-01</x:v>
+        <x:v>EFCS-LIGHT-01</x:v>
       </x:c>
       <x:c r="B37" s="17" t="n">
         <x:v>32</x:v>
@@ -3233,22 +3170,22 @@
         <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D37" s="15" t="str">
-        <x:v>Burst cadence, tracking, and viewfinder behavior are recorded for EFCS and Mechanical.</x:v>
+        <x:v>Exposure and color consistency are assessed at Sports shutter speeds with Anti-flicker Off and On.</x:v>
       </x:c>
       <x:c r="E37" s="15" t="str">
-        <x:v>Compare High and High Speed Continuous+ burst behavior.</x:v>
+        <x:v>Compare EFCS and Mechanical under representative LED or fluorescent lighting.</x:v>
       </x:c>
       <x:c r="F37" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A37,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MM-SWITCH; Q for Drive mode</x:v>
+        <x:f>IFERROR(VLOOKUP($A37,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MM-SWITCH; MENU for Anti-flicker</x:v>
       </x:c>
       <x:c r="G37" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A37,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A37,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H37" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A37,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shooting 6: Shutter mode; AF menu/Quick Control: Drive mode</x:v>
+        <x:f>IFERROR(VLOOKUP($A37,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Shooting 6: Shutter mode; Shooting 2: Anti-flicker shoot.</x:v>
       </x:c>
       <x:c r="I37" s="13" t="str">
         <x:v>Not started</x:v>
@@ -3258,7 +3195,7 @@
       <x:c r="L37" s="15" t="str"/>
       <x:c r="M37" s="15" t="str"/>
       <x:c r="N37" s="15" t="str">
-        <x:v>Record battery, lens, shutter, aperture, card, and Anti-flicker state.</x:v>
+        <x:v>Use actual indoor Sports lighting when practical.</x:v>
       </x:c>
       <x:c r="O37" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -3267,7 +3204,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q37" s="15" t="str">
-        <x:v>EFCS decision; R5 Quick Reference</x:v>
+        <x:v>Sports profile; EFCS decision; R5 Quick Reference</x:v>
       </x:c>
       <x:c r="R37" s="17" t="str">
         <x:v>No</x:v>
@@ -3275,7 +3212,7 @@
     </x:row>
     <x:row r="38" hidden="0">
       <x:c r="A38" s="17" t="str">
-        <x:v>FLASH-PLUTO-01</x:v>
+        <x:v>EFCS-BURST-01</x:v>
       </x:c>
       <x:c r="B38" s="17" t="n">
         <x:v>33</x:v>
@@ -3284,22 +3221,22 @@
         <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D38" s="15" t="str">
-        <x:v>Trigger timing, sync, exposure consistency, flash duration, and recycle behavior pass.</x:v>
+        <x:v>Burst cadence, tracking, and viewfinder behavior are recorded for EFCS and Mechanical.</x:v>
       </x:c>
       <x:c r="E38" s="15" t="str">
-        <x:v>Verify the Mechanical 1/200-sec. Pluto/manual-flash Waterdrops setup.</x:v>
+        <x:v>Compare High and High Speed Continuous+ burst behavior.</x:v>
       </x:c>
       <x:c r="F38" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A38,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MM-SWITCH; shooting controls</x:v>
+        <x:f>IFERROR(VLOOKUP($A38,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MM-SWITCH; Q for Drive mode</x:v>
       </x:c>
       <x:c r="G38" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A38,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A38,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H38" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A38,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Shooting 6: Shutter mode &gt; Mechanical; shooting screen: M, 1/200 sec., aperture, ISO; Shooting 2: External Speedlite control when applicable</x:v>
+        <x:f>IFERROR(VLOOKUP($A38,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Shooting 6: Shutter mode; AF menu/Quick Control: Drive mode</x:v>
       </x:c>
       <x:c r="I38" s="13" t="str">
         <x:v>Not started</x:v>
@@ -3309,7 +3246,7 @@
       <x:c r="L38" s="15" t="str"/>
       <x:c r="M38" s="15" t="str"/>
       <x:c r="N38" s="15" t="str">
-        <x:v>Start at manual flash 1/16–1/64 and record the complete setup.</x:v>
+        <x:v>Record battery, lens, shutter, aperture, card, and Anti-flicker state.</x:v>
       </x:c>
       <x:c r="O38" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -3318,7 +3255,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q38" s="15" t="str">
-        <x:v>Waterdrops profile; Flash Photography; EFCS decision</x:v>
+        <x:v>EFCS decision; R5 Quick Reference</x:v>
       </x:c>
       <x:c r="R38" s="17" t="str">
         <x:v>No</x:v>
@@ -3326,31 +3263,31 @@
     </x:row>
     <x:row r="39" hidden="0">
       <x:c r="A39" s="17" t="str">
-        <x:v>FINAL-READ-01</x:v>
+        <x:v>FLASH-PLUTO-01</x:v>
       </x:c>
       <x:c r="B39" s="17" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C39" s="22" t="str">
-        <x:v>Finalization</x:v>
+        <x:v>EFCS Tests</x:v>
       </x:c>
       <x:c r="D39" s="15" t="str">
-        <x:v>All three custom modes, My Menu, and shared controls remain correct; Auto update remains disabled.</x:v>
+        <x:v>Trigger timing, sync, exposure consistency, flash duration, and recycle behavior pass.</x:v>
       </x:c>
       <x:c r="E39" s="15" t="str">
-        <x:v>Recall C1, C2, and C3 and complete a final read-back.</x:v>
+        <x:v>Verify the Mechanical 1/200-sec. Pluto/manual-flash Waterdrops setup.</x:v>
       </x:c>
       <x:c r="F39" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A39,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>M-Fn; MM-SWITCH; Q; MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A39,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MM-SWITCH; shooting controls</x:v>
       </x:c>
       <x:c r="G39" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A39,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
+        <x:f>IFERROR(VLOOKUP($A39,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H39" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A39,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Recall C1-C3 with M-Fn; verify SWITCH; Set-up 5 confirm Auto update is disabled; Custom Functions 3 confirm control assignments</x:v>
+        <x:f>IFERROR(VLOOKUP($A39,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Shooting 6: Shutter mode &gt; Mechanical; shooting screen: M, 1/200 sec., aperture, ISO; Shooting 2: External Speedlite control when applicable</x:v>
       </x:c>
       <x:c r="I39" s="13" t="str">
         <x:v>Not started</x:v>
@@ -3360,7 +3297,7 @@
       <x:c r="L39" s="15" t="str"/>
       <x:c r="M39" s="15" t="str"/>
       <x:c r="N39" s="15" t="str">
-        <x:v>Resolve every discrepancy before saving the final configuration.</x:v>
+        <x:v>Start at manual flash 1/16–1/64 and record the complete setup.</x:v>
       </x:c>
       <x:c r="O39" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
@@ -3369,7 +3306,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="Q39" s="15" t="str">
-        <x:v>controls.md; project memory</x:v>
+        <x:v>Waterdrops profile; Flash Photography; EFCS decision</x:v>
       </x:c>
       <x:c r="R39" s="17" t="str">
         <x:v>No</x:v>
@@ -3377,7 +3314,7 @@
     </x:row>
     <x:row r="40" hidden="0">
       <x:c r="A40" s="17" t="str">
-        <x:v>FINAL-SAVE-01</x:v>
+        <x:v>FINAL-READ-01</x:v>
       </x:c>
       <x:c r="B40" s="17" t="n">
         <x:v>35</x:v>
@@ -3386,22 +3323,22 @@
         <x:v>Finalization</x:v>
       </x:c>
       <x:c r="D40" s="15" t="str">
-        <x:v>A named post-verification settings file exists and is recorded in the Sessions sheet.</x:v>
+        <x:v>All three custom modes, both approved My Menu tabs, and shared controls remain correct; Auto update remains disabled.</x:v>
       </x:c>
       <x:c r="E40" s="15" t="str">
-        <x:v>Save the verified complete camera configuration to the card.</x:v>
+        <x:v>Recall C1, C2, and C3 and complete a final read-back.</x:v>
       </x:c>
       <x:c r="F40" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A40,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>MENU</x:v>
+        <x:f>IFERROR(VLOOKUP($A40,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>M-Fn; MM-SWITCH; MM-AF Case; Q; MENU</x:v>
       </x:c>
       <x:c r="G40" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A40,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>Set-up 5</x:v>
+        <x:f>IFERROR(VLOOKUP($A40,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="H40" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A40,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
+        <x:f>IFERROR(VLOOKUP($A40,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Recall C1-C3 with M-Fn; verify SWITCH and AF Case; Set-up 5 confirm Auto update is disabled; Custom Functions 3 confirm control assignments</x:v>
       </x:c>
       <x:c r="I40" s="13" t="str">
         <x:v>Not started</x:v>
@@ -3411,72 +3348,123 @@
       <x:c r="L40" s="15" t="str"/>
       <x:c r="M40" s="15" t="str"/>
       <x:c r="N40" s="15" t="str">
-        <x:v>Preserve the completed workbook and test images.</x:v>
+        <x:v>Resolve every discrepancy before saving the final configuration.</x:v>
       </x:c>
       <x:c r="O40" s="15" t="str">
         <x:v>Approved target pending verification</x:v>
       </x:c>
       <x:c r="P40" s="17" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Q40" s="15" t="str">
+        <x:v>controls.md; project memory</x:v>
+      </x:c>
+      <x:c r="R40" s="17" t="str">
         <x:v>No</x:v>
-      </x:c>
-      <x:c r="Q40" s="15" t="str"/>
-      <x:c r="R40" s="17" t="str">
-        <x:v>Not applicable</x:v>
       </x:c>
     </x:row>
     <x:row r="41" hidden="0">
       <x:c r="A41" s="17" t="str">
-        <x:v>PROJECT-UPDATE-01</x:v>
+        <x:v>FINAL-SAVE-01</x:v>
       </x:c>
       <x:c r="B41" s="17" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="C41" s="22" t="str">
-        <x:v>Project Update</x:v>
+        <x:v>Finalization</x:v>
       </x:c>
       <x:c r="D41" s="15" t="str">
-        <x:v>Only completed, unambiguous evidence is promoted to owner-confirmed status.</x:v>
+        <x:v>A named post-verification settings file exists and is recorded in the Sessions sheet.</x:v>
       </x:c>
       <x:c r="E41" s="15" t="str">
-        <x:v>Review Verified rows that require a project update.</x:v>
+        <x:v>Save the verified complete camera configuration to the card.</x:v>
       </x:c>
       <x:c r="F41" s="13" t="str">
-        <x:f>IFERROR(VLOOKUP($A41,'Menu'!$A$2:$E$37,2,FALSE),"")</x:f>
-        <x:v>Completed tracker</x:v>
+        <x:f>IFERROR(VLOOKUP($A41,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="G41" s="29" t="str">
-        <x:f>IFERROR(VLOOKUP($A41,'Menu'!$A$2:$E$37,3,FALSE),"")</x:f>
-        <x:v>No camera menu</x:v>
+        <x:f>IFERROR(VLOOKUP($A41,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="H41" s="15" t="str">
-        <x:f>IFERROR(VLOOKUP($A41,'Menu'!$A$2:$E$37,4,FALSE),"")</x:f>
-        <x:v>Review the completed tracker and update the reference-system evidence states</x:v>
+        <x:f>IFERROR(VLOOKUP($A41,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
       </x:c>
       <x:c r="I41" s="13" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J41" s="30" t="str"/>
       <x:c r="K41" s="17" t="str"/>
       <x:c r="L41" s="15" t="str"/>
       <x:c r="M41" s="15" t="str"/>
       <x:c r="N41" s="15" t="str">
+        <x:v>Preserve the completed workbook and test images.</x:v>
+      </x:c>
+      <x:c r="O41" s="15" t="str">
+        <x:v>Approved target pending verification</x:v>
+      </x:c>
+      <x:c r="P41" s="17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="Q41" s="15" t="str"/>
+      <x:c r="R41" s="17" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" hidden="0">
+      <x:c r="A42" s="17" t="str">
+        <x:v>PROJECT-UPDATE-01</x:v>
+      </x:c>
+      <x:c r="B42" s="17" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C42" s="22" t="str">
+        <x:v>Project Update</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="str">
+        <x:v>Only completed, unambiguous evidence is promoted to owner-confirmed status.</x:v>
+      </x:c>
+      <x:c r="E42" s="15" t="str">
+        <x:v>Review Verified rows that require a project update.</x:v>
+      </x:c>
+      <x:c r="F42" s="13" t="str">
+        <x:f>IFERROR(VLOOKUP($A42,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
+        <x:v>Completed tracker</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="str">
+        <x:f>IFERROR(VLOOKUP($A42,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
+        <x:v>No camera menu</x:v>
+      </x:c>
+      <x:c r="H42" s="15" t="str">
+        <x:f>IFERROR(VLOOKUP($A42,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
+        <x:v>Review the completed tracker and update the reference-system evidence states</x:v>
+      </x:c>
+      <x:c r="I42" s="13" t="str">
+        <x:v>Blocked</x:v>
+      </x:c>
+      <x:c r="J42" s="30" t="str"/>
+      <x:c r="K42" s="17" t="str"/>
+      <x:c r="L42" s="15" t="str"/>
+      <x:c r="M42" s="15" t="str"/>
+      <x:c r="N42" s="15" t="str">
         <x:v>Complete physical testing before updating project evidence states.</x:v>
       </x:c>
-      <x:c r="O41" s="15" t="str">
+      <x:c r="O42" s="15" t="str">
         <x:v>Unresolved</x:v>
       </x:c>
-      <x:c r="P41" s="17" t="str">
+      <x:c r="P42" s="17" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q41" s="15" t="str">
+      <x:c r="Q42" s="15" t="str">
         <x:v>TODO; controls.md; project memory; applicable profiles and guides</x:v>
       </x:c>
-      <x:c r="R41" s="17" t="str">
+      <x:c r="R42" s="17" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="I6:I41">
+  <x:conditionalFormatting sqref="I6:I42">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Backup-Settings"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Verified"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="In progress"/>
@@ -3484,23 +3472,23 @@
     <x:cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Failed"/>
   </x:conditionalFormatting>
   <x:dataValidations count="4">
-    <x:dataValidation type="list" sqref="I6:I41">
+    <x:dataValidation type="list" sqref="I6:I42">
       <x:formula1>"Not started,In progress,Configured—not registered,Registered—pending read-back,Backup-Settings,Verified,Failed—needs correction,Inconclusive—needs retest,Blocked,Not applicable"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="O6:O41">
+    <x:dataValidation type="list" sqref="O6:O42">
       <x:formula1>"Approved target pending verification,Owner-confirmed current configuration,Verified Canon capability,Project recommendation,Unresolved"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="P6:P41">
+    <x:dataValidation type="list" sqref="P6:P42">
       <x:formula1>"Yes,No,Not applicable"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="R6:R41">
+    <x:dataValidation type="list" sqref="R6:R42">
       <x:formula1>"Yes,No,Not applicable"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rc6659296c774453e"/>
+  <x:drawing ns1:id="Rb374eecfc9f84421"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R07faa2ff69f14cfa"/>
+    <x:tablePart ns1:id="Raa392843d73441f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3530,87 +3518,87 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="53" t="str">
+      <x:c r="A1" s="48" t="str">
         <x:v>C1–C3 Registration: Configure → Register → Read Back → Verify</x:v>
       </x:c>
-      <x:c r="B1" s="53"/>
-      <x:c r="C1" s="61"/>
-      <x:c r="D1" s="62"/>
-      <x:c r="E1" s="62"/>
-      <x:c r="F1" s="63"/>
-      <x:c r="G1" s="61"/>
-      <x:c r="H1" s="62"/>
-      <x:c r="I1" s="62"/>
-      <x:c r="J1" s="63"/>
-      <x:c r="K1" s="61"/>
-      <x:c r="L1" s="62"/>
-      <x:c r="M1" s="62"/>
-      <x:c r="N1" s="63"/>
-      <x:c r="O1" s="52"/>
-      <x:c r="P1" s="52"/>
-      <x:c r="Q1" s="52"/>
-      <x:c r="R1" s="52"/>
+      <x:c r="B1" s="48"/>
+      <x:c r="C1" s="56"/>
+      <x:c r="D1" s="57"/>
+      <x:c r="E1" s="57"/>
+      <x:c r="F1" s="58"/>
+      <x:c r="G1" s="56"/>
+      <x:c r="H1" s="57"/>
+      <x:c r="I1" s="57"/>
+      <x:c r="J1" s="58"/>
+      <x:c r="K1" s="56"/>
+      <x:c r="L1" s="57"/>
+      <x:c r="M1" s="57"/>
+      <x:c r="N1" s="58"/>
+      <x:c r="O1" s="47"/>
+      <x:c r="P1" s="47"/>
+      <x:c r="Q1" s="47"/>
+      <x:c r="R1" s="47"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="54" t="str">
+      <x:c r="A2" s="49" t="str">
         <x:v>Work from a normal shooting mode. Validate the complete column before registering a slot. Record configuration and read-back separately for every setting.</x:v>
       </x:c>
-      <x:c r="B2" s="54"/>
-      <x:c r="C2" s="64"/>
+      <x:c r="B2" s="49"/>
+      <x:c r="C2" s="59"/>
       <x:c r="D2" s="38"/>
       <x:c r="E2" s="38"/>
-      <x:c r="F2" s="65"/>
-      <x:c r="G2" s="64"/>
+      <x:c r="F2" s="60"/>
+      <x:c r="G2" s="59"/>
       <x:c r="H2" s="38"/>
       <x:c r="I2" s="38"/>
-      <x:c r="J2" s="65"/>
-      <x:c r="K2" s="64"/>
+      <x:c r="J2" s="60"/>
+      <x:c r="K2" s="59"/>
       <x:c r="L2" s="38"/>
       <x:c r="M2" s="38"/>
-      <x:c r="N2" s="65"/>
-      <x:c r="O2" s="52"/>
-      <x:c r="P2" s="52"/>
-      <x:c r="Q2" s="52"/>
-      <x:c r="R2" s="52"/>
+      <x:c r="N2" s="60"/>
+      <x:c r="O2" s="47"/>
+      <x:c r="P2" s="47"/>
+      <x:c r="Q2" s="47"/>
+      <x:c r="R2" s="47"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="55" t="str">
+      <x:c r="A3" s="50" t="str">
         <x:v>Compare to:</x:v>
       </x:c>
-      <x:c r="B3" s="55" t="str">
+      <x:c r="B3" s="50" t="str">
         <x:v>Default Settings</x:v>
       </x:c>
-      <x:c r="C3" s="66" t="str">
+      <x:c r="C3" s="61" t="str">
         <x:v>Default Settings</x:v>
       </x:c>
       <x:c r="D3" s="6"/>
       <x:c r="E3" s="6"/>
-      <x:c r="F3" s="67"/>
-      <x:c r="G3" s="66" t="str">
+      <x:c r="F3" s="62"/>
+      <x:c r="G3" s="61" t="str">
         <x:v>Default Settings</x:v>
       </x:c>
       <x:c r="H3" s="6"/>
       <x:c r="I3" s="6"/>
-      <x:c r="J3" s="67"/>
-      <x:c r="K3" s="66" t="str">
+      <x:c r="J3" s="62"/>
+      <x:c r="K3" s="61" t="str">
         <x:v>Default Settings</x:v>
       </x:c>
       <x:c r="L3" s="6"/>
       <x:c r="M3" s="6"/>
-      <x:c r="N3" s="67"/>
-      <x:c r="O3" s="52"/>
-      <x:c r="P3" s="52"/>
-      <x:c r="Q3" s="52"/>
-      <x:c r="R3" s="52"/>
+      <x:c r="N3" s="62"/>
+      <x:c r="O3" s="47"/>
+      <x:c r="P3" s="47"/>
+      <x:c r="Q3" s="47"/>
+      <x:c r="R3" s="47"/>
     </x:row>
     <x:row r="4" hidden="0">
-      <x:c r="A4" s="56" t="str">
+      <x:c r="A4" s="51" t="str">
         <x:v>Setting</x:v>
       </x:c>
-      <x:c r="B4" s="56" t="str">
+      <x:c r="B4" s="51" t="str">
         <x:v>Default Settings</x:v>
       </x:c>
-      <x:c r="C4" s="68" t="str">
+      <x:c r="C4" s="63" t="str">
         <x:v>C1 Wildlife Target</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
@@ -3619,10 +3607,10 @@
       <x:c r="E4" s="5" t="str">
         <x:v>C1 Read-back</x:v>
       </x:c>
-      <x:c r="F4" s="69" t="str">
+      <x:c r="F4" s="64" t="str">
         <x:v>C1 Notes</x:v>
       </x:c>
-      <x:c r="G4" s="68" t="str">
+      <x:c r="G4" s="63" t="str">
         <x:v>C2 Birds in Flight Target</x:v>
       </x:c>
       <x:c r="H4" s="5" t="str">
@@ -3631,10 +3619,10 @@
       <x:c r="I4" s="5" t="str">
         <x:v>C2 Read-back</x:v>
       </x:c>
-      <x:c r="J4" s="69" t="str">
+      <x:c r="J4" s="64" t="str">
         <x:v>C2 Notes</x:v>
       </x:c>
-      <x:c r="K4" s="68" t="str">
+      <x:c r="K4" s="63" t="str">
         <x:v>C3 Landscape Target</x:v>
       </x:c>
       <x:c r="L4" s="5" t="str">
@@ -3643,929 +3631,983 @@
       <x:c r="M4" s="5" t="str">
         <x:v>C3 Read-back</x:v>
       </x:c>
-      <x:c r="N4" s="69" t="str">
+      <x:c r="N4" s="64" t="str">
         <x:v>C3 Notes</x:v>
       </x:c>
-      <x:c r="O4" s="52"/>
-      <x:c r="P4" s="52"/>
-      <x:c r="Q4" s="52"/>
-      <x:c r="R4" s="52"/>
+      <x:c r="O4" s="47"/>
+      <x:c r="P4" s="47"/>
+      <x:c r="Q4" s="47"/>
+      <x:c r="R4" s="47"/>
     </x:row>
     <x:row r="5" hidden="0">
-      <x:c r="A5" s="57" t="str">
+      <x:c r="A5" s="52" t="str">
         <x:v>Mode</x:v>
       </x:c>
-      <x:c r="B5" s="59" t="str">
+      <x:c r="B5" s="54" t="str">
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="C5" s="70" t="str">
+      <x:c r="C5" s="65" t="str">
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="D5" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E5" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F5" s="71" t="str"/>
-      <x:c r="G5" s="70" t="str">
+      <x:c r="D5" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E5" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F5" s="66" t="str"/>
+      <x:c r="G5" s="65" t="str">
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="H5" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I5" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J5" s="71" t="str"/>
-      <x:c r="K5" s="70" t="str">
+      <x:c r="H5" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I5" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J5" s="66" t="str"/>
+      <x:c r="K5" s="65" t="str">
         <x:v>Av</x:v>
       </x:c>
-      <x:c r="L5" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M5" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N5" s="71" t="str"/>
-      <x:c r="O5" s="52" t="str">
+      <x:c r="L5" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M5" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N5" s="66" t="str"/>
+      <x:c r="O5" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B5,IF($B$3="C1 Wildlife",C5,IF($B$3="C2 Birds in Flight",G5,IF($B$3="C3 Landscape",K5,""))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="P5" s="52" t="str">
+      <x:c r="P5" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B5,IF($C$3="C1 Wildlife",C5,IF($C$3="C2 Birds in Flight",G5,IF($C$3="C3 Landscape",K5,""))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="Q5" s="52" t="str">
+      <x:c r="Q5" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B5,IF($G$3="C1 Wildlife",C5,IF($G$3="C2 Birds in Flight",G5,IF($G$3="C3 Landscape",K5,""))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="R5" s="52" t="str">
+      <x:c r="R5" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B5,IF($K$3="C1 Wildlife",C5,IF($K$3="C2 Birds in Flight",G5,IF($K$3="C3 Landscape",K5,""))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
     </x:row>
     <x:row r="6" hidden="0">
-      <x:c r="A6" s="57" t="str">
+      <x:c r="A6" s="52" t="str">
         <x:v>Metering</x:v>
       </x:c>
-      <x:c r="B6" s="59" t="str">
+      <x:c r="B6" s="54" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="C6" s="70" t="str">
+      <x:c r="C6" s="65" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="D6" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E6" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F6" s="71" t="str"/>
-      <x:c r="G6" s="70" t="str">
+      <x:c r="D6" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E6" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F6" s="66" t="str"/>
+      <x:c r="G6" s="65" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="H6" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I6" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J6" s="71" t="str"/>
-      <x:c r="K6" s="70" t="str">
+      <x:c r="H6" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I6" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J6" s="66" t="str"/>
+      <x:c r="K6" s="65" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="L6" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M6" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N6" s="71" t="str"/>
-      <x:c r="O6" s="52" t="str">
+      <x:c r="L6" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M6" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N6" s="66" t="str"/>
+      <x:c r="O6" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B6,IF($B$3="C1 Wildlife",C6,IF($B$3="C2 Birds in Flight",G6,IF($B$3="C3 Landscape",K6,""))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="P6" s="52" t="str">
+      <x:c r="P6" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B6,IF($C$3="C1 Wildlife",C6,IF($C$3="C2 Birds in Flight",G6,IF($C$3="C3 Landscape",K6,""))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="Q6" s="52" t="str">
+      <x:c r="Q6" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B6,IF($G$3="C1 Wildlife",C6,IF($G$3="C2 Birds in Flight",G6,IF($G$3="C3 Landscape",K6,""))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="R6" s="52" t="str">
+      <x:c r="R6" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B6,IF($K$3="C1 Wildlife",C6,IF($K$3="C2 Birds in Flight",G6,IF($K$3="C3 Landscape",K6,""))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
     </x:row>
     <x:row r="7" hidden="0">
-      <x:c r="A7" s="57" t="str">
+      <x:c r="A7" s="52" t="str">
         <x:v>Exposure Compensation</x:v>
       </x:c>
-      <x:c r="B7" s="59" t="str">
+      <x:c r="B7" s="54" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C7" s="70" t="str">
+      <x:c r="C7" s="65" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E7" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F7" s="71" t="str"/>
-      <x:c r="G7" s="70" t="str">
+      <x:c r="D7" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E7" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F7" s="66" t="str"/>
+      <x:c r="G7" s="65" t="str">
         <x:v>0 starting point</x:v>
       </x:c>
-      <x:c r="H7" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I7" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J7" s="71" t="str"/>
-      <x:c r="K7" s="70" t="str">
+      <x:c r="H7" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I7" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J7" s="66" t="str"/>
+      <x:c r="K7" s="65" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L7" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M7" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N7" s="71" t="str"/>
-      <x:c r="O7" s="52" t="str">
+      <x:c r="L7" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M7" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N7" s="66" t="str"/>
+      <x:c r="O7" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B7,IF($B$3="C1 Wildlife",C7,IF($B$3="C2 Birds in Flight",G7,IF($B$3="C3 Landscape",K7,""))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P7" s="52" t="str">
+      <x:c r="P7" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B7,IF($C$3="C1 Wildlife",C7,IF($C$3="C2 Birds in Flight",G7,IF($C$3="C3 Landscape",K7,""))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q7" s="52" t="str">
+      <x:c r="Q7" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B7,IF($G$3="C1 Wildlife",C7,IF($G$3="C2 Birds in Flight",G7,IF($G$3="C3 Landscape",K7,""))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R7" s="52" t="str">
+      <x:c r="R7" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B7,IF($K$3="C1 Wildlife",C7,IF($K$3="C2 Birds in Flight",G7,IF($K$3="C3 Landscape",K7,""))))</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" hidden="0">
-      <x:c r="A8" s="57" t="str">
+      <x:c r="A8" s="52" t="str">
         <x:v>Shutter Speed</x:v>
       </x:c>
-      <x:c r="B8" s="59" t="str">
+      <x:c r="B8" s="54" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="C8" s="70" t="str">
+      <x:c r="C8" s="65" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="D8" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E8" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F8" s="71" t="str"/>
-      <x:c r="G8" s="70" t="str">
+      <x:c r="D8" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E8" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F8" s="66" t="str"/>
+      <x:c r="G8" s="65" t="str">
         <x:v>1/2500 sec.</x:v>
       </x:c>
-      <x:c r="H8" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I8" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J8" s="71" t="str"/>
-      <x:c r="K8" s="70" t="str">
+      <x:c r="H8" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I8" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J8" s="66" t="str"/>
+      <x:c r="K8" s="65" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="L8" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M8" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N8" s="71" t="str"/>
-      <x:c r="O8" s="52" t="str">
+      <x:c r="L8" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M8" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N8" s="66" t="str"/>
+      <x:c r="O8" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B8,IF($B$3="C1 Wildlife",C8,IF($B$3="C2 Birds in Flight",G8,IF($B$3="C3 Landscape",K8,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="P8" s="52" t="str">
+      <x:c r="P8" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B8,IF($C$3="C1 Wildlife",C8,IF($C$3="C2 Birds in Flight",G8,IF($C$3="C3 Landscape",K8,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="Q8" s="52" t="str">
+      <x:c r="Q8" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B8,IF($G$3="C1 Wildlife",C8,IF($G$3="C2 Birds in Flight",G8,IF($G$3="C3 Landscape",K8,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="R8" s="52" t="str">
+      <x:c r="R8" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B8,IF($K$3="C1 Wildlife",C8,IF($K$3="C2 Birds in Flight",G8,IF($K$3="C3 Landscape",K8,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
     </x:row>
     <x:row r="9" hidden="0">
-      <x:c r="A9" s="57" t="str">
+      <x:c r="A9" s="52" t="str">
         <x:v>Aperture</x:v>
       </x:c>
-      <x:c r="B9" s="59" t="str">
+      <x:c r="B9" s="54" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="C9" s="70" t="str">
+      <x:c r="C9" s="65" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="D9" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E9" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F9" s="71" t="str"/>
-      <x:c r="G9" s="70" t="str">
+      <x:c r="D9" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E9" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F9" s="66" t="str"/>
+      <x:c r="G9" s="65" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="H9" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I9" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J9" s="71" t="str"/>
-      <x:c r="K9" s="70" t="str">
+      <x:c r="H9" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I9" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J9" s="66" t="str"/>
+      <x:c r="K9" s="65" t="str">
         <x:v>f/9</x:v>
       </x:c>
-      <x:c r="L9" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M9" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N9" s="71" t="str"/>
-      <x:c r="O9" s="52" t="str">
+      <x:c r="L9" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M9" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N9" s="66" t="str"/>
+      <x:c r="O9" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B9,IF($B$3="C1 Wildlife",C9,IF($B$3="C2 Birds in Flight",G9,IF($B$3="C3 Landscape",K9,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="P9" s="52" t="str">
+      <x:c r="P9" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B9,IF($C$3="C1 Wildlife",C9,IF($C$3="C2 Birds in Flight",G9,IF($C$3="C3 Landscape",K9,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="Q9" s="52" t="str">
+      <x:c r="Q9" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B9,IF($G$3="C1 Wildlife",C9,IF($G$3="C2 Birds in Flight",G9,IF($G$3="C3 Landscape",K9,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="R9" s="52" t="str">
+      <x:c r="R9" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B9,IF($K$3="C1 Wildlife",C9,IF($K$3="C2 Birds in Flight",G9,IF($K$3="C3 Landscape",K9,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
     </x:row>
     <x:row r="10" hidden="0">
-      <x:c r="A10" s="57" t="str">
+      <x:c r="A10" s="52" t="str">
         <x:v>ISO</x:v>
       </x:c>
-      <x:c r="B10" s="59" t="str">
+      <x:c r="B10" s="54" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="C10" s="70" t="str">
+      <x:c r="C10" s="65" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="D10" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E10" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F10" s="71" t="str"/>
-      <x:c r="G10" s="70" t="str">
+      <x:c r="D10" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E10" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F10" s="66" t="str"/>
+      <x:c r="G10" s="65" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="H10" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I10" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J10" s="71" t="str"/>
-      <x:c r="K10" s="70" t="str">
+      <x:c r="H10" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I10" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J10" s="66" t="str"/>
+      <x:c r="K10" s="65" t="str">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="L10" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M10" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N10" s="71" t="str"/>
-      <x:c r="O10" s="52" t="str">
+      <x:c r="L10" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M10" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N10" s="66" t="str"/>
+      <x:c r="O10" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B10,IF($B$3="C1 Wildlife",C10,IF($B$3="C2 Birds in Flight",G10,IF($B$3="C3 Landscape",K10,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="P10" s="52" t="str">
+      <x:c r="P10" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B10,IF($C$3="C1 Wildlife",C10,IF($C$3="C2 Birds in Flight",G10,IF($C$3="C3 Landscape",K10,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="Q10" s="52" t="str">
+      <x:c r="Q10" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B10,IF($G$3="C1 Wildlife",C10,IF($G$3="C2 Birds in Flight",G10,IF($G$3="C3 Landscape",K10,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="R10" s="52" t="str">
+      <x:c r="R10" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B10,IF($K$3="C1 Wildlife",C10,IF($K$3="C2 Birds in Flight",G10,IF($K$3="C3 Landscape",K10,""))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
     </x:row>
     <x:row r="11" hidden="0">
-      <x:c r="A11" s="57" t="str">
+      <x:c r="A11" s="52" t="str">
         <x:v>Auto ISO Maximum</x:v>
       </x:c>
-      <x:c r="B11" s="59" t="str">
+      <x:c r="B11" s="54" t="str">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="C11" s="70" t="str">
+      <x:c r="C11" s="65" t="str">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="D11" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E11" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F11" s="71" t="str"/>
-      <x:c r="G11" s="70" t="str">
+      <x:c r="D11" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E11" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F11" s="66" t="str"/>
+      <x:c r="G11" s="65" t="str">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="H11" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I11" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J11" s="71" t="str"/>
-      <x:c r="K11" s="70" t="str">
-        <x:v>12800; inactive at ISO 100</x:v>
-      </x:c>
-      <x:c r="L11" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M11" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N11" s="71" t="str"/>
-      <x:c r="O11" s="52" t="str">
+      <x:c r="H11" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I11" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J11" s="66" t="str"/>
+      <x:c r="K11" s="65" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="L11" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M11" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N11" s="66" t="str"/>
+      <x:c r="O11" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B11,IF($B$3="C1 Wildlife",C11,IF($B$3="C2 Birds in Flight",G11,IF($B$3="C3 Landscape",K11,""))))</x:f>
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="P11" s="52" t="str">
+      <x:c r="P11" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B11,IF($C$3="C1 Wildlife",C11,IF($C$3="C2 Birds in Flight",G11,IF($C$3="C3 Landscape",K11,""))))</x:f>
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="Q11" s="52" t="str">
+      <x:c r="Q11" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B11,IF($G$3="C1 Wildlife",C11,IF($G$3="C2 Birds in Flight",G11,IF($G$3="C3 Landscape",K11,""))))</x:f>
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="R11" s="52" t="str">
+      <x:c r="R11" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B11,IF($K$3="C1 Wildlife",C11,IF($K$3="C2 Birds in Flight",G11,IF($K$3="C3 Landscape",K11,""))))</x:f>
         <x:v>12800</x:v>
       </x:c>
     </x:row>
     <x:row r="12" hidden="0">
-      <x:c r="A12" s="57" t="str">
+      <x:c r="A12" s="52" t="str">
         <x:v>AF Operation</x:v>
       </x:c>
-      <x:c r="B12" s="59" t="str">
+      <x:c r="B12" s="54" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="C12" s="70" t="str">
+      <x:c r="C12" s="65" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="D12" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E12" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F12" s="71" t="str"/>
-      <x:c r="G12" s="70" t="str">
+      <x:c r="D12" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E12" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F12" s="66" t="str"/>
+      <x:c r="G12" s="65" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="H12" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I12" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J12" s="71" t="str"/>
-      <x:c r="K12" s="70" t="str">
+      <x:c r="H12" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I12" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J12" s="66" t="str"/>
+      <x:c r="K12" s="65" t="str">
         <x:v>One-Shot AF</x:v>
       </x:c>
-      <x:c r="L12" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M12" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N12" s="71" t="str"/>
-      <x:c r="O12" s="52" t="str">
+      <x:c r="L12" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M12" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N12" s="66" t="str"/>
+      <x:c r="O12" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B12,IF($B$3="C1 Wildlife",C12,IF($B$3="C2 Birds in Flight",G12,IF($B$3="C3 Landscape",K12,""))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="P12" s="52" t="str">
+      <x:c r="P12" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B12,IF($C$3="C1 Wildlife",C12,IF($C$3="C2 Birds in Flight",G12,IF($C$3="C3 Landscape",K12,""))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="Q12" s="52" t="str">
+      <x:c r="Q12" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B12,IF($G$3="C1 Wildlife",C12,IF($G$3="C2 Birds in Flight",G12,IF($G$3="C3 Landscape",K12,""))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="R12" s="52" t="str">
+      <x:c r="R12" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B12,IF($K$3="C1 Wildlife",C12,IF($K$3="C2 Birds in Flight",G12,IF($K$3="C3 Landscape",K12,""))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
     </x:row>
     <x:row r="13" hidden="0">
-      <x:c r="A13" s="57" t="str">
+      <x:c r="A13" s="52" t="str">
+        <x:v>Servo AF Case</x:v>
+      </x:c>
+      <x:c r="B13" s="54" t="str">
+        <x:v>Case A (Auto)</x:v>
+      </x:c>
+      <x:c r="C13" s="65" t="str">
+        <x:v>Case A (Auto)</x:v>
+      </x:c>
+      <x:c r="D13" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E13" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F13" s="66" t="str"/>
+      <x:c r="G13" s="65" t="str">
+        <x:v>Case 4</x:v>
+      </x:c>
+      <x:c r="H13" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I13" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J13" s="66" t="str"/>
+      <x:c r="K13" s="65" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="L13" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M13" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N13" s="66" t="str"/>
+      <x:c r="O13" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B13,IF($B$3="C1 Wildlife",C13,IF($B$3="C2 Birds in Flight",G13,IF($B$3="C3 Landscape",K13,""))))</x:f>
+        <x:v>Case A (Auto)</x:v>
+      </x:c>
+      <x:c r="P13" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B13,IF($C$3="C1 Wildlife",C13,IF($C$3="C2 Birds in Flight",G13,IF($C$3="C3 Landscape",K13,""))))</x:f>
+        <x:v>Case A (Auto)</x:v>
+      </x:c>
+      <x:c r="Q13" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B13,IF($G$3="C1 Wildlife",C13,IF($G$3="C2 Birds in Flight",G13,IF($G$3="C3 Landscape",K13,""))))</x:f>
+        <x:v>Case A (Auto)</x:v>
+      </x:c>
+      <x:c r="R13" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B13,IF($K$3="C1 Wildlife",C13,IF($K$3="C2 Birds in Flight",G13,IF($K$3="C3 Landscape",K13,""))))</x:f>
+        <x:v>Case A (Auto)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" hidden="0">
+      <x:c r="A14" s="52" t="str">
         <x:v>AF Method</x:v>
       </x:c>
-      <x:c r="B13" s="59" t="str">
+      <x:c r="B14" s="54" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="C13" s="70" t="str">
+      <x:c r="C14" s="65" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="D13" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E13" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F13" s="71" t="str"/>
-      <x:c r="G13" s="70" t="str">
+      <x:c r="D14" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E14" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F14" s="66" t="str"/>
+      <x:c r="G14" s="65" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="H13" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I13" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J13" s="71" t="str"/>
-      <x:c r="K13" s="70" t="str">
+      <x:c r="H14" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I14" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J14" s="66" t="str"/>
+      <x:c r="K14" s="65" t="str">
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="L13" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M13" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N13" s="71" t="str"/>
-      <x:c r="O13" s="52" t="str">
-        <x:f>IF($B$3="Default Settings",B13,IF($B$3="C1 Wildlife",C13,IF($B$3="C2 Birds in Flight",G13,IF($B$3="C3 Landscape",K13,""))))</x:f>
+      <x:c r="L14" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M14" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N14" s="66" t="str"/>
+      <x:c r="O14" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B14,IF($B$3="C1 Wildlife",C14,IF($B$3="C2 Birds in Flight",G14,IF($B$3="C3 Landscape",K14,""))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="P13" s="52" t="str">
-        <x:f>IF($C$3="Default Settings",B13,IF($C$3="C1 Wildlife",C13,IF($C$3="C2 Birds in Flight",G13,IF($C$3="C3 Landscape",K13,""))))</x:f>
+      <x:c r="P14" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B14,IF($C$3="C1 Wildlife",C14,IF($C$3="C2 Birds in Flight",G14,IF($C$3="C3 Landscape",K14,""))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="Q13" s="52" t="str">
-        <x:f>IF($G$3="Default Settings",B13,IF($G$3="C1 Wildlife",C13,IF($G$3="C2 Birds in Flight",G13,IF($G$3="C3 Landscape",K13,""))))</x:f>
+      <x:c r="Q14" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B14,IF($G$3="C1 Wildlife",C14,IF($G$3="C2 Birds in Flight",G14,IF($G$3="C3 Landscape",K14,""))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="R13" s="52" t="str">
-        <x:f>IF($K$3="Default Settings",B13,IF($K$3="C1 Wildlife",C13,IF($K$3="C2 Birds in Flight",G13,IF($K$3="C3 Landscape",K13,""))))</x:f>
+      <x:c r="R14" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B14,IF($K$3="C1 Wildlife",C14,IF($K$3="C2 Birds in Flight",G14,IF($K$3="C3 Landscape",K14,""))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" hidden="0">
-      <x:c r="A14" s="57" t="str">
+    <x:row r="15" hidden="0">
+      <x:c r="A15" s="52" t="str">
         <x:v>Subject Detection</x:v>
       </x:c>
-      <x:c r="B14" s="59" t="str">
+      <x:c r="B15" s="54" t="str">
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="C14" s="70" t="str">
+      <x:c r="C15" s="65" t="str">
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="D14" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E14" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F14" s="71" t="str"/>
-      <x:c r="G14" s="70" t="str">
+      <x:c r="D15" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E15" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F15" s="66" t="str"/>
+      <x:c r="G15" s="65" t="str">
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="H14" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I14" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J14" s="71" t="str"/>
-      <x:c r="K14" s="70" t="str">
+      <x:c r="H15" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I15" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J15" s="66" t="str"/>
+      <x:c r="K15" s="65" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="L14" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M14" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N14" s="71" t="str"/>
-      <x:c r="O14" s="52" t="str">
-        <x:f>IF($B$3="Default Settings",B14,IF($B$3="C1 Wildlife",C14,IF($B$3="C2 Birds in Flight",G14,IF($B$3="C3 Landscape",K14,""))))</x:f>
+      <x:c r="L15" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M15" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N15" s="66" t="str"/>
+      <x:c r="O15" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B15,IF($B$3="C1 Wildlife",C15,IF($B$3="C2 Birds in Flight",G15,IF($B$3="C3 Landscape",K15,""))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="P14" s="52" t="str">
-        <x:f>IF($C$3="Default Settings",B14,IF($C$3="C1 Wildlife",C14,IF($C$3="C2 Birds in Flight",G14,IF($C$3="C3 Landscape",K14,""))))</x:f>
+      <x:c r="P15" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B15,IF($C$3="C1 Wildlife",C15,IF($C$3="C2 Birds in Flight",G15,IF($C$3="C3 Landscape",K15,""))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="Q14" s="52" t="str">
-        <x:f>IF($G$3="Default Settings",B14,IF($G$3="C1 Wildlife",C14,IF($G$3="C2 Birds in Flight",G14,IF($G$3="C3 Landscape",K14,""))))</x:f>
+      <x:c r="Q15" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B15,IF($G$3="C1 Wildlife",C15,IF($G$3="C2 Birds in Flight",G15,IF($G$3="C3 Landscape",K15,""))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="R14" s="52" t="str">
-        <x:f>IF($K$3="Default Settings",B14,IF($K$3="C1 Wildlife",C14,IF($K$3="C2 Birds in Flight",G14,IF($K$3="C3 Landscape",K14,""))))</x:f>
+      <x:c r="R15" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B15,IF($K$3="C1 Wildlife",C15,IF($K$3="C2 Birds in Flight",G15,IF($K$3="C3 Landscape",K15,""))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" hidden="0">
-      <x:c r="A15" s="57" t="str">
+    <x:row r="16" hidden="0">
+      <x:c r="A16" s="52" t="str">
         <x:v>Eye Detection</x:v>
       </x:c>
-      <x:c r="B15" s="59" t="str">
+      <x:c r="B16" s="54" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="C15" s="70" t="str">
+      <x:c r="C16" s="65" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="D15" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E15" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F15" s="71" t="str"/>
-      <x:c r="G15" s="70" t="str">
+      <x:c r="D16" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E16" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F16" s="66" t="str"/>
+      <x:c r="G16" s="65" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="H15" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I15" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J15" s="71" t="str"/>
-      <x:c r="K15" s="70" t="str">
+      <x:c r="H16" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I16" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J16" s="66" t="str"/>
+      <x:c r="K16" s="65" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="L15" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M15" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N15" s="71" t="str"/>
-      <x:c r="O15" s="52" t="str">
-        <x:f>IF($B$3="Default Settings",B15,IF($B$3="C1 Wildlife",C15,IF($B$3="C2 Birds in Flight",G15,IF($B$3="C3 Landscape",K15,""))))</x:f>
+      <x:c r="L16" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M16" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N16" s="66" t="str"/>
+      <x:c r="O16" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B16,IF($B$3="C1 Wildlife",C16,IF($B$3="C2 Birds in Flight",G16,IF($B$3="C3 Landscape",K16,""))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="P15" s="52" t="str">
-        <x:f>IF($C$3="Default Settings",B15,IF($C$3="C1 Wildlife",C15,IF($C$3="C2 Birds in Flight",G15,IF($C$3="C3 Landscape",K15,""))))</x:f>
+      <x:c r="P16" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B16,IF($C$3="C1 Wildlife",C16,IF($C$3="C2 Birds in Flight",G16,IF($C$3="C3 Landscape",K16,""))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="Q15" s="52" t="str">
-        <x:f>IF($G$3="Default Settings",B15,IF($G$3="C1 Wildlife",C15,IF($G$3="C2 Birds in Flight",G15,IF($G$3="C3 Landscape",K15,""))))</x:f>
+      <x:c r="Q16" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B16,IF($G$3="C1 Wildlife",C16,IF($G$3="C2 Birds in Flight",G16,IF($G$3="C3 Landscape",K16,""))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="R15" s="52" t="str">
-        <x:f>IF($K$3="Default Settings",B15,IF($K$3="C1 Wildlife",C15,IF($K$3="C2 Birds in Flight",G15,IF($K$3="C3 Landscape",K15,""))))</x:f>
+      <x:c r="R16" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B16,IF($K$3="C1 Wildlife",C16,IF($K$3="C2 Birds in Flight",G16,IF($K$3="C3 Landscape",K16,""))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" hidden="0">
-      <x:c r="A16" s="57" t="str">
+    <x:row r="17" hidden="0">
+      <x:c r="A17" s="52" t="str">
         <x:v>Drive Mode</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
+      <x:c r="B17" s="54" t="str">
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="C16" s="70" t="str">
+      <x:c r="C17" s="65" t="str">
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="D16" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E16" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F16" s="71" t="str"/>
-      <x:c r="G16" s="70" t="str">
+      <x:c r="D17" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E17" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F17" s="66" t="str"/>
+      <x:c r="G17" s="65" t="str">
         <x:v>High Speed Continuous+</x:v>
       </x:c>
-      <x:c r="H16" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I16" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J16" s="71" t="str"/>
-      <x:c r="K16" s="70" t="str">
+      <x:c r="H17" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I17" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J17" s="66" t="str"/>
+      <x:c r="K17" s="65" t="str">
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="L16" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M16" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N16" s="71" t="str"/>
-      <x:c r="O16" s="52" t="str">
-        <x:f>IF($B$3="Default Settings",B16,IF($B$3="C1 Wildlife",C16,IF($B$3="C2 Birds in Flight",G16,IF($B$3="C3 Landscape",K16,""))))</x:f>
+      <x:c r="L17" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M17" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N17" s="66" t="str"/>
+      <x:c r="O17" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B17,IF($B$3="C1 Wildlife",C17,IF($B$3="C2 Birds in Flight",G17,IF($B$3="C3 Landscape",K17,""))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="P16" s="52" t="str">
-        <x:f>IF($C$3="Default Settings",B16,IF($C$3="C1 Wildlife",C16,IF($C$3="C2 Birds in Flight",G16,IF($C$3="C3 Landscape",K16,""))))</x:f>
+      <x:c r="P17" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B17,IF($C$3="C1 Wildlife",C17,IF($C$3="C2 Birds in Flight",G17,IF($C$3="C3 Landscape",K17,""))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="Q16" s="52" t="str">
-        <x:f>IF($G$3="Default Settings",B16,IF($G$3="C1 Wildlife",C16,IF($G$3="C2 Birds in Flight",G16,IF($G$3="C3 Landscape",K16,""))))</x:f>
+      <x:c r="Q17" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B17,IF($G$3="C1 Wildlife",C17,IF($G$3="C2 Birds in Flight",G17,IF($G$3="C3 Landscape",K17,""))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="R16" s="52" t="str">
-        <x:f>IF($K$3="Default Settings",B16,IF($K$3="C1 Wildlife",C16,IF($K$3="C2 Birds in Flight",G16,IF($K$3="C3 Landscape",K16,""))))</x:f>
+      <x:c r="R17" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B17,IF($K$3="C1 Wildlife",C17,IF($K$3="C2 Birds in Flight",G17,IF($K$3="C3 Landscape",K17,""))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" hidden="0">
-      <x:c r="A17" s="57" t="str">
+    <x:row r="18" hidden="0">
+      <x:c r="A18" s="52" t="str">
         <x:v>Shutter Type</x:v>
       </x:c>
-      <x:c r="B17" s="59" t="str">
+      <x:c r="B18" s="54" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="C17" s="70" t="str">
+      <x:c r="C18" s="65" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="D17" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E17" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F17" s="71" t="str"/>
-      <x:c r="G17" s="70" t="str">
+      <x:c r="D18" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E18" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F18" s="66" t="str"/>
+      <x:c r="G18" s="65" t="str">
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="H17" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I17" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J17" s="71" t="str"/>
-      <x:c r="K17" s="70" t="str">
+      <x:c r="H18" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I18" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J18" s="66" t="str"/>
+      <x:c r="K18" s="65" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="L17" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M17" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N17" s="71" t="str"/>
-      <x:c r="O17" s="52" t="str">
-        <x:f>IF($B$3="Default Settings",B17,IF($B$3="C1 Wildlife",C17,IF($B$3="C2 Birds in Flight",G17,IF($B$3="C3 Landscape",K17,""))))</x:f>
+      <x:c r="L18" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M18" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N18" s="66" t="str"/>
+      <x:c r="O18" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B18,IF($B$3="C1 Wildlife",C18,IF($B$3="C2 Birds in Flight",G18,IF($B$3="C3 Landscape",K18,""))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="P17" s="52" t="str">
-        <x:f>IF($C$3="Default Settings",B17,IF($C$3="C1 Wildlife",C17,IF($C$3="C2 Birds in Flight",G17,IF($C$3="C3 Landscape",K17,""))))</x:f>
+      <x:c r="P18" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B18,IF($C$3="C1 Wildlife",C18,IF($C$3="C2 Birds in Flight",G18,IF($C$3="C3 Landscape",K18,""))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="Q17" s="52" t="str">
-        <x:f>IF($G$3="Default Settings",B17,IF($G$3="C1 Wildlife",C17,IF($G$3="C2 Birds in Flight",G17,IF($G$3="C3 Landscape",K17,""))))</x:f>
+      <x:c r="Q18" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B18,IF($G$3="C1 Wildlife",C18,IF($G$3="C2 Birds in Flight",G18,IF($G$3="C3 Landscape",K18,""))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="R17" s="52" t="str">
-        <x:f>IF($K$3="Default Settings",B17,IF($K$3="C1 Wildlife",C17,IF($K$3="C2 Birds in Flight",G17,IF($K$3="C3 Landscape",K17,""))))</x:f>
+      <x:c r="R18" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B18,IF($K$3="C1 Wildlife",C18,IF($K$3="C2 Birds in Flight",G18,IF($K$3="C3 Landscape",K18,""))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" hidden="0">
-      <x:c r="A18" s="57" t="str">
+    <x:row r="19" hidden="0">
+      <x:c r="A19" s="52" t="str">
         <x:v>Image Stabilizer Mode</x:v>
       </x:c>
-      <x:c r="B18" s="59" t="str">
+      <x:c r="B19" s="54" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="C18" s="70" t="str">
+      <x:c r="C19" s="65" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="D18" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E18" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F18" s="71" t="str"/>
-      <x:c r="G18" s="70" t="str">
+      <x:c r="D19" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E19" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F19" s="66" t="str"/>
+      <x:c r="G19" s="65" t="str">
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="H18" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I18" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J18" s="71" t="str"/>
-      <x:c r="K18" s="70" t="str">
+      <x:c r="H19" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I19" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J19" s="66" t="str"/>
+      <x:c r="K19" s="65" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="L18" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M18" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N18" s="71" t="str"/>
-      <x:c r="O18" s="52" t="str">
-        <x:f>IF($B$3="Default Settings",B18,IF($B$3="C1 Wildlife",C18,IF($B$3="C2 Birds in Flight",G18,IF($B$3="C3 Landscape",K18,""))))</x:f>
+      <x:c r="L19" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M19" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N19" s="66" t="str"/>
+      <x:c r="O19" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B19,IF($B$3="C1 Wildlife",C19,IF($B$3="C2 Birds in Flight",G19,IF($B$3="C3 Landscape",K19,""))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="P18" s="52" t="str">
-        <x:f>IF($C$3="Default Settings",B18,IF($C$3="C1 Wildlife",C18,IF($C$3="C2 Birds in Flight",G18,IF($C$3="C3 Landscape",K18,""))))</x:f>
+      <x:c r="P19" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B19,IF($C$3="C1 Wildlife",C19,IF($C$3="C2 Birds in Flight",G19,IF($C$3="C3 Landscape",K19,""))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="Q18" s="52" t="str">
-        <x:f>IF($G$3="Default Settings",B18,IF($G$3="C1 Wildlife",C18,IF($G$3="C2 Birds in Flight",G18,IF($G$3="C3 Landscape",K18,""))))</x:f>
+      <x:c r="Q19" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B19,IF($G$3="C1 Wildlife",C19,IF($G$3="C2 Birds in Flight",G19,IF($G$3="C3 Landscape",K19,""))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="R18" s="52" t="str">
-        <x:f>IF($K$3="Default Settings",B18,IF($K$3="C1 Wildlife",C18,IF($K$3="C2 Birds in Flight",G18,IF($K$3="C3 Landscape",K18,""))))</x:f>
+      <x:c r="R19" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B19,IF($K$3="C1 Wildlife",C19,IF($K$3="C2 Birds in Flight",G19,IF($K$3="C3 Landscape",K19,""))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" hidden="0">
-      <x:c r="A19" s="57" t="str">
+    <x:row r="20" hidden="0">
+      <x:c r="A20" s="52" t="str">
         <x:v>IBIS</x:v>
       </x:c>
-      <x:c r="B19" s="59" t="str">
+      <x:c r="B20" s="54" t="str">
         <x:v>On</x:v>
       </x:c>
-      <x:c r="C19" s="72" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E19" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F19" s="71" t="str"/>
-      <x:c r="G19" s="72" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I19" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J19" s="71" t="str"/>
-      <x:c r="K19" s="72" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L19" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M19" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N19" s="71" t="str"/>
-      <x:c r="O19" s="52" t="str">
-        <x:f>IF($B$3="Default Settings",B19,IF($B$3="C1 Wildlife",C19,IF($B$3="C2 Birds in Flight",G19,IF($B$3="C3 Landscape",K19,""))))</x:f>
+      <x:c r="C20" s="65" t="str">
         <x:v>On</x:v>
       </x:c>
-      <x:c r="P19" s="52" t="str">
-        <x:f>IF($C$3="Default Settings",B19,IF($C$3="C1 Wildlife",C19,IF($C$3="C2 Birds in Flight",G19,IF($C$3="C3 Landscape",K19,""))))</x:f>
+      <x:c r="D20" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E20" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F20" s="66" t="str"/>
+      <x:c r="G20" s="65" t="str">
         <x:v>On</x:v>
       </x:c>
-      <x:c r="Q19" s="52" t="str">
-        <x:f>IF($G$3="Default Settings",B19,IF($G$3="C1 Wildlife",C19,IF($G$3="C2 Birds in Flight",G19,IF($G$3="C3 Landscape",K19,""))))</x:f>
+      <x:c r="H20" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I20" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J20" s="66" t="str"/>
+      <x:c r="K20" s="65" t="str">
         <x:v>On</x:v>
       </x:c>
-      <x:c r="R19" s="52" t="str">
-        <x:f>IF($K$3="Default Settings",B19,IF($K$3="C1 Wildlife",C19,IF($K$3="C2 Birds in Flight",G19,IF($K$3="C3 Landscape",K19,""))))</x:f>
+      <x:c r="L20" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M20" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N20" s="66" t="str"/>
+      <x:c r="O20" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B20,IF($B$3="C1 Wildlife",C20,IF($B$3="C2 Birds in Flight",G20,IF($B$3="C3 Landscape",K20,""))))</x:f>
         <x:v>On</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" hidden="0">
-      <x:c r="A20" s="57" t="str">
+      <x:c r="P20" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B20,IF($C$3="C1 Wildlife",C20,IF($C$3="C2 Birds in Flight",G20,IF($C$3="C3 Landscape",K20,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="Q20" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B20,IF($G$3="C1 Wildlife",C20,IF($G$3="C2 Birds in Flight",G20,IF($G$3="C3 Landscape",K20,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="R20" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B20,IF($K$3="C1 Wildlife",C20,IF($K$3="C2 Birds in Flight",G20,IF($K$3="C3 Landscape",K20,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" hidden="0">
+      <x:c r="A21" s="52" t="str">
         <x:v>Focus Bracketing</x:v>
       </x:c>
-      <x:c r="B20" s="59" t="str">
+      <x:c r="B21" s="54" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="C20" s="70" t="str">
+      <x:c r="C21" s="65" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="D20" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E20" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F20" s="71" t="str"/>
-      <x:c r="G20" s="70" t="str">
+      <x:c r="D21" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E21" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F21" s="66" t="str"/>
+      <x:c r="G21" s="65" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="H20" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I20" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J20" s="71" t="str"/>
-      <x:c r="K20" s="70" t="str">
-        <x:v>Disable; enable situationally</x:v>
-      </x:c>
-      <x:c r="L20" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M20" s="43" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N20" s="71" t="str"/>
-      <x:c r="O20" s="52" t="str">
-        <x:f>IF($B$3="Default Settings",B20,IF($B$3="C1 Wildlife",C20,IF($B$3="C2 Birds in Flight",G20,IF($B$3="C3 Landscape",K20,""))))</x:f>
+      <x:c r="H21" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I21" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J21" s="66" t="str"/>
+      <x:c r="K21" s="65" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="P20" s="52" t="str">
-        <x:f>IF($C$3="Default Settings",B20,IF($C$3="C1 Wildlife",C20,IF($C$3="C2 Birds in Flight",G20,IF($C$3="C3 Landscape",K20,""))))</x:f>
+      <x:c r="L21" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M21" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N21" s="66" t="str"/>
+      <x:c r="O21" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B21,IF($B$3="C1 Wildlife",C21,IF($B$3="C2 Birds in Flight",G21,IF($B$3="C3 Landscape",K21,""))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="Q20" s="52" t="str">
-        <x:f>IF($G$3="Default Settings",B20,IF($G$3="C1 Wildlife",C20,IF($G$3="C2 Birds in Flight",G20,IF($G$3="C3 Landscape",K20,""))))</x:f>
+      <x:c r="P21" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B21,IF($C$3="C1 Wildlife",C21,IF($C$3="C2 Birds in Flight",G21,IF($C$3="C3 Landscape",K21,""))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="R20" s="52" t="str">
-        <x:f>IF($K$3="Default Settings",B20,IF($K$3="C1 Wildlife",C20,IF($K$3="C2 Birds in Flight",G20,IF($K$3="C3 Landscape",K20,""))))</x:f>
+      <x:c r="Q21" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B21,IF($G$3="C1 Wildlife",C21,IF($G$3="C2 Birds in Flight",G21,IF($G$3="C3 Landscape",K21,""))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" hidden="0">
-      <x:c r="A21" s="58" t="str">
+      <x:c r="R21" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B21,IF($K$3="C1 Wildlife",C21,IF($K$3="C2 Birds in Flight",G21,IF($K$3="C3 Landscape",K21,""))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" hidden="0">
+      <x:c r="A22" s="53" t="str">
         <x:v>Lens IS switch</x:v>
       </x:c>
-      <x:c r="B21" s="60" t="str">
+      <x:c r="B22" s="55" t="str">
         <x:v>On</x:v>
       </x:c>
-      <x:c r="C21" s="73" t="str">
-        <x:v>On; physical check</x:v>
-      </x:c>
-      <x:c r="D21" s="74" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E21" s="74" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F21" s="75" t="str"/>
-      <x:c r="G21" s="73" t="str">
-        <x:v>On; physical check</x:v>
-      </x:c>
-      <x:c r="H21" s="74" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I21" s="74" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J21" s="75" t="str"/>
-      <x:c r="K21" s="73" t="str">
-        <x:v>On; handheld registration</x:v>
-      </x:c>
-      <x:c r="L21" s="74" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M21" s="74" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N21" s="75" t="str"/>
-      <x:c r="O21" s="52" t="str">
-        <x:f>IF($B$3="Default Settings",B21,IF($B$3="C1 Wildlife",C21,IF($B$3="C2 Birds in Flight",G21,IF($B$3="C3 Landscape",K21,""))))</x:f>
+      <x:c r="C22" s="67" t="str">
         <x:v>On</x:v>
       </x:c>
-      <x:c r="P21" s="52" t="str">
-        <x:f>IF($C$3="Default Settings",B21,IF($C$3="C1 Wildlife",C21,IF($C$3="C2 Birds in Flight",G21,IF($C$3="C3 Landscape",K21,""))))</x:f>
+      <x:c r="D22" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E22" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F22" s="69" t="str"/>
+      <x:c r="G22" s="67" t="str">
         <x:v>On</x:v>
       </x:c>
-      <x:c r="Q21" s="52" t="str">
-        <x:f>IF($G$3="Default Settings",B21,IF($G$3="C1 Wildlife",C21,IF($G$3="C2 Birds in Flight",G21,IF($G$3="C3 Landscape",K21,""))))</x:f>
+      <x:c r="H22" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I22" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J22" s="69" t="str"/>
+      <x:c r="K22" s="67" t="str">
         <x:v>On</x:v>
       </x:c>
-      <x:c r="R21" s="52" t="str">
-        <x:f>IF($K$3="Default Settings",B21,IF($K$3="C1 Wildlife",C21,IF($K$3="C2 Birds in Flight",G21,IF($K$3="C3 Landscape",K21,""))))</x:f>
+      <x:c r="L22" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M22" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N22" s="69" t="str"/>
+      <x:c r="O22" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B22,IF($B$3="C1 Wildlife",C22,IF($B$3="C2 Birds in Flight",G22,IF($B$3="C3 Landscape",K22,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="P22" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B22,IF($C$3="C1 Wildlife",C22,IF($C$3="C2 Birds in Flight",G22,IF($C$3="C3 Landscape",K22,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="Q22" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B22,IF($G$3="C1 Wildlife",C22,IF($G$3="C2 Birds in Flight",G22,IF($G$3="C3 Landscape",K22,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="R22" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B22,IF($K$3="C1 Wildlife",C22,IF($K$3="C2 Birds in Flight",G22,IF($K$3="C3 Landscape",K22,""))))</x:f>
         <x:v>On</x:v>
       </x:c>
     </x:row>
@@ -4574,22 +4616,22 @@
     <x:mergeCell ref="A1:N1"/>
     <x:mergeCell ref="A2:N2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="B5:B21">
+  <x:conditionalFormatting sqref="B5:B22">
     <x:cfRule type="cellIs" dxfId="5" priority="1" operator="notEqual">
       <x:formula>$O5</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="C5:C21">
+  <x:conditionalFormatting sqref="C5:C22">
     <x:cfRule type="cellIs" dxfId="6" priority="2" operator="notEqual">
       <x:formula>$P5</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G5:G21">
+  <x:conditionalFormatting sqref="G5:G22">
     <x:cfRule type="cellIs" dxfId="7" priority="3" operator="notEqual">
       <x:formula>$Q5</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="K5:K21">
+  <x:conditionalFormatting sqref="K5:K22">
     <x:cfRule type="cellIs" dxfId="8" priority="4" operator="notEqual">
       <x:formula>$R5</x:formula>
     </x:cfRule>
@@ -4607,19 +4649,19 @@
     <x:dataValidation type="list" sqref="K3">
       <x:formula1>"Default Settings,C1 Wildlife,C2 Birds in Flight,C3 Landscape"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="D5:E21">
+    <x:dataValidation type="list" sqref="D5:E22">
       <x:formula1>"Not started,Pass,Fail,Needs retest,Not applicable"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="H5:I21">
+    <x:dataValidation type="list" sqref="H5:I22">
       <x:formula1>"Not started,Pass,Fail,Needs retest,Not applicable"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="L5:M21">
+    <x:dataValidation type="list" sqref="L5:M22">
       <x:formula1>"Not started,Pass,Fail,Needs retest,Not applicable"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Ra4d32262cf3447ac"/>
+    <x:tablePart ns1:id="Ra8a2c5e16f8743df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4714,284 +4756,284 @@
       </x:c>
     </x:row>
     <x:row r="5" hidden="0">
-      <x:c r="A5" s="43" t="str"/>
-      <x:c r="B5" s="76" t="str"/>
-      <x:c r="C5" s="43" t="str"/>
-      <x:c r="D5" s="43" t="str"/>
-      <x:c r="E5" s="43" t="str"/>
-      <x:c r="F5" s="43" t="str"/>
-      <x:c r="G5" s="43" t="str"/>
-      <x:c r="H5" s="43" t="str"/>
-      <x:c r="I5" s="43" t="str"/>
-      <x:c r="J5" s="43" t="str"/>
-      <x:c r="K5" s="43" t="str"/>
-      <x:c r="L5" s="43" t="str"/>
+      <x:c r="A5" s="40" t="str"/>
+      <x:c r="B5" s="70" t="str"/>
+      <x:c r="C5" s="40" t="str"/>
+      <x:c r="D5" s="40" t="str"/>
+      <x:c r="E5" s="40" t="str"/>
+      <x:c r="F5" s="40" t="str"/>
+      <x:c r="G5" s="40" t="str"/>
+      <x:c r="H5" s="40" t="str"/>
+      <x:c r="I5" s="40" t="str"/>
+      <x:c r="J5" s="40" t="str"/>
+      <x:c r="K5" s="40" t="str"/>
+      <x:c r="L5" s="40" t="str"/>
     </x:row>
     <x:row r="6" hidden="0">
-      <x:c r="A6" s="43" t="str"/>
-      <x:c r="B6" s="76" t="str"/>
-      <x:c r="C6" s="43" t="str"/>
-      <x:c r="D6" s="43" t="str"/>
-      <x:c r="E6" s="43" t="str"/>
-      <x:c r="F6" s="43" t="str"/>
-      <x:c r="G6" s="43" t="str"/>
-      <x:c r="H6" s="43" t="str"/>
-      <x:c r="I6" s="43" t="str"/>
-      <x:c r="J6" s="43" t="str"/>
-      <x:c r="K6" s="43" t="str"/>
-      <x:c r="L6" s="43" t="str"/>
+      <x:c r="A6" s="40" t="str"/>
+      <x:c r="B6" s="70" t="str"/>
+      <x:c r="C6" s="40" t="str"/>
+      <x:c r="D6" s="40" t="str"/>
+      <x:c r="E6" s="40" t="str"/>
+      <x:c r="F6" s="40" t="str"/>
+      <x:c r="G6" s="40" t="str"/>
+      <x:c r="H6" s="40" t="str"/>
+      <x:c r="I6" s="40" t="str"/>
+      <x:c r="J6" s="40" t="str"/>
+      <x:c r="K6" s="40" t="str"/>
+      <x:c r="L6" s="40" t="str"/>
     </x:row>
     <x:row r="7" hidden="0">
-      <x:c r="A7" s="43" t="str"/>
-      <x:c r="B7" s="76" t="str"/>
-      <x:c r="C7" s="43" t="str"/>
-      <x:c r="D7" s="43" t="str"/>
-      <x:c r="E7" s="43" t="str"/>
-      <x:c r="F7" s="43" t="str"/>
-      <x:c r="G7" s="43" t="str"/>
-      <x:c r="H7" s="43" t="str"/>
-      <x:c r="I7" s="43" t="str"/>
-      <x:c r="J7" s="43" t="str"/>
-      <x:c r="K7" s="43" t="str"/>
-      <x:c r="L7" s="43" t="str"/>
+      <x:c r="A7" s="40" t="str"/>
+      <x:c r="B7" s="70" t="str"/>
+      <x:c r="C7" s="40" t="str"/>
+      <x:c r="D7" s="40" t="str"/>
+      <x:c r="E7" s="40" t="str"/>
+      <x:c r="F7" s="40" t="str"/>
+      <x:c r="G7" s="40" t="str"/>
+      <x:c r="H7" s="40" t="str"/>
+      <x:c r="I7" s="40" t="str"/>
+      <x:c r="J7" s="40" t="str"/>
+      <x:c r="K7" s="40" t="str"/>
+      <x:c r="L7" s="40" t="str"/>
     </x:row>
     <x:row r="8" hidden="0">
-      <x:c r="A8" s="43" t="str"/>
-      <x:c r="B8" s="76" t="str"/>
-      <x:c r="C8" s="43" t="str"/>
-      <x:c r="D8" s="43" t="str"/>
-      <x:c r="E8" s="43" t="str"/>
-      <x:c r="F8" s="43" t="str"/>
-      <x:c r="G8" s="43" t="str"/>
-      <x:c r="H8" s="43" t="str"/>
-      <x:c r="I8" s="43" t="str"/>
-      <x:c r="J8" s="43" t="str"/>
-      <x:c r="K8" s="43" t="str"/>
-      <x:c r="L8" s="43" t="str"/>
+      <x:c r="A8" s="40" t="str"/>
+      <x:c r="B8" s="70" t="str"/>
+      <x:c r="C8" s="40" t="str"/>
+      <x:c r="D8" s="40" t="str"/>
+      <x:c r="E8" s="40" t="str"/>
+      <x:c r="F8" s="40" t="str"/>
+      <x:c r="G8" s="40" t="str"/>
+      <x:c r="H8" s="40" t="str"/>
+      <x:c r="I8" s="40" t="str"/>
+      <x:c r="J8" s="40" t="str"/>
+      <x:c r="K8" s="40" t="str"/>
+      <x:c r="L8" s="40" t="str"/>
     </x:row>
     <x:row r="9" hidden="0">
-      <x:c r="A9" s="43" t="str"/>
-      <x:c r="B9" s="76" t="str"/>
-      <x:c r="C9" s="43" t="str"/>
-      <x:c r="D9" s="43" t="str"/>
-      <x:c r="E9" s="43" t="str"/>
-      <x:c r="F9" s="43" t="str"/>
-      <x:c r="G9" s="43" t="str"/>
-      <x:c r="H9" s="43" t="str"/>
-      <x:c r="I9" s="43" t="str"/>
-      <x:c r="J9" s="43" t="str"/>
-      <x:c r="K9" s="43" t="str"/>
-      <x:c r="L9" s="43" t="str"/>
+      <x:c r="A9" s="40" t="str"/>
+      <x:c r="B9" s="70" t="str"/>
+      <x:c r="C9" s="40" t="str"/>
+      <x:c r="D9" s="40" t="str"/>
+      <x:c r="E9" s="40" t="str"/>
+      <x:c r="F9" s="40" t="str"/>
+      <x:c r="G9" s="40" t="str"/>
+      <x:c r="H9" s="40" t="str"/>
+      <x:c r="I9" s="40" t="str"/>
+      <x:c r="J9" s="40" t="str"/>
+      <x:c r="K9" s="40" t="str"/>
+      <x:c r="L9" s="40" t="str"/>
     </x:row>
     <x:row r="10" hidden="0">
-      <x:c r="A10" s="43" t="str"/>
-      <x:c r="B10" s="76" t="str"/>
-      <x:c r="C10" s="43" t="str"/>
-      <x:c r="D10" s="43" t="str"/>
-      <x:c r="E10" s="43" t="str"/>
-      <x:c r="F10" s="43" t="str"/>
-      <x:c r="G10" s="43" t="str"/>
-      <x:c r="H10" s="43" t="str"/>
-      <x:c r="I10" s="43" t="str"/>
-      <x:c r="J10" s="43" t="str"/>
-      <x:c r="K10" s="43" t="str"/>
-      <x:c r="L10" s="43" t="str"/>
+      <x:c r="A10" s="40" t="str"/>
+      <x:c r="B10" s="70" t="str"/>
+      <x:c r="C10" s="40" t="str"/>
+      <x:c r="D10" s="40" t="str"/>
+      <x:c r="E10" s="40" t="str"/>
+      <x:c r="F10" s="40" t="str"/>
+      <x:c r="G10" s="40" t="str"/>
+      <x:c r="H10" s="40" t="str"/>
+      <x:c r="I10" s="40" t="str"/>
+      <x:c r="J10" s="40" t="str"/>
+      <x:c r="K10" s="40" t="str"/>
+      <x:c r="L10" s="40" t="str"/>
     </x:row>
     <x:row r="11" hidden="0">
-      <x:c r="A11" s="43" t="str"/>
-      <x:c r="B11" s="76" t="str"/>
-      <x:c r="C11" s="43" t="str"/>
-      <x:c r="D11" s="43" t="str"/>
-      <x:c r="E11" s="43" t="str"/>
-      <x:c r="F11" s="43" t="str"/>
-      <x:c r="G11" s="43" t="str"/>
-      <x:c r="H11" s="43" t="str"/>
-      <x:c r="I11" s="43" t="str"/>
-      <x:c r="J11" s="43" t="str"/>
-      <x:c r="K11" s="43" t="str"/>
-      <x:c r="L11" s="43" t="str"/>
+      <x:c r="A11" s="40" t="str"/>
+      <x:c r="B11" s="70" t="str"/>
+      <x:c r="C11" s="40" t="str"/>
+      <x:c r="D11" s="40" t="str"/>
+      <x:c r="E11" s="40" t="str"/>
+      <x:c r="F11" s="40" t="str"/>
+      <x:c r="G11" s="40" t="str"/>
+      <x:c r="H11" s="40" t="str"/>
+      <x:c r="I11" s="40" t="str"/>
+      <x:c r="J11" s="40" t="str"/>
+      <x:c r="K11" s="40" t="str"/>
+      <x:c r="L11" s="40" t="str"/>
     </x:row>
     <x:row r="12" hidden="0">
-      <x:c r="A12" s="43" t="str"/>
-      <x:c r="B12" s="76" t="str"/>
-      <x:c r="C12" s="43" t="str"/>
-      <x:c r="D12" s="43" t="str"/>
-      <x:c r="E12" s="43" t="str"/>
-      <x:c r="F12" s="43" t="str"/>
-      <x:c r="G12" s="43" t="str"/>
-      <x:c r="H12" s="43" t="str"/>
-      <x:c r="I12" s="43" t="str"/>
-      <x:c r="J12" s="43" t="str"/>
-      <x:c r="K12" s="43" t="str"/>
-      <x:c r="L12" s="43" t="str"/>
+      <x:c r="A12" s="40" t="str"/>
+      <x:c r="B12" s="70" t="str"/>
+      <x:c r="C12" s="40" t="str"/>
+      <x:c r="D12" s="40" t="str"/>
+      <x:c r="E12" s="40" t="str"/>
+      <x:c r="F12" s="40" t="str"/>
+      <x:c r="G12" s="40" t="str"/>
+      <x:c r="H12" s="40" t="str"/>
+      <x:c r="I12" s="40" t="str"/>
+      <x:c r="J12" s="40" t="str"/>
+      <x:c r="K12" s="40" t="str"/>
+      <x:c r="L12" s="40" t="str"/>
     </x:row>
     <x:row r="13" hidden="0">
-      <x:c r="A13" s="43" t="str"/>
-      <x:c r="B13" s="76" t="str"/>
-      <x:c r="C13" s="43" t="str"/>
-      <x:c r="D13" s="43" t="str"/>
-      <x:c r="E13" s="43" t="str"/>
-      <x:c r="F13" s="43" t="str"/>
-      <x:c r="G13" s="43" t="str"/>
-      <x:c r="H13" s="43" t="str"/>
-      <x:c r="I13" s="43" t="str"/>
-      <x:c r="J13" s="43" t="str"/>
-      <x:c r="K13" s="43" t="str"/>
-      <x:c r="L13" s="43" t="str"/>
+      <x:c r="A13" s="40" t="str"/>
+      <x:c r="B13" s="70" t="str"/>
+      <x:c r="C13" s="40" t="str"/>
+      <x:c r="D13" s="40" t="str"/>
+      <x:c r="E13" s="40" t="str"/>
+      <x:c r="F13" s="40" t="str"/>
+      <x:c r="G13" s="40" t="str"/>
+      <x:c r="H13" s="40" t="str"/>
+      <x:c r="I13" s="40" t="str"/>
+      <x:c r="J13" s="40" t="str"/>
+      <x:c r="K13" s="40" t="str"/>
+      <x:c r="L13" s="40" t="str"/>
     </x:row>
     <x:row r="14" hidden="0">
-      <x:c r="A14" s="43" t="str"/>
-      <x:c r="B14" s="76" t="str"/>
-      <x:c r="C14" s="43" t="str"/>
-      <x:c r="D14" s="43" t="str"/>
-      <x:c r="E14" s="43" t="str"/>
-      <x:c r="F14" s="43" t="str"/>
-      <x:c r="G14" s="43" t="str"/>
-      <x:c r="H14" s="43" t="str"/>
-      <x:c r="I14" s="43" t="str"/>
-      <x:c r="J14" s="43" t="str"/>
-      <x:c r="K14" s="43" t="str"/>
-      <x:c r="L14" s="43" t="str"/>
+      <x:c r="A14" s="40" t="str"/>
+      <x:c r="B14" s="70" t="str"/>
+      <x:c r="C14" s="40" t="str"/>
+      <x:c r="D14" s="40" t="str"/>
+      <x:c r="E14" s="40" t="str"/>
+      <x:c r="F14" s="40" t="str"/>
+      <x:c r="G14" s="40" t="str"/>
+      <x:c r="H14" s="40" t="str"/>
+      <x:c r="I14" s="40" t="str"/>
+      <x:c r="J14" s="40" t="str"/>
+      <x:c r="K14" s="40" t="str"/>
+      <x:c r="L14" s="40" t="str"/>
     </x:row>
     <x:row r="15" hidden="0">
-      <x:c r="A15" s="43" t="str"/>
-      <x:c r="B15" s="76" t="str"/>
-      <x:c r="C15" s="43" t="str"/>
-      <x:c r="D15" s="43" t="str"/>
-      <x:c r="E15" s="43" t="str"/>
-      <x:c r="F15" s="43" t="str"/>
-      <x:c r="G15" s="43" t="str"/>
-      <x:c r="H15" s="43" t="str"/>
-      <x:c r="I15" s="43" t="str"/>
-      <x:c r="J15" s="43" t="str"/>
-      <x:c r="K15" s="43" t="str"/>
-      <x:c r="L15" s="43" t="str"/>
+      <x:c r="A15" s="40" t="str"/>
+      <x:c r="B15" s="70" t="str"/>
+      <x:c r="C15" s="40" t="str"/>
+      <x:c r="D15" s="40" t="str"/>
+      <x:c r="E15" s="40" t="str"/>
+      <x:c r="F15" s="40" t="str"/>
+      <x:c r="G15" s="40" t="str"/>
+      <x:c r="H15" s="40" t="str"/>
+      <x:c r="I15" s="40" t="str"/>
+      <x:c r="J15" s="40" t="str"/>
+      <x:c r="K15" s="40" t="str"/>
+      <x:c r="L15" s="40" t="str"/>
     </x:row>
     <x:row r="16" hidden="0">
-      <x:c r="A16" s="43" t="str"/>
-      <x:c r="B16" s="76" t="str"/>
-      <x:c r="C16" s="43" t="str"/>
-      <x:c r="D16" s="43" t="str"/>
-      <x:c r="E16" s="43" t="str"/>
-      <x:c r="F16" s="43" t="str"/>
-      <x:c r="G16" s="43" t="str"/>
-      <x:c r="H16" s="43" t="str"/>
-      <x:c r="I16" s="43" t="str"/>
-      <x:c r="J16" s="43" t="str"/>
-      <x:c r="K16" s="43" t="str"/>
-      <x:c r="L16" s="43" t="str"/>
+      <x:c r="A16" s="40" t="str"/>
+      <x:c r="B16" s="70" t="str"/>
+      <x:c r="C16" s="40" t="str"/>
+      <x:c r="D16" s="40" t="str"/>
+      <x:c r="E16" s="40" t="str"/>
+      <x:c r="F16" s="40" t="str"/>
+      <x:c r="G16" s="40" t="str"/>
+      <x:c r="H16" s="40" t="str"/>
+      <x:c r="I16" s="40" t="str"/>
+      <x:c r="J16" s="40" t="str"/>
+      <x:c r="K16" s="40" t="str"/>
+      <x:c r="L16" s="40" t="str"/>
     </x:row>
     <x:row r="17" hidden="0">
-      <x:c r="A17" s="43" t="str"/>
-      <x:c r="B17" s="76" t="str"/>
-      <x:c r="C17" s="43" t="str"/>
-      <x:c r="D17" s="43" t="str"/>
-      <x:c r="E17" s="43" t="str"/>
-      <x:c r="F17" s="43" t="str"/>
-      <x:c r="G17" s="43" t="str"/>
-      <x:c r="H17" s="43" t="str"/>
-      <x:c r="I17" s="43" t="str"/>
-      <x:c r="J17" s="43" t="str"/>
-      <x:c r="K17" s="43" t="str"/>
-      <x:c r="L17" s="43" t="str"/>
+      <x:c r="A17" s="40" t="str"/>
+      <x:c r="B17" s="70" t="str"/>
+      <x:c r="C17" s="40" t="str"/>
+      <x:c r="D17" s="40" t="str"/>
+      <x:c r="E17" s="40" t="str"/>
+      <x:c r="F17" s="40" t="str"/>
+      <x:c r="G17" s="40" t="str"/>
+      <x:c r="H17" s="40" t="str"/>
+      <x:c r="I17" s="40" t="str"/>
+      <x:c r="J17" s="40" t="str"/>
+      <x:c r="K17" s="40" t="str"/>
+      <x:c r="L17" s="40" t="str"/>
     </x:row>
     <x:row r="18" hidden="0">
-      <x:c r="A18" s="43" t="str"/>
-      <x:c r="B18" s="76" t="str"/>
-      <x:c r="C18" s="43" t="str"/>
-      <x:c r="D18" s="43" t="str"/>
-      <x:c r="E18" s="43" t="str"/>
-      <x:c r="F18" s="43" t="str"/>
-      <x:c r="G18" s="43" t="str"/>
-      <x:c r="H18" s="43" t="str"/>
-      <x:c r="I18" s="43" t="str"/>
-      <x:c r="J18" s="43" t="str"/>
-      <x:c r="K18" s="43" t="str"/>
-      <x:c r="L18" s="43" t="str"/>
+      <x:c r="A18" s="40" t="str"/>
+      <x:c r="B18" s="70" t="str"/>
+      <x:c r="C18" s="40" t="str"/>
+      <x:c r="D18" s="40" t="str"/>
+      <x:c r="E18" s="40" t="str"/>
+      <x:c r="F18" s="40" t="str"/>
+      <x:c r="G18" s="40" t="str"/>
+      <x:c r="H18" s="40" t="str"/>
+      <x:c r="I18" s="40" t="str"/>
+      <x:c r="J18" s="40" t="str"/>
+      <x:c r="K18" s="40" t="str"/>
+      <x:c r="L18" s="40" t="str"/>
     </x:row>
     <x:row r="19" hidden="0">
-      <x:c r="A19" s="43" t="str"/>
-      <x:c r="B19" s="76" t="str"/>
-      <x:c r="C19" s="43" t="str"/>
-      <x:c r="D19" s="43" t="str"/>
-      <x:c r="E19" s="43" t="str"/>
-      <x:c r="F19" s="43" t="str"/>
-      <x:c r="G19" s="43" t="str"/>
-      <x:c r="H19" s="43" t="str"/>
-      <x:c r="I19" s="43" t="str"/>
-      <x:c r="J19" s="43" t="str"/>
-      <x:c r="K19" s="43" t="str"/>
-      <x:c r="L19" s="43" t="str"/>
+      <x:c r="A19" s="40" t="str"/>
+      <x:c r="B19" s="70" t="str"/>
+      <x:c r="C19" s="40" t="str"/>
+      <x:c r="D19" s="40" t="str"/>
+      <x:c r="E19" s="40" t="str"/>
+      <x:c r="F19" s="40" t="str"/>
+      <x:c r="G19" s="40" t="str"/>
+      <x:c r="H19" s="40" t="str"/>
+      <x:c r="I19" s="40" t="str"/>
+      <x:c r="J19" s="40" t="str"/>
+      <x:c r="K19" s="40" t="str"/>
+      <x:c r="L19" s="40" t="str"/>
     </x:row>
     <x:row r="20" hidden="0">
-      <x:c r="A20" s="43" t="str"/>
-      <x:c r="B20" s="76" t="str"/>
-      <x:c r="C20" s="43" t="str"/>
-      <x:c r="D20" s="43" t="str"/>
-      <x:c r="E20" s="43" t="str"/>
-      <x:c r="F20" s="43" t="str"/>
-      <x:c r="G20" s="43" t="str"/>
-      <x:c r="H20" s="43" t="str"/>
-      <x:c r="I20" s="43" t="str"/>
-      <x:c r="J20" s="43" t="str"/>
-      <x:c r="K20" s="43" t="str"/>
-      <x:c r="L20" s="43" t="str"/>
+      <x:c r="A20" s="40" t="str"/>
+      <x:c r="B20" s="70" t="str"/>
+      <x:c r="C20" s="40" t="str"/>
+      <x:c r="D20" s="40" t="str"/>
+      <x:c r="E20" s="40" t="str"/>
+      <x:c r="F20" s="40" t="str"/>
+      <x:c r="G20" s="40" t="str"/>
+      <x:c r="H20" s="40" t="str"/>
+      <x:c r="I20" s="40" t="str"/>
+      <x:c r="J20" s="40" t="str"/>
+      <x:c r="K20" s="40" t="str"/>
+      <x:c r="L20" s="40" t="str"/>
     </x:row>
     <x:row r="21" hidden="0">
-      <x:c r="A21" s="43" t="str"/>
-      <x:c r="B21" s="76" t="str"/>
-      <x:c r="C21" s="43" t="str"/>
-      <x:c r="D21" s="43" t="str"/>
-      <x:c r="E21" s="43" t="str"/>
-      <x:c r="F21" s="43" t="str"/>
-      <x:c r="G21" s="43" t="str"/>
-      <x:c r="H21" s="43" t="str"/>
-      <x:c r="I21" s="43" t="str"/>
-      <x:c r="J21" s="43" t="str"/>
-      <x:c r="K21" s="43" t="str"/>
-      <x:c r="L21" s="43" t="str"/>
+      <x:c r="A21" s="40" t="str"/>
+      <x:c r="B21" s="70" t="str"/>
+      <x:c r="C21" s="40" t="str"/>
+      <x:c r="D21" s="40" t="str"/>
+      <x:c r="E21" s="40" t="str"/>
+      <x:c r="F21" s="40" t="str"/>
+      <x:c r="G21" s="40" t="str"/>
+      <x:c r="H21" s="40" t="str"/>
+      <x:c r="I21" s="40" t="str"/>
+      <x:c r="J21" s="40" t="str"/>
+      <x:c r="K21" s="40" t="str"/>
+      <x:c r="L21" s="40" t="str"/>
     </x:row>
     <x:row r="22" hidden="0">
-      <x:c r="A22" s="43" t="str"/>
-      <x:c r="B22" s="76" t="str"/>
-      <x:c r="C22" s="43" t="str"/>
-      <x:c r="D22" s="43" t="str"/>
-      <x:c r="E22" s="43" t="str"/>
-      <x:c r="F22" s="43" t="str"/>
-      <x:c r="G22" s="43" t="str"/>
-      <x:c r="H22" s="43" t="str"/>
-      <x:c r="I22" s="43" t="str"/>
-      <x:c r="J22" s="43" t="str"/>
-      <x:c r="K22" s="43" t="str"/>
-      <x:c r="L22" s="43" t="str"/>
+      <x:c r="A22" s="40" t="str"/>
+      <x:c r="B22" s="70" t="str"/>
+      <x:c r="C22" s="40" t="str"/>
+      <x:c r="D22" s="40" t="str"/>
+      <x:c r="E22" s="40" t="str"/>
+      <x:c r="F22" s="40" t="str"/>
+      <x:c r="G22" s="40" t="str"/>
+      <x:c r="H22" s="40" t="str"/>
+      <x:c r="I22" s="40" t="str"/>
+      <x:c r="J22" s="40" t="str"/>
+      <x:c r="K22" s="40" t="str"/>
+      <x:c r="L22" s="40" t="str"/>
     </x:row>
     <x:row r="23" hidden="0">
-      <x:c r="A23" s="43" t="str"/>
-      <x:c r="B23" s="76" t="str"/>
-      <x:c r="C23" s="43" t="str"/>
-      <x:c r="D23" s="43" t="str"/>
-      <x:c r="E23" s="43" t="str"/>
-      <x:c r="F23" s="43" t="str"/>
-      <x:c r="G23" s="43" t="str"/>
-      <x:c r="H23" s="43" t="str"/>
-      <x:c r="I23" s="43" t="str"/>
-      <x:c r="J23" s="43" t="str"/>
-      <x:c r="K23" s="43" t="str"/>
-      <x:c r="L23" s="43" t="str"/>
+      <x:c r="A23" s="40" t="str"/>
+      <x:c r="B23" s="70" t="str"/>
+      <x:c r="C23" s="40" t="str"/>
+      <x:c r="D23" s="40" t="str"/>
+      <x:c r="E23" s="40" t="str"/>
+      <x:c r="F23" s="40" t="str"/>
+      <x:c r="G23" s="40" t="str"/>
+      <x:c r="H23" s="40" t="str"/>
+      <x:c r="I23" s="40" t="str"/>
+      <x:c r="J23" s="40" t="str"/>
+      <x:c r="K23" s="40" t="str"/>
+      <x:c r="L23" s="40" t="str"/>
     </x:row>
     <x:row r="24" hidden="0">
-      <x:c r="A24" s="43" t="str"/>
-      <x:c r="B24" s="76" t="str"/>
-      <x:c r="C24" s="43" t="str"/>
-      <x:c r="D24" s="43" t="str"/>
-      <x:c r="E24" s="43" t="str"/>
-      <x:c r="F24" s="43" t="str"/>
-      <x:c r="G24" s="43" t="str"/>
-      <x:c r="H24" s="43" t="str"/>
-      <x:c r="I24" s="43" t="str"/>
-      <x:c r="J24" s="43" t="str"/>
-      <x:c r="K24" s="43" t="str"/>
-      <x:c r="L24" s="43" t="str"/>
+      <x:c r="A24" s="40" t="str"/>
+      <x:c r="B24" s="70" t="str"/>
+      <x:c r="C24" s="40" t="str"/>
+      <x:c r="D24" s="40" t="str"/>
+      <x:c r="E24" s="40" t="str"/>
+      <x:c r="F24" s="40" t="str"/>
+      <x:c r="G24" s="40" t="str"/>
+      <x:c r="H24" s="40" t="str"/>
+      <x:c r="I24" s="40" t="str"/>
+      <x:c r="J24" s="40" t="str"/>
+      <x:c r="K24" s="40" t="str"/>
+      <x:c r="L24" s="40" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5000,7 +5042,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R0998df073d3a4758"/>
+    <x:tablePart ns1:id="R2462fbfcaf824ac5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5252,7 +5294,7 @@
         <x:v>My Menu</x:v>
       </x:c>
       <x:c r="D5" s="15" t="str">
-        <x:v>Create tab SWITCH; register in order: Subject to detect, Shutter mode, Focus bracketing, IS (Image Stabilizer) mode, Cropping/aspect ratio; leave position 6 open</x:v>
+        <x:v>Create tab SWITCH; register Subject to detect, Shutter mode, Focus bracketing, IS (Image Stabilizer) mode, and Cropping/aspect ratio in order; leave position 6 open.</x:v>
       </x:c>
       <x:c r="E5" s="17" t="n">
         <x:v>4</x:v>
@@ -5260,16 +5302,16 @@
     </x:row>
     <x:row r="6" hidden="0">
       <x:c r="A6" s="10" t="str">
-        <x:v>SETUP-04</x:v>
+        <x:v>SETUP-MM-AF-01</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
-        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio</x:v>
+        <x:v>My Menu</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>Multiple</x:v>
+        <x:v>My Menu</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting menu: IS (Image Stabilizer) mode</x:v>
+        <x:v>Create tab AF Case; register Servo AF, Tracking Sensitivity, and Accel./Decel. tracking in order; confirm Servo AF opens the complete Case 1–4 / Case A selector and does not change AF Operation.</x:v>
       </x:c>
       <x:c r="E6" s="17" t="n">
         <x:v>5</x:v>
@@ -5277,16 +5319,16 @@
     </x:row>
     <x:row r="7" hidden="0">
       <x:c r="A7" s="10" t="str">
-        <x:v>SETUP-05</x:v>
+        <x:v>SETUP-04</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>MENU</x:v>
+        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio; MM-AF Case for Servo AF Case</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
-        <x:v>Shooting 7: Shooting info. disp. &gt; Screen info. settings &gt; Histogram &gt; RGB; Playback 5: Highlight alert &gt; Enable</x:v>
+        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; My Menu AF Case &gt; Servo AF or AF3 &gt; Servo AF characteristics: Case A; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting menu: IS (Image Stabilizer) mode</x:v>
       </x:c>
       <x:c r="E7" s="17" t="n">
         <x:v>6</x:v>
@@ -5294,7 +5336,7 @@
     </x:row>
     <x:row r="8" hidden="0">
       <x:c r="A8" s="10" t="str">
-        <x:v>SETUP-06</x:v>
+        <x:v>SETUP-05</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
         <x:v>MENU</x:v>
@@ -5303,7 +5345,7 @@
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
-        <x:v>Shooting 4: Long exp. noise reduction and High ISO speed NR; AF1: Continuous AF; AF menu: Lens electronic MF; Shooting 5: IBIS High resolution shot</x:v>
+        <x:v>Shooting 7: Shooting info. disp. &gt; Screen info. settings &gt; Histogram &gt; RGB; Playback 5: Highlight alert &gt; Enable</x:v>
       </x:c>
       <x:c r="E8" s="17" t="n">
         <x:v>7</x:v>
@@ -5311,16 +5353,16 @@
     </x:row>
     <x:row r="9" hidden="0">
       <x:c r="A9" s="10" t="str">
-        <x:v>SETUP-07</x:v>
+        <x:v>SETUP-06</x:v>
       </x:c>
       <x:c r="B9" s="13" t="str">
         <x:v>MENU</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>AF menu</x:v>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>MF peaking settings &gt; Peaking: On; Level: Low; Color: Red</x:v>
+        <x:v>Shooting 4: Long exp. noise reduction and High ISO speed NR; AF1: Continuous AF; AF menu: Lens electronic MF; Shooting 5: IBIS High resolution shot</x:v>
       </x:c>
       <x:c r="E9" s="17" t="n">
         <x:v>8</x:v>
@@ -5328,16 +5370,16 @@
     </x:row>
     <x:row r="10" hidden="0">
       <x:c r="A10" s="10" t="str">
-        <x:v>CTRL-CONFIG-01</x:v>
+        <x:v>SETUP-07</x:v>
       </x:c>
       <x:c r="B10" s="13" t="str">
-        <x:v>Physical controls; MENU</x:v>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>Custom Functions 3</x:v>
+        <x:v>AF menu</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>Customize buttons and Customize dials; use Customize buttons for shutter half-press, AF-ON, AE Lock, AF Point Selection, lens AF, DOF, SET, joystick, and M-Fn</x:v>
+        <x:v>MF peaking settings &gt; Peaking: On; Level: Low; Color: Red</x:v>
       </x:c>
       <x:c r="E10" s="17" t="n">
         <x:v>9</x:v>
@@ -5345,16 +5387,16 @@
     </x:row>
     <x:row r="11" hidden="0">
       <x:c r="A11" s="10" t="str">
-        <x:v>BACKUP-SET-01</x:v>
+        <x:v>CTRL-CONFIG-01</x:v>
       </x:c>
       <x:c r="B11" s="13" t="str">
-        <x:v>MENU</x:v>
+        <x:v>Physical controls; MENU</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>Set-up 5</x:v>
+        <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="D11" s="15" t="str">
-        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
+        <x:v>Customize buttons and Customize dials; use Customize buttons for shutter half-press, AF-ON, AE Lock, AF Point Selection, lens AF, DOF, SET, joystick, and M-Fn</x:v>
       </x:c>
       <x:c r="E11" s="17" t="n">
         <x:v>10</x:v>
@@ -5362,16 +5404,16 @@
     </x:row>
     <x:row r="12" hidden="0">
       <x:c r="A12" s="10" t="str">
-        <x:v>C1-CONFIG-01</x:v>
+        <x:v>BACKUP-SET-01</x:v>
       </x:c>
       <x:c r="B12" s="13" t="str">
-        <x:v>Q, dials, AF controls, MM-SWITCH, lens IS switch</x:v>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>Multiple</x:v>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="D12" s="15" t="str">
-        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, AF Drive mode, and lens IS switch</x:v>
+        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
       </x:c>
       <x:c r="E12" s="17" t="n">
         <x:v>11</x:v>
@@ -5379,16 +5421,16 @@
     </x:row>
     <x:row r="13" hidden="0">
       <x:c r="A13" s="10" t="str">
-        <x:v>C1-REG-01</x:v>
+        <x:v>C1-CONFIG-01</x:v>
       </x:c>
       <x:c r="B13" s="13" t="str">
-        <x:v>MENU</x:v>
+        <x:v>Q, dials, AF controls, MM-SWITCH, MM-AF Case, lens IS switch</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>Set-up 5</x:v>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D13" s="15" t="str">
-        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C1</x:v>
+        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, My Menu AF Case or AF3 Servo AF characteristics, AF Drive mode, and lens IS switch</x:v>
       </x:c>
       <x:c r="E13" s="17" t="n">
         <x:v>12</x:v>
@@ -5396,16 +5438,16 @@
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14" s="10" t="str">
-        <x:v>C1-READ-01</x:v>
+        <x:v>C1-REG-01</x:v>
       </x:c>
       <x:c r="B14" s="13" t="str">
-        <x:v>M-Fn recall; Q; MM-SWITCH; MENU</x:v>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>No single menu</x:v>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="D14" s="15" t="str">
-        <x:v>Recall C1 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
+        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C1</x:v>
       </x:c>
       <x:c r="E14" s="17" t="n">
         <x:v>13</x:v>
@@ -5413,16 +5455,16 @@
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="10" t="str">
-        <x:v>C1-OPS-01</x:v>
+        <x:v>C1-READ-01</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
-        <x:v>Physical controls</x:v>
+        <x:v>M-Fn recall; Q; MM-SWITCH; MM-AF Case; MENU</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>No menu</x:v>
+        <x:v>No single menu</x:v>
       </x:c>
       <x:c r="D15" s="15" t="str">
-        <x:v>Operational shooting test</x:v>
+        <x:v>Recall C1 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
       </x:c>
       <x:c r="E15" s="17" t="n">
         <x:v>14</x:v>
@@ -5430,16 +5472,16 @@
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="10" t="str">
-        <x:v>C2-CONFIG-01</x:v>
+        <x:v>C1-OPS-01</x:v>
       </x:c>
       <x:c r="B16" s="13" t="str">
-        <x:v>Q, dials, AF controls, MM-SWITCH, lens IS switch</x:v>
+        <x:v>Physical controls</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>Multiple</x:v>
+        <x:v>No menu</x:v>
       </x:c>
       <x:c r="D16" s="15" t="str">
-        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, AF Drive mode, and lens IS switch</x:v>
+        <x:v>Operational shooting test</x:v>
       </x:c>
       <x:c r="E16" s="17" t="n">
         <x:v>15</x:v>
@@ -5447,16 +5489,16 @@
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="10" t="str">
-        <x:v>C2-REG-01</x:v>
+        <x:v>C2-CONFIG-01</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>MENU</x:v>
+        <x:v>Q, dials, AF controls, MM-SWITCH, MM-AF Case, lens IS switch</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>Set-up 5</x:v>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
-        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C2</x:v>
+        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, My Menu AF Case or AF3 Servo AF characteristics, AF Drive mode, and lens IS switch</x:v>
       </x:c>
       <x:c r="E17" s="17" t="n">
         <x:v>16</x:v>
@@ -5464,16 +5506,16 @@
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="10" t="str">
-        <x:v>C2-READ-01</x:v>
+        <x:v>C2-REG-01</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>M-Fn recall; Q; MM-SWITCH; MENU</x:v>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>No single menu</x:v>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="D18" s="15" t="str">
-        <x:v>Recall C2 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
+        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C2</x:v>
       </x:c>
       <x:c r="E18" s="17" t="n">
         <x:v>17</x:v>
@@ -5481,16 +5523,16 @@
     </x:row>
     <x:row r="19" hidden="0">
       <x:c r="A19" s="10" t="str">
-        <x:v>C2-OPS-01</x:v>
+        <x:v>C2-READ-01</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
-        <x:v>Physical controls</x:v>
+        <x:v>M-Fn recall; Q; MM-SWITCH; MM-AF Case; MENU</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>No menu</x:v>
+        <x:v>No single menu</x:v>
       </x:c>
       <x:c r="D19" s="15" t="str">
-        <x:v>Operational shooting test</x:v>
+        <x:v>Recall C2 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
       </x:c>
       <x:c r="E19" s="17" t="n">
         <x:v>18</x:v>
@@ -5498,16 +5540,16 @@
     </x:row>
     <x:row r="20" hidden="0">
       <x:c r="A20" s="10" t="str">
-        <x:v>C3-CONFIG-01</x:v>
+        <x:v>C2-OPS-01</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>Q, dials, AF controls, MM-SWITCH, lens IS switch</x:v>
+        <x:v>Physical controls</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>Multiple</x:v>
+        <x:v>No menu</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
-        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, AF Drive mode, and lens IS switch</x:v>
+        <x:v>Operational shooting test</x:v>
       </x:c>
       <x:c r="E20" s="17" t="n">
         <x:v>19</x:v>
@@ -5515,16 +5557,16 @@
     </x:row>
     <x:row r="21" hidden="0">
       <x:c r="A21" s="10" t="str">
-        <x:v>C3-REG-01</x:v>
+        <x:v>C3-CONFIG-01</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
-        <x:v>MENU</x:v>
+        <x:v>Q, dials, AF controls, MM-SWITCH, lens IS switch</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Set-up 5</x:v>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D21" s="15" t="str">
-        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C3</x:v>
+        <x:v>Shooting screen/Quick Control plus Shooting 1, Shooting 2, Shooting 5, Shooting 6, Shooting 7, AF1, AF Drive mode, and lens IS switch</x:v>
       </x:c>
       <x:c r="E21" s="17" t="n">
         <x:v>20</x:v>
@@ -5532,16 +5574,16 @@
     </x:row>
     <x:row r="22" hidden="0">
       <x:c r="A22" s="10" t="str">
-        <x:v>C3-READ-01</x:v>
+        <x:v>C3-REG-01</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>M-Fn recall; Q; MM-SWITCH; MENU</x:v>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>No single menu</x:v>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="D22" s="15" t="str">
-        <x:v>Recall C3 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
+        <x:v>Custom shooting mode (C1-C3) &gt; Register settings &gt; C3</x:v>
       </x:c>
       <x:c r="E22" s="17" t="n">
         <x:v>21</x:v>
@@ -5549,16 +5591,16 @@
     </x:row>
     <x:row r="23" hidden="0">
       <x:c r="A23" s="10" t="str">
-        <x:v>BACKUP-SET-02</x:v>
+        <x:v>C3-READ-01</x:v>
       </x:c>
       <x:c r="B23" s="13" t="str">
-        <x:v>MENU</x:v>
+        <x:v>M-Fn recall; Q; MM-SWITCH; MENU</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>Set-up 5</x:v>
+        <x:v>No single menu</x:v>
       </x:c>
       <x:c r="D23" s="15" t="str">
-        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
+        <x:v>Recall C3 with M-Fn; verify the shooting screen, Quick Control screen, My Menu shortcuts, and applicable menu settings</x:v>
       </x:c>
       <x:c r="E23" s="17" t="n">
         <x:v>22</x:v>
@@ -5566,16 +5608,16 @@
     </x:row>
     <x:row r="24" hidden="0">
       <x:c r="A24" s="10" t="str">
-        <x:v>C3-OPS-01</x:v>
+        <x:v>BACKUP-SET-02</x:v>
       </x:c>
       <x:c r="B24" s="13" t="str">
-        <x:v>Physical controls</x:v>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>No menu</x:v>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="D24" s="15" t="str">
-        <x:v>Operational shooting test</x:v>
+        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
       </x:c>
       <x:c r="E24" s="17" t="n">
         <x:v>23</x:v>
@@ -5583,16 +5625,16 @@
     </x:row>
     <x:row r="25" hidden="0">
       <x:c r="A25" s="10" t="str">
-        <x:v>CTRL-AFON-01</x:v>
+        <x:v>C3-OPS-01</x:v>
       </x:c>
       <x:c r="B25" s="13" t="str">
-        <x:v>AF-ON; INFO</x:v>
+        <x:v>Physical controls</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Custom Functions 3</x:v>
+        <x:v>No menu</x:v>
       </x:c>
       <x:c r="D25" s="15" t="str">
-        <x:v>Customize buttons &gt; AF-ON; press INFO to verify AF Operation, AF Method, and Servo AF characteristics</x:v>
+        <x:v>Operational shooting test</x:v>
       </x:c>
       <x:c r="E25" s="17" t="n">
         <x:v>24</x:v>
@@ -5600,16 +5642,16 @@
     </x:row>
     <x:row r="26" hidden="0">
       <x:c r="A26" s="10" t="str">
-        <x:v>CTRL-AELOCK-01</x:v>
+        <x:v>CTRL-AFON-01</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
-        <x:v>AE Lock; INFO</x:v>
+        <x:v>AF-ON; INFO</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
         <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="D26" s="15" t="str">
-        <x:v>Customize buttons &gt; AE Lock; press INFO to verify AF Operation, AF Method, and Servo AF characteristics</x:v>
+        <x:v>Customize buttons &gt; AF-ON; press INFO to verify AF Operation, AF Method, and Servo AF characteristics</x:v>
       </x:c>
       <x:c r="E26" s="17" t="n">
         <x:v>25</x:v>
@@ -5617,16 +5659,16 @@
     </x:row>
     <x:row r="27" hidden="0">
       <x:c r="A27" s="10" t="str">
-        <x:v>CTRL-DOF-01</x:v>
+        <x:v>CTRL-AELOCK-01</x:v>
       </x:c>
       <x:c r="B27" s="13" t="str">
-        <x:v>DOF button</x:v>
+        <x:v>AE Lock; INFO</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
         <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="D27" s="15" t="str">
-        <x:v>Customize buttons &gt; Depth-of-field preview &gt; One-Shot AF ↔ Servo AF</x:v>
+        <x:v>Customize buttons &gt; AE Lock; press INFO to verify AF Operation, AF Method, and Servo AF characteristics</x:v>
       </x:c>
       <x:c r="E27" s="17" t="n">
         <x:v>26</x:v>
@@ -5634,16 +5676,16 @@
     </x:row>
     <x:row r="28" hidden="0">
       <x:c r="A28" s="10" t="str">
-        <x:v>CTRL-SET-01</x:v>
+        <x:v>CTRL-DOF-01</x:v>
       </x:c>
       <x:c r="B28" s="13" t="str">
-        <x:v>SET button</x:v>
+        <x:v>DOF button</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
         <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="D28" s="15" t="str">
-        <x:v>Customize buttons &gt; SET &gt; Eye detection</x:v>
+        <x:v>Customize buttons &gt; Depth-of-field preview &gt; One-Shot AF ↔ Servo AF</x:v>
       </x:c>
       <x:c r="E28" s="17" t="n">
         <x:v>27</x:v>
@@ -5651,16 +5693,16 @@
     </x:row>
     <x:row r="29" hidden="0">
       <x:c r="A29" s="10" t="str">
-        <x:v>CTRL-JOY-01</x:v>
+        <x:v>CTRL-SET-01</x:v>
       </x:c>
       <x:c r="B29" s="13" t="str">
-        <x:v>Joystick</x:v>
+        <x:v>SET button</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="D29" s="15" t="str">
-        <x:v>Customize buttons &gt; Multi-controller &gt; Direct AF point selection</x:v>
+        <x:v>Customize buttons &gt; SET &gt; Eye detection</x:v>
       </x:c>
       <x:c r="E29" s="17" t="n">
         <x:v>28</x:v>
@@ -5668,16 +5710,16 @@
     </x:row>
     <x:row r="30" hidden="0">
       <x:c r="A30" s="10" t="str">
-        <x:v>EFCS-SHOCK-01</x:v>
+        <x:v>CTRL-JOY-01</x:v>
       </x:c>
       <x:c r="B30" s="13" t="str">
-        <x:v>MM-SWITCH</x:v>
+        <x:v>Joystick</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>Shooting 6</x:v>
+        <x:v>Custom Functions 3</x:v>
       </x:c>
       <x:c r="D30" s="15" t="str">
-        <x:v>Shutter mode; use EFCS and Mechanical for the comparison</x:v>
+        <x:v>Customize buttons &gt; Multi-controller &gt; Direct AF point selection</x:v>
       </x:c>
       <x:c r="E30" s="17" t="n">
         <x:v>29</x:v>
@@ -5685,7 +5727,7 @@
     </x:row>
     <x:row r="31" hidden="0">
       <x:c r="A31" s="10" t="str">
-        <x:v>EFCS-BOKEH-01</x:v>
+        <x:v>EFCS-SHOCK-01</x:v>
       </x:c>
       <x:c r="B31" s="13" t="str">
         <x:v>MM-SWITCH</x:v>
@@ -5702,16 +5744,16 @@
     </x:row>
     <x:row r="32" hidden="0">
       <x:c r="A32" s="10" t="str">
-        <x:v>EFCS-LIGHT-01</x:v>
+        <x:v>EFCS-BOKEH-01</x:v>
       </x:c>
       <x:c r="B32" s="13" t="str">
-        <x:v>MM-SWITCH; MENU for Anti-flicker</x:v>
+        <x:v>MM-SWITCH</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>Multiple</x:v>
+        <x:v>Shooting 6</x:v>
       </x:c>
       <x:c r="D32" s="15" t="str">
-        <x:v>Shooting 6: Shutter mode; Shooting 2: Anti-flicker shoot.</x:v>
+        <x:v>Shutter mode; use EFCS and Mechanical for the comparison</x:v>
       </x:c>
       <x:c r="E32" s="17" t="n">
         <x:v>31</x:v>
@@ -5719,16 +5761,16 @@
     </x:row>
     <x:row r="33" hidden="0">
       <x:c r="A33" s="10" t="str">
-        <x:v>EFCS-BURST-01</x:v>
+        <x:v>EFCS-LIGHT-01</x:v>
       </x:c>
       <x:c r="B33" s="13" t="str">
-        <x:v>MM-SWITCH; Q for Drive mode</x:v>
+        <x:v>MM-SWITCH; MENU for Anti-flicker</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D33" s="15" t="str">
-        <x:v>Shooting 6: Shutter mode; AF menu/Quick Control: Drive mode</x:v>
+        <x:v>Shooting 6: Shutter mode; Shooting 2: Anti-flicker shoot.</x:v>
       </x:c>
       <x:c r="E33" s="17" t="n">
         <x:v>32</x:v>
@@ -5736,16 +5778,16 @@
     </x:row>
     <x:row r="34" hidden="0">
       <x:c r="A34" s="10" t="str">
-        <x:v>FLASH-PLUTO-01</x:v>
+        <x:v>EFCS-BURST-01</x:v>
       </x:c>
       <x:c r="B34" s="13" t="str">
-        <x:v>MM-SWITCH; shooting controls</x:v>
+        <x:v>MM-SWITCH; Q for Drive mode</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D34" s="15" t="str">
-        <x:v>Shooting 6: Shutter mode &gt; Mechanical; shooting screen: M, 1/200 sec., aperture, ISO; Shooting 2: External Speedlite control when applicable</x:v>
+        <x:v>Shooting 6: Shutter mode; AF menu/Quick Control: Drive mode</x:v>
       </x:c>
       <x:c r="E34" s="17" t="n">
         <x:v>33</x:v>
@@ -5753,16 +5795,16 @@
     </x:row>
     <x:row r="35" hidden="0">
       <x:c r="A35" s="10" t="str">
-        <x:v>FINAL-READ-01</x:v>
+        <x:v>FLASH-PLUTO-01</x:v>
       </x:c>
       <x:c r="B35" s="13" t="str">
-        <x:v>M-Fn; MM-SWITCH; Q; MENU</x:v>
+        <x:v>MM-SWITCH; shooting controls</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D35" s="15" t="str">
-        <x:v>Recall C1-C3 with M-Fn; verify SWITCH; Set-up 5 confirm Auto update is disabled; Custom Functions 3 confirm control assignments</x:v>
+        <x:v>Shooting 6: Shutter mode &gt; Mechanical; shooting screen: M, 1/200 sec., aperture, ISO; Shooting 2: External Speedlite control when applicable</x:v>
       </x:c>
       <x:c r="E35" s="17" t="n">
         <x:v>34</x:v>
@@ -5770,16 +5812,16 @@
     </x:row>
     <x:row r="36" hidden="0">
       <x:c r="A36" s="10" t="str">
-        <x:v>FINAL-SAVE-01</x:v>
+        <x:v>FINAL-READ-01</x:v>
       </x:c>
       <x:c r="B36" s="13" t="str">
-        <x:v>MENU</x:v>
+        <x:v>M-Fn; MM-SWITCH; MM-AF Case; Q; MENU</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>Set-up 5</x:v>
+        <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D36" s="15" t="str">
-        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
+        <x:v>Recall C1-C3 with M-Fn; verify SWITCH and AF Case; Set-up 5 confirm Auto update is disabled; Custom Functions 3 confirm control assignments</x:v>
       </x:c>
       <x:c r="E36" s="17" t="n">
         <x:v>35</x:v>
@@ -5787,25 +5829,42 @@
     </x:row>
     <x:row r="37" hidden="0">
       <x:c r="A37" s="10" t="str">
-        <x:v>PROJECT-UPDATE-01</x:v>
+        <x:v>FINAL-SAVE-01</x:v>
       </x:c>
       <x:c r="B37" s="13" t="str">
-        <x:v>Completed tracker</x:v>
+        <x:v>MENU</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>No camera menu</x:v>
+        <x:v>Set-up 5</x:v>
       </x:c>
       <x:c r="D37" s="15" t="str">
-        <x:v>Review the completed tracker and update the reference-system evidence states</x:v>
+        <x:v>Save/load cam settings on card &gt; Save to card</x:v>
       </x:c>
       <x:c r="E37" s="17" t="n">
         <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" hidden="0">
+      <x:c r="A38" s="10" t="str">
+        <x:v>PROJECT-UPDATE-01</x:v>
+      </x:c>
+      <x:c r="B38" s="13" t="str">
+        <x:v>Completed tracker</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="str">
+        <x:v>No camera menu</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="str">
+        <x:v>Review the completed tracker and update the reference-system evidence states</x:v>
+      </x:c>
+      <x:c r="E38" s="17" t="n">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R6190d70f3fae42e6"/>
+    <x:tablePart ns1:id="Rbbe7f96db5da4d45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5831,604 +5890,626 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="105" t="str">
+      <x:c r="A2" s="99" t="str">
         <x:v>workbook_revision</x:v>
       </x:c>
-      <x:c r="B2" s="105" t="str"/>
-      <x:c r="C2" s="105" t="str">
-        <x:v>1</x:v>
+      <x:c r="B2" s="99" t="str"/>
+      <x:c r="C2" s="99" t="str">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="105" t="str">
+      <x:c r="A3" s="99" t="str">
         <x:v>source_fingerprint</x:v>
       </x:c>
-      <x:c r="B3" s="105" t="str"/>
-      <x:c r="C3" s="105" t="str">
-        <x:v>sha256:968f506ee79f26894f64dc617f7c33cbb260fc0ded6fe3e573fbf7549e79da56</x:v>
+      <x:c r="B3" s="99" t="str"/>
+      <x:c r="C3" s="99" t="str">
+        <x:v>sha256:63ee9d6d18b374f3ee3b85a67466c6b5a0fe162dfa586934cf4fd911acf6e3fe</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="105" t="str">
+      <x:c r="A4" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B4" s="105" t="str">
+      <x:c r="B4" s="99" t="str">
         <x:v>SETUP-01</x:v>
       </x:c>
-      <x:c r="C4" s="105" t="str">
+      <x:c r="C4" s="99" t="str">
         <x:v>sha256:6298d64e10367b2e38e5d41253bb816c1012479ab7612afc5a53ad66630e975f</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="105" t="str">
+      <x:c r="A5" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B5" s="105" t="str">
+      <x:c r="B5" s="99" t="str">
         <x:v>SETUP-02</x:v>
       </x:c>
-      <x:c r="C5" s="105" t="str">
+      <x:c r="C5" s="99" t="str">
         <x:v>sha256:2c28c37a65e2efee3349ec9d9c3a6e75de10e76697f1c3b5ec5ca8d1ceae0030</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="105" t="str">
+      <x:c r="A6" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B6" s="105" t="str">
+      <x:c r="B6" s="99" t="str">
         <x:v>SETUP-03</x:v>
       </x:c>
-      <x:c r="C6" s="105" t="str">
+      <x:c r="C6" s="99" t="str">
         <x:v>sha256:eb596d6e2a1ad3dba500a053b487e07af4813566f59012575380f500c95740a3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="105" t="str">
+      <x:c r="A7" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B7" s="105" t="str">
+      <x:c r="B7" s="99" t="str">
         <x:v>SETUP-MM-01</x:v>
       </x:c>
-      <x:c r="C7" s="105" t="str">
-        <x:v>sha256:10c1951c74b44263db5ff6b5725ac0017ef930c909beb4e4acb1fb7b0d6a1e37</x:v>
+      <x:c r="C7" s="99" t="str">
+        <x:v>sha256:c760cc1bea9609da89be5d36089ba2323849d51903b5f40f43c986536aab0cc0</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="105" t="str">
+      <x:c r="A8" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B8" s="105" t="str">
+      <x:c r="B8" s="99" t="str">
+        <x:v>SETUP-MM-AF-01</x:v>
+      </x:c>
+      <x:c r="C8" s="99" t="str">
+        <x:v>sha256:640095557a45fc26bff30bed84e3dd0f081eee4f34666a3ac6f03baffad58ba1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="99" t="str">
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B9" s="99" t="str">
         <x:v>SETUP-04</x:v>
       </x:c>
-      <x:c r="C8" s="105" t="str">
-        <x:v>sha256:0fd3d39f08967cfa6c6072c55ec3ea4582751e1df839097908d8157e9e08ce0a</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="105" t="str">
+      <x:c r="C9" s="99" t="str">
+        <x:v>sha256:0810980437956c762e776c7d3c3c83ace9e5e624352479bd6ec652a9c66f8a65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B9" s="105" t="str">
+      <x:c r="B10" s="99" t="str">
         <x:v>SETUP-05</x:v>
       </x:c>
-      <x:c r="C9" s="105" t="str">
-        <x:v>sha256:fe40d0591ea5bb918a95096896c88e57973a17e604de841f7b2e42718910d160</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="105" t="str">
+      <x:c r="C10" s="99" t="str">
+        <x:v>sha256:67ea99e7324822765d73c9e1a978991ba090dd1fcb01bc4f819eb693e2018f1b</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B10" s="105" t="str">
+      <x:c r="B11" s="99" t="str">
         <x:v>SETUP-06</x:v>
       </x:c>
-      <x:c r="C10" s="105" t="str">
-        <x:v>sha256:beaf13d7430d2d3162636f073285172d26c909da7a8d59e4fa99be242e35555d</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="105" t="str">
+      <x:c r="C11" s="99" t="str">
+        <x:v>sha256:50a7bb1d684b76be2ecaf5dd70540adcc5036481c265a2d6e4348a13c0d3f061</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B11" s="105" t="str">
+      <x:c r="B12" s="99" t="str">
         <x:v>SETUP-07</x:v>
       </x:c>
-      <x:c r="C11" s="105" t="str">
-        <x:v>sha256:ae9a5f9d945a50c4ccc176c38f7c0029989fda3f1c58b5a69600eafb1b80cb79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="105" t="str">
+      <x:c r="C12" s="99" t="str">
+        <x:v>sha256:4465ab573d202c4fbb497291b08a1c5ffffad91c48872e300991471bef2567f4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B12" s="105" t="str">
+      <x:c r="B13" s="99" t="str">
         <x:v>CTRL-CONFIG-01</x:v>
       </x:c>
-      <x:c r="C12" s="105" t="str">
-        <x:v>sha256:5255a806565847c3cb210c1f8d9507d27ff69d5f711fbcaebfc48b18d08d9ffd</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="105" t="str">
+      <x:c r="C13" s="99" t="str">
+        <x:v>sha256:bf207e6d54b48768207e423d534c48709f88f234d55bdcb9613e260a68c411f2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B13" s="105" t="str">
+      <x:c r="B14" s="99" t="str">
         <x:v>BACKUP-SET-01</x:v>
       </x:c>
-      <x:c r="C13" s="105" t="str">
-        <x:v>sha256:c8b709cad4c4eb614fa10afd8f3ee3e509cc2c66a5a1da4652b50dee3412f853</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="105" t="str">
+      <x:c r="C14" s="99" t="str">
+        <x:v>sha256:a17b1005496620e34a1ee11e646e9a1fc082c4eb20ac617592011ba5e6ceae8a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B14" s="105" t="str">
+      <x:c r="B15" s="99" t="str">
         <x:v>C1-CONFIG-01</x:v>
       </x:c>
-      <x:c r="C14" s="105" t="str">
-        <x:v>sha256:bb51b8b1302bce99686d64b8b0cbf269285b79f05cdb854749bd64aea89b1012</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="105" t="str">
+      <x:c r="C15" s="99" t="str">
+        <x:v>sha256:1507d79e9f067c7c5b2099b8101a3d17938d127abce04324c2c3ac3d6b72efd7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B15" s="105" t="str">
+      <x:c r="B16" s="99" t="str">
         <x:v>C1-REG-01</x:v>
       </x:c>
-      <x:c r="C15" s="105" t="str">
-        <x:v>sha256:f461ea2e61ae1e9b6979dce7f6745b9816601528fb68a6618d8eadcbdd17a502</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="105" t="str">
+      <x:c r="C16" s="99" t="str">
+        <x:v>sha256:04a561cd1850599049f01a2ec97355afe25fe8c5fc4c4c81d52f639897d63b03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B16" s="105" t="str">
+      <x:c r="B17" s="99" t="str">
         <x:v>C1-READ-01</x:v>
       </x:c>
-      <x:c r="C16" s="105" t="str">
-        <x:v>sha256:10a6be7db7226c276100bc1736c6201418a5cd05438549f1159ce0ce561d47bd</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="105" t="str">
+      <x:c r="C17" s="99" t="str">
+        <x:v>sha256:2c25a1c907b5edcc56c06bd4e4bd1d8dde41fa6faebde85baec2ab4a2acefd87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B17" s="105" t="str">
+      <x:c r="B18" s="99" t="str">
         <x:v>C1-OPS-01</x:v>
       </x:c>
-      <x:c r="C17" s="105" t="str">
-        <x:v>sha256:a9eb069693e2acc07f7f74fef525c73def1af24177d2490618dfb430558f3447</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="105" t="str">
+      <x:c r="C18" s="99" t="str">
+        <x:v>sha256:91738d7d064f766c1edb2c710fe5f029e24037f657476aa2df79914c67ce7318</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B18" s="105" t="str">
+      <x:c r="B19" s="99" t="str">
         <x:v>C2-CONFIG-01</x:v>
       </x:c>
-      <x:c r="C18" s="105" t="str">
-        <x:v>sha256:f6bd4b38d09cefcd6ef7d79d6df02a5f7d08811ad471c4c65c5dba1acede5797</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="105" t="str">
+      <x:c r="C19" s="99" t="str">
+        <x:v>sha256:cb99fda58735522dedf306188a4a8f12400a51676d686f840b660c38650789c3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B19" s="105" t="str">
+      <x:c r="B20" s="99" t="str">
         <x:v>C2-REG-01</x:v>
       </x:c>
-      <x:c r="C19" s="105" t="str">
-        <x:v>sha256:63fb5022c877bccd92feb9c02cb90b74feda63d1eb9993f889d0fe1420a6485e</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="105" t="str">
+      <x:c r="C20" s="99" t="str">
+        <x:v>sha256:f4b28c92d9a20605b591f5721dd3ad3beff4e7b5105c8c15a65d23398e8e2d56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B20" s="105" t="str">
+      <x:c r="B21" s="99" t="str">
         <x:v>C2-READ-01</x:v>
       </x:c>
-      <x:c r="C20" s="105" t="str">
-        <x:v>sha256:ff4e52f0766604bfc924d274273adb0fecb5f24fa22997163f0ff7ca62568e84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="105" t="str">
+      <x:c r="C21" s="99" t="str">
+        <x:v>sha256:cda561c58eb3b3eeb7b5d8b86836960a48f9ee79058073e4943561aa9c9b39d1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B21" s="105" t="str">
+      <x:c r="B22" s="99" t="str">
         <x:v>C2-OPS-01</x:v>
       </x:c>
-      <x:c r="C21" s="105" t="str">
-        <x:v>sha256:1a9d7974ba1beac809f4901e4932230f9975a65d4fd4dc0095e2b7020b9ff262</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="105" t="str">
+      <x:c r="C22" s="99" t="str">
+        <x:v>sha256:d939e6407cadc5480c2f88547845d69f1e2e36a37b7ae6635cebcdde0e9ce030</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B22" s="105" t="str">
+      <x:c r="B23" s="99" t="str">
         <x:v>C3-CONFIG-01</x:v>
       </x:c>
-      <x:c r="C22" s="105" t="str">
-        <x:v>sha256:45e2ad8ae739d2475bad363b56afd793dbfeacf56f7a9c09cfe62d4d90d73b76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="105" t="str">
+      <x:c r="C23" s="99" t="str">
+        <x:v>sha256:633063511fb285503511b318ef26bf092ac48be8afda4df5ef008ab645d4f712</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B23" s="105" t="str">
+      <x:c r="B24" s="99" t="str">
         <x:v>C3-REG-01</x:v>
       </x:c>
-      <x:c r="C23" s="105" t="str">
-        <x:v>sha256:9f5660b058d96ef2a52760a2323d545f63f41f2a651403cd58fde27e840fe894</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="105" t="str">
+      <x:c r="C24" s="99" t="str">
+        <x:v>sha256:f692886e78e72d84e31a5ef91aa281938d0529b8b7ea1a220bbf200993144e29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B24" s="105" t="str">
+      <x:c r="B25" s="99" t="str">
         <x:v>C3-READ-01</x:v>
       </x:c>
-      <x:c r="C24" s="105" t="str">
-        <x:v>sha256:778742d0d1c3d1effa3c73595a59bb77f362c9568e066b27aa362f9b7ce7d860</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="105" t="str">
+      <x:c r="C25" s="99" t="str">
+        <x:v>sha256:44b63514e2b1f8af98d36c6a4a25a22b7d554a7055c63b717a390b5801f4f72f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B25" s="105" t="str">
+      <x:c r="B26" s="99" t="str">
         <x:v>BACKUP-SET-02</x:v>
       </x:c>
-      <x:c r="C25" s="105" t="str">
-        <x:v>sha256:884924d58217f4016aef83b195bd222dfb574f9d5ebf19c384f8014e3b0f6dc4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="105" t="str">
+      <x:c r="C26" s="99" t="str">
+        <x:v>sha256:d8e92939499af335b6f4493b97c7fa8671ad4fc3910cca9a5f8eda4ef41cfc2f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B26" s="105" t="str">
+      <x:c r="B27" s="99" t="str">
         <x:v>C3-OPS-01</x:v>
       </x:c>
-      <x:c r="C26" s="105" t="str">
-        <x:v>sha256:871d4c0cc392fa3e52b4d6f8ac15b759922a8b710c12006e6b1633d076ffeec3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="105" t="str">
+      <x:c r="C27" s="99" t="str">
+        <x:v>sha256:c60f649504d508a81fa0bd19f172421676472153728093142a04d2ba4e5c96ad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B27" s="105" t="str">
+      <x:c r="B28" s="99" t="str">
         <x:v>CTRL-AFON-01</x:v>
       </x:c>
-      <x:c r="C27" s="105" t="str">
-        <x:v>sha256:f252e2d863b240907c921c3d4a3d318917f1ece11491b1efac56eed5ac7d0f96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="105" t="str">
+      <x:c r="C28" s="99" t="str">
+        <x:v>sha256:2c3055256d014c23ff48c71e8998a544186d8606fc4ad766773ec6c14976f6d7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B28" s="105" t="str">
+      <x:c r="B29" s="99" t="str">
         <x:v>CTRL-AELOCK-01</x:v>
       </x:c>
-      <x:c r="C28" s="105" t="str">
-        <x:v>sha256:d4faf5d8ee507a918a0c8e2b0879dcc44f1777165fc676dcbda956e992fcc0f5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="105" t="str">
+      <x:c r="C29" s="99" t="str">
+        <x:v>sha256:888daf7bc311ea1a395e8a7406c8caac4655da1853803ba28df50d40a03fda9b</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B29" s="105" t="str">
+      <x:c r="B30" s="99" t="str">
         <x:v>CTRL-DOF-01</x:v>
       </x:c>
-      <x:c r="C29" s="105" t="str">
-        <x:v>sha256:84542934d1112e37aa42040c8d95b637393d4366ac13c443bf47ef2be662b860</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="105" t="str">
+      <x:c r="C30" s="99" t="str">
+        <x:v>sha256:606ba83c6c6ef93bebe9f6f0451a7c80fead0f83b62fd48fe2137c5a72fa3b19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B30" s="105" t="str">
+      <x:c r="B31" s="99" t="str">
         <x:v>CTRL-SET-01</x:v>
       </x:c>
-      <x:c r="C30" s="105" t="str">
-        <x:v>sha256:16342ed08b4fc44ea0451a0a8935c8504303e9e01dae091aa87ab20c45ad6ad8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="105" t="str">
+      <x:c r="C31" s="99" t="str">
+        <x:v>sha256:ad0d38b06de1f9f53cde8acce71775385e4aaef6588e771934320e4124431e25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B31" s="105" t="str">
+      <x:c r="B32" s="99" t="str">
         <x:v>CTRL-JOY-01</x:v>
       </x:c>
-      <x:c r="C31" s="105" t="str">
-        <x:v>sha256:828c831b73117d3abc47657bd6986e93ca40a08458c77603a0085569656a2ed7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="105" t="str">
+      <x:c r="C32" s="99" t="str">
+        <x:v>sha256:957387ec73ac18ab4785a4aaf972f7e285c513c90769f009edece0c97f044600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B32" s="105" t="str">
+      <x:c r="B33" s="99" t="str">
         <x:v>EFCS-SHOCK-01</x:v>
       </x:c>
-      <x:c r="C32" s="105" t="str">
-        <x:v>sha256:ea49c5e02cf4986fa87a0e77a31a16b4c8dceb72d35bf6ec4fa8b2ad5bf29018</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="105" t="str">
+      <x:c r="C33" s="99" t="str">
+        <x:v>sha256:5536143e9808461e6a2779baa6f8d2adf0dd969cccb0b7d2a28598a924d61203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B33" s="105" t="str">
+      <x:c r="B34" s="99" t="str">
         <x:v>EFCS-BOKEH-01</x:v>
       </x:c>
-      <x:c r="C33" s="105" t="str">
-        <x:v>sha256:3661cf4b3c827113f1bd6729a9c71f07e0934b73d2c287dac02bf2a66ff2a0ca</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="105" t="str">
+      <x:c r="C34" s="99" t="str">
+        <x:v>sha256:4e1bd076174191e3341b0eb9a6f2279f745b35cc3425dbd6e1360e771e5f3a42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B34" s="105" t="str">
+      <x:c r="B35" s="99" t="str">
         <x:v>EFCS-LIGHT-01</x:v>
       </x:c>
-      <x:c r="C34" s="105" t="str">
-        <x:v>sha256:97d1e6a03c7b029effa20b0c6994d82a304032923a0d6e76b693d8b2fe262568</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="105" t="str">
+      <x:c r="C35" s="99" t="str">
+        <x:v>sha256:0294347c51bd94b65f8eec9fad44b39d00e5433c4dc12aeee06c48c0e5ae9c08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B35" s="105" t="str">
+      <x:c r="B36" s="99" t="str">
         <x:v>EFCS-BURST-01</x:v>
       </x:c>
-      <x:c r="C35" s="105" t="str">
-        <x:v>sha256:8fb04d8e137c7ade904313a65469ab549111962f3eef56b6d7645d3ebc58646c</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="105" t="str">
+      <x:c r="C36" s="99" t="str">
+        <x:v>sha256:10966e281790e9619773bd99c263d1a8c3f83170403b36c2fbb2a490499e7130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B36" s="105" t="str">
+      <x:c r="B37" s="99" t="str">
         <x:v>FLASH-PLUTO-01</x:v>
       </x:c>
-      <x:c r="C36" s="105" t="str">
-        <x:v>sha256:ae8d9581ed75d71e4f14e03057c0bdafeb110616c4390fce4cdc615093a09344</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="105" t="str">
+      <x:c r="C37" s="99" t="str">
+        <x:v>sha256:5c00b09991f26e6b8bedd930e7304b53dae8f93819c7135c765aac82e970d87c</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B37" s="105" t="str">
+      <x:c r="B38" s="99" t="str">
         <x:v>FINAL-READ-01</x:v>
       </x:c>
-      <x:c r="C37" s="105" t="str">
-        <x:v>sha256:aabf42c50d977426a03aa33990ea7c2cf562640633a1fb7737e64ea5d5562d87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="105" t="str">
+      <x:c r="C38" s="99" t="str">
+        <x:v>sha256:688b6db6bd3d38070dfd682da54402cf8678093cb1014766953f9f5da49d7407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B38" s="105" t="str">
+      <x:c r="B39" s="99" t="str">
         <x:v>FINAL-SAVE-01</x:v>
       </x:c>
-      <x:c r="C38" s="105" t="str">
-        <x:v>sha256:2fe904eeee80a16c99d57a854d738093275a60b8573ff8d27ce3745b1913d636</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="105" t="str">
+      <x:c r="C39" s="99" t="str">
+        <x:v>sha256:3d3558eaa54a0fdee859a544db2bccada6d3a8749fda96001422741914b6d0a6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="99" t="str">
         <x:v>test</x:v>
       </x:c>
-      <x:c r="B39" s="105" t="str">
+      <x:c r="B40" s="99" t="str">
         <x:v>PROJECT-UPDATE-01</x:v>
       </x:c>
-      <x:c r="C39" s="105" t="str">
-        <x:v>sha256:fe0cbf03abfcc198510bcde5ef3fcd5f24e8de8a06946a6521c2e4c4ed3d4885</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="105" t="str">
+      <x:c r="C40" s="99" t="str">
+        <x:v>sha256:9312ccf684ccf233900950855d7a3457eb01e52e1c8fcb90e3c7c7daa72e17a6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B40" s="105" t="str">
+      <x:c r="B41" s="99" t="str">
         <x:v>Mode</x:v>
       </x:c>
-      <x:c r="C40" s="105" t="str">
+      <x:c r="C41" s="99" t="str">
         <x:v>sha256:16380d447ae550758ff49c344119374224a6b1c009504e23f6f4f93c11c00533</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="105" t="str">
+    <x:row r="42">
+      <x:c r="A42" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B41" s="105" t="str">
+      <x:c r="B42" s="99" t="str">
         <x:v>Metering</x:v>
       </x:c>
-      <x:c r="C41" s="105" t="str">
+      <x:c r="C42" s="99" t="str">
         <x:v>sha256:bc76af3dd5f76e718fe876deafcfbc0fd4a3f64d2a2eb64d2253751bd18f4eae</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="105" t="str">
+    <x:row r="43">
+      <x:c r="A43" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B42" s="105" t="str">
+      <x:c r="B43" s="99" t="str">
         <x:v>Exposure Compensation</x:v>
       </x:c>
-      <x:c r="C42" s="105" t="str">
+      <x:c r="C43" s="99" t="str">
         <x:v>sha256:88e1331bb1792dc8c402253666af51d91b4ff14bdf848d8f5715f7c5735374ee</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="105" t="str">
+    <x:row r="44">
+      <x:c r="A44" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B43" s="105" t="str">
+      <x:c r="B44" s="99" t="str">
         <x:v>Shutter Speed</x:v>
       </x:c>
-      <x:c r="C43" s="105" t="str">
+      <x:c r="C44" s="99" t="str">
         <x:v>sha256:50a59b23cd80339f63a7068a9f9b6618357bcc05eb6f986cc5c7a707e50c0a74</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="105" t="str">
+    <x:row r="45">
+      <x:c r="A45" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B44" s="105" t="str">
+      <x:c r="B45" s="99" t="str">
         <x:v>Aperture</x:v>
       </x:c>
-      <x:c r="C44" s="105" t="str">
+      <x:c r="C45" s="99" t="str">
         <x:v>sha256:74b8c602aefe9109b324a5d3d0f5af54cafeaceae6f80e96effd7b7e7b7512a0</x:v>
       </x:c>
     </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="105" t="str">
+    <x:row r="46">
+      <x:c r="A46" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B45" s="105" t="str">
+      <x:c r="B46" s="99" t="str">
         <x:v>ISO</x:v>
       </x:c>
-      <x:c r="C45" s="105" t="str">
+      <x:c r="C46" s="99" t="str">
         <x:v>sha256:3c57560fdad255af8dddd4afe759bf3a638ced62cd0b435fbcb39f539ed4d5cd</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="105" t="str">
+    <x:row r="47">
+      <x:c r="A47" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B46" s="105" t="str">
+      <x:c r="B47" s="99" t="str">
         <x:v>Auto ISO Maximum</x:v>
       </x:c>
-      <x:c r="C46" s="105" t="str">
-        <x:v>sha256:d9e3a1f832be05121fba7873fe44f0c6a69f48a85b28c62358a17838bc551386</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="105" t="str">
+      <x:c r="C47" s="99" t="str">
+        <x:v>sha256:215087f96f2c5d379e4931bbcffe7ea4f1ebe59cc0229f5dae23f52e08edbba5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B47" s="105" t="str">
+      <x:c r="B48" s="99" t="str">
         <x:v>AF Operation</x:v>
       </x:c>
-      <x:c r="C47" s="105" t="str">
+      <x:c r="C48" s="99" t="str">
         <x:v>sha256:e52a8877636b9e990324e5e59a10b6b8a0723c7699f752ac41a4e39a25ed8c94</x:v>
       </x:c>
     </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="105" t="str">
+    <x:row r="49">
+      <x:c r="A49" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B48" s="105" t="str">
+      <x:c r="B49" s="99" t="str">
+        <x:v>Servo AF Case</x:v>
+      </x:c>
+      <x:c r="C49" s="99" t="str">
+        <x:v>sha256:7d49940351b317a763b5a0986fb61b4ddc79ee1d97ef9394e1ac26973ba4dfbc</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="99" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B50" s="99" t="str">
         <x:v>AF Method</x:v>
       </x:c>
-      <x:c r="C48" s="105" t="str">
+      <x:c r="C50" s="99" t="str">
         <x:v>sha256:ac30ce5e48a2e9e69db02806afb6a8c836dd8220dce399b57ed50b6ec3569d82</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="105" t="str">
+    <x:row r="51">
+      <x:c r="A51" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B49" s="105" t="str">
+      <x:c r="B51" s="99" t="str">
         <x:v>Subject Detection</x:v>
       </x:c>
-      <x:c r="C49" s="105" t="str">
+      <x:c r="C51" s="99" t="str">
         <x:v>sha256:ca630f9c8761b1ba9bc261fc0264e1fdff6c6ebce7d3d60f68453c6e6c0fb66e</x:v>
       </x:c>
     </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="105" t="str">
+    <x:row r="52">
+      <x:c r="A52" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B50" s="105" t="str">
+      <x:c r="B52" s="99" t="str">
         <x:v>Eye Detection</x:v>
       </x:c>
-      <x:c r="C50" s="105" t="str">
+      <x:c r="C52" s="99" t="str">
         <x:v>sha256:d4f49e58f189bc2a85058e8030bdba5867549892594d4961911a877fc7774cc1</x:v>
       </x:c>
     </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="105" t="str">
+    <x:row r="53">
+      <x:c r="A53" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B51" s="105" t="str">
+      <x:c r="B53" s="99" t="str">
         <x:v>Drive Mode</x:v>
       </x:c>
-      <x:c r="C51" s="105" t="str">
+      <x:c r="C53" s="99" t="str">
         <x:v>sha256:a407ab25d86c6b32e4618dffadce1bc9f7375731cceb32a9b15154cb636bbc93</x:v>
       </x:c>
     </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="105" t="str">
+    <x:row r="54">
+      <x:c r="A54" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B52" s="105" t="str">
+      <x:c r="B54" s="99" t="str">
         <x:v>Shutter Type</x:v>
       </x:c>
-      <x:c r="C52" s="105" t="str">
+      <x:c r="C54" s="99" t="str">
         <x:v>sha256:e0eb3a601149113b744968c8d35c10e22707716e94c780644837edcabff082bb</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="105" t="str">
+    <x:row r="55">
+      <x:c r="A55" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B53" s="105" t="str">
+      <x:c r="B55" s="99" t="str">
         <x:v>Image Stabilizer Mode</x:v>
       </x:c>
-      <x:c r="C53" s="105" t="str">
+      <x:c r="C55" s="99" t="str">
         <x:v>sha256:cc5907ea77c17b747bda000cb9d24e886022b15d9be9b15be2fd7d3a6aa18fba</x:v>
       </x:c>
     </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="105" t="str">
+    <x:row r="56">
+      <x:c r="A56" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B54" s="105" t="str">
+      <x:c r="B56" s="99" t="str">
         <x:v>IBIS</x:v>
       </x:c>
-      <x:c r="C54" s="105" t="str">
-        <x:v>sha256:d10f56172a85e3588b70cb9cc38fe4e1ddd6b261fb5185b7581241dda0d7e9ad</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="105" t="str">
+      <x:c r="C56" s="99" t="str">
+        <x:v>sha256:f88432494f6ce6fd467acf866dcb7285209af0daa97f23211b4c2e9a2fca510a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B55" s="105" t="str">
+      <x:c r="B57" s="99" t="str">
         <x:v>Focus Bracketing</x:v>
       </x:c>
-      <x:c r="C55" s="105" t="str">
-        <x:v>sha256:e8a1df3755fa1c6498cccfce7b113140b022e928f10c8ad2a3ff3ddf8690000a</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="105" t="str">
+      <x:c r="C57" s="99" t="str">
+        <x:v>sha256:faa653558ccc3ca42def02cffceb2449676221f3e2b701a95cb76c734a606a66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="99" t="str">
         <x:v>registration</x:v>
       </x:c>
-      <x:c r="B56" s="105" t="str">
+      <x:c r="B58" s="99" t="str">
         <x:v>Lens IS switch</x:v>
       </x:c>
-      <x:c r="C56" s="105" t="str">
-        <x:v>sha256:5a2f7cf7e224aef797784c3a79eb70c0a5ed8f1ae66c3227c01e8b25a206903e</x:v>
+      <x:c r="C58" s="99" t="str">
+        <x:v>sha256:77c1f08d541f8a95c354155213e1184f193765664d2faca4e6245806067b6735</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rf42239416cc64623"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="Rca956a9c1da54fc0"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R822032b91d324fac"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="R30b3a13289ae4a64"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="R6e29e7f967294565"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="R801ae5ee8d96480c"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="Rb1d06e4697ee430a"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="Recd26521703a4720"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="R2304b5c2e9354a78"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R0ef5c894f8ea48a1"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="Rda2db011efcd4617"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="Re2459321ac224684"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="Rad61659c565f4844"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="Ra3656a58efc8410a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="95b3fb75-e462-4be5-bffc-f6f83026826f"/>
+        <xdr:cNvPr id="1" name="3544ae01-ab54-4b03-9450-04148d0e63c3"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R35548a0a0f5e42c5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R97175aa6d9f54ec2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -752,8 +752,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegistrationTable" displayName="RegistrationTable" ref="A4:N22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:N22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegistrationTable" displayName="RegistrationTable" ref="A4:N26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:N26"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Setting"/>
     <x:tableColumn id="2" name="Default Settings"/>
@@ -1797,7 +1797,7 @@
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>The approved AF Case My Menu tab exists with all three shortcuts in the correct order, and Servo AF opens the complete Case selector without changing AF Operation.</x:v>
+        <x:v>The approved AF Case My Menu tab exists with all four shortcuts in the correct order, Servo AF opens the complete Case selector without changing AF Operation, and Switching tracked subjects opens the AF4 control.</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
         <x:v>Configure and verify My Menu: AF Case before shared setup or profile registration.</x:v>
@@ -1812,7 +1812,7 @@
       </x:c>
       <x:c r="H10" s="15" t="str">
         <x:f>IFERROR(VLOOKUP($A10,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
-        <x:v>Create tab AF Case; register Servo AF, Tracking Sensitivity, and Accel./Decel. tracking in order; confirm Servo AF opens the complete Case 1–4 / Case A selector and does not change AF Operation.</x:v>
+        <x:v>Create tab AF Case; register Servo AF, Tracking Sensitivity, Accel./Decel. tracking, and Switching tracked subjects in order; confirm Servo AF opens the complete Case 1–4 / Case A selector without changing AF Operation and Switching tracked subjects opens the AF4 Initial priority / On subject / Switch subject control.</x:v>
       </x:c>
       <x:c r="I10" s="13" t="str">
         <x:v>Not started</x:v>
@@ -1848,14 +1848,14 @@
         <x:v>Camera Setup</x:v>
       </x:c>
       <x:c r="D11" s="15" t="str">
-        <x:v>Shared operational defaults match the complete C1-aligned reference baseline.</x:v>
+        <x:v>Shared operational defaults match the general-purpose reference baseline; the separate custom Case 1 preset is ready for C1 registration.</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
-        <x:v>Confirm Fv, shutter and aperture Auto, Auto ISO maximum 12800, Servo AF with Case A (Auto), Face + Tracking, Animals, Eye Detection Enable, High Speed Continuous, EFCS, Mode 1, cRAW, Full-frame, and Evaluative metering.</x:v>
+        <x:v>Confirm Fv, shutter and aperture Auto, Auto ISO maximum 12800, Servo AF with Case A (Auto) and automatic parameters, Switching tracked subjects On subject, Face + Tracking, Animals, Eye Detection Enable, High Speed Continuous, High speed display Enable, EFCS, Mode 1, cRAW, Full-frame, and Evaluative metering. Configure Case 1 separately to Tracking Sensitivity -1 and Accel./Decel. tracking +1, noting that Canon's factory Case 1 is 0 / 0.</x:v>
       </x:c>
       <x:c r="F11" s="13" t="str">
         <x:f>IFERROR(VLOOKUP($A11,'Menu'!$A$2:$E$38,2,FALSE),"")</x:f>
-        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio; MM-AF Case for Servo AF Case</x:v>
+        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio; MM-AF Case for Servo AF Case, parameters, and subject switching; Shooting 7 for High speed display</x:v>
       </x:c>
       <x:c r="G11" s="29" t="str">
         <x:f>IFERROR(VLOOKUP($A11,'Menu'!$A$2:$E$38,3,FALSE),"")</x:f>
@@ -1863,7 +1863,7 @@
       </x:c>
       <x:c r="H11" s="15" t="str">
         <x:f>IFERROR(VLOOKUP($A11,'Menu'!$A$2:$E$38,4,FALSE),"")</x:f>
-        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; My Menu AF Case &gt; Servo AF or AF3 &gt; Servo AF characteristics: Case A; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting menu: IS (Image Stabilizer) mode</x:v>
+        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; My Menu AF Case or AF3: baseline Case A with automatic parameters, plus configure Case 1 to -1 / +1 without leaving it selected for the baseline; My Menu AF Case or AF4: Switching tracked subjects On subject; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting 7: High speed display Enable; Shooting menu: IS (Image Stabilizer) mode</x:v>
       </x:c>
       <x:c r="I11" s="13" t="str">
         <x:v>Not started</x:v>
@@ -2305,7 +2305,7 @@
         <x:v>C1 Wildlife</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
-        <x:v>C1 recalls a usable Wildlife environment and controls behave as intended.</x:v>
+        <x:v>C1 recalls a usable Wildlife environment with Case 1 (Custom) at -1 / +1 and controls behave as intended.</x:v>
       </x:c>
       <x:c r="E20" s="15" t="str">
         <x:v>Perform a short Wildlife operational test.</x:v>
@@ -3486,9 +3486,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rb374eecfc9f84421"/>
+  <x:drawing ns1:id="R26b78721132347c5"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Raa392843d73441f9"/>
+    <x:tablePart ns1:id="Rffced0f786dc4baf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4079,7 +4079,7 @@
         <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="C13" s="65" t="str">
-        <x:v>Case A (Auto)</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="D13" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4127,13 +4127,13 @@
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14" s="52" t="str">
-        <x:v>AF Method</x:v>
+        <x:v>Tracking Sensitivity</x:v>
       </x:c>
       <x:c r="B14" s="54" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="C14" s="65" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D14" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4143,7 +4143,7 @@
       </x:c>
       <x:c r="F14" s="66" t="str"/>
       <x:c r="G14" s="65" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4153,7 +4153,7 @@
       </x:c>
       <x:c r="J14" s="66" t="str"/>
       <x:c r="K14" s="65" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L14" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4164,30 +4164,30 @@
       <x:c r="N14" s="66" t="str"/>
       <x:c r="O14" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B14,IF($B$3="C1 Wildlife",C14,IF($B$3="C2 Birds in Flight",G14,IF($B$3="C3 Landscape",K14,""))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="P14" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B14,IF($C$3="C1 Wildlife",C14,IF($C$3="C2 Birds in Flight",G14,IF($C$3="C3 Landscape",K14,""))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="Q14" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B14,IF($G$3="C1 Wildlife",C14,IF($G$3="C2 Birds in Flight",G14,IF($G$3="C3 Landscape",K14,""))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="R14" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B14,IF($K$3="C1 Wildlife",C14,IF($K$3="C2 Birds in Flight",G14,IF($K$3="C3 Landscape",K14,""))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
       </x:c>
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="52" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>Accel./Decel. Tracking</x:v>
       </x:c>
       <x:c r="B15" s="54" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="C15" s="65" t="str">
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="D15" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4197,7 +4197,7 @@
       </x:c>
       <x:c r="F15" s="66" t="str"/>
       <x:c r="G15" s="65" t="str">
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="H15" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4207,7 +4207,7 @@
       </x:c>
       <x:c r="J15" s="66" t="str"/>
       <x:c r="K15" s="65" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L15" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4218,30 +4218,30 @@
       <x:c r="N15" s="66" t="str"/>
       <x:c r="O15" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B15,IF($B$3="C1 Wildlife",C15,IF($B$3="C2 Birds in Flight",G15,IF($B$3="C3 Landscape",K15,""))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="P15" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B15,IF($C$3="C1 Wildlife",C15,IF($C$3="C2 Birds in Flight",G15,IF($C$3="C3 Landscape",K15,""))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="Q15" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B15,IF($G$3="C1 Wildlife",C15,IF($G$3="C2 Birds in Flight",G15,IF($G$3="C3 Landscape",K15,""))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="R15" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B15,IF($K$3="C1 Wildlife",C15,IF($K$3="C2 Birds in Flight",G15,IF($K$3="C3 Landscape",K15,""))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Auto</x:v>
       </x:c>
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="52" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>Switching Tracked Subjects</x:v>
       </x:c>
       <x:c r="B16" s="54" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="C16" s="65" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="D16" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4251,7 +4251,7 @@
       </x:c>
       <x:c r="F16" s="66" t="str"/>
       <x:c r="G16" s="65" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="H16" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4261,7 +4261,7 @@
       </x:c>
       <x:c r="J16" s="66" t="str"/>
       <x:c r="K16" s="65" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L16" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4272,30 +4272,30 @@
       <x:c r="N16" s="66" t="str"/>
       <x:c r="O16" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B16,IF($B$3="C1 Wildlife",C16,IF($B$3="C2 Birds in Flight",G16,IF($B$3="C3 Landscape",K16,""))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="P16" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B16,IF($C$3="C1 Wildlife",C16,IF($C$3="C2 Birds in Flight",G16,IF($C$3="C3 Landscape",K16,""))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="Q16" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B16,IF($G$3="C1 Wildlife",C16,IF($G$3="C2 Birds in Flight",G16,IF($G$3="C3 Landscape",K16,""))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="R16" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B16,IF($K$3="C1 Wildlife",C16,IF($K$3="C2 Birds in Flight",G16,IF($K$3="C3 Landscape",K16,""))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="52" t="str">
-        <x:v>Drive Mode</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="B17" s="54" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="C17" s="65" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="D17" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4305,7 +4305,7 @@
       </x:c>
       <x:c r="F17" s="66" t="str"/>
       <x:c r="G17" s="65" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="H17" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4315,7 +4315,7 @@
       </x:c>
       <x:c r="J17" s="66" t="str"/>
       <x:c r="K17" s="65" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="L17" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4326,30 +4326,30 @@
       <x:c r="N17" s="66" t="str"/>
       <x:c r="O17" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B17,IF($B$3="C1 Wildlife",C17,IF($B$3="C2 Birds in Flight",G17,IF($B$3="C3 Landscape",K17,""))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="P17" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B17,IF($C$3="C1 Wildlife",C17,IF($C$3="C2 Birds in Flight",G17,IF($C$3="C3 Landscape",K17,""))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="Q17" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B17,IF($G$3="C1 Wildlife",C17,IF($G$3="C2 Birds in Flight",G17,IF($G$3="C3 Landscape",K17,""))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="R17" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B17,IF($K$3="C1 Wildlife",C17,IF($K$3="C2 Birds in Flight",G17,IF($K$3="C3 Landscape",K17,""))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="52" t="str">
-        <x:v>Shutter Type</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="B18" s="54" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="C18" s="65" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="D18" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4359,7 +4359,7 @@
       </x:c>
       <x:c r="F18" s="66" t="str"/>
       <x:c r="G18" s="65" t="str">
-        <x:v>Mechanical</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="H18" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4369,7 +4369,7 @@
       </x:c>
       <x:c r="J18" s="66" t="str"/>
       <x:c r="K18" s="65" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="L18" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4380,30 +4380,30 @@
       <x:c r="N18" s="66" t="str"/>
       <x:c r="O18" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B18,IF($B$3="C1 Wildlife",C18,IF($B$3="C2 Birds in Flight",G18,IF($B$3="C3 Landscape",K18,""))))</x:f>
-        <x:v>EFCS</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="P18" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B18,IF($C$3="C1 Wildlife",C18,IF($C$3="C2 Birds in Flight",G18,IF($C$3="C3 Landscape",K18,""))))</x:f>
-        <x:v>EFCS</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="Q18" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B18,IF($G$3="C1 Wildlife",C18,IF($G$3="C2 Birds in Flight",G18,IF($G$3="C3 Landscape",K18,""))))</x:f>
-        <x:v>EFCS</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="R18" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B18,IF($K$3="C1 Wildlife",C18,IF($K$3="C2 Birds in Flight",G18,IF($K$3="C3 Landscape",K18,""))))</x:f>
-        <x:v>EFCS</x:v>
+        <x:v>Animals</x:v>
       </x:c>
     </x:row>
     <x:row r="19" hidden="0">
       <x:c r="A19" s="52" t="str">
-        <x:v>Image Stabilizer Mode</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="B19" s="54" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="C19" s="65" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="D19" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4413,7 +4413,7 @@
       </x:c>
       <x:c r="F19" s="66" t="str"/>
       <x:c r="G19" s="65" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="H19" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4423,7 +4423,7 @@
       </x:c>
       <x:c r="J19" s="66" t="str"/>
       <x:c r="K19" s="65" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="L19" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4434,30 +4434,30 @@
       <x:c r="N19" s="66" t="str"/>
       <x:c r="O19" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B19,IF($B$3="C1 Wildlife",C19,IF($B$3="C2 Birds in Flight",G19,IF($B$3="C3 Landscape",K19,""))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="P19" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B19,IF($C$3="C1 Wildlife",C19,IF($C$3="C2 Birds in Flight",G19,IF($C$3="C3 Landscape",K19,""))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Q19" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B19,IF($G$3="C1 Wildlife",C19,IF($G$3="C2 Birds in Flight",G19,IF($G$3="C3 Landscape",K19,""))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="R19" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B19,IF($K$3="C1 Wildlife",C19,IF($K$3="C2 Birds in Flight",G19,IF($K$3="C3 Landscape",K19,""))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
     </x:row>
     <x:row r="20" hidden="0">
       <x:c r="A20" s="52" t="str">
-        <x:v>IBIS</x:v>
+        <x:v>Drive Mode</x:v>
       </x:c>
       <x:c r="B20" s="54" t="str">
-        <x:v>On</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="C20" s="65" t="str">
-        <x:v>On</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="D20" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4467,7 +4467,7 @@
       </x:c>
       <x:c r="F20" s="66" t="str"/>
       <x:c r="G20" s="65" t="str">
-        <x:v>On</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="H20" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4477,7 +4477,7 @@
       </x:c>
       <x:c r="J20" s="66" t="str"/>
       <x:c r="K20" s="65" t="str">
-        <x:v>On</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="L20" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4488,30 +4488,30 @@
       <x:c r="N20" s="66" t="str"/>
       <x:c r="O20" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B20,IF($B$3="C1 Wildlife",C20,IF($B$3="C2 Birds in Flight",G20,IF($B$3="C3 Landscape",K20,""))))</x:f>
-        <x:v>On</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="P20" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B20,IF($C$3="C1 Wildlife",C20,IF($C$3="C2 Birds in Flight",G20,IF($C$3="C3 Landscape",K20,""))))</x:f>
-        <x:v>On</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="Q20" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B20,IF($G$3="C1 Wildlife",C20,IF($G$3="C2 Birds in Flight",G20,IF($G$3="C3 Landscape",K20,""))))</x:f>
-        <x:v>On</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="R20" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B20,IF($K$3="C1 Wildlife",C20,IF($K$3="C2 Birds in Flight",G20,IF($K$3="C3 Landscape",K20,""))))</x:f>
-        <x:v>On</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
     </x:row>
     <x:row r="21" hidden="0">
       <x:c r="A21" s="52" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>High Speed Display</x:v>
       </x:c>
       <x:c r="B21" s="54" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="C21" s="65" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="D21" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4521,7 +4521,7 @@
       </x:c>
       <x:c r="F21" s="66" t="str"/>
       <x:c r="G21" s="65" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="H21" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4531,7 +4531,7 @@
       </x:c>
       <x:c r="J21" s="66" t="str"/>
       <x:c r="K21" s="65" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L21" s="40" t="str">
         <x:v>Not started</x:v>
@@ -4542,72 +4542,288 @@
       <x:c r="N21" s="66" t="str"/>
       <x:c r="O21" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B21,IF($B$3="C1 Wildlife",C21,IF($B$3="C2 Birds in Flight",G21,IF($B$3="C3 Landscape",K21,""))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="P21" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B21,IF($C$3="C1 Wildlife",C21,IF($C$3="C2 Birds in Flight",G21,IF($C$3="C3 Landscape",K21,""))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Q21" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B21,IF($G$3="C1 Wildlife",C21,IF($G$3="C2 Birds in Flight",G21,IF($G$3="C3 Landscape",K21,""))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="R21" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B21,IF($K$3="C1 Wildlife",C21,IF($K$3="C2 Birds in Flight",G21,IF($K$3="C3 Landscape",K21,""))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Enable</x:v>
       </x:c>
     </x:row>
     <x:row r="22" hidden="0">
-      <x:c r="A22" s="53" t="str">
-        <x:v>Lens IS switch</x:v>
-      </x:c>
-      <x:c r="B22" s="55" t="str">
-        <x:v>On</x:v>
-      </x:c>
-      <x:c r="C22" s="67" t="str">
-        <x:v>On</x:v>
-      </x:c>
-      <x:c r="D22" s="68" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="E22" s="68" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="F22" s="69" t="str"/>
-      <x:c r="G22" s="67" t="str">
-        <x:v>On</x:v>
-      </x:c>
-      <x:c r="H22" s="68" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="I22" s="68" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="J22" s="69" t="str"/>
-      <x:c r="K22" s="67" t="str">
-        <x:v>On</x:v>
-      </x:c>
-      <x:c r="L22" s="68" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="M22" s="68" t="str">
-        <x:v>Not started</x:v>
-      </x:c>
-      <x:c r="N22" s="69" t="str"/>
+      <x:c r="A22" s="52" t="str">
+        <x:v>Shutter Type</x:v>
+      </x:c>
+      <x:c r="B22" s="54" t="str">
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="C22" s="65" t="str">
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="D22" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E22" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F22" s="66" t="str"/>
+      <x:c r="G22" s="65" t="str">
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="H22" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I22" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J22" s="66" t="str"/>
+      <x:c r="K22" s="65" t="str">
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="L22" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M22" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N22" s="66" t="str"/>
       <x:c r="O22" s="47" t="str">
         <x:f>IF($B$3="Default Settings",B22,IF($B$3="C1 Wildlife",C22,IF($B$3="C2 Birds in Flight",G22,IF($B$3="C3 Landscape",K22,""))))</x:f>
-        <x:v>On</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="P22" s="47" t="str">
         <x:f>IF($C$3="Default Settings",B22,IF($C$3="C1 Wildlife",C22,IF($C$3="C2 Birds in Flight",G22,IF($C$3="C3 Landscape",K22,""))))</x:f>
-        <x:v>On</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="Q22" s="47" t="str">
         <x:f>IF($G$3="Default Settings",B22,IF($G$3="C1 Wildlife",C22,IF($G$3="C2 Birds in Flight",G22,IF($G$3="C3 Landscape",K22,""))))</x:f>
-        <x:v>On</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="R22" s="47" t="str">
         <x:f>IF($K$3="Default Settings",B22,IF($K$3="C1 Wildlife",C22,IF($K$3="C2 Birds in Flight",G22,IF($K$3="C3 Landscape",K22,""))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" hidden="0">
+      <x:c r="A23" s="52" t="str">
+        <x:v>Image Stabilizer Mode</x:v>
+      </x:c>
+      <x:c r="B23" s="54" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="C23" s="65" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="D23" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E23" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F23" s="66" t="str"/>
+      <x:c r="G23" s="65" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="H23" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I23" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J23" s="66" t="str"/>
+      <x:c r="K23" s="65" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="L23" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M23" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N23" s="66" t="str"/>
+      <x:c r="O23" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B23,IF($B$3="C1 Wildlife",C23,IF($B$3="C2 Birds in Flight",G23,IF($B$3="C3 Landscape",K23,""))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="P23" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B23,IF($C$3="C1 Wildlife",C23,IF($C$3="C2 Birds in Flight",G23,IF($C$3="C3 Landscape",K23,""))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="Q23" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B23,IF($G$3="C1 Wildlife",C23,IF($G$3="C2 Birds in Flight",G23,IF($G$3="C3 Landscape",K23,""))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="R23" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B23,IF($K$3="C1 Wildlife",C23,IF($K$3="C2 Birds in Flight",G23,IF($K$3="C3 Landscape",K23,""))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" hidden="0">
+      <x:c r="A24" s="52" t="str">
+        <x:v>IBIS</x:v>
+      </x:c>
+      <x:c r="B24" s="54" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="C24" s="65" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="D24" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E24" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F24" s="66" t="str"/>
+      <x:c r="G24" s="65" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="H24" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I24" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J24" s="66" t="str"/>
+      <x:c r="K24" s="65" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L24" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M24" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N24" s="66" t="str"/>
+      <x:c r="O24" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B24,IF($B$3="C1 Wildlife",C24,IF($B$3="C2 Birds in Flight",G24,IF($B$3="C3 Landscape",K24,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="P24" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B24,IF($C$3="C1 Wildlife",C24,IF($C$3="C2 Birds in Flight",G24,IF($C$3="C3 Landscape",K24,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="Q24" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B24,IF($G$3="C1 Wildlife",C24,IF($G$3="C2 Birds in Flight",G24,IF($G$3="C3 Landscape",K24,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="R24" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B24,IF($K$3="C1 Wildlife",C24,IF($K$3="C2 Birds in Flight",G24,IF($K$3="C3 Landscape",K24,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" hidden="0">
+      <x:c r="A25" s="52" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="B25" s="54" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="C25" s="65" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="D25" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E25" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F25" s="66" t="str"/>
+      <x:c r="G25" s="65" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="H25" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I25" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J25" s="66" t="str"/>
+      <x:c r="K25" s="65" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="L25" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M25" s="40" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N25" s="66" t="str"/>
+      <x:c r="O25" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B25,IF($B$3="C1 Wildlife",C25,IF($B$3="C2 Birds in Flight",G25,IF($B$3="C3 Landscape",K25,""))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P25" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B25,IF($C$3="C1 Wildlife",C25,IF($C$3="C2 Birds in Flight",G25,IF($C$3="C3 Landscape",K25,""))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Q25" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B25,IF($G$3="C1 Wildlife",C25,IF($G$3="C2 Birds in Flight",G25,IF($G$3="C3 Landscape",K25,""))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="R25" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B25,IF($K$3="C1 Wildlife",C25,IF($K$3="C2 Birds in Flight",G25,IF($K$3="C3 Landscape",K25,""))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" hidden="0">
+      <x:c r="A26" s="53" t="str">
+        <x:v>Lens IS switch</x:v>
+      </x:c>
+      <x:c r="B26" s="55" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="C26" s="67" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="D26" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="E26" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="F26" s="69" t="str"/>
+      <x:c r="G26" s="67" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="H26" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="I26" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="J26" s="69" t="str"/>
+      <x:c r="K26" s="67" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L26" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="M26" s="68" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="N26" s="69" t="str"/>
+      <x:c r="O26" s="47" t="str">
+        <x:f>IF($B$3="Default Settings",B26,IF($B$3="C1 Wildlife",C26,IF($B$3="C2 Birds in Flight",G26,IF($B$3="C3 Landscape",K26,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="P26" s="47" t="str">
+        <x:f>IF($C$3="Default Settings",B26,IF($C$3="C1 Wildlife",C26,IF($C$3="C2 Birds in Flight",G26,IF($C$3="C3 Landscape",K26,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="Q26" s="47" t="str">
+        <x:f>IF($G$3="Default Settings",B26,IF($G$3="C1 Wildlife",C26,IF($G$3="C2 Birds in Flight",G26,IF($G$3="C3 Landscape",K26,""))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="R26" s="47" t="str">
+        <x:f>IF($K$3="Default Settings",B26,IF($K$3="C1 Wildlife",C26,IF($K$3="C2 Birds in Flight",G26,IF($K$3="C3 Landscape",K26,""))))</x:f>
         <x:v>On</x:v>
       </x:c>
     </x:row>
@@ -4616,22 +4832,22 @@
     <x:mergeCell ref="A1:N1"/>
     <x:mergeCell ref="A2:N2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="B5:B22">
+  <x:conditionalFormatting sqref="B5:B26">
     <x:cfRule type="cellIs" dxfId="5" priority="1" operator="notEqual">
       <x:formula>$O5</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="C5:C22">
+  <x:conditionalFormatting sqref="C5:C26">
     <x:cfRule type="cellIs" dxfId="6" priority="2" operator="notEqual">
       <x:formula>$P5</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G5:G22">
+  <x:conditionalFormatting sqref="G5:G26">
     <x:cfRule type="cellIs" dxfId="7" priority="3" operator="notEqual">
       <x:formula>$Q5</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="K5:K22">
+  <x:conditionalFormatting sqref="K5:K26">
     <x:cfRule type="cellIs" dxfId="8" priority="4" operator="notEqual">
       <x:formula>$R5</x:formula>
     </x:cfRule>
@@ -4649,19 +4865,19 @@
     <x:dataValidation type="list" sqref="K3">
       <x:formula1>"Default Settings,C1 Wildlife,C2 Birds in Flight,C3 Landscape"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="D5:E22">
+    <x:dataValidation type="list" sqref="D5:E26">
       <x:formula1>"Not started,Pass,Fail,Needs retest,Not applicable"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="H5:I22">
+    <x:dataValidation type="list" sqref="H5:I26">
       <x:formula1>"Not started,Pass,Fail,Needs retest,Not applicable"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="L5:M22">
+    <x:dataValidation type="list" sqref="L5:M26">
       <x:formula1>"Not started,Pass,Fail,Needs retest,Not applicable"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Ra8a2c5e16f8743df"/>
+    <x:tablePart ns1:id="R2c420cc194434f05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5042,7 +5258,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R2462fbfcaf824ac5"/>
+    <x:tablePart ns1:id="Rf2ca06ff9cca49d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5311,7 +5527,7 @@
         <x:v>My Menu</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>Create tab AF Case; register Servo AF, Tracking Sensitivity, and Accel./Decel. tracking in order; confirm Servo AF opens the complete Case 1–4 / Case A selector and does not change AF Operation.</x:v>
+        <x:v>Create tab AF Case; register Servo AF, Tracking Sensitivity, Accel./Decel. tracking, and Switching tracked subjects in order; confirm Servo AF opens the complete Case 1–4 / Case A selector without changing AF Operation and Switching tracked subjects opens the AF4 Initial priority / On subject / Switch subject control.</x:v>
       </x:c>
       <x:c r="E6" s="17" t="n">
         <x:v>5</x:v>
@@ -5322,13 +5538,13 @@
         <x:v>SETUP-04</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio; MM-AF Case for Servo AF Case</x:v>
+        <x:v>Q screen; direct exposure controls; AF Point Selection button; MM-SWITCH for Subject to detect, Shutter mode, and Cropping/aspect ratio; MM-AF Case for Servo AF Case, parameters, and subject switching; Shooting 7 for High speed display</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
         <x:v>Multiple</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
-        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; My Menu AF Case &gt; Servo AF or AF3 &gt; Servo AF characteristics: Case A; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting menu: IS (Image Stabilizer) mode</x:v>
+        <x:v>Direct/Q: Fv, shutter Auto, aperture Auto, Auto ISO, Servo AF, High Speed Continuous, Evaluative metering; AF1: AF method, Subject to detect, Eye detection; My Menu AF Case or AF3: baseline Case A with automatic parameters, plus configure Case 1 to -1 / +1 without leaving it selected for the baseline; My Menu AF Case or AF4: Switching tracked subjects On subject; Shooting 1: Image quality and Cropping/aspect ratio; Shooting 2: ISO speed settings; Shooting 6: Shutter mode; Shooting 7: High speed display Enable; Shooting menu: IS (Image Stabilizer) mode</x:v>
       </x:c>
       <x:c r="E7" s="17" t="n">
         <x:v>6</x:v>
@@ -5864,7 +6080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rbbe7f96db5da4d45"/>
+    <x:tablePart ns1:id="Rb025e9d5cd32400a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5904,7 +6120,7 @@
       </x:c>
       <x:c r="B3" s="99" t="str"/>
       <x:c r="C3" s="99" t="str">
-        <x:v>sha256:63ee9d6d18b374f3ee3b85a67466c6b5a0fe162dfa586934cf4fd911acf6e3fe</x:v>
+        <x:v>sha256:68155f752a1bcdfaa7efe2721eec0cd65228e333a447afbd9fe4793d1fc50329</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5959,7 +6175,7 @@
         <x:v>SETUP-MM-AF-01</x:v>
       </x:c>
       <x:c r="C8" s="99" t="str">
-        <x:v>sha256:640095557a45fc26bff30bed84e3dd0f081eee4f34666a3ac6f03baffad58ba1</x:v>
+        <x:v>sha256:2b88f49e05b245e31f0d823f6ef4e5d71a2bd0398b2cf9cd8205610832364ab9</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5970,7 +6186,7 @@
         <x:v>SETUP-04</x:v>
       </x:c>
       <x:c r="C9" s="99" t="str">
-        <x:v>sha256:0810980437956c762e776c7d3c3c83ace9e5e624352479bd6ec652a9c66f8a65</x:v>
+        <x:v>sha256:b6bd467f6a89f821e9373cc530c60d121981c3be1f93118148955e75331daaa4</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6069,7 +6285,7 @@
         <x:v>C1-OPS-01</x:v>
       </x:c>
       <x:c r="C18" s="99" t="str">
-        <x:v>sha256:91738d7d064f766c1edb2c710fe5f029e24037f657476aa2df79914c67ce7318</x:v>
+        <x:v>sha256:88304c030b7adb56fe9666b1d5541eb373d1615173ce399a06f9538b960dfc1e</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -6410,7 +6626,7 @@
         <x:v>Servo AF Case</x:v>
       </x:c>
       <x:c r="C49" s="99" t="str">
-        <x:v>sha256:7d49940351b317a763b5a0986fb61b4ddc79ee1d97ef9394e1ac26973ba4dfbc</x:v>
+        <x:v>sha256:c9f1ca7567fd410ce854474a770e020fea6e9904b6872801ebc1b2f20b392fbf</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -6418,10 +6634,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B50" s="99" t="str">
-        <x:v>AF Method</x:v>
+        <x:v>Tracking Sensitivity</x:v>
       </x:c>
       <x:c r="C50" s="99" t="str">
-        <x:v>sha256:ac30ce5e48a2e9e69db02806afb6a8c836dd8220dce399b57ed50b6ec3569d82</x:v>
+        <x:v>sha256:dfe83819227cc879db8a3ff1c5b898a2d1c1b0f74d6b3364ad9a92ed7b018424</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -6429,10 +6645,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B51" s="99" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>Accel./Decel. Tracking</x:v>
       </x:c>
       <x:c r="C51" s="99" t="str">
-        <x:v>sha256:ca630f9c8761b1ba9bc261fc0264e1fdff6c6ebce7d3d60f68453c6e6c0fb66e</x:v>
+        <x:v>sha256:e11fda77b702b46abfbda7bbf4de92c162668fd479106b46da999dcd11ba28cf</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -6440,10 +6656,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B52" s="99" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>Switching Tracked Subjects</x:v>
       </x:c>
       <x:c r="C52" s="99" t="str">
-        <x:v>sha256:d4f49e58f189bc2a85058e8030bdba5867549892594d4961911a877fc7774cc1</x:v>
+        <x:v>sha256:1866e2e49cd4159a2f76e301df8394efb14ebc00f49606d84fedb5501875eeb7</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -6451,10 +6667,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B53" s="99" t="str">
-        <x:v>Drive Mode</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="C53" s="99" t="str">
-        <x:v>sha256:a407ab25d86c6b32e4618dffadce1bc9f7375731cceb32a9b15154cb636bbc93</x:v>
+        <x:v>sha256:ac30ce5e48a2e9e69db02806afb6a8c836dd8220dce399b57ed50b6ec3569d82</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -6462,10 +6678,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B54" s="99" t="str">
-        <x:v>Shutter Type</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="C54" s="99" t="str">
-        <x:v>sha256:e0eb3a601149113b744968c8d35c10e22707716e94c780644837edcabff082bb</x:v>
+        <x:v>sha256:ca630f9c8761b1ba9bc261fc0264e1fdff6c6ebce7d3d60f68453c6e6c0fb66e</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -6473,10 +6689,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B55" s="99" t="str">
-        <x:v>Image Stabilizer Mode</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="C55" s="99" t="str">
-        <x:v>sha256:cc5907ea77c17b747bda000cb9d24e886022b15d9be9b15be2fd7d3a6aa18fba</x:v>
+        <x:v>sha256:d4f49e58f189bc2a85058e8030bdba5867549892594d4961911a877fc7774cc1</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -6484,10 +6700,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B56" s="99" t="str">
-        <x:v>IBIS</x:v>
+        <x:v>Drive Mode</x:v>
       </x:c>
       <x:c r="C56" s="99" t="str">
-        <x:v>sha256:f88432494f6ce6fd467acf866dcb7285209af0daa97f23211b4c2e9a2fca510a</x:v>
+        <x:v>sha256:a407ab25d86c6b32e4618dffadce1bc9f7375731cceb32a9b15154cb636bbc93</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -6495,10 +6711,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B57" s="99" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>High Speed Display</x:v>
       </x:c>
       <x:c r="C57" s="99" t="str">
-        <x:v>sha256:faa653558ccc3ca42def02cffceb2449676221f3e2b701a95cb76c734a606a66</x:v>
+        <x:v>sha256:0af962b70870008b8b495ab863d5b9773e68daa4e052c10a5157bbb6e9b09a04</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -6506,9 +6722,53 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B58" s="99" t="str">
+        <x:v>Shutter Type</x:v>
+      </x:c>
+      <x:c r="C58" s="99" t="str">
+        <x:v>sha256:e0eb3a601149113b744968c8d35c10e22707716e94c780644837edcabff082bb</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="99" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B59" s="99" t="str">
+        <x:v>Image Stabilizer Mode</x:v>
+      </x:c>
+      <x:c r="C59" s="99" t="str">
+        <x:v>sha256:cc5907ea77c17b747bda000cb9d24e886022b15d9be9b15be2fd7d3a6aa18fba</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="99" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B60" s="99" t="str">
+        <x:v>IBIS</x:v>
+      </x:c>
+      <x:c r="C60" s="99" t="str">
+        <x:v>sha256:f88432494f6ce6fd467acf866dcb7285209af0daa97f23211b4c2e9a2fca510a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="99" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B61" s="99" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="C61" s="99" t="str">
+        <x:v>sha256:faa653558ccc3ca42def02cffceb2449676221f3e2b701a95cb76c734a606a66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="99" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B62" s="99" t="str">
         <x:v>Lens IS switch</x:v>
       </x:c>
-      <x:c r="C58" s="99" t="str">
+      <x:c r="C62" s="99" t="str">
         <x:v>sha256:77c1f08d541f8a95c354155213e1184f193765664d2faca4e6245806067b6735</x:v>
       </x:c>
     </x:row>

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="Recd26521703a4720"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="R2304b5c2e9354a78"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R0ef5c894f8ea48a1"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="Rda2db011efcd4617"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="Re2459321ac224684"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="Rad61659c565f4844"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="Ra3656a58efc8410a"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="R77218055b27e4810"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="Rc4bf3ef903b547e9"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R5fd072085f094a6c"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="Rea518725c20b4907"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="R3ad4d67de87c4141"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="Rc80750e94ed143e5"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="R0357963323764849"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="3544ae01-ab54-4b03-9450-04148d0e63c3"/>
+        <xdr:cNvPr id="1" name="4b5f01c2-8e28-48d8-8143-5424b4015d9b"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R97175aa6d9f54ec2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6f045d231ca24286"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3486,9 +3486,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R26b78721132347c5"/>
+  <x:drawing ns1:id="R297f19de2f584ee8"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rffced0f786dc4baf"/>
+    <x:tablePart ns1:id="R99a5a32194a24006"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4877,7 +4877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R2c420cc194434f05"/>
+    <x:tablePart ns1:id="R2340c13e8dd14d05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5258,7 +5258,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rf2ca06ff9cca49d8"/>
+    <x:tablePart ns1:id="R020519f0ed7a4363"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6080,7 +6080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rb025e9d5cd32400a"/>
+    <x:tablePart ns1:id="Rbbc8483def1944ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6120,7 +6120,7 @@
       </x:c>
       <x:c r="B3" s="99" t="str"/>
       <x:c r="C3" s="99" t="str">
-        <x:v>sha256:68155f752a1bcdfaa7efe2721eec0cd65228e333a447afbd9fe4793d1fc50329</x:v>
+        <x:v>sha256:0cad54af271f69d5d4518d88888c79acc207f64b1538bcc7d6b3fefefdcf8bfd</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="R77218055b27e4810"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="Rc4bf3ef903b547e9"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R5fd072085f094a6c"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="Rea518725c20b4907"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="R3ad4d67de87c4141"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="Rc80750e94ed143e5"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="R0357963323764849"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rc6435873938f4a68"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="Rc2ece388063b444c"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="Rc376cbfddd3a49b2"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="Rf8c305fc7c564a8e"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="Rf28e705ca5e34901"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="R2c389ab70f724530"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="R9d4b0327fe434936"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="4b5f01c2-8e28-48d8-8143-5424b4015d9b"/>
+        <xdr:cNvPr id="1" name="a98550f3-ee28-495b-8e1f-edd7e3eb7e27"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6f045d231ca24286"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R004b67ca2e5844ec"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3486,9 +3486,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R297f19de2f584ee8"/>
+  <x:drawing ns1:id="Rf27844338bb5419f"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R99a5a32194a24006"/>
+    <x:tablePart ns1:id="R68db433293694ea3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4877,7 +4877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R2340c13e8dd14d05"/>
+    <x:tablePart ns1:id="R7e30b5f4a5014df2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5258,7 +5258,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R020519f0ed7a4363"/>
+    <x:tablePart ns1:id="R4ced039f02a54366"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6080,7 +6080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rbbc8483def1944ee"/>
+    <x:tablePart ns1:id="R9d812126885e4251"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6120,7 +6120,7 @@
       </x:c>
       <x:c r="B3" s="99" t="str"/>
       <x:c r="C3" s="99" t="str">
-        <x:v>sha256:0cad54af271f69d5d4518d88888c79acc207f64b1538bcc7d6b3fefefdcf8bfd</x:v>
+        <x:v>sha256:5f5822a7acae425dbb4e9b7323e8bcb7c2933e99c8d0f270d1592e4eac4e883e</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rc6435873938f4a68"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="Rc2ece388063b444c"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="Rc376cbfddd3a49b2"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="Rf8c305fc7c564a8e"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="Rf28e705ca5e34901"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="R2c389ab70f724530"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="R9d4b0327fe434936"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="Recd26521703a4720"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="R2304b5c2e9354a78"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R0ef5c894f8ea48a1"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="Rda2db011efcd4617"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="Re2459321ac224684"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="Rad61659c565f4844"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="Ra3656a58efc8410a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="a98550f3-ee28-495b-8e1f-edd7e3eb7e27"/>
+        <xdr:cNvPr id="1" name="3544ae01-ab54-4b03-9450-04148d0e63c3"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R004b67ca2e5844ec"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R97175aa6d9f54ec2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3486,9 +3486,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rf27844338bb5419f"/>
+  <x:drawing ns1:id="R26b78721132347c5"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R68db433293694ea3"/>
+    <x:tablePart ns1:id="Rffced0f786dc4baf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4877,7 +4877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R7e30b5f4a5014df2"/>
+    <x:tablePart ns1:id="R2c420cc194434f05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5258,7 +5258,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R4ced039f02a54366"/>
+    <x:tablePart ns1:id="Rf2ca06ff9cca49d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6080,7 +6080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R9d812126885e4251"/>
+    <x:tablePart ns1:id="Rb025e9d5cd32400a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6120,7 +6120,7 @@
       </x:c>
       <x:c r="B3" s="99" t="str"/>
       <x:c r="C3" s="99" t="str">
-        <x:v>sha256:5f5822a7acae425dbb4e9b7323e8bcb7c2933e99c8d0f270d1592e4eac4e883e</x:v>
+        <x:v>sha256:68155f752a1bcdfaa7efe2721eec0cd65228e333a447afbd9fe4793d1fc50329</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="Recd26521703a4720"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="R2304b5c2e9354a78"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R0ef5c894f8ea48a1"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="Rda2db011efcd4617"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="Re2459321ac224684"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="Rad61659c565f4844"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="Ra3656a58efc8410a"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rc6435873938f4a68"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="Rc2ece388063b444c"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="Rc376cbfddd3a49b2"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="Rf8c305fc7c564a8e"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="Rf28e705ca5e34901"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="R2c389ab70f724530"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="R9d4b0327fe434936"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="3544ae01-ab54-4b03-9450-04148d0e63c3"/>
+        <xdr:cNvPr id="1" name="a98550f3-ee28-495b-8e1f-edd7e3eb7e27"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R97175aa6d9f54ec2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R004b67ca2e5844ec"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3486,9 +3486,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R26b78721132347c5"/>
+  <x:drawing ns1:id="Rf27844338bb5419f"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rffced0f786dc4baf"/>
+    <x:tablePart ns1:id="R68db433293694ea3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4877,7 +4877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R2c420cc194434f05"/>
+    <x:tablePart ns1:id="R7e30b5f4a5014df2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5258,7 +5258,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rf2ca06ff9cca49d8"/>
+    <x:tablePart ns1:id="R4ced039f02a54366"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6080,7 +6080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rb025e9d5cd32400a"/>
+    <x:tablePart ns1:id="R9d812126885e4251"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6120,7 +6120,7 @@
       </x:c>
       <x:c r="B3" s="99" t="str"/>
       <x:c r="C3" s="99" t="str">
-        <x:v>sha256:68155f752a1bcdfaa7efe2721eec0cd65228e333a447afbd9fe4793d1fc50329</x:v>
+        <x:v>sha256:5f5822a7acae425dbb4e9b7323e8bcb7c2933e99c8d0f270d1592e4eac4e883e</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rc6435873938f4a68"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="Rc2ece388063b444c"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="Rc376cbfddd3a49b2"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="Rf8c305fc7c564a8e"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="Rf28e705ca5e34901"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="R2c389ab70f724530"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="R9d4b0327fe434936"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="R3b4624d52a354fff"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="R17c924773ef144b0"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R47b2830b56fd4eab"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="R50e330cbaa7e4f24"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="R380a0179589e4f13"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="R0f34f017b6dc4fc6"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="Ra5a9ab3bf42d4f71"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="a98550f3-ee28-495b-8e1f-edd7e3eb7e27"/>
+        <xdr:cNvPr id="1" name="62a24901-1ef3-4ff1-adba-3a249c35557d"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R004b67ca2e5844ec"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5d94f8ca10b6403d"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3486,9 +3486,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rf27844338bb5419f"/>
+  <x:drawing ns1:id="Rdf37c0e7b43b47e1"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R68db433293694ea3"/>
+    <x:tablePart ns1:id="Re5b60396c6d745a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4877,7 +4877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R7e30b5f4a5014df2"/>
+    <x:tablePart ns1:id="R9ec7d47d58de443d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5258,7 +5258,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R4ced039f02a54366"/>
+    <x:tablePart ns1:id="R6e27681e97e548e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6080,7 +6080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R9d812126885e4251"/>
+    <x:tablePart ns1:id="Rd14a0597aa0048b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="R3b4624d52a354fff"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="R17c924773ef144b0"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R47b2830b56fd4eab"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="R50e330cbaa7e4f24"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="R380a0179589e4f13"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="R0f34f017b6dc4fc6"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="Ra5a9ab3bf42d4f71"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="Rc6435873938f4a68"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="Rc2ece388063b444c"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="Rc376cbfddd3a49b2"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="Rf8c305fc7c564a8e"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="Rf28e705ca5e34901"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="R2c389ab70f724530"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="R9d4b0327fe434936"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="62a24901-1ef3-4ff1-adba-3a249c35557d"/>
+        <xdr:cNvPr id="1" name="a98550f3-ee28-495b-8e1f-edd7e3eb7e27"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5d94f8ca10b6403d"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R004b67ca2e5844ec"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3486,9 +3486,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rdf37c0e7b43b47e1"/>
+  <x:drawing ns1:id="Rf27844338bb5419f"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Re5b60396c6d745a4"/>
+    <x:tablePart ns1:id="R68db433293694ea3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4877,7 +4877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R9ec7d47d58de443d"/>
+    <x:tablePart ns1:id="R7e30b5f4a5014df2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5258,7 +5258,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R6e27681e97e548e8"/>
+    <x:tablePart ns1:id="R4ced039f02a54366"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6080,7 +6080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rd14a0597aa0048b8"/>
+    <x:tablePart ns1:id="R9d812126885e4251"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="R3b4624d52a354fff"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="R17c924773ef144b0"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R47b2830b56fd4eab"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="R50e330cbaa7e4f24"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="R380a0179589e4f13"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="R0f34f017b6dc4fc6"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="Ra5a9ab3bf42d4f71"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="R652895637daa487c"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="R594c446137cc4cac"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R0260dc22b23d40d1"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="R3a8aae84195f42a3"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="R865ac3c4c3a8485c"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="R934677c968d640cd"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="R9e32fb1623594543"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="62a24901-1ef3-4ff1-adba-3a249c35557d"/>
+        <xdr:cNvPr id="1" name="547f717f-9c71-4eab-8f9c-a606ce33b96e"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5d94f8ca10b6403d"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re6665a6309014528"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3486,9 +3486,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rdf37c0e7b43b47e1"/>
+  <x:drawing ns1:id="R4ba3a0213cea4066"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Re5b60396c6d745a4"/>
+    <x:tablePart ns1:id="Rf00f98d73cdb4ecd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4877,7 +4877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R9ec7d47d58de443d"/>
+    <x:tablePart ns1:id="Rce19ceaabda14f84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5258,7 +5258,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R6e27681e97e548e8"/>
+    <x:tablePart ns1:id="R9fafa41c0b3c42ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6080,7 +6080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rd14a0597aa0048b8"/>
+    <x:tablePart ns1:id="R958a2fe5e2764966"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6111,27 +6111,25 @@
       </x:c>
       <x:c r="B2" s="99" t="str"/>
       <x:c r="C2" s="99" t="str">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="99" t="str">
-        <x:v>source_fingerprint</x:v>
+        <x:v>spreadsheet_build_id</x:v>
       </x:c>
       <x:c r="B3" s="99" t="str"/>
       <x:c r="C3" s="99" t="str">
-        <x:v>sha256:5f5822a7acae425dbb4e9b7323e8bcb7c2933e99c8d0f270d1592e4eac4e883e</x:v>
+        <x:v>S3-08d641519318</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="99" t="str">
-        <x:v>test</x:v>
-      </x:c>
-      <x:c r="B4" s="99" t="str">
-        <x:v>SETUP-01</x:v>
-      </x:c>
+        <x:v>source_fingerprint</x:v>
+      </x:c>
+      <x:c r="B4" s="99" t="str"/>
       <x:c r="C4" s="99" t="str">
-        <x:v>sha256:6298d64e10367b2e38e5d41253bb816c1012479ab7612afc5a53ad66630e975f</x:v>
+        <x:v>sha256:08d6415193181337fead9371040d20422e94b4ed704294692294a69805dca6db</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6139,10 +6137,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B5" s="99" t="str">
-        <x:v>SETUP-02</x:v>
+        <x:v>SETUP-01</x:v>
       </x:c>
       <x:c r="C5" s="99" t="str">
-        <x:v>sha256:2c28c37a65e2efee3349ec9d9c3a6e75de10e76697f1c3b5ec5ca8d1ceae0030</x:v>
+        <x:v>sha256:6298d64e10367b2e38e5d41253bb816c1012479ab7612afc5a53ad66630e975f</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6150,10 +6148,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B6" s="99" t="str">
-        <x:v>SETUP-03</x:v>
+        <x:v>SETUP-02</x:v>
       </x:c>
       <x:c r="C6" s="99" t="str">
-        <x:v>sha256:eb596d6e2a1ad3dba500a053b487e07af4813566f59012575380f500c95740a3</x:v>
+        <x:v>sha256:2c28c37a65e2efee3349ec9d9c3a6e75de10e76697f1c3b5ec5ca8d1ceae0030</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6161,10 +6159,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B7" s="99" t="str">
-        <x:v>SETUP-MM-01</x:v>
+        <x:v>SETUP-03</x:v>
       </x:c>
       <x:c r="C7" s="99" t="str">
-        <x:v>sha256:c760cc1bea9609da89be5d36089ba2323849d51903b5f40f43c986536aab0cc0</x:v>
+        <x:v>sha256:eb596d6e2a1ad3dba500a053b487e07af4813566f59012575380f500c95740a3</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6172,10 +6170,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B8" s="99" t="str">
-        <x:v>SETUP-MM-AF-01</x:v>
+        <x:v>SETUP-MM-01</x:v>
       </x:c>
       <x:c r="C8" s="99" t="str">
-        <x:v>sha256:2b88f49e05b245e31f0d823f6ef4e5d71a2bd0398b2cf9cd8205610832364ab9</x:v>
+        <x:v>sha256:c760cc1bea9609da89be5d36089ba2323849d51903b5f40f43c986536aab0cc0</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6183,10 +6181,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B9" s="99" t="str">
-        <x:v>SETUP-04</x:v>
+        <x:v>SETUP-MM-AF-01</x:v>
       </x:c>
       <x:c r="C9" s="99" t="str">
-        <x:v>sha256:b6bd467f6a89f821e9373cc530c60d121981c3be1f93118148955e75331daaa4</x:v>
+        <x:v>sha256:2b88f49e05b245e31f0d823f6ef4e5d71a2bd0398b2cf9cd8205610832364ab9</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6194,10 +6192,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B10" s="99" t="str">
-        <x:v>SETUP-05</x:v>
+        <x:v>SETUP-04</x:v>
       </x:c>
       <x:c r="C10" s="99" t="str">
-        <x:v>sha256:67ea99e7324822765d73c9e1a978991ba090dd1fcb01bc4f819eb693e2018f1b</x:v>
+        <x:v>sha256:b6bd467f6a89f821e9373cc530c60d121981c3be1f93118148955e75331daaa4</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6205,10 +6203,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B11" s="99" t="str">
-        <x:v>SETUP-06</x:v>
+        <x:v>SETUP-05</x:v>
       </x:c>
       <x:c r="C11" s="99" t="str">
-        <x:v>sha256:50a7bb1d684b76be2ecaf5dd70540adcc5036481c265a2d6e4348a13c0d3f061</x:v>
+        <x:v>sha256:67ea99e7324822765d73c9e1a978991ba090dd1fcb01bc4f819eb693e2018f1b</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -6216,10 +6214,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B12" s="99" t="str">
-        <x:v>SETUP-07</x:v>
+        <x:v>SETUP-06</x:v>
       </x:c>
       <x:c r="C12" s="99" t="str">
-        <x:v>sha256:4465ab573d202c4fbb497291b08a1c5ffffad91c48872e300991471bef2567f4</x:v>
+        <x:v>sha256:50a7bb1d684b76be2ecaf5dd70540adcc5036481c265a2d6e4348a13c0d3f061</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6227,10 +6225,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B13" s="99" t="str">
-        <x:v>CTRL-CONFIG-01</x:v>
+        <x:v>SETUP-07</x:v>
       </x:c>
       <x:c r="C13" s="99" t="str">
-        <x:v>sha256:bf207e6d54b48768207e423d534c48709f88f234d55bdcb9613e260a68c411f2</x:v>
+        <x:v>sha256:4465ab573d202c4fbb497291b08a1c5ffffad91c48872e300991471bef2567f4</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -6238,10 +6236,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B14" s="99" t="str">
-        <x:v>BACKUP-SET-01</x:v>
+        <x:v>CTRL-CONFIG-01</x:v>
       </x:c>
       <x:c r="C14" s="99" t="str">
-        <x:v>sha256:a17b1005496620e34a1ee11e646e9a1fc082c4eb20ac617592011ba5e6ceae8a</x:v>
+        <x:v>sha256:bf207e6d54b48768207e423d534c48709f88f234d55bdcb9613e260a68c411f2</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -6249,10 +6247,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B15" s="99" t="str">
-        <x:v>C1-CONFIG-01</x:v>
+        <x:v>BACKUP-SET-01</x:v>
       </x:c>
       <x:c r="C15" s="99" t="str">
-        <x:v>sha256:1507d79e9f067c7c5b2099b8101a3d17938d127abce04324c2c3ac3d6b72efd7</x:v>
+        <x:v>sha256:a17b1005496620e34a1ee11e646e9a1fc082c4eb20ac617592011ba5e6ceae8a</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -6260,10 +6258,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B16" s="99" t="str">
-        <x:v>C1-REG-01</x:v>
+        <x:v>C1-CONFIG-01</x:v>
       </x:c>
       <x:c r="C16" s="99" t="str">
-        <x:v>sha256:04a561cd1850599049f01a2ec97355afe25fe8c5fc4c4c81d52f639897d63b03</x:v>
+        <x:v>sha256:1507d79e9f067c7c5b2099b8101a3d17938d127abce04324c2c3ac3d6b72efd7</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -6271,10 +6269,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B17" s="99" t="str">
-        <x:v>C1-READ-01</x:v>
+        <x:v>C1-REG-01</x:v>
       </x:c>
       <x:c r="C17" s="99" t="str">
-        <x:v>sha256:2c25a1c907b5edcc56c06bd4e4bd1d8dde41fa6faebde85baec2ab4a2acefd87</x:v>
+        <x:v>sha256:04a561cd1850599049f01a2ec97355afe25fe8c5fc4c4c81d52f639897d63b03</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -6282,10 +6280,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B18" s="99" t="str">
-        <x:v>C1-OPS-01</x:v>
+        <x:v>C1-READ-01</x:v>
       </x:c>
       <x:c r="C18" s="99" t="str">
-        <x:v>sha256:88304c030b7adb56fe9666b1d5541eb373d1615173ce399a06f9538b960dfc1e</x:v>
+        <x:v>sha256:2c25a1c907b5edcc56c06bd4e4bd1d8dde41fa6faebde85baec2ab4a2acefd87</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -6293,10 +6291,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B19" s="99" t="str">
-        <x:v>C2-CONFIG-01</x:v>
+        <x:v>C1-OPS-01</x:v>
       </x:c>
       <x:c r="C19" s="99" t="str">
-        <x:v>sha256:cb99fda58735522dedf306188a4a8f12400a51676d686f840b660c38650789c3</x:v>
+        <x:v>sha256:88304c030b7adb56fe9666b1d5541eb373d1615173ce399a06f9538b960dfc1e</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6304,10 +6302,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B20" s="99" t="str">
-        <x:v>C2-REG-01</x:v>
+        <x:v>C2-CONFIG-01</x:v>
       </x:c>
       <x:c r="C20" s="99" t="str">
-        <x:v>sha256:f4b28c92d9a20605b591f5721dd3ad3beff4e7b5105c8c15a65d23398e8e2d56</x:v>
+        <x:v>sha256:cb99fda58735522dedf306188a4a8f12400a51676d686f840b660c38650789c3</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -6315,10 +6313,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B21" s="99" t="str">
-        <x:v>C2-READ-01</x:v>
+        <x:v>C2-REG-01</x:v>
       </x:c>
       <x:c r="C21" s="99" t="str">
-        <x:v>sha256:cda561c58eb3b3eeb7b5d8b86836960a48f9ee79058073e4943561aa9c9b39d1</x:v>
+        <x:v>sha256:f4b28c92d9a20605b591f5721dd3ad3beff4e7b5105c8c15a65d23398e8e2d56</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -6326,10 +6324,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B22" s="99" t="str">
-        <x:v>C2-OPS-01</x:v>
+        <x:v>C2-READ-01</x:v>
       </x:c>
       <x:c r="C22" s="99" t="str">
-        <x:v>sha256:d939e6407cadc5480c2f88547845d69f1e2e36a37b7ae6635cebcdde0e9ce030</x:v>
+        <x:v>sha256:cda561c58eb3b3eeb7b5d8b86836960a48f9ee79058073e4943561aa9c9b39d1</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -6337,10 +6335,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B23" s="99" t="str">
-        <x:v>C3-CONFIG-01</x:v>
+        <x:v>C2-OPS-01</x:v>
       </x:c>
       <x:c r="C23" s="99" t="str">
-        <x:v>sha256:633063511fb285503511b318ef26bf092ac48be8afda4df5ef008ab645d4f712</x:v>
+        <x:v>sha256:d939e6407cadc5480c2f88547845d69f1e2e36a37b7ae6635cebcdde0e9ce030</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -6348,10 +6346,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B24" s="99" t="str">
-        <x:v>C3-REG-01</x:v>
+        <x:v>C3-CONFIG-01</x:v>
       </x:c>
       <x:c r="C24" s="99" t="str">
-        <x:v>sha256:f692886e78e72d84e31a5ef91aa281938d0529b8b7ea1a220bbf200993144e29</x:v>
+        <x:v>sha256:633063511fb285503511b318ef26bf092ac48be8afda4df5ef008ab645d4f712</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -6359,10 +6357,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B25" s="99" t="str">
-        <x:v>C3-READ-01</x:v>
+        <x:v>C3-REG-01</x:v>
       </x:c>
       <x:c r="C25" s="99" t="str">
-        <x:v>sha256:44b63514e2b1f8af98d36c6a4a25a22b7d554a7055c63b717a390b5801f4f72f</x:v>
+        <x:v>sha256:f692886e78e72d84e31a5ef91aa281938d0529b8b7ea1a220bbf200993144e29</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -6370,10 +6368,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B26" s="99" t="str">
-        <x:v>BACKUP-SET-02</x:v>
+        <x:v>C3-READ-01</x:v>
       </x:c>
       <x:c r="C26" s="99" t="str">
-        <x:v>sha256:d8e92939499af335b6f4493b97c7fa8671ad4fc3910cca9a5f8eda4ef41cfc2f</x:v>
+        <x:v>sha256:44b63514e2b1f8af98d36c6a4a25a22b7d554a7055c63b717a390b5801f4f72f</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -6381,10 +6379,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B27" s="99" t="str">
-        <x:v>C3-OPS-01</x:v>
+        <x:v>BACKUP-SET-02</x:v>
       </x:c>
       <x:c r="C27" s="99" t="str">
-        <x:v>sha256:c60f649504d508a81fa0bd19f172421676472153728093142a04d2ba4e5c96ad</x:v>
+        <x:v>sha256:d8e92939499af335b6f4493b97c7fa8671ad4fc3910cca9a5f8eda4ef41cfc2f</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -6392,10 +6390,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B28" s="99" t="str">
-        <x:v>CTRL-AFON-01</x:v>
+        <x:v>C3-OPS-01</x:v>
       </x:c>
       <x:c r="C28" s="99" t="str">
-        <x:v>sha256:2c3055256d014c23ff48c71e8998a544186d8606fc4ad766773ec6c14976f6d7</x:v>
+        <x:v>sha256:c60f649504d508a81fa0bd19f172421676472153728093142a04d2ba4e5c96ad</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -6403,10 +6401,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B29" s="99" t="str">
-        <x:v>CTRL-AELOCK-01</x:v>
+        <x:v>CTRL-AFON-01</x:v>
       </x:c>
       <x:c r="C29" s="99" t="str">
-        <x:v>sha256:888daf7bc311ea1a395e8a7406c8caac4655da1853803ba28df50d40a03fda9b</x:v>
+        <x:v>sha256:2c3055256d014c23ff48c71e8998a544186d8606fc4ad766773ec6c14976f6d7</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -6414,10 +6412,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B30" s="99" t="str">
-        <x:v>CTRL-DOF-01</x:v>
+        <x:v>CTRL-AELOCK-01</x:v>
       </x:c>
       <x:c r="C30" s="99" t="str">
-        <x:v>sha256:606ba83c6c6ef93bebe9f6f0451a7c80fead0f83b62fd48fe2137c5a72fa3b19</x:v>
+        <x:v>sha256:888daf7bc311ea1a395e8a7406c8caac4655da1853803ba28df50d40a03fda9b</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -6425,10 +6423,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B31" s="99" t="str">
-        <x:v>CTRL-SET-01</x:v>
+        <x:v>CTRL-DOF-01</x:v>
       </x:c>
       <x:c r="C31" s="99" t="str">
-        <x:v>sha256:ad0d38b06de1f9f53cde8acce71775385e4aaef6588e771934320e4124431e25</x:v>
+        <x:v>sha256:606ba83c6c6ef93bebe9f6f0451a7c80fead0f83b62fd48fe2137c5a72fa3b19</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -6436,10 +6434,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B32" s="99" t="str">
-        <x:v>CTRL-JOY-01</x:v>
+        <x:v>CTRL-SET-01</x:v>
       </x:c>
       <x:c r="C32" s="99" t="str">
-        <x:v>sha256:957387ec73ac18ab4785a4aaf972f7e285c513c90769f009edece0c97f044600</x:v>
+        <x:v>sha256:ad0d38b06de1f9f53cde8acce71775385e4aaef6588e771934320e4124431e25</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -6447,10 +6445,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B33" s="99" t="str">
-        <x:v>EFCS-SHOCK-01</x:v>
+        <x:v>CTRL-JOY-01</x:v>
       </x:c>
       <x:c r="C33" s="99" t="str">
-        <x:v>sha256:5536143e9808461e6a2779baa6f8d2adf0dd969cccb0b7d2a28598a924d61203</x:v>
+        <x:v>sha256:957387ec73ac18ab4785a4aaf972f7e285c513c90769f009edece0c97f044600</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -6458,10 +6456,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B34" s="99" t="str">
-        <x:v>EFCS-BOKEH-01</x:v>
+        <x:v>EFCS-SHOCK-01</x:v>
       </x:c>
       <x:c r="C34" s="99" t="str">
-        <x:v>sha256:4e1bd076174191e3341b0eb9a6f2279f745b35cc3425dbd6e1360e771e5f3a42</x:v>
+        <x:v>sha256:5536143e9808461e6a2779baa6f8d2adf0dd969cccb0b7d2a28598a924d61203</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -6469,10 +6467,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B35" s="99" t="str">
-        <x:v>EFCS-LIGHT-01</x:v>
+        <x:v>EFCS-BOKEH-01</x:v>
       </x:c>
       <x:c r="C35" s="99" t="str">
-        <x:v>sha256:0294347c51bd94b65f8eec9fad44b39d00e5433c4dc12aeee06c48c0e5ae9c08</x:v>
+        <x:v>sha256:4e1bd076174191e3341b0eb9a6f2279f745b35cc3425dbd6e1360e771e5f3a42</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -6480,10 +6478,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B36" s="99" t="str">
-        <x:v>EFCS-BURST-01</x:v>
+        <x:v>EFCS-LIGHT-01</x:v>
       </x:c>
       <x:c r="C36" s="99" t="str">
-        <x:v>sha256:10966e281790e9619773bd99c263d1a8c3f83170403b36c2fbb2a490499e7130</x:v>
+        <x:v>sha256:0294347c51bd94b65f8eec9fad44b39d00e5433c4dc12aeee06c48c0e5ae9c08</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -6491,10 +6489,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B37" s="99" t="str">
-        <x:v>FLASH-PLUTO-01</x:v>
+        <x:v>EFCS-BURST-01</x:v>
       </x:c>
       <x:c r="C37" s="99" t="str">
-        <x:v>sha256:5c00b09991f26e6b8bedd930e7304b53dae8f93819c7135c765aac82e970d87c</x:v>
+        <x:v>sha256:10966e281790e9619773bd99c263d1a8c3f83170403b36c2fbb2a490499e7130</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -6502,10 +6500,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B38" s="99" t="str">
-        <x:v>FINAL-READ-01</x:v>
+        <x:v>FLASH-PLUTO-01</x:v>
       </x:c>
       <x:c r="C38" s="99" t="str">
-        <x:v>sha256:688b6db6bd3d38070dfd682da54402cf8678093cb1014766953f9f5da49d7407</x:v>
+        <x:v>sha256:5c00b09991f26e6b8bedd930e7304b53dae8f93819c7135c765aac82e970d87c</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -6513,10 +6511,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B39" s="99" t="str">
-        <x:v>FINAL-SAVE-01</x:v>
+        <x:v>FINAL-READ-01</x:v>
       </x:c>
       <x:c r="C39" s="99" t="str">
-        <x:v>sha256:3d3558eaa54a0fdee859a544db2bccada6d3a8749fda96001422741914b6d0a6</x:v>
+        <x:v>sha256:688b6db6bd3d38070dfd682da54402cf8678093cb1014766953f9f5da49d7407</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -6524,21 +6522,21 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B40" s="99" t="str">
-        <x:v>PROJECT-UPDATE-01</x:v>
+        <x:v>FINAL-SAVE-01</x:v>
       </x:c>
       <x:c r="C40" s="99" t="str">
-        <x:v>sha256:9312ccf684ccf233900950855d7a3457eb01e52e1c8fcb90e3c7c7daa72e17a6</x:v>
+        <x:v>sha256:3d3558eaa54a0fdee859a544db2bccada6d3a8749fda96001422741914b6d0a6</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="99" t="str">
-        <x:v>registration</x:v>
+        <x:v>test</x:v>
       </x:c>
       <x:c r="B41" s="99" t="str">
-        <x:v>Mode</x:v>
+        <x:v>PROJECT-UPDATE-01</x:v>
       </x:c>
       <x:c r="C41" s="99" t="str">
-        <x:v>sha256:16380d447ae550758ff49c344119374224a6b1c009504e23f6f4f93c11c00533</x:v>
+        <x:v>sha256:9312ccf684ccf233900950855d7a3457eb01e52e1c8fcb90e3c7c7daa72e17a6</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -6546,10 +6544,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B42" s="99" t="str">
-        <x:v>Metering</x:v>
+        <x:v>Mode</x:v>
       </x:c>
       <x:c r="C42" s="99" t="str">
-        <x:v>sha256:bc76af3dd5f76e718fe876deafcfbc0fd4a3f64d2a2eb64d2253751bd18f4eae</x:v>
+        <x:v>sha256:16380d447ae550758ff49c344119374224a6b1c009504e23f6f4f93c11c00533</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -6557,10 +6555,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B43" s="99" t="str">
-        <x:v>Exposure Compensation</x:v>
+        <x:v>Metering</x:v>
       </x:c>
       <x:c r="C43" s="99" t="str">
-        <x:v>sha256:88e1331bb1792dc8c402253666af51d91b4ff14bdf848d8f5715f7c5735374ee</x:v>
+        <x:v>sha256:bc76af3dd5f76e718fe876deafcfbc0fd4a3f64d2a2eb64d2253751bd18f4eae</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -6568,10 +6566,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B44" s="99" t="str">
-        <x:v>Shutter Speed</x:v>
+        <x:v>Exposure Compensation</x:v>
       </x:c>
       <x:c r="C44" s="99" t="str">
-        <x:v>sha256:50a59b23cd80339f63a7068a9f9b6618357bcc05eb6f986cc5c7a707e50c0a74</x:v>
+        <x:v>sha256:88e1331bb1792dc8c402253666af51d91b4ff14bdf848d8f5715f7c5735374ee</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -6579,10 +6577,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B45" s="99" t="str">
-        <x:v>Aperture</x:v>
+        <x:v>Shutter Speed</x:v>
       </x:c>
       <x:c r="C45" s="99" t="str">
-        <x:v>sha256:74b8c602aefe9109b324a5d3d0f5af54cafeaceae6f80e96effd7b7e7b7512a0</x:v>
+        <x:v>sha256:50a59b23cd80339f63a7068a9f9b6618357bcc05eb6f986cc5c7a707e50c0a74</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -6590,10 +6588,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B46" s="99" t="str">
-        <x:v>ISO</x:v>
+        <x:v>Aperture</x:v>
       </x:c>
       <x:c r="C46" s="99" t="str">
-        <x:v>sha256:3c57560fdad255af8dddd4afe759bf3a638ced62cd0b435fbcb39f539ed4d5cd</x:v>
+        <x:v>sha256:74b8c602aefe9109b324a5d3d0f5af54cafeaceae6f80e96effd7b7e7b7512a0</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -6601,10 +6599,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B47" s="99" t="str">
-        <x:v>Auto ISO Maximum</x:v>
+        <x:v>ISO</x:v>
       </x:c>
       <x:c r="C47" s="99" t="str">
-        <x:v>sha256:215087f96f2c5d379e4931bbcffe7ea4f1ebe59cc0229f5dae23f52e08edbba5</x:v>
+        <x:v>sha256:3c57560fdad255af8dddd4afe759bf3a638ced62cd0b435fbcb39f539ed4d5cd</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -6612,10 +6610,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B48" s="99" t="str">
-        <x:v>AF Operation</x:v>
+        <x:v>Auto ISO Maximum</x:v>
       </x:c>
       <x:c r="C48" s="99" t="str">
-        <x:v>sha256:e52a8877636b9e990324e5e59a10b6b8a0723c7699f752ac41a4e39a25ed8c94</x:v>
+        <x:v>sha256:215087f96f2c5d379e4931bbcffe7ea4f1ebe59cc0229f5dae23f52e08edbba5</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -6623,10 +6621,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B49" s="99" t="str">
-        <x:v>Servo AF Case</x:v>
+        <x:v>AF Operation</x:v>
       </x:c>
       <x:c r="C49" s="99" t="str">
-        <x:v>sha256:c9f1ca7567fd410ce854474a770e020fea6e9904b6872801ebc1b2f20b392fbf</x:v>
+        <x:v>sha256:e52a8877636b9e990324e5e59a10b6b8a0723c7699f752ac41a4e39a25ed8c94</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -6634,10 +6632,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B50" s="99" t="str">
-        <x:v>Tracking Sensitivity</x:v>
+        <x:v>Servo AF Case</x:v>
       </x:c>
       <x:c r="C50" s="99" t="str">
-        <x:v>sha256:dfe83819227cc879db8a3ff1c5b898a2d1c1b0f74d6b3364ad9a92ed7b018424</x:v>
+        <x:v>sha256:c9f1ca7567fd410ce854474a770e020fea6e9904b6872801ebc1b2f20b392fbf</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -6645,10 +6643,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B51" s="99" t="str">
-        <x:v>Accel./Decel. Tracking</x:v>
+        <x:v>Tracking Sensitivity</x:v>
       </x:c>
       <x:c r="C51" s="99" t="str">
-        <x:v>sha256:e11fda77b702b46abfbda7bbf4de92c162668fd479106b46da999dcd11ba28cf</x:v>
+        <x:v>sha256:dfe83819227cc879db8a3ff1c5b898a2d1c1b0f74d6b3364ad9a92ed7b018424</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -6656,10 +6654,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B52" s="99" t="str">
-        <x:v>Switching Tracked Subjects</x:v>
+        <x:v>Accel./Decel. Tracking</x:v>
       </x:c>
       <x:c r="C52" s="99" t="str">
-        <x:v>sha256:1866e2e49cd4159a2f76e301df8394efb14ebc00f49606d84fedb5501875eeb7</x:v>
+        <x:v>sha256:e11fda77b702b46abfbda7bbf4de92c162668fd479106b46da999dcd11ba28cf</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -6667,10 +6665,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B53" s="99" t="str">
-        <x:v>AF Method</x:v>
+        <x:v>Switching Tracked Subjects</x:v>
       </x:c>
       <x:c r="C53" s="99" t="str">
-        <x:v>sha256:ac30ce5e48a2e9e69db02806afb6a8c836dd8220dce399b57ed50b6ec3569d82</x:v>
+        <x:v>sha256:1866e2e49cd4159a2f76e301df8394efb14ebc00f49606d84fedb5501875eeb7</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -6678,10 +6676,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B54" s="99" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="C54" s="99" t="str">
-        <x:v>sha256:ca630f9c8761b1ba9bc261fc0264e1fdff6c6ebce7d3d60f68453c6e6c0fb66e</x:v>
+        <x:v>sha256:ac30ce5e48a2e9e69db02806afb6a8c836dd8220dce399b57ed50b6ec3569d82</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -6689,10 +6687,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B55" s="99" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="C55" s="99" t="str">
-        <x:v>sha256:d4f49e58f189bc2a85058e8030bdba5867549892594d4961911a877fc7774cc1</x:v>
+        <x:v>sha256:ca630f9c8761b1ba9bc261fc0264e1fdff6c6ebce7d3d60f68453c6e6c0fb66e</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -6700,10 +6698,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B56" s="99" t="str">
-        <x:v>Drive Mode</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="C56" s="99" t="str">
-        <x:v>sha256:a407ab25d86c6b32e4618dffadce1bc9f7375731cceb32a9b15154cb636bbc93</x:v>
+        <x:v>sha256:d4f49e58f189bc2a85058e8030bdba5867549892594d4961911a877fc7774cc1</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -6711,10 +6709,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B57" s="99" t="str">
-        <x:v>High Speed Display</x:v>
+        <x:v>Drive Mode</x:v>
       </x:c>
       <x:c r="C57" s="99" t="str">
-        <x:v>sha256:0af962b70870008b8b495ab863d5b9773e68daa4e052c10a5157bbb6e9b09a04</x:v>
+        <x:v>sha256:a407ab25d86c6b32e4618dffadce1bc9f7375731cceb32a9b15154cb636bbc93</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -6722,10 +6720,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B58" s="99" t="str">
-        <x:v>Shutter Type</x:v>
+        <x:v>High Speed Display</x:v>
       </x:c>
       <x:c r="C58" s="99" t="str">
-        <x:v>sha256:e0eb3a601149113b744968c8d35c10e22707716e94c780644837edcabff082bb</x:v>
+        <x:v>sha256:0af962b70870008b8b495ab863d5b9773e68daa4e052c10a5157bbb6e9b09a04</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -6733,10 +6731,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B59" s="99" t="str">
-        <x:v>Image Stabilizer Mode</x:v>
+        <x:v>Shutter Type</x:v>
       </x:c>
       <x:c r="C59" s="99" t="str">
-        <x:v>sha256:cc5907ea77c17b747bda000cb9d24e886022b15d9be9b15be2fd7d3a6aa18fba</x:v>
+        <x:v>sha256:e0eb3a601149113b744968c8d35c10e22707716e94c780644837edcabff082bb</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -6744,10 +6742,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B60" s="99" t="str">
-        <x:v>IBIS</x:v>
+        <x:v>Image Stabilizer Mode</x:v>
       </x:c>
       <x:c r="C60" s="99" t="str">
-        <x:v>sha256:f88432494f6ce6fd467acf866dcb7285209af0daa97f23211b4c2e9a2fca510a</x:v>
+        <x:v>sha256:cc5907ea77c17b747bda000cb9d24e886022b15d9be9b15be2fd7d3a6aa18fba</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -6755,10 +6753,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B61" s="99" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>IBIS</x:v>
       </x:c>
       <x:c r="C61" s="99" t="str">
-        <x:v>sha256:faa653558ccc3ca42def02cffceb2449676221f3e2b701a95cb76c734a606a66</x:v>
+        <x:v>sha256:f88432494f6ce6fd467acf866dcb7285209af0daa97f23211b4c2e9a2fca510a</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -6766,9 +6764,20 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B62" s="99" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="C62" s="99" t="str">
+        <x:v>sha256:faa653558ccc3ca42def02cffceb2449676221f3e2b701a95cb76c734a606a66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="99" t="str">
+        <x:v>registration</x:v>
+      </x:c>
+      <x:c r="B63" s="99" t="str">
         <x:v>Lens IS switch</x:v>
       </x:c>
-      <x:c r="C62" s="99" t="str">
+      <x:c r="C63" s="99" t="str">
         <x:v>sha256:77c1f08d541f8a95c354155213e1184f193765664d2faca4e6245806067b6735</x:v>
       </x:c>
     </x:row>

--- a/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
+++ b/docs/downloads/EOS R5 Setup & Verification Tracker.xlsx
@@ -5,13 +5,13 @@
     <x:workbookView activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Dashboard" sheetId="1" ns1:id="R652895637daa487c"/>
-    <x:sheet name="Checklist" sheetId="2" ns1:id="R594c446137cc4cac"/>
-    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R0260dc22b23d40d1"/>
-    <x:sheet name="Sessions" sheetId="4" ns1:id="R3a8aae84195f42a3"/>
-    <x:sheet name="Lists" sheetId="5" ns1:id="R865ac3c4c3a8485c"/>
-    <x:sheet name="Menu" sheetId="6" ns1:id="R934677c968d640cd"/>
-    <x:sheet name="Metadata" sheetId="7" ns1:id="R9e32fb1623594543"/>
+    <x:sheet name="Dashboard" sheetId="1" ns1:id="R3b4624d52a354fff"/>
+    <x:sheet name="Checklist" sheetId="2" ns1:id="R17c924773ef144b0"/>
+    <x:sheet name="C1-C3 Registration" sheetId="3" ns1:id="R47b2830b56fd4eab"/>
+    <x:sheet name="Sessions" sheetId="4" ns1:id="R50e330cbaa7e4f24"/>
+    <x:sheet name="Lists" sheetId="5" ns1:id="R380a0179589e4f13"/>
+    <x:sheet name="Menu" sheetId="6" ns1:id="R0f34f017b6dc4fc6"/>
+    <x:sheet name="Metadata" sheetId="7" ns1:id="Ra5a9ab3bf42d4f71"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="547f717f-9c71-4eab-8f9c-a606ce33b96e"/>
+        <xdr:cNvPr id="1" name="62a24901-1ef3-4ff1-adba-3a249c35557d"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re6665a6309014528"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5d94f8ca10b6403d"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3486,9 +3486,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R4ba3a0213cea4066"/>
+  <x:drawing ns1:id="Rdf37c0e7b43b47e1"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rf00f98d73cdb4ecd"/>
+    <x:tablePart ns1:id="Re5b60396c6d745a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4877,7 +4877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rce19ceaabda14f84"/>
+    <x:tablePart ns1:id="R9ec7d47d58de443d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5258,7 +5258,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R9fafa41c0b3c42ff"/>
+    <x:tablePart ns1:id="R6e27681e97e548e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6080,7 +6080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R958a2fe5e2764966"/>
+    <x:tablePart ns1:id="Rd14a0597aa0048b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6111,25 +6111,27 @@
       </x:c>
       <x:c r="B2" s="99" t="str"/>
       <x:c r="C2" s="99" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="99" t="str">
-        <x:v>spreadsheet_build_id</x:v>
+        <x:v>source_fingerprint</x:v>
       </x:c>
       <x:c r="B3" s="99" t="str"/>
       <x:c r="C3" s="99" t="str">
-        <x:v>S3-08d641519318</x:v>
+        <x:v>sha256:5f5822a7acae425dbb4e9b7323e8bcb7c2933e99c8d0f270d1592e4eac4e883e</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="99" t="str">
-        <x:v>source_fingerprint</x:v>
-      </x:c>
-      <x:c r="B4" s="99" t="str"/>
+        <x:v>test</x:v>
+      </x:c>
+      <x:c r="B4" s="99" t="str">
+        <x:v>SETUP-01</x:v>
+      </x:c>
       <x:c r="C4" s="99" t="str">
-        <x:v>sha256:08d6415193181337fead9371040d20422e94b4ed704294692294a69805dca6db</x:v>
+        <x:v>sha256:6298d64e10367b2e38e5d41253bb816c1012479ab7612afc5a53ad66630e975f</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6137,10 +6139,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B5" s="99" t="str">
-        <x:v>SETUP-01</x:v>
+        <x:v>SETUP-02</x:v>
       </x:c>
       <x:c r="C5" s="99" t="str">
-        <x:v>sha256:6298d64e10367b2e38e5d41253bb816c1012479ab7612afc5a53ad66630e975f</x:v>
+        <x:v>sha256:2c28c37a65e2efee3349ec9d9c3a6e75de10e76697f1c3b5ec5ca8d1ceae0030</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6148,10 +6150,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B6" s="99" t="str">
-        <x:v>SETUP-02</x:v>
+        <x:v>SETUP-03</x:v>
       </x:c>
       <x:c r="C6" s="99" t="str">
-        <x:v>sha256:2c28c37a65e2efee3349ec9d9c3a6e75de10e76697f1c3b5ec5ca8d1ceae0030</x:v>
+        <x:v>sha256:eb596d6e2a1ad3dba500a053b487e07af4813566f59012575380f500c95740a3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6159,10 +6161,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B7" s="99" t="str">
-        <x:v>SETUP-03</x:v>
+        <x:v>SETUP-MM-01</x:v>
       </x:c>
       <x:c r="C7" s="99" t="str">
-        <x:v>sha256:eb596d6e2a1ad3dba500a053b487e07af4813566f59012575380f500c95740a3</x:v>
+        <x:v>sha256:c760cc1bea9609da89be5d36089ba2323849d51903b5f40f43c986536aab0cc0</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6170,10 +6172,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B8" s="99" t="str">
-        <x:v>SETUP-MM-01</x:v>
+        <x:v>SETUP-MM-AF-01</x:v>
       </x:c>
       <x:c r="C8" s="99" t="str">
-        <x:v>sha256:c760cc1bea9609da89be5d36089ba2323849d51903b5f40f43c986536aab0cc0</x:v>
+        <x:v>sha256:2b88f49e05b245e31f0d823f6ef4e5d71a2bd0398b2cf9cd8205610832364ab9</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6181,10 +6183,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B9" s="99" t="str">
-        <x:v>SETUP-MM-AF-01</x:v>
+        <x:v>SETUP-04</x:v>
       </x:c>
       <x:c r="C9" s="99" t="str">
-        <x:v>sha256:2b88f49e05b245e31f0d823f6ef4e5d71a2bd0398b2cf9cd8205610832364ab9</x:v>
+        <x:v>sha256:b6bd467f6a89f821e9373cc530c60d121981c3be1f93118148955e75331daaa4</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6192,10 +6194,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B10" s="99" t="str">
-        <x:v>SETUP-04</x:v>
+        <x:v>SETUP-05</x:v>
       </x:c>
       <x:c r="C10" s="99" t="str">
-        <x:v>sha256:b6bd467f6a89f821e9373cc530c60d121981c3be1f93118148955e75331daaa4</x:v>
+        <x:v>sha256:67ea99e7324822765d73c9e1a978991ba090dd1fcb01bc4f819eb693e2018f1b</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6203,10 +6205,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B11" s="99" t="str">
-        <x:v>SETUP-05</x:v>
+        <x:v>SETUP-06</x:v>
       </x:c>
       <x:c r="C11" s="99" t="str">
-        <x:v>sha256:67ea99e7324822765d73c9e1a978991ba090dd1fcb01bc4f819eb693e2018f1b</x:v>
+        <x:v>sha256:50a7bb1d684b76be2ecaf5dd70540adcc5036481c265a2d6e4348a13c0d3f061</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -6214,10 +6216,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B12" s="99" t="str">
-        <x:v>SETUP-06</x:v>
+        <x:v>SETUP-07</x:v>
       </x:c>
       <x:c r="C12" s="99" t="str">
-        <x:v>sha256:50a7bb1d684b76be2ecaf5dd70540adcc5036481c265a2d6e4348a13c0d3f061</x:v>
+        <x:v>sha256:4465ab573d202c4fbb497291b08a1c5ffffad91c48872e300991471bef2567f4</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6225,10 +6227,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B13" s="99" t="str">
-        <x:v>SETUP-07</x:v>
+        <x:v>CTRL-CONFIG-01</x:v>
       </x:c>
       <x:c r="C13" s="99" t="str">
-        <x:v>sha256:4465ab573d202c4fbb497291b08a1c5ffffad91c48872e300991471bef2567f4</x:v>
+        <x:v>sha256:bf207e6d54b48768207e423d534c48709f88f234d55bdcb9613e260a68c411f2</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -6236,10 +6238,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B14" s="99" t="str">
-        <x:v>CTRL-CONFIG-01</x:v>
+        <x:v>BACKUP-SET-01</x:v>
       </x:c>
       <x:c r="C14" s="99" t="str">
-        <x:v>sha256:bf207e6d54b48768207e423d534c48709f88f234d55bdcb9613e260a68c411f2</x:v>
+        <x:v>sha256:a17b1005496620e34a1ee11e646e9a1fc082c4eb20ac617592011ba5e6ceae8a</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -6247,10 +6249,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B15" s="99" t="str">
-        <x:v>BACKUP-SET-01</x:v>
+        <x:v>C1-CONFIG-01</x:v>
       </x:c>
       <x:c r="C15" s="99" t="str">
-        <x:v>sha256:a17b1005496620e34a1ee11e646e9a1fc082c4eb20ac617592011ba5e6ceae8a</x:v>
+        <x:v>sha256:1507d79e9f067c7c5b2099b8101a3d17938d127abce04324c2c3ac3d6b72efd7</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -6258,10 +6260,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B16" s="99" t="str">
-        <x:v>C1-CONFIG-01</x:v>
+        <x:v>C1-REG-01</x:v>
       </x:c>
       <x:c r="C16" s="99" t="str">
-        <x:v>sha256:1507d79e9f067c7c5b2099b8101a3d17938d127abce04324c2c3ac3d6b72efd7</x:v>
+        <x:v>sha256:04a561cd1850599049f01a2ec97355afe25fe8c5fc4c4c81d52f639897d63b03</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -6269,10 +6271,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B17" s="99" t="str">
-        <x:v>C1-REG-01</x:v>
+        <x:v>C1-READ-01</x:v>
       </x:c>
       <x:c r="C17" s="99" t="str">
-        <x:v>sha256:04a561cd1850599049f01a2ec97355afe25fe8c5fc4c4c81d52f639897d63b03</x:v>
+        <x:v>sha256:2c25a1c907b5edcc56c06bd4e4bd1d8dde41fa6faebde85baec2ab4a2acefd87</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -6280,10 +6282,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B18" s="99" t="str">
-        <x:v>C1-READ-01</x:v>
+        <x:v>C1-OPS-01</x:v>
       </x:c>
       <x:c r="C18" s="99" t="str">
-        <x:v>sha256:2c25a1c907b5edcc56c06bd4e4bd1d8dde41fa6faebde85baec2ab4a2acefd87</x:v>
+        <x:v>sha256:88304c030b7adb56fe9666b1d5541eb373d1615173ce399a06f9538b960dfc1e</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -6291,10 +6293,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B19" s="99" t="str">
-        <x:v>C1-OPS-01</x:v>
+        <x:v>C2-CONFIG-01</x:v>
       </x:c>
       <x:c r="C19" s="99" t="str">
-        <x:v>sha256:88304c030b7adb56fe9666b1d5541eb373d1615173ce399a06f9538b960dfc1e</x:v>
+        <x:v>sha256:cb99fda58735522dedf306188a4a8f12400a51676d686f840b660c38650789c3</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6302,10 +6304,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B20" s="99" t="str">
-        <x:v>C2-CONFIG-01</x:v>
+        <x:v>C2-REG-01</x:v>
       </x:c>
       <x:c r="C20" s="99" t="str">
-        <x:v>sha256:cb99fda58735522dedf306188a4a8f12400a51676d686f840b660c38650789c3</x:v>
+        <x:v>sha256:f4b28c92d9a20605b591f5721dd3ad3beff4e7b5105c8c15a65d23398e8e2d56</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -6313,10 +6315,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B21" s="99" t="str">
-        <x:v>C2-REG-01</x:v>
+        <x:v>C2-READ-01</x:v>
       </x:c>
       <x:c r="C21" s="99" t="str">
-        <x:v>sha256:f4b28c92d9a20605b591f5721dd3ad3beff4e7b5105c8c15a65d23398e8e2d56</x:v>
+        <x:v>sha256:cda561c58eb3b3eeb7b5d8b86836960a48f9ee79058073e4943561aa9c9b39d1</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -6324,10 +6326,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B22" s="99" t="str">
-        <x:v>C2-READ-01</x:v>
+        <x:v>C2-OPS-01</x:v>
       </x:c>
       <x:c r="C22" s="99" t="str">
-        <x:v>sha256:cda561c58eb3b3eeb7b5d8b86836960a48f9ee79058073e4943561aa9c9b39d1</x:v>
+        <x:v>sha256:d939e6407cadc5480c2f88547845d69f1e2e36a37b7ae6635cebcdde0e9ce030</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -6335,10 +6337,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B23" s="99" t="str">
-        <x:v>C2-OPS-01</x:v>
+        <x:v>C3-CONFIG-01</x:v>
       </x:c>
       <x:c r="C23" s="99" t="str">
-        <x:v>sha256:d939e6407cadc5480c2f88547845d69f1e2e36a37b7ae6635cebcdde0e9ce030</x:v>
+        <x:v>sha256:633063511fb285503511b318ef26bf092ac48be8afda4df5ef008ab645d4f712</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -6346,10 +6348,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B24" s="99" t="str">
-        <x:v>C3-CONFIG-01</x:v>
+        <x:v>C3-REG-01</x:v>
       </x:c>
       <x:c r="C24" s="99" t="str">
-        <x:v>sha256:633063511fb285503511b318ef26bf092ac48be8afda4df5ef008ab645d4f712</x:v>
+        <x:v>sha256:f692886e78e72d84e31a5ef91aa281938d0529b8b7ea1a220bbf200993144e29</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -6357,10 +6359,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B25" s="99" t="str">
-        <x:v>C3-REG-01</x:v>
+        <x:v>C3-READ-01</x:v>
       </x:c>
       <x:c r="C25" s="99" t="str">
-        <x:v>sha256:f692886e78e72d84e31a5ef91aa281938d0529b8b7ea1a220bbf200993144e29</x:v>
+        <x:v>sha256:44b63514e2b1f8af98d36c6a4a25a22b7d554a7055c63b717a390b5801f4f72f</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -6368,10 +6370,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B26" s="99" t="str">
-        <x:v>C3-READ-01</x:v>
+        <x:v>BACKUP-SET-02</x:v>
       </x:c>
       <x:c r="C26" s="99" t="str">
-        <x:v>sha256:44b63514e2b1f8af98d36c6a4a25a22b7d554a7055c63b717a390b5801f4f72f</x:v>
+        <x:v>sha256:d8e92939499af335b6f4493b97c7fa8671ad4fc3910cca9a5f8eda4ef41cfc2f</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -6379,10 +6381,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B27" s="99" t="str">
-        <x:v>BACKUP-SET-02</x:v>
+        <x:v>C3-OPS-01</x:v>
       </x:c>
       <x:c r="C27" s="99" t="str">
-        <x:v>sha256:d8e92939499af335b6f4493b97c7fa8671ad4fc3910cca9a5f8eda4ef41cfc2f</x:v>
+        <x:v>sha256:c60f649504d508a81fa0bd19f172421676472153728093142a04d2ba4e5c96ad</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -6390,10 +6392,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B28" s="99" t="str">
-        <x:v>C3-OPS-01</x:v>
+        <x:v>CTRL-AFON-01</x:v>
       </x:c>
       <x:c r="C28" s="99" t="str">
-        <x:v>sha256:c60f649504d508a81fa0bd19f172421676472153728093142a04d2ba4e5c96ad</x:v>
+        <x:v>sha256:2c3055256d014c23ff48c71e8998a544186d8606fc4ad766773ec6c14976f6d7</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -6401,10 +6403,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B29" s="99" t="str">
-        <x:v>CTRL-AFON-01</x:v>
+        <x:v>CTRL-AELOCK-01</x:v>
       </x:c>
       <x:c r="C29" s="99" t="str">
-        <x:v>sha256:2c3055256d014c23ff48c71e8998a544186d8606fc4ad766773ec6c14976f6d7</x:v>
+        <x:v>sha256:888daf7bc311ea1a395e8a7406c8caac4655da1853803ba28df50d40a03fda9b</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -6412,10 +6414,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B30" s="99" t="str">
-        <x:v>CTRL-AELOCK-01</x:v>
+        <x:v>CTRL-DOF-01</x:v>
       </x:c>
       <x:c r="C30" s="99" t="str">
-        <x:v>sha256:888daf7bc311ea1a395e8a7406c8caac4655da1853803ba28df50d40a03fda9b</x:v>
+        <x:v>sha256:606ba83c6c6ef93bebe9f6f0451a7c80fead0f83b62fd48fe2137c5a72fa3b19</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -6423,10 +6425,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B31" s="99" t="str">
-        <x:v>CTRL-DOF-01</x:v>
+        <x:v>CTRL-SET-01</x:v>
       </x:c>
       <x:c r="C31" s="99" t="str">
-        <x:v>sha256:606ba83c6c6ef93bebe9f6f0451a7c80fead0f83b62fd48fe2137c5a72fa3b19</x:v>
+        <x:v>sha256:ad0d38b06de1f9f53cde8acce71775385e4aaef6588e771934320e4124431e25</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -6434,10 +6436,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B32" s="99" t="str">
-        <x:v>CTRL-SET-01</x:v>
+        <x:v>CTRL-JOY-01</x:v>
       </x:c>
       <x:c r="C32" s="99" t="str">
-        <x:v>sha256:ad0d38b06de1f9f53cde8acce71775385e4aaef6588e771934320e4124431e25</x:v>
+        <x:v>sha256:957387ec73ac18ab4785a4aaf972f7e285c513c90769f009edece0c97f044600</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -6445,10 +6447,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B33" s="99" t="str">
-        <x:v>CTRL-JOY-01</x:v>
+        <x:v>EFCS-SHOCK-01</x:v>
       </x:c>
       <x:c r="C33" s="99" t="str">
-        <x:v>sha256:957387ec73ac18ab4785a4aaf972f7e285c513c90769f009edece0c97f044600</x:v>
+        <x:v>sha256:5536143e9808461e6a2779baa6f8d2adf0dd969cccb0b7d2a28598a924d61203</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -6456,10 +6458,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B34" s="99" t="str">
-        <x:v>EFCS-SHOCK-01</x:v>
+        <x:v>EFCS-BOKEH-01</x:v>
       </x:c>
       <x:c r="C34" s="99" t="str">
-        <x:v>sha256:5536143e9808461e6a2779baa6f8d2adf0dd969cccb0b7d2a28598a924d61203</x:v>
+        <x:v>sha256:4e1bd076174191e3341b0eb9a6f2279f745b35cc3425dbd6e1360e771e5f3a42</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -6467,10 +6469,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B35" s="99" t="str">
-        <x:v>EFCS-BOKEH-01</x:v>
+        <x:v>EFCS-LIGHT-01</x:v>
       </x:c>
       <x:c r="C35" s="99" t="str">
-        <x:v>sha256:4e1bd076174191e3341b0eb9a6f2279f745b35cc3425dbd6e1360e771e5f3a42</x:v>
+        <x:v>sha256:0294347c51bd94b65f8eec9fad44b39d00e5433c4dc12aeee06c48c0e5ae9c08</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -6478,10 +6480,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B36" s="99" t="str">
-        <x:v>EFCS-LIGHT-01</x:v>
+        <x:v>EFCS-BURST-01</x:v>
       </x:c>
       <x:c r="C36" s="99" t="str">
-        <x:v>sha256:0294347c51bd94b65f8eec9fad44b39d00e5433c4dc12aeee06c48c0e5ae9c08</x:v>
+        <x:v>sha256:10966e281790e9619773bd99c263d1a8c3f83170403b36c2fbb2a490499e7130</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -6489,10 +6491,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B37" s="99" t="str">
-        <x:v>EFCS-BURST-01</x:v>
+        <x:v>FLASH-PLUTO-01</x:v>
       </x:c>
       <x:c r="C37" s="99" t="str">
-        <x:v>sha256:10966e281790e9619773bd99c263d1a8c3f83170403b36c2fbb2a490499e7130</x:v>
+        <x:v>sha256:5c00b09991f26e6b8bedd930e7304b53dae8f93819c7135c765aac82e970d87c</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -6500,10 +6502,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B38" s="99" t="str">
-        <x:v>FLASH-PLUTO-01</x:v>
+        <x:v>FINAL-READ-01</x:v>
       </x:c>
       <x:c r="C38" s="99" t="str">
-        <x:v>sha256:5c00b09991f26e6b8bedd930e7304b53dae8f93819c7135c765aac82e970d87c</x:v>
+        <x:v>sha256:688b6db6bd3d38070dfd682da54402cf8678093cb1014766953f9f5da49d7407</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -6511,10 +6513,10 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B39" s="99" t="str">
-        <x:v>FINAL-READ-01</x:v>
+        <x:v>FINAL-SAVE-01</x:v>
       </x:c>
       <x:c r="C39" s="99" t="str">
-        <x:v>sha256:688b6db6bd3d38070dfd682da54402cf8678093cb1014766953f9f5da49d7407</x:v>
+        <x:v>sha256:3d3558eaa54a0fdee859a544db2bccada6d3a8749fda96001422741914b6d0a6</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -6522,21 +6524,21 @@
         <x:v>test</x:v>
       </x:c>
       <x:c r="B40" s="99" t="str">
-        <x:v>FINAL-SAVE-01</x:v>
+        <x:v>PROJECT-UPDATE-01</x:v>
       </x:c>
       <x:c r="C40" s="99" t="str">
-        <x:v>sha256:3d3558eaa54a0fdee859a544db2bccada6d3a8749fda96001422741914b6d0a6</x:v>
+        <x:v>sha256:9312ccf684ccf233900950855d7a3457eb01e52e1c8fcb90e3c7c7daa72e17a6</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="99" t="str">
-        <x:v>test</x:v>
+        <x:v>registration</x:v>
       </x:c>
       <x:c r="B41" s="99" t="str">
-        <x:v>PROJECT-UPDATE-01</x:v>
+        <x:v>Mode</x:v>
       </x:c>
       <x:c r="C41" s="99" t="str">
-        <x:v>sha256:9312ccf684ccf233900950855d7a3457eb01e52e1c8fcb90e3c7c7daa72e17a6</x:v>
+        <x:v>sha256:16380d447ae550758ff49c344119374224a6b1c009504e23f6f4f93c11c00533</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -6544,10 +6546,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B42" s="99" t="str">
-        <x:v>Mode</x:v>
+        <x:v>Metering</x:v>
       </x:c>
       <x:c r="C42" s="99" t="str">
-        <x:v>sha256:16380d447ae550758ff49c344119374224a6b1c009504e23f6f4f93c11c00533</x:v>
+        <x:v>sha256:bc76af3dd5f76e718fe876deafcfbc0fd4a3f64d2a2eb64d2253751bd18f4eae</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -6555,10 +6557,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B43" s="99" t="str">
-        <x:v>Metering</x:v>
+        <x:v>Exposure Compensation</x:v>
       </x:c>
       <x:c r="C43" s="99" t="str">
-        <x:v>sha256:bc76af3dd5f76e718fe876deafcfbc0fd4a3f64d2a2eb64d2253751bd18f4eae</x:v>
+        <x:v>sha256:88e1331bb1792dc8c402253666af51d91b4ff14bdf848d8f5715f7c5735374ee</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -6566,10 +6568,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B44" s="99" t="str">
-        <x:v>Exposure Compensation</x:v>
+        <x:v>Shutter Speed</x:v>
       </x:c>
       <x:c r="C44" s="99" t="str">
-        <x:v>sha256:88e1331bb1792dc8c402253666af51d91b4ff14bdf848d8f5715f7c5735374ee</x:v>
+        <x:v>sha256:50a59b23cd80339f63a7068a9f9b6618357bcc05eb6f986cc5c7a707e50c0a74</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -6577,10 +6579,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B45" s="99" t="str">
-        <x:v>Shutter Speed</x:v>
+        <x:v>Aperture</x:v>
       </x:c>
       <x:c r="C45" s="99" t="str">
-        <x:v>sha256:50a59b23cd80339f63a7068a9f9b6618357bcc05eb6f986cc5c7a707e50c0a74</x:v>
+        <x:v>sha256:74b8c602aefe9109b324a5d3d0f5af54cafeaceae6f80e96effd7b7e7b7512a0</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -6588,10 +6590,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B46" s="99" t="str">
-        <x:v>Aperture</x:v>
+        <x:v>ISO</x:v>
       </x:c>
       <x:c r="C46" s="99" t="str">
-        <x:v>sha256:74b8c602aefe9109b324a5d3d0f5af54cafeaceae6f80e96effd7b7e7b7512a0</x:v>
+        <x:v>sha256:3c57560fdad255af8dddd4afe759bf3a638ced62cd0b435fbcb39f539ed4d5cd</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -6599,10 +6601,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B47" s="99" t="str">
-        <x:v>ISO</x:v>
+        <x:v>Auto ISO Maximum</x:v>
       </x:c>
       <x:c r="C47" s="99" t="str">
-        <x:v>sha256:3c57560fdad255af8dddd4afe759bf3a638ced62cd0b435fbcb39f539ed4d5cd</x:v>
+        <x:v>sha256:215087f96f2c5d379e4931bbcffe7ea4f1ebe59cc0229f5dae23f52e08edbba5</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -6610,10 +6612,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B48" s="99" t="str">
-        <x:v>Auto ISO Maximum</x:v>
+        <x:v>AF Operation</x:v>
       </x:c>
       <x:c r="C48" s="99" t="str">
-        <x:v>sha256:215087f96f2c5d379e4931bbcffe7ea4f1ebe59cc0229f5dae23f52e08edbba5</x:v>
+        <x:v>sha256:e52a8877636b9e990324e5e59a10b6b8a0723c7699f752ac41a4e39a25ed8c94</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -6621,10 +6623,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B49" s="99" t="str">
-        <x:v>AF Operation</x:v>
+        <x:v>Servo AF Case</x:v>
       </x:c>
       <x:c r="C49" s="99" t="str">
-        <x:v>sha256:e52a8877636b9e990324e5e59a10b6b8a0723c7699f752ac41a4e39a25ed8c94</x:v>
+        <x:v>sha256:c9f1ca7567fd410ce854474a770e020fea6e9904b6872801ebc1b2f20b392fbf</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -6632,10 +6634,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B50" s="99" t="str">
-        <x:v>Servo AF Case</x:v>
+        <x:v>Tracking Sensitivity</x:v>
       </x:c>
       <x:c r="C50" s="99" t="str">
-        <x:v>sha256:c9f1ca7567fd410ce854474a770e020fea6e9904b6872801ebc1b2f20b392fbf</x:v>
+        <x:v>sha256:dfe83819227cc879db8a3ff1c5b898a2d1c1b0f74d6b3364ad9a92ed7b018424</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -6643,10 +6645,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B51" s="99" t="str">
-        <x:v>Tracking Sensitivity</x:v>
+        <x:v>Accel./Decel. Tracking</x:v>
       </x:c>
       <x:c r="C51" s="99" t="str">
-        <x:v>sha256:dfe83819227cc879db8a3ff1c5b898a2d1c1b0f74d6b3364ad9a92ed7b018424</x:v>
+        <x:v>sha256:e11fda77b702b46abfbda7bbf4de92c162668fd479106b46da999dcd11ba28cf</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -6654,10 +6656,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B52" s="99" t="str">
-        <x:v>Accel./Decel. Tracking</x:v>
+        <x:v>Switching Tracked Subjects</x:v>
       </x:c>
       <x:c r="C52" s="99" t="str">
-        <x:v>sha256:e11fda77b702b46abfbda7bbf4de92c162668fd479106b46da999dcd11ba28cf</x:v>
+        <x:v>sha256:1866e2e49cd4159a2f76e301df8394efb14ebc00f49606d84fedb5501875eeb7</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -6665,10 +6667,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B53" s="99" t="str">
-        <x:v>Switching Tracked Subjects</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="C53" s="99" t="str">
-        <x:v>sha256:1866e2e49cd4159a2f76e301df8394efb14ebc00f49606d84fedb5501875eeb7</x:v>
+        <x:v>sha256:ac30ce5e48a2e9e69db02806afb6a8c836dd8220dce399b57ed50b6ec3569d82</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -6676,10 +6678,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B54" s="99" t="str">
-        <x:v>AF Method</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="C54" s="99" t="str">
-        <x:v>sha256:ac30ce5e48a2e9e69db02806afb6a8c836dd8220dce399b57ed50b6ec3569d82</x:v>
+        <x:v>sha256:ca630f9c8761b1ba9bc261fc0264e1fdff6c6ebce7d3d60f68453c6e6c0fb66e</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -6687,10 +6689,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B55" s="99" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="C55" s="99" t="str">
-        <x:v>sha256:ca630f9c8761b1ba9bc261fc0264e1fdff6c6ebce7d3d60f68453c6e6c0fb66e</x:v>
+        <x:v>sha256:d4f49e58f189bc2a85058e8030bdba5867549892594d4961911a877fc7774cc1</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -6698,10 +6700,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B56" s="99" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>Drive Mode</x:v>
       </x:c>
       <x:c r="C56" s="99" t="str">
-        <x:v>sha256:d4f49e58f189bc2a85058e8030bdba5867549892594d4961911a877fc7774cc1</x:v>
+        <x:v>sha256:a407ab25d86c6b32e4618dffadce1bc9f7375731cceb32a9b15154cb636bbc93</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -6709,10 +6711,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B57" s="99" t="str">
-        <x:v>Drive Mode</x:v>
+        <x:v>High Speed Display</x:v>
       </x:c>
       <x:c r="C57" s="99" t="str">
-        <x:v>sha256:a407ab25d86c6b32e4618dffadce1bc9f7375731cceb32a9b15154cb636bbc93</x:v>
+        <x:v>sha256:0af962b70870008b8b495ab863d5b9773e68daa4e052c10a5157bbb6e9b09a04</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -6720,10 +6722,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B58" s="99" t="str">
-        <x:v>High Speed Display</x:v>
+        <x:v>Shutter Type</x:v>
       </x:c>
       <x:c r="C58" s="99" t="str">
-        <x:v>sha256:0af962b70870008b8b495ab863d5b9773e68daa4e052c10a5157bbb6e9b09a04</x:v>
+        <x:v>sha256:e0eb3a601149113b744968c8d35c10e22707716e94c780644837edcabff082bb</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -6731,10 +6733,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B59" s="99" t="str">
-        <x:v>Shutter Type</x:v>
+        <x:v>Image Stabilizer Mode</x:v>
       </x:c>
       <x:c r="C59" s="99" t="str">
-        <x:v>sha256:e0eb3a601149113b744968c8d35c10e22707716e94c780644837edcabff082bb</x:v>
+        <x:v>sha256:cc5907ea77c17b747bda000cb9d24e886022b15d9be9b15be2fd7d3a6aa18fba</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -6742,10 +6744,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B60" s="99" t="str">
-        <x:v>Image Stabilizer Mode</x:v>
+        <x:v>IBIS</x:v>
       </x:c>
       <x:c r="C60" s="99" t="str">
-        <x:v>sha256:cc5907ea77c17b747bda000cb9d24e886022b15d9be9b15be2fd7d3a6aa18fba</x:v>
+        <x:v>sha256:f88432494f6ce6fd467acf866dcb7285209af0daa97f23211b4c2e9a2fca510a</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -6753,10 +6755,10 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B61" s="99" t="str">
-        <x:v>IBIS</x:v>
+        <x:v>Focus Bracketing</x:v>
       </x:c>
       <x:c r="C61" s="99" t="str">
-        <x:v>sha256:f88432494f6ce6fd467acf866dcb7285209af0daa97f23211b4c2e9a2fca510a</x:v>
+        <x:v>sha256:faa653558ccc3ca42def02cffceb2449676221f3e2b701a95cb76c734a606a66</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -6764,20 +6766,9 @@
         <x:v>registration</x:v>
       </x:c>
       <x:c r="B62" s="99" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>Lens IS switch</x:v>
       </x:c>
       <x:c r="C62" s="99" t="str">
-        <x:v>sha256:faa653558ccc3ca42def02cffceb2449676221f3e2b701a95cb76c734a606a66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="99" t="str">
-        <x:v>registration</x:v>
-      </x:c>
-      <x:c r="B63" s="99" t="str">
-        <x:v>Lens IS switch</x:v>
-      </x:c>
-      <x:c r="C63" s="99" t="str">
         <x:v>sha256:77c1f08d541f8a95c354155213e1184f193765664d2faca4e6245806067b6735</x:v>
       </x:c>
     </x:row>
